--- a/Source/BCIO-source-hierarchy.xlsx
+++ b/Source/BCIO-source-hierarchy.xlsx
@@ -445,32 +445,32 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>synonyms</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>crossreference</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>subontology</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>crossreference</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>examples</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>synonyms</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OGMS:0000087</t>
+          <t>OBI:0000245</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -626,7 +626,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>extended organism</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -638,26 +638,34 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>An object aggregate consisting of an organism and all material entities located within the organism, overlapping the organism, or occupying sites formed in part by the organism.</t>
+          <t>An entity that can bear roles, has members, and has a set of organization rules. Members of organizations are either organizations themselves or individual people. Members can bear specific organization member roles that are determined in the organization rules. The organization rules also determine how decisions are made on behalf of the organization by the organization members.</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MF:0000016</t>
+          <t>OGMS:0000087</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>human being</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>extended organism</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -666,22 +674,14 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>An extended organism that is a member of the species Homo sapiens.</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+          <t>An object aggregate consisting of an organism and all material entities located within the organism, overlapping the organism, or occupying sites formed in part by the organism.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:050842</t>
+          <t>MF:0000016</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -689,12 +689,12 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>role model for a person</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -702,20 +702,15 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>A &lt;person&gt; that influences a recipient by being perceived to be similar or admired.</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An extended organism that is a member of the species Homo sapiens.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>This class lies at the intersection between a person and their environment and is defined from the perspective of the person.</t>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
@@ -746,14 +741,14 @@
           <t>A person who is the bearer of a behaviour change intervention source role.</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -782,19 +777,19 @@
           <t>A person who is a member of a group of persons united by blood, or by marriage or other legal arrangement, or by self-identity as belonging to the same family.</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:010099</t>
+          <t>BCIO:010097</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -806,7 +801,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>child relationship</t>
+          <t>spouse or partner</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -815,21 +810,21 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>A family member that is an offspring relationship from a person to their parent.</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A family member that is an individual who is married or in a committed relationship with another individual.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>daughter, son, step-daughter, step-son</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>boyfriend, girlfriend, partner, fiance, wife, husband</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -858,18 +853,18 @@
           <t>A family member that is a family relationship between two persons with at least one shared parent.</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>brother, sister, step-brother, step-sister</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -898,23 +893,23 @@
           <t>A family member that is a mother, father or legal carer of a child.</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>mother, father, step-mother, step-father, guardian</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:010097</t>
+          <t>BCIO:010099</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -926,7 +921,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>spouse or partner</t>
+          <t>child relationship</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -935,39 +930,39 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>A family member that is an individual who is married or in a committed relationship with another individual.</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A family member that is an offspring relationship from a person to their parent.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>boyfriend, girlfriend, partner, fiance, wife, husband</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>daughter, son, step-daughter, step-son</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:010139</t>
+          <t>BCIO:050842</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>organisation source</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>role model for a person</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -975,22 +970,27 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>An organisation that is the bearer of a behaviour change intervention source role, such as voluntary, public or commercial organisations delivering a behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A &lt;person&gt; that influences a recipient by being perceived to be similar or admired.</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>This class lies at the intersection between a person and their environment and is defined from the perspective of the person.</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OBI:0000245</t>
+          <t>BCIO:010139</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -999,7 +999,7 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>organisation source</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1011,29 +1011,29 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>An entity that can bear roles, has members, and has a set of organization rules. Members of organizations are either organizations themselves or individual people. Members can bear specific organization member roles that are determined in the organization rules. The organization rules also determine how decisions are made on behalf of the organization by the organization members.</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An organisation that is the bearer of a behaviour change intervention source role, such as voluntary, public or commercial organisations delivering a behaviour change intervention.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BFO:0000020</t>
+          <t>BFO:0000031</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>characteristic</t>
+          <t>generically dependent continuant</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1047,14 +1047,14 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
+          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BFO:0000017</t>
+          <t>IAO:0000030</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>realizable</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1075,14 +1075,14 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>A specifically dependent continuant  that inheres in continuant  entities and are not exhibited in full at every time in which it inheres in an entity or group of entities. The exhibition or actualization of a realizable entity is a particular manifestation, functioning or process that occurs under certain circumstances.</t>
+          <t>A generically dependent continuant that is about some thing.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BFO:0000023</t>
+          <t>IAO:0000027</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1103,14 +1103,14 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>A realizable entity  the manifestation of which brings about some result or end that is not essential to a continuant  in virtue of the kind of thing that it is but that can be served or participated in by that kind of continuant  in some kinds of natural, social or institutional contexts.</t>
+          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:010000</t>
+          <t>BCIO:010106</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1120,7 +1120,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>behaviour change intervention source</t>
+          <t>number of people delivering intervention to each participant</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -1131,22 +1131,22 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>A role played by a person, population or organisation that provides a BCI.</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A count data item that is the number of providers that an individual participant in the intervention encounters.</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:010133</t>
+          <t>BCIO:010126</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1154,12 +1154,12 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>source role related to intervention</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>amount of experience</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1167,22 +1167,26 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>A BCI source whose occupational or voluntary role is focused on delivery of the behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A knowledge or skill that is the duration of experience in related domain held by person source.</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>full-day, 6 years</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:010138</t>
+          <t>BCIO:010107</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1190,12 +1194,12 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>organisational source role</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>total number of people able to deliver intervention</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1203,35 +1207,35 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>A BCI source role that is borne by an organisation.</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A count data item that is the total number of providers that are available and able to deliver the intervention.</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:010134</t>
+          <t>BFO:0000020</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>specifically dependent continuant</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>source involved in development of intervention</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1239,71 +1243,55 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>A BCI source that is involved in the development of intervention content.</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
+          <t>b is a relational specifically dependent continuant = Def. b is a specifically dependent continuant and there are n &amp;gt; 1 independent continuants c1, … cn which are not spatial regions are such that for all 1  i &amp;lt; j  n, ci  and cj share no common parts, are such that for each 1  i  n, b s-depends_on ci at every time t during the course of b’s existence (axiom label in BFO2 Reference: [131-004])</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:010135</t>
+          <t>MF:0000030</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>representation</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>source involved in co-production of intervention</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>A source involved in development of intervention that has developed the intervention content in collaboration with key stakeholders such as patients or community members.</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+          <t>A dependent continuant which is about a portion of reality.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:010001</t>
+          <t>MF:0000031</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>cognitive representation</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>person source role</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1311,22 +1299,14 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>A behaviour change intervention source role that inheres in a person.</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
+          <t>A representation which specifically depends on an anatomical structure in the cognitive system of an organism.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:010003</t>
+          <t>ADDICTO:0000381</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1336,7 +1316,7 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>personal role of source</t>
+          <t>identity</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1347,22 +1327,14 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>A role that inheres in a person source.</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
+          <t>A cognitive representation of themselves by a person or a group about themselves.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:010004</t>
+          <t>ADDICTO:0000399</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1373,7 +1345,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t>self-identity</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1383,26 +1355,14 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>A personal role of source that is realised by doing a specified type of work or working in a specified way.</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Interventionist, facilitator, study staff</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
+          <t>An identity that a person has about themselves.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:010067</t>
+          <t>BCIO:015098</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1414,7 +1374,7 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>clerical support worker</t>
+          <t>gender identity</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -1423,26 +1383,22 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>An occupational role that records, organizes, stores, computes and retrieves information, and performs a number of clerical duties in connection with money-handling operations, travel arrangements, requests for information, and appointments.</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>General and Keyboard Clerk, customers Services Clerk, Numerical and Material Recording Clerk</t>
-        </is>
-      </c>
       <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:010068</t>
+          <t>BCIO:010111</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1452,33 +1408,37 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>services and sales worker</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>female gender</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>An occupational role that provides personal or protective services related to travel, house-keeping, catering, personal care, protection against fire and unlawful acts, or sells goods in retail or markets.</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A gender identity as being female.</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>female, woman</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:010070</t>
+          <t>BCIO:010112</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1491,7 +1451,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>sales worker</t>
+          <t>male gender</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -1499,106 +1459,82 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>A services and sales worker that demonstrates goods in wholesale or retail shops, at stalls and markets, door to door, via telephone or customer contact centres. They may record and accept payment for goods and services purchased, and may operate small retail outlets.</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A gender identity as being male.</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Street Salesperson, Market Salesperson, Shop Salesperson, Cashier, Ticket Clerk, Model, Sales Demonstrator, Door-to-door Salesperson, Contact Centre Salesperson, Service Station Attendant, Food Service Counter Attendant</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>male, man</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:010069</t>
+          <t>BFO:0000017</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>realizable entity</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>personal services worker</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>A services and sales worker that provides personal services related to travel, housekeeping, catering and hospitality, hairdressing and beauty treatment, animal care grooming and training, companionship and other services of a personal nature.</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Travel Attendant, Conductor, Guide, Cook, Waiter, Bartender, Hairdresser, Beautician, Housekeeping Supervisor, Astrologer, Fortune-teller, Valet, Undertaker, Embalmer, Pet Groomer, Animal Care Worker</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr"/>
+          <t>A specifically dependent continuant  that inheres in continuant  entities and are not exhibited in full at every time in which it inheres in an entity or group of entities. The exhibition or actualization of a realizable entity is a particular manifestation, functioning or process that occurs under certain circumstances.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:010071</t>
+          <t>BFO:0000023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>personal care worker</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>A services and sales worker that provides care, supervision and assistance for children, patients and elderly, convalescent or disabled persons in institutional and residential settings.</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Personal carer</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr"/>
+          <t>A realizable entity  the manifestation of which brings about some result or end that is not essential to a continuant  in virtue of the kind of thing that it is but that can be served or participated in by that kind of continuant  in some kinds of natural, social or institutional contexts.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:010074</t>
+          <t>BCIO:010003</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1606,39 +1542,35 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>personal role of source</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>health care assistant</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>A personal care worker that provides direct personal care and assistance with activities of daily living to patients and residents in a variety of health care settings, working  in implementation of established care plans and practices, and under the direct supervision of medical, nursing or other health professionals or associate professionals.</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A role that inheres in a person source.</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Nursing aide (clinic or hospital), Patient care assistant, Psychiatric aid</t>
-        </is>
-      </c>
       <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:010072</t>
+          <t>BCIO:010004</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1647,38 +1579,38 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>occupational role of source</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>child care worker</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>A personal care worker that provides care and supervision for children in non-domestic settings.</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A personal role of source that is realised by doing a specified type of work or working in a specified way.</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Babysitter, Child care worker, Creche ayah, Family day care worker, Nanny, Out of school hours care worker</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Interventionist, facilitator, study staff</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:010075</t>
+          <t>BCIO:010067</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1688,37 +1620,37 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>clerical support worker</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>home-based personal care worker</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>A personal care worker that provide routine personal care and assistance with activities of daily living to persons who are in need of such care due to effects of ageing, illness, injury, or other physical or mental conditions, in private homes and other independent residential settings.</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role that records, organizes, stores, computes and retrieves information, and performs a number of clerical duties in connection with money-handling operations, travel arrangements, requests for information, and appointments.</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Home birth assistant, Home care aide, Nursing aide (home), Personal care provider</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>General and Keyboard Clerk, customers Services Clerk, Numerical and Material Recording Clerk</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:010073</t>
+          <t>BCIO:010080</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1728,37 +1660,33 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>assembler</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teachers’ aide</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>A personal care worker that performs non-teaching duties to assist teaching staff, and provides care and supervision for children in schools and pre-schools.</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role that assembles products from component parts according to strict specifications and procedures.</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Pre-school assistant, Teacher’s assistant</t>
-        </is>
-      </c>
       <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:010076</t>
+          <t>BCIO:010079</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1768,37 +1696,37 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>protective services worker</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>plant and machine operator</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>A services and sales worker that protects individuals and property against fire and other hazards, maintain law and order and enforce laws and regulations.</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role that operates and monitors industrial and agricultural machinery and equipment on the spot or by remote control, or drives and operates trains, motor vehicles and mobile machinery and equipment.</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Firefighter, Police officer, Prison guard, Security guard, Offender manager</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Stationary Plant and Machine Operator, Driver, Mobile Plant Operator</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:010082</t>
+          <t>BCIO:010081</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1810,7 +1738,7 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>armed forces occupation</t>
+          <t>elementary occupation</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -1819,26 +1747,26 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>An occupational role that includes all jobs held by members of the armed forces.</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role that involves the performance of simple and routine tasks which may require the use of hand-held tools and considerable physical effort.</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Admiral, Air commodore, Air marshal, Airman, Brigadier (army), Bombardier, Captain (air force), Captain (army), Captain (navy), Colonel (army), Corporal,  Field marshal, Flight lieutenant (air force), Flying officer (military), General (army), Gunner, Group captain, (air force), Lieutenant (army), Major (army), Midshipman, Naval officer (military) , Navy commander, Officer cadet (armed forces), Paratrooper, Rifleman, Sergeant (army), Second lieutenant (army), Seaman, Squadron leader, Sublieutenant (navy), Wing commander</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Cleaner, Labourer, Food Preparation Assistant, Street and Related Services Worker, Street Vendor (excluding Food), Refuse Worker</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:010077</t>
+          <t>BCIO:010083</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1850,7 +1778,7 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>skilled agricultural, forestry and fishery worker</t>
+          <t>researcher</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -1859,26 +1787,26 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>An occupational role that grows and harvests plants or animals to provide food, shelter and income for themselves and their households.</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role that is a researcher but unclear what discipline.</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Market gardener, Crop grower, Animal Producer, Mixed Crop and Animal Producer, Forestry worker, Fishery worker, Hunter. Subsistence Crop Farmer, Subsistence Livestock Farmer</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>researcher, research assistant, investigator</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:010080</t>
+          <t>BCIO:010078</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1890,7 +1818,7 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>assembler</t>
+          <t>craft and related trades worker</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -1899,22 +1827,26 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>An occupational role that assembles products from component parts according to strict specifications and procedures.</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role that applies specific technical and practical knowledge and skills to construct and maintain buildings, machinery, equipment or tools, carries out printing work, and produces or processes foodstuffs, textiles and wooden, metal and other articles, including handicraft goods.</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Building Trade Worker, Metal Workers, Machinery Worker, Handicraft Worker, Printing Worker, Electrical Equipment Installers and Repairer, Electronics and Telecommunications Installer and Repairer, Food Processing Worker, Woodworker, Tobacco Product Maker</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:010005</t>
+          <t>BCIO:010077</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1926,7 +1858,7 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>manager</t>
+          <t>skilled agricultural, forestry and fishery worker</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
@@ -1935,26 +1867,26 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>An occupational role of source that manages, plans and coordinates the overall activities of enterprises, governments and other organisations.</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role that grows and harvests plants or animals to provide food, shelter and income for themselves and their households.</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>Chief Executive Officers; Administrative Managers;  Commercial Managers</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Market gardener, Crop grower, Animal Producer, Mixed Crop and Animal Producer, Forestry worker, Fishery worker, Hunter. Subsistence Crop Farmer, Subsistence Livestock Farmer</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:010078</t>
+          <t>BCIO:010082</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1966,7 +1898,7 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>craft and related trades worker</t>
+          <t>armed forces occupation</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -1975,26 +1907,26 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>An occupational role that applies specific technical and practical knowledge and skills to construct and maintain buildings, machinery, equipment or tools, carries out printing work, and produces or processes foodstuffs, textiles and wooden, metal and other articles, including handicraft goods.</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role that includes all jobs held by members of the armed forces.</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>Building Trade Worker, Metal Workers, Machinery Worker, Handicraft Worker, Printing Worker, Electrical Equipment Installers and Repairer, Electronics and Telecommunications Installer and Repairer, Food Processing Worker, Woodworker, Tobacco Product Maker</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Admiral, Air commodore, Air marshal, Airman, Brigadier (army), Bombardier, Captain (air force), Captain (army), Captain (navy), Colonel (army), Corporal,  Field marshal, Flight lieutenant (air force), Flying officer (military), General (army), Gunner, Group captain, (air force), Lieutenant (army), Major (army), Midshipman, Naval officer (military) , Navy commander, Officer cadet (armed forces), Paratrooper, Rifleman, Sergeant (army), Second lieutenant (army), Seaman, Squadron leader, Sublieutenant (navy), Wing commander</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:010079</t>
+          <t>BCIO:010068</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2006,7 +1938,7 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>plant and machine operator</t>
+          <t>services and sales worker</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -2015,26 +1947,22 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>An occupational role that operates and monitors industrial and agricultural machinery and equipment on the spot or by remote control, or drives and operates trains, motor vehicles and mobile machinery and equipment.</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role that provides personal or protective services related to travel, house-keeping, catering, personal care, protection against fire and unlawful acts, or sells goods in retail or markets.</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>Stationary Plant and Machine Operator, Driver, Mobile Plant Operator</t>
-        </is>
-      </c>
       <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:010083</t>
+          <t>BCIO:010071</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2044,37 +1972,37 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>researcher</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>personal care worker</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>An occupational role that is a researcher but unclear what discipline.</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A services and sales worker that provides care, supervision and assistance for children, patients and elderly, convalescent or disabled persons in institutional and residential settings.</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>researcher, research assistant, investigator</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Personal carer</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:010006</t>
+          <t>BCIO:010074</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2084,33 +2012,37 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>professional</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>health care assistant</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>An occupational role that works in knowledge building activities, applies scientific or artistic concepts and theories or teaches about the foregoing in a systematic manner.</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A personal care worker that provides direct personal care and assistance with activities of daily living to patients and residents in a variety of health care settings, working  in implementation of established care plans and practices, and under the direct supervision of medical, nursing or other health professionals or associate professionals.</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Nursing aide (clinic or hospital), Patient care assistant, Psychiatric aid</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:010034</t>
+          <t>BCIO:010073</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2121,32 +2053,36 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>legal, social and cultural professional</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teachers’ aide</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>A professional that conducts research, improves or develops concepts, theories and operational methods, or applies knowledge relating to the law, social or cultural studies.</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A personal care worker that performs non-teaching duties to assist teaching staff, and provides care and supervision for children in schools and pre-schools.</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Pre-school assistant, Teacher’s assistant</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:010041</t>
+          <t>BCIO:010075</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2160,33 +2096,33 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>author and journalist</t>
+          <t>home-based personal care worker</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conceives and creates literary works, and interprets and communicates news and public affairs through the media.</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A personal care worker that provide routine personal care and assistance with activities of daily living to persons who are in need of such care due to effects of ageing, illness, injury, or other physical or mental conditions, in private homes and other independent residential settings.</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Author, Writer, Journalist, Translator, News anchor</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Home birth assistant, Home care aide, Nursing aide (home), Personal care provider</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:010035</t>
+          <t>BCIO:010072</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2200,33 +2136,33 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>legal professional</t>
+          <t>child care worker</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conducts research on legal problems, advises clients on legal aspects of problems, pleads cases or conducts prosecutions in courts of law, presides over judicial proceedings in courts of law and draft laws and regulations.</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A personal care worker that provides care and supervision for children in non-domestic settings.</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>Lawyer, Judge, Coroner</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Babysitter, Child care worker, Creche ayah, Family day care worker, Nanny, Out of school hours care worker</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:010036</t>
+          <t>BCIO:010069</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2237,36 +2173,36 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>librarian, archivist and curator</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>personal services worker</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that develops and maintains collections of archives, libraries, museums, art galleries and similar establishments.</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A services and sales worker that provides personal services related to travel, housekeeping, catering and hospitality, hairdressing and beauty treatment, animal care grooming and training, companionship and other services of a personal nature.</t>
         </is>
       </c>
       <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>Librarian, Archivist,  Curator</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Travel Attendant, Conductor, Guide, Cook, Waiter, Bartender, Hairdresser, Beautician, Housekeeping Supervisor, Astrologer, Fortune-teller, Valet, Undertaker, Embalmer, Pet Groomer, Animal Care Worker</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:010040</t>
+          <t>BCIO:010076</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2277,36 +2213,36 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>religious professional</t>
-        </is>
-      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>protective services worker</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that functions  as a perpetuator of sacred traditions, practices and beliefs. They conduct religious services, celebrate or administer the rites of a religious faith or denomination, provide spiritual and moral guidance and perform other functions associated with the practice of a religion.</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A services and sales worker that protects individuals and property against fire and other hazards, maintain law and order and enforce laws and regulations.</t>
         </is>
       </c>
       <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>Bonze, Imam, Minister of religion, Poojari, Priest, Rabbi</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Firefighter, Police officer, Prison guard, Security guard, Offender manager</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:010043</t>
+          <t>BCIO:010070</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2317,36 +2253,36 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>creative and performing artist</t>
-        </is>
-      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>sales worker</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that communicates ideas, impressions and facts in a wide range of media to achieve particular effects, interprets a composition such as a musical score or a script to perform or direct the performance, and hosts the presentation of such performance and other media events.</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A services and sales worker that demonstrates goods in wholesale or retail shops, at stalls and markets, door to door, via telephone or customer contact centres. They may record and accept payment for goods and services purchased, and may operate small retail outlets.</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>Visual artist, Musician, Singer, Composer, Dancer, Choreographer, Director, Producer, Actor, Announcer on radio, television and other media</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Street Salesperson, Market Salesperson, Shop Salesperson, Cashier, Ticket Clerk, Model, Sales Demonstrator, Door-to-door Salesperson, Contact Centre Salesperson, Service Station Attendant, Food Service Counter Attendant</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:010042</t>
+          <t>BCIO:010005</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2356,37 +2292,37 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>linguist</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that translates or interprets from one language into another.</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role of source that manages, plans and coordinates the overall activities of enterprises, governments and other organisations.</t>
         </is>
       </c>
       <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>Interpretator; other linguist</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Chief Executive Officers; Administrative Managers;  Commercial Managers</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:010037</t>
+          <t>BCIO:010006</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2396,37 +2332,33 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>professional</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>social professional</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conducts research, improves or develops concepts, theories and operational methods or applies knowledge relating to psychology, sociology, philosophy, politics, economics, sociology, anthropology, history and other social sciences, or provides social services to meet the needs of individuals and families in a community.</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role that works in knowledge building activities, applies scientific or artistic concepts and theories or teaches about the foregoing in a systematic manner.</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>Economist, Sociologist, Anthropologist, Philosopher, Historian, Political Scientist</t>
-        </is>
-      </c>
       <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:010039</t>
+          <t>BCIO:010007</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2437,36 +2369,36 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>science and engineering professional</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>social work and counselling professional</t>
-        </is>
-      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>A social professional that provides advice and guidance to individuals, families, groups, communities and organizations in response to social and personal difficulties. They assist clients to develop skills and access resources and support services needed to respond to issues arising from unemployment, poverty, disability, addiction, criminal and delinquent behaviour, marital and other problems.</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A professional that conducts research, improves or develops concepts, theories and operational methods or applies scientific knowledge.</t>
         </is>
       </c>
       <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>Counsellor, Addictions counsellor, Bereavement counsellor, Child and youth counsellor, District social welfare officer, Family counsellor, Marriage counsellor, Parole officer, Probation officer, Sexual assault counsellor, Social worker, Women’s welfare organizer</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Science Professional, Mathematician, Actuary, Statistician, Life Science Professional, Engineering Professional, Electrotechnology Engineer, Architect, Planner, Surveyor, Designer</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:010038</t>
+          <t>BCIO:010008</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2477,36 +2409,36 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>health professional</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>psychologist</t>
-        </is>
-      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>A social professional that studies the mental processes and behaviour of human beings as individuals or in groups, and applies this knowledge to promote personal, social, educational or occupational adjustment and development.</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A professional that improves or develops concepts, theories and operational method, and applied scientific knowledge relating to medicine, nursing, dentistry, veterinary medicine, pharmacy, and promotion of health.</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>Clinical psychologist, Counselling psychologist, Educational psychologist, Forensic psychologist, Health psychologist, Neuropsychologist, Organizational psychologist, Psychotherapist, Sport and exercise psychologist</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Health professional; Arts therapist, Chiropractor, Dance and movement therapist, Occupational therapist, Osteopath, Podiatrist, Recreational therapist, Health staff, Clinic staff</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:010044</t>
+          <t>BCIO:010017</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2517,32 +2449,36 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>technician and associate professional</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>veterinarian</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>A professional that performs technical and related tasks connected with research and the application of scientific or artistic concepts and operational methods, and government or business regulations.</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that diagnoses, prevents and treats diseases, injuries and dysfunctions of animals.</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Animal pathologist, Veterinarian, Veterinary epidemiologist, Veterinary intern, Veterinary surgeon</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:010045</t>
+          <t>BCIO:010012</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2556,33 +2492,29 @@
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>health associate professional</t>
+          <t>nursing and midwifery professional</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs technical and practical tasks to support diagnosis and treatment of illness, disease, injuries and impairments in humans or animals, and supports the implementation of health care usually established by medical, veterinary, nursing and other health professionals.</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that provides treatment and care services for people who are physically or mentally ill, disabled or infirm, and those with potential risks to health including before, during and after childbirth. They assume responsibility for the planning, management and evaluation of the care of patients, including the supervision of other health care workers, working autonomously or in teams with medical doctors and others in the practical application of preventive and curative measures.</t>
         </is>
       </c>
       <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>Veterinary Technician</t>
-        </is>
-      </c>
       <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:010055</t>
+          <t>BCIO:010021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2594,36 +2526,35 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>environmental and occupational health inspector and associate</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>physiotherapist</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>A health associate professional that investigates the implementation of rules and regulations relating to environmental factors that may affect human health, safety in the 
-workplace, and safety of processes for the production of goods and services. They may implement and evaluate programmes to restore or improve safety and sanitary conditions under the supervision of a health professional.</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional  that assesses, plans and implements rehabilitative programmes that improve or restore human motor functions, maximize movement ability, relieve pain syndromes, and treat or prevent physical challenges associated with injuries, diseases and other impairments.</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>Food sanitation and safety inspector, Health inspector, Occupational health and safety inspector, Pollution inspector, Product safety inspector, Sanitarian, Sanitary inspector</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Geriatric physical therapist, Manipulative therapist, Orthopaedic physical therapist, Paediatric physical therapist, Physical therapist, Physiotherapist</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:010053</t>
+          <t>BCIO:010013</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2635,35 +2566,35 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>physiotherapy technician and assistant</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>nursing professional</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>A health associate professional that provides physical therapeutic treatments to patients in circumstances where functional movement is threatened by injury, disease or impairment. Therapies are usually provided according to rehabilitative plans established by a physiotherapist or other health professional.</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that provides treatment, support and care services for people who are in need of nursing care due to the effects of ageing, injury, illness or other physical or mental impairment, or potential risks to health.</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>Acupressure therapist, Electrotherapist, Hydrotherapist, Massage therapist, Physical rehabilitation technician, Physiotherapy technician, Shiatsu therapist</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Clinical nurse consultant, District nurse, Nurse anaesthetist, Nurse educator, Nurse practitioner, Operating theatre nurse, Professional nurse, Public health nurse, Specialist nurse, Nursing Counsellor, Study Nurse</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:010054</t>
+          <t>BCIO:010023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2675,35 +2606,35 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>medical assistant</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>audiologist and speech therapist</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>A health associate professional that performs basic clinical and administrative tasks to support patient care under the direct supervision of a medical practitioner or other health professional.</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional  that evaluates, manages and treats physical disorders affecting human hearing, speech, communication and swallowing.</t>
         </is>
       </c>
       <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>Clinical assistant, Medical assistant, Ophthalmic assistant</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Audiologist, Language therapist, Speech pathologist, Speech therapist</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:010047</t>
+          <t>BCIO:010020</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2715,35 +2646,35 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>nursing and midwifery associate professional</t>
-        </is>
-      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>environmental and occupational health and hygiene professional</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>A health associate professional that provides basic nursing and personal care for people who are physically or mentally ill, disabled or infirm, and for others in need of care due to potential risks to health including before, during and after childbirth. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing, midwifery and other health professionals.</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that assesses, plans and implements programmes to recognize, monitor and control environmental factors that can potentially affect human health, to ensure safe and healthy working conditions and to prevent disease or injury caused by chemical, physical, radiological and biological agents or ergonomic factors.</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>Practice assistant, Quit Smoking Counsellor, Health educator, Dispensing Optician, Information Technician</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Environmental health officer, Occupational health and safety adviser, Occupational hygienist, Radiation protection expert</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:010048</t>
+          <t>BCIO:010009</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2755,35 +2686,35 @@
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>medical doctor</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>nursing associate professional</t>
-        </is>
-      </c>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>A nursing and midwifery associate professional that provides basic nursing and personal care for people in need of such care due to effects of ageing, illness, injury, or other physical or mental impairment. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing and other health professionals.</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that studies, diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans through the application of modern medicine. They plan, supervise and evaluate the implementation of care and treatment plans by other health care providers, and conduct medical education and research activities.</t>
         </is>
       </c>
       <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Assistant nurse, Associate professional nurse, Enrolled nurse, Practical nurse</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>District medical doctor-therapist, family medical practitioner, general practitioner, medical doctor (general), medical officer (general), physician (general), primary health care physician, resident medical officer specializing in general practice</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:010049</t>
+          <t>BCIO:010010</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2796,34 +2727,34 @@
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>midwifery associate professional</t>
-        </is>
-      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>generalist medical practitioner</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>A nursing and midwifery associate professional that provides basic health care and advice before, during and after pregnancy and childbirth. They implement care, treatment and referral plans usually established by medical, midwifery and other health professionals.</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments and maintains general health in humans through application of modern medicine. They do not limit their practice to certain disease categories or methods of treatment, and may assume responsibility for the provision of continuing and comprehensive medical care to individuals, families and communities.</t>
         </is>
       </c>
       <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>Assistant midwife, Traditional midwife</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Primary care physician, family doctor, GP</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:010056</t>
+          <t>BCIO:010011</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2838,32 +2769,32 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>ambulance worker</t>
+          <t>specialist medical practitioner</t>
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>A health associate professional that provides emergency health care to patients who are injured, sick, infirm or otherwise physically or mentally impaired prior to and during transport to medical facilities.</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans, using specialized testing, diagnostic, medical, surgical, physical and psychiatric techniques through application of the principles and procedures of modern medicine. They specialize in certain disease categories, types of patient or methods of treatment and may conduct medical education and research in their chosen areas of specialization.</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>Ambulance officer, Ambulance paramedic, Emergency medical technician, Emergency paramedic</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Anaesthetist, Cardiologist, Emergency medicine specialist, Gynaecologist, Obstetrician, Ophthalmologist, Paediatrician, Pathologist, Preventive medicine specialist, Psychiatrist, Radiation oncologist, Radiologist, Resident medical officer in specialist training, Specialist medical practitioner (public health), Specialist physician (internal medicine), Specialist physician (nuclear medicine), Surgeon</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:010050</t>
+          <t>BCIO:010019</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2875,35 +2806,35 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>traditional and complementary medicine associate professional</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>pharmacist</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>A health associate professional that prevents and treats human physical and mental illnesses, disorders and injuries using herbal and other therapies based on theories, beliefs and experiences originating in specific cultures. They administer treatments using traditional techniques and medicaments, either acting independently or according to therapeutic care plans established by a traditional medicine or other health professional.</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that stores, preserves, compounds and dispenses medicinal products and counsel on the proper use and adverse effects of drugs and medicines following prescriptions issued by medical doctors and other health professionals.</t>
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>Acupuncture technician, Ayurvedic technician, Bonesetter, Herbalist , Homeopathy technician, Scraping and cupping therapist, Village healer, Witch doctor</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr"/>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Dispensing chemist, Hospital pharmacist, Industrial pharmacist, Retail pharmacist</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:010052</t>
+          <t>BCIO:010016</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2915,35 +2846,35 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>community health worker</t>
-        </is>
-      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>paramedical practitioner</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>A health associate professional that provides health education, referral and follow-up, case management, basic preventive health care and home visiting services to specific communities. They provide support and assistance to individuals and families in navigating the health and social services system.</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that provides advisory, diagnostic, curative and preventive medical services more limited in scope and complexity than those carried out by medical doctors. They work autonomously or with limited supervision of medical doctors, and apply advanced clinical procedures for treating and preventing diseases, injuries and other physical or mental impairments common to specific communities.</t>
         </is>
       </c>
       <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>Community health aide, Community health promoter, Community health worker, Village health worker, outreach worker, health worker</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Advanced care paramedic, Clinical officer (paramedical), Feldscher, Primary care paramedic, Surgical technician</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:010046</t>
+          <t>BCIO:010024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2955,35 +2886,35 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>medical and pharmaceutical technician</t>
-        </is>
-      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>optometrist and ophthalmic optician</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>A health associate professional that performs technical tasks to assist in diagnosis and treatment of illness, disease, injuries and impairments.</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional  that provides diagnosis, management and treatment services for disorders of the eyes and visual system.</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>Medical imaging and therapeutic equipment technician, Medical and Pathology laboratory technician, Pharmaceutical technician, Medical and dental prosthetic technician</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr"/>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Ophthalmic optician , Optometrist, Orthoptist</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:010051</t>
+          <t>BCIO:010015</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2995,35 +2926,35 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>dental assistant and therapist</t>
-        </is>
-      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>traditional and complementary medicine professional</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>A health associate professional that provides basic dental care services for the prevention and treatment of diseases and disorders of the teeth and mouth, according to care plans and procedures established by a dentist or other oral health professional.</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that examines patients, prevents and treats illness, disease, injury and other physical and mental impairments and maintains general health in humans. They do this by applying knowledge, skills and practices acquired through extensive study of the theories, beliefs and experiences originating in specific cultures.</t>
         </is>
       </c>
       <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>Dental assistant, Dental hygienist , Dental therapist</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Acupuncturist, Ayurvedic practitioner,  Chinese herbal medicine practitioner, Homeopath, Naturopath, Unani practitioner</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:010060</t>
+          <t>BCIO:010022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -3037,33 +2968,33 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>religious associate professional</t>
+          <t>dietician and nutritionist</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>A technician and associate professional that provides support to ministers of religion or to a religious community, undertake religious works, preach and propagate the teachings of a particular religion and endeavour to improve well-being through the power of faith and spiritual advice.</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional  that assesses, plans and implements programmes to enhance the impact of food and nutrition on human health.</t>
         </is>
       </c>
       <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>Faith healer, Lay preacher, Monk, Nun</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Clinical dietician, Food service dietician, Nutritionist, Public health nutritionist, Sports nutritionist</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCIO:010065</t>
+          <t>BCIO:010018</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3077,33 +3008,33 @@
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>artistic, cultural and culinary associate professional</t>
+          <t>dentist</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>A technician and associate professional that combines creative skills and technical and cultural knowledge in creative media or food.</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that diagnoses treats and prevents diseases, injuries and abnormalities of the teeth, mouth, jaws and associated tissues by applying the principles and procedures of modern dentistry.</t>
         </is>
       </c>
       <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>Photographer, Interior designers and decorator, Gallery, museum and library technician, Chef</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr"/>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Dental practitioner, Dental surgeon, Dentist, Endodontist, Oral and maxillofacial surgeon, Oral pathologist, Orthodontist, Paedodontist, Periodontist, Prosthodontist, Stomatologist</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIO:010059</t>
+          <t>BCIO:010014</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3117,33 +3048,33 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>social work associate professional</t>
+          <t>midwifery professional</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>A technician and associate professional that implements social assistance programmes and community services and assist clients to deal with personal and social problems.</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that plans, manages, provides and evaluates midwifery care services before, during and after pregnancy and childbirth. They provide delivery care for reducing health risks to women and newborn children, working autonomously or in teams with other health care providers.</t>
         </is>
       </c>
       <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>Community development worker, Community services worker, Crisis intervention worker, Disability services worker, Family services worker, Life skills instructor, Mental health support worker, Welfare support worker, Women’s shelter supervisor, Youth services worker</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr"/>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Midwife</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BCIO:010057</t>
+          <t>BCIO:010034</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3154,36 +3085,32 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>business and administration associate professional</t>
-        </is>
-      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>legal, social and cultural professional</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs mostly technical tasks connected with the practical application of knowledge relating to financial accounting and transaction matters, mathematical calculations, human resource development, selling and buying financial instruments, specialized secretarial tasks and enforcing or applying government rules.</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A professional that conducts research, improves or develops concepts, theories and operational methods, or applies knowledge relating to the law, social or cultural studies.</t>
         </is>
       </c>
       <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>Financial and Mathematical associate professional, Sales and purchasing agent, Broker, Business Services Agent, Administrative and Specialized Secretary, Government regulatory associate professional, Medical secretary</t>
-        </is>
-      </c>
       <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BCIO:010061</t>
+          <t>BCIO:010043</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3197,33 +3124,33 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>sport and fitness worker</t>
+          <t>creative and performing artist</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>A technician and associate professional that prepares for and competes in sporting events for financial gain, trains amateur and professional sportsmen and women to enhance performance, promotes participation and standards in sport, organises and officiates sporting events, or provides instruction, training and supervision for various forms of exercise and other recreational activities.</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A legal, social and cultural professional that communicates ideas, impressions and facts in a wide range of media to achieve particular effects, interprets a composition such as a musical score or a script to perform or direct the performance, and hosts the presentation of such performance and other media events.</t>
         </is>
       </c>
       <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>physical activity professional, exercise physiologist, exercise therapist, exercise specialist</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Visual artist, Musician, Singer, Composer, Dancer, Choreographer, Director, Producer, Actor, Announcer on radio, television and other media</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BCIO:010062</t>
+          <t>BCIO:010040</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3235,35 +3162,35 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>athlete and sports player</t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>religious professional</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that participates in competitive sporting events. They train and compete, either individually or as part of a team, in their chosen sport.</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A legal, social and cultural professional that functions  as a perpetuator of sacred traditions, practices and beliefs. They conduct religious services, celebrate or administer the rites of a religious faith or denomination, provide spiritual and moral guidance and perform other functions associated with the practice of a religion.</t>
         </is>
       </c>
       <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>Athlete, Bicycle racer, Boxer, Chess player , Footballer, Golfer, Hockey player, Jockey, Poker player, Racing driver, Skier, Tennis player, Wrestler</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Bonze, Imam, Minister of religion, Poojari, Priest, Rabbi</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BCIO:010064</t>
+          <t>BCIO:010036</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3275,35 +3202,35 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>fitness and recreation instructor and programme leader</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>librarian, archivist and curator</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that leads, guides and instructs groups and individuals in recreational, fitness or outdoor adventure activities.</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A legal, social and cultural professional that develops and maintains collections of archives, libraries, museums, art galleries and similar establishments.</t>
         </is>
       </c>
       <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>Aerobics instructor, Fitness instructor, Horse riding instructor, Outdoor adventure guide, Personal trainer, Sailing instructor, Underwater diving instructor</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Librarian, Archivist,  Curator</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BCIO:010063</t>
+          <t>BCIO:010035</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3315,35 +3242,35 @@
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>sports coach, instructor and official</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>legal professional</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that works with amateur and professional sportspersons to enhance performance and encourage greater participation in sport, and organizes and officiates in sporting events according to established rules.</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A legal, social and cultural professional that conducts research on legal problems, advises clients on legal aspects of problems, pleads cases or conducts prosecutions in courts of law, presides over judicial proceedings in courts of law and draft laws and regulations.</t>
         </is>
       </c>
       <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>Referee, Ski instructor, Sports coach, Sports official, Swimming instructor</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Lawyer, Judge, Coroner</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BCIO:010066</t>
+          <t>BCIO:010037</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3357,33 +3284,33 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>information and communications technician</t>
+          <t>social professional</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>A technician and associate professional that provides support for the day to day running of computer systems, communication systems and networks, broadcast images and sound, telecommunication signals on land, sea or in aircraft.</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A legal, social and cultural professional that conducts research, improves or develops concepts, theories and operational methods or applies knowledge relating to psychology, sociology, philosophy, politics, economics, sociology, anthropology, history and other social sciences, or provides social services to meet the needs of individuals and families in a community.</t>
         </is>
       </c>
       <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>Information and Communications Technology Operations and User Support Technician, Telecommunications and Broadcasting Technician</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr"/>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Economist, Sociologist, Anthropologist, Philosopher, Historian, Political Scientist</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCIO:010058</t>
+          <t>BCIO:010038</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3395,35 +3322,35 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>legal and related associate professional</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>psychologist</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs support functions in courts of law or in law offices, provide services related to such legal matters as insurance contracts, the transferring of property and the granting of loans and other financial transactions, or conduct investigations for clients.</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A social professional that studies the mental processes and behaviour of human beings as individuals or in groups, and applies this knowledge to promote personal, social, educational or occupational adjustment and development.</t>
         </is>
       </c>
       <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>Bailiff, Judge’s clerk, Conveyancing clerk, Court clerk, Justice of the peace, Law clerk, Legal assistant, Paralegal, Private detective, Title searcher</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr"/>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Clinical psychologist, Counselling psychologist, Educational psychologist, Forensic psychologist, Health psychologist, Neuropsychologist, Organizational psychologist, Psychotherapist, Sport and exercise psychologist</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIO:010025</t>
+          <t>BCIO:010039</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3434,36 +3361,36 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>teaching professional</t>
-        </is>
-      </c>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>social work and counselling professional</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>A professional that teaches the theory and practice of one or more disciplines at different educational levels.</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A social professional that provides advice and guidance to individuals, families, groups, communities and organizations in response to social and personal difficulties. They assist clients to develop skills and access resources and support services needed to respond to issues arising from unemployment, poverty, disability, addiction, criminal and delinquent behaviour, marital and other problems.</t>
         </is>
       </c>
       <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>Education Methods Specialist, Other Language Teacher, Information Technology Teacher, Private Tutor, School Counsellor, Student Advisor</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Counsellor, Addictions counsellor, Bereavement counsellor, Child and youth counsellor, District social welfare officer, Family counsellor, Marriage counsellor, Parole officer, Probation officer, Sexual assault counsellor, Social worker, Women’s welfare organizer</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BCIO:010033</t>
+          <t>BCIO:010042</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3477,33 +3404,33 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>arts teacher</t>
+          <t>linguist</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>A teaching professional  that teaches students in the practice, theory and performance of dance, drama, visual and other arts (excluding music) in private or small group tuition or within mainstream educational institutions.</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A legal, social and cultural professional that translates or interprets from one language into another.</t>
         </is>
       </c>
       <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>Dance teacher (private tuition), Drama teacher (private tuition), Painting teacher (private tuition), Sculpture teacher (private tuition)</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr"/>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Interpretator; other linguist</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BCIO:010031</t>
+          <t>BCIO:010041</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3517,33 +3444,33 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>special needs teacher</t>
+          <t>author and journalist</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches children, young persons or adults with physical or intellectual special needs.</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A legal, social and cultural professional that conceives and creates literary works, and interprets and communicates news and public affairs through the media.</t>
         </is>
       </c>
       <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>Learning disabilities special education teacher, Learning support teacher, Remedial teacher, Teacher of gifted children, Teacher of the hearing impaired, Teacher of the sight impaired</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr"/>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Author, Writer, Journalist, Translator, News anchor</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BCIO:010032</t>
+          <t>BCIO:010044</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3554,36 +3481,32 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>music teacher</t>
-        </is>
-      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>technician and associate professional</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches students in the practice, theory and performance of music in private or small group tuition or within mainstream educational institutions.</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A professional that performs technical and related tasks connected with research and the application of scientific or artistic concepts and operational methods, and government or business regulations.</t>
         </is>
       </c>
       <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>Guitar teacher (private tuition), Piano teacher (private tuition), Singing teacher (private tuition), Violin teacher (private tuition)</t>
-        </is>
-      </c>
       <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BCIO:010026</t>
+          <t>BCIO:010057</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3597,33 +3520,33 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>university and higher education teacher</t>
+          <t>business and administration associate professional</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
-          <t>A teaching professional that prepares and delivers lectures and conduct tutorials in one or more subjects within a prescribed course of study at a university or other higher educational institution. They conduct research, and prepare scholarly papers and books.</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A technician and associate professional that performs mostly technical tasks connected with the practical application of knowledge relating to financial accounting and transaction matters, mathematical calculations, human resource development, selling and buying financial instruments, specialized secretarial tasks and enforcing or applying government rules.</t>
         </is>
       </c>
       <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>Higher education lecturer, Professor, University lecturer, University tutor</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr"/>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Financial and Mathematical associate professional, Sales and purchasing agent, Broker, Business Services Agent, Administrative and Specialized Secretary, Government regulatory associate professional, Medical secretary</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BCIO:010027</t>
+          <t>BCIO:010065</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3637,33 +3560,33 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>vocational education teacher</t>
+          <t>artistic, cultural and culinary associate professional</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches or instructs vocational or occupational subjects in adult and further education institutions and to senior students in secondary schools and colleges.</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A technician and associate professional that combines creative skills and technical and cultural knowledge in creative media or food.</t>
         </is>
       </c>
       <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>Automotive technology instructor, Cosmetology instructor, Vocational education teacher</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr"/>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Photographer, Interior designers and decorator, Gallery, museum and library technician, Chef</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BCIO:010028</t>
+          <t>BCIO:010059</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3677,33 +3600,33 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>secondary education teacher</t>
+          <t>social work associate professional</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches one or more subjects at secondary education level.</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A technician and associate professional that implements social assistance programmes and community services and assist clients to deal with personal and social problems.</t>
         </is>
       </c>
       <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>Secondary school teacher, High school teacher</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr"/>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Community development worker, Community services worker, Crisis intervention worker, Disability services worker, Family services worker, Life skills instructor, Mental health support worker, Welfare support worker, Women’s shelter supervisor, Youth services worker</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BCIO:010030</t>
+          <t>BCIO:010061</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3717,33 +3640,33 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>early childhood educator</t>
+          <t>sport and fitness worker</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
-          <t>A teaching professional that promotes the social, physical, and intellectual development of children below primary school age through the provision of educational and play activities.</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A technician and associate professional that prepares for and competes in sporting events for financial gain, trains amateur and professional sportsmen and women to enhance performance, promotes participation and standards in sport, organises and officiates sporting events, or provides instruction, training and supervision for various forms of exercise and other recreational activities.</t>
         </is>
       </c>
       <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>Early childhood educator, Pre-school teacher</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr"/>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>physical activity professional, exercise physiologist, exercise therapist, exercise specialist</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BCIO:010029</t>
+          <t>BCIO:010064</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3755,31 +3678,35 @@
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>primary school teacher</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>fitness and recreation instructor and programme leader</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches teach a range of subjects at the primary education level.</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A sport and fitness worker that leads, guides and instructs groups and individuals in recreational, fitness or outdoor adventure activities.</t>
         </is>
       </c>
       <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Aerobics instructor, Fitness instructor, Horse riding instructor, Outdoor adventure guide, Personal trainer, Sailing instructor, Underwater diving instructor</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BCIO:010008</t>
+          <t>BCIO:010063</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3790,36 +3717,36 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>health professional</t>
-        </is>
-      </c>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>sports coach, instructor and official</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>A professional that improves or develops concepts, theories and operational method, and applied scientific knowledge relating to medicine, nursing, dentistry, veterinary medicine, pharmacy, and promotion of health.</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A sport and fitness worker that works with amateur and professional sportspersons to enhance performance and encourage greater participation in sport, and organizes and officiates in sporting events according to established rules.</t>
         </is>
       </c>
       <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>Health professional; Arts therapist, Chiropractor, Dance and movement therapist, Occupational therapist, Osteopath, Podiatrist, Recreational therapist, Health staff, Clinic staff</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr"/>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Referee, Ski instructor, Sports coach, Sports official, Swimming instructor</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BCIO:010023</t>
+          <t>BCIO:010062</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3831,35 +3758,35 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>audiologist and speech therapist</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>athlete and sports player</t>
+        </is>
+      </c>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>A health professional  that evaluates, manages and treats physical disorders affecting human hearing, speech, communication and swallowing.</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A sport and fitness worker that participates in competitive sporting events. They train and compete, either individually or as part of a team, in their chosen sport.</t>
         </is>
       </c>
       <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>Audiologist, Language therapist, Speech pathologist, Speech therapist</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr"/>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Athlete, Bicycle racer, Boxer, Chess player , Footballer, Golfer, Hockey player, Jockey, Poker player, Racing driver, Skier, Tennis player, Wrestler</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BCIO:010009</t>
+          <t>BCIO:010066</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3873,33 +3800,33 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>medical doctor</t>
+          <t>information and communications technician</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>A health professional that studies, diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans through the application of modern medicine. They plan, supervise and evaluate the implementation of care and treatment plans by other health care providers, and conduct medical education and research activities.</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A technician and associate professional that provides support for the day to day running of computer systems, communication systems and networks, broadcast images and sound, telecommunication signals on land, sea or in aircraft.</t>
         </is>
       </c>
       <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>District medical doctor-therapist, family medical practitioner, general practitioner, medical doctor (general), medical officer (general), physician (general), primary health care physician, resident medical officer specializing in general practice</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr"/>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Information and Communications Technology Operations and User Support Technician, Telecommunications and Broadcasting Technician</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BCIO:010011</t>
+          <t>BCIO:010060</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3911,35 +3838,35 @@
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>specialist medical practitioner</t>
-        </is>
-      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>religious associate professional</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans, using specialized testing, diagnostic, medical, surgical, physical and psychiatric techniques through application of the principles and procedures of modern medicine. They specialize in certain disease categories, types of patient or methods of treatment and may conduct medical education and research in their chosen areas of specialization.</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A technician and associate professional that provides support to ministers of religion or to a religious community, undertake religious works, preach and propagate the teachings of a particular religion and endeavour to improve well-being through the power of faith and spiritual advice.</t>
         </is>
       </c>
       <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>Anaesthetist, Cardiologist, Emergency medicine specialist, Gynaecologist, Obstetrician, Ophthalmologist, Paediatrician, Pathologist, Preventive medicine specialist, Psychiatrist, Radiation oncologist, Radiologist, Resident medical officer in specialist training, Specialist medical practitioner (public health), Specialist physician (internal medicine), Specialist physician (nuclear medicine), Surgeon</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr"/>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Faith healer, Lay preacher, Monk, Nun</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BCIO:010010</t>
+          <t>BCIO:010045</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3951,35 +3878,35 @@
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>generalist medical practitioner</t>
-        </is>
-      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>health associate professional</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments and maintains general health in humans through application of modern medicine. They do not limit their practice to certain disease categories or methods of treatment, and may assume responsibility for the provision of continuing and comprehensive medical care to individuals, families and communities.</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A technician and associate professional that performs technical and practical tasks to support diagnosis and treatment of illness, disease, injuries and impairments in humans or animals, and supports the implementation of health care usually established by medical, veterinary, nursing and other health professionals.</t>
         </is>
       </c>
       <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>Primary care physician, family doctor, GP</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr"/>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Veterinary Technician</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BCIO:010022</t>
+          <t>BCIO:010046</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -3991,35 +3918,35 @@
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>dietician and nutritionist</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>medical and pharmaceutical technician</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
-          <t>A health professional  that assesses, plans and implements programmes to enhance the impact of food and nutrition on human health.</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health associate professional that performs technical tasks to assist in diagnosis and treatment of illness, disease, injuries and impairments.</t>
         </is>
       </c>
       <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>Clinical dietician, Food service dietician, Nutritionist, Public health nutritionist, Sports nutritionist</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr"/>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Medical imaging and therapeutic equipment technician, Medical and Pathology laboratory technician, Pharmaceutical technician, Medical and dental prosthetic technician</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BCIO:010013</t>
+          <t>BCIO:010050</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -4031,35 +3958,35 @@
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>nursing professional</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>traditional and complementary medicine associate professional</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
-          <t>A health professional that provides treatment, support and care services for people who are in need of nursing care due to the effects of ageing, injury, illness or other physical or mental impairment, or potential risks to health.</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health associate professional that prevents and treats human physical and mental illnesses, disorders and injuries using herbal and other therapies based on theories, beliefs and experiences originating in specific cultures. They administer treatments using traditional techniques and medicaments, either acting independently or according to therapeutic care plans established by a traditional medicine or other health professional.</t>
         </is>
       </c>
       <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>Clinical nurse consultant, District nurse, Nurse anaesthetist, Nurse educator, Nurse practitioner, Operating theatre nurse, Professional nurse, Public health nurse, Specialist nurse, Nursing Counsellor, Study Nurse</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr"/>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Acupuncture technician, Ayurvedic technician, Bonesetter, Herbalist , Homeopathy technician, Scraping and cupping therapist, Village healer, Witch doctor</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BCIO:010019</t>
+          <t>BCIO:010054</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -4071,35 +3998,35 @@
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>pharmacist</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>medical assistant</t>
+        </is>
+      </c>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
-          <t>A health professional that stores, preserves, compounds and dispenses medicinal products and counsel on the proper use and adverse effects of drugs and medicines following prescriptions issued by medical doctors and other health professionals.</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health associate professional that performs basic clinical and administrative tasks to support patient care under the direct supervision of a medical practitioner or other health professional.</t>
         </is>
       </c>
       <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>Dispensing chemist, Hospital pharmacist, Industrial pharmacist, Retail pharmacist</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr"/>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Clinical assistant, Medical assistant, Ophthalmic assistant</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BCIO:010016</t>
+          <t>BCIO:010053</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -4111,35 +4038,35 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>paramedical practitioner</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>physiotherapy technician and assistant</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
-          <t>A health professional that provides advisory, diagnostic, curative and preventive medical services more limited in scope and complexity than those carried out by medical doctors. They work autonomously or with limited supervision of medical doctors, and apply advanced clinical procedures for treating and preventing diseases, injuries and other physical or mental impairments common to specific communities.</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health associate professional that provides physical therapeutic treatments to patients in circumstances where functional movement is threatened by injury, disease or impairment. Therapies are usually provided according to rehabilitative plans established by a physiotherapist or other health professional.</t>
         </is>
       </c>
       <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>Advanced care paramedic, Clinical officer (paramedical), Feldscher, Primary care paramedic, Surgical technician</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr"/>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>Acupressure therapist, Electrotherapist, Hydrotherapist, Massage therapist, Physical rehabilitation technician, Physiotherapy technician, Shiatsu therapist</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BCIO:010017</t>
+          <t>BCIO:010047</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4151,35 +4078,35 @@
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>veterinarian</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>nursing and midwifery associate professional</t>
+        </is>
+      </c>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>A health professional that diagnoses, prevents and treats diseases, injuries and dysfunctions of animals.</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health associate professional that provides basic nursing and personal care for people who are physically or mentally ill, disabled or infirm, and for others in need of care due to potential risks to health including before, during and after childbirth. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing, midwifery and other health professionals.</t>
         </is>
       </c>
       <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>Animal pathologist, Veterinarian, Veterinary epidemiologist, Veterinary intern, Veterinary surgeon</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr"/>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Practice assistant, Quit Smoking Counsellor, Health educator, Dispensing Optician, Information Technician</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BCIO:010015</t>
+          <t>BCIO:010049</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4191,35 +4118,35 @@
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>traditional and complementary medicine professional</t>
-        </is>
-      </c>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>midwifery associate professional</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>A health professional that examines patients, prevents and treats illness, disease, injury and other physical and mental impairments and maintains general health in humans. They do this by applying knowledge, skills and practices acquired through extensive study of the theories, beliefs and experiences originating in specific cultures.</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A nursing and midwifery associate professional that provides basic health care and advice before, during and after pregnancy and childbirth. They implement care, treatment and referral plans usually established by medical, midwifery and other health professionals.</t>
         </is>
       </c>
       <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>Acupuncturist, Ayurvedic practitioner,  Chinese herbal medicine practitioner, Homeopath, Naturopath, Unani practitioner</t>
-        </is>
-      </c>
-      <c r="R99" t="inlineStr"/>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>Assistant midwife, Traditional midwife</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BCIO:010014</t>
+          <t>BCIO:010048</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4231,35 +4158,35 @@
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>midwifery professional</t>
-        </is>
-      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>nursing associate professional</t>
+        </is>
+      </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>A health professional that plans, manages, provides and evaluates midwifery care services before, during and after pregnancy and childbirth. They provide delivery care for reducing health risks to women and newborn children, working autonomously or in teams with other health care providers.</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A nursing and midwifery associate professional that provides basic nursing and personal care for people in need of such care due to effects of ageing, illness, injury, or other physical or mental impairment. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing and other health professionals.</t>
         </is>
       </c>
       <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>Midwife</t>
-        </is>
-      </c>
-      <c r="R100" t="inlineStr"/>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Assistant nurse, Associate professional nurse, Enrolled nurse, Practical nurse</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BCIO:010018</t>
+          <t>BCIO:010056</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4271,35 +4198,35 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>dentist</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>ambulance worker</t>
+        </is>
+      </c>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
-          <t>A health professional that diagnoses treats and prevents diseases, injuries and abnormalities of the teeth, mouth, jaws and associated tissues by applying the principles and procedures of modern dentistry.</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health associate professional that provides emergency health care to patients who are injured, sick, infirm or otherwise physically or mentally impaired prior to and during transport to medical facilities.</t>
         </is>
       </c>
       <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>Dental practitioner, Dental surgeon, Dentist, Endodontist, Oral and maxillofacial surgeon, Oral pathologist, Orthodontist, Paedodontist, Periodontist, Prosthodontist, Stomatologist</t>
-        </is>
-      </c>
-      <c r="R101" t="inlineStr"/>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Ambulance officer, Ambulance paramedic, Emergency medical technician, Emergency paramedic</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BCIO:010024</t>
+          <t>BCIO:010052</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4311,35 +4238,35 @@
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>optometrist and ophthalmic optician</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>community health worker</t>
+        </is>
+      </c>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
-          <t>A health professional  that provides diagnosis, management and treatment services for disorders of the eyes and visual system.</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health associate professional that provides health education, referral and follow-up, case management, basic preventive health care and home visiting services to specific communities. They provide support and assistance to individuals and families in navigating the health and social services system.</t>
         </is>
       </c>
       <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>Ophthalmic optician , Optometrist, Orthoptist</t>
-        </is>
-      </c>
-      <c r="R102" t="inlineStr"/>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Community health aide, Community health promoter, Community health worker, Village health worker, outreach worker, health worker</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BCIO:010012</t>
+          <t>BCIO:010055</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4351,31 +4278,36 @@
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>nursing and midwifery professional</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>environmental and occupational health inspector and associate</t>
+        </is>
+      </c>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
-          <t>A health professional that provides treatment and care services for people who are physically or mentally ill, disabled or infirm, and those with potential risks to health including before, during and after childbirth. They assume responsibility for the planning, management and evaluation of the care of patients, including the supervision of other health care workers, working autonomously or in teams with medical doctors and others in the practical application of preventive and curative measures.</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health associate professional that investigates the implementation of rules and regulations relating to environmental factors that may affect human health, safety in the 
+workplace, and safety of processes for the production of goods and services. They may implement and evaluate programmes to restore or improve safety and sanitary conditions under the supervision of a health professional.</t>
         </is>
       </c>
       <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="inlineStr"/>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>Food sanitation and safety inspector, Health inspector, Occupational health and safety inspector, Pollution inspector, Product safety inspector, Sanitarian, Sanitary inspector</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BCIO:010020</t>
+          <t>BCIO:010051</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4387,35 +4319,35 @@
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>environmental and occupational health and hygiene professional</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>dental assistant and therapist</t>
+        </is>
+      </c>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t>A health professional that assesses, plans and implements programmes to recognize, monitor and control environmental factors that can potentially affect human health, to ensure safe and healthy working conditions and to prevent disease or injury caused by chemical, physical, radiological and biological agents or ergonomic factors.</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health associate professional that provides basic dental care services for the prevention and treatment of diseases and disorders of the teeth and mouth, according to care plans and procedures established by a dentist or other oral health professional.</t>
         </is>
       </c>
       <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>Environmental health officer, Occupational health and safety adviser, Occupational hygienist, Radiation protection expert</t>
-        </is>
-      </c>
-      <c r="R104" t="inlineStr"/>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>Dental assistant, Dental hygienist , Dental therapist</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BCIO:010021</t>
+          <t>BCIO:010058</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4429,33 +4361,33 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>physiotherapist</t>
+          <t>legal and related associate professional</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
-          <t>A health professional  that assesses, plans and implements rehabilitative programmes that improve or restore human motor functions, maximize movement ability, relieve pain syndromes, and treat or prevent physical challenges associated with injuries, diseases and other impairments.</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A technician and associate professional that performs support functions in courts of law or in law offices, provide services related to such legal matters as insurance contracts, the transferring of property and the granting of loans and other financial transactions, or conduct investigations for clients.</t>
         </is>
       </c>
       <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr">
-        <is>
-          <t>Geriatric physical therapist, Manipulative therapist, Orthopaedic physical therapist, Paediatric physical therapist, Physical therapist, Physiotherapist</t>
-        </is>
-      </c>
-      <c r="R105" t="inlineStr"/>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>Bailiff, Judge’s clerk, Conveyancing clerk, Court clerk, Justice of the peace, Law clerk, Legal assistant, Paralegal, Private detective, Title searcher</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BCIO:010007</t>
+          <t>BCIO:010025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4468,7 +4400,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>science and engineering professional</t>
+          <t>teaching professional</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -4476,26 +4408,26 @@
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
-          <t>A professional that conducts research, improves or develops concepts, theories and operational methods or applies scientific knowledge.</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A professional that teaches the theory and practice of one or more disciplines at different educational levels.</t>
         </is>
       </c>
       <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>Science Professional, Mathematician, Actuary, Statistician, Life Science Professional, Engineering Professional, Electrotechnology Engineer, Architect, Planner, Surveyor, Designer</t>
-        </is>
-      </c>
-      <c r="R106" t="inlineStr"/>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>Education Methods Specialist, Other Language Teacher, Information Technology Teacher, Private Tutor, School Counsellor, Student Advisor</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BCIO:010081</t>
+          <t>BCIO:010032</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4505,37 +4437,37 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>elementary occupation</t>
-        </is>
-      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>music teacher</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
-          <t>An occupational role that involves the performance of simple and routine tasks which may require the use of hand-held tools and considerable physical effort.</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A teaching professional that teaches students in the practice, theory and performance of music in private or small group tuition or within mainstream educational institutions.</t>
         </is>
       </c>
       <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>Cleaner, Labourer, Food Preparation Assistant, Street and Related Services Worker, Street Vendor (excluding Food), Refuse Worker</t>
-        </is>
-      </c>
-      <c r="R107" t="inlineStr"/>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>Guitar teacher (private tuition), Piano teacher (private tuition), Singing teacher (private tuition), Violin teacher (private tuition)</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BCIO:010094</t>
+          <t>BCIO:010029</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4544,34 +4476,34 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>relatedness between person source and the target population</t>
-        </is>
-      </c>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>primary school teacher</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
-          <t>A personal role of source that is realised in some relationship to the characteristics of the intervention participants.</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A teaching professional that teaches teach a range of subjects at the primary education level.</t>
         </is>
       </c>
       <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BCIO:010102</t>
+          <t>BCIO:010026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4581,33 +4513,37 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>colleague</t>
-        </is>
-      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>university and higher education teacher</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person with whom the participant works in a profession or business.</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A teaching professional that prepares and delivers lectures and conduct tutorials in one or more subjects within a prescribed course of study at a university or other higher educational institution. They conduct research, and prepare scholarly papers and books.</t>
         </is>
       </c>
       <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
-      <c r="R109" t="inlineStr"/>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>Higher education lecturer, Professor, University lecturer, University tutor</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BCIO:010100</t>
+          <t>BCIO:010031</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4617,37 +4553,37 @@
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>carer</t>
-        </is>
-      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>special needs teacher</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is an individual who cares, unpaid, for a friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A teaching professional that teaches children, young persons or adults with physical or intellectual special needs.</t>
         </is>
       </c>
       <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>carer</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr"/>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>Learning disabilities special education teacher, Learning support teacher, Remedial teacher, Teacher of gifted children, Teacher of the hearing impaired, Teacher of the sight impaired</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BCIO:010101</t>
+          <t>BCIO:010030</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4657,33 +4593,37 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>friend</t>
-        </is>
-      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>early childhood educator</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person whom the participant knows, likes and trusts, typically exclusive of sexual or family relations.</t>
-        </is>
-      </c>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A teaching professional that promotes the social, physical, and intellectual development of children below primary school age through the provision of educational and play activities.</t>
         </is>
       </c>
       <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr"/>
-      <c r="R111" t="inlineStr"/>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>Early childhood educator, Pre-school teacher</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BCIO:010105</t>
+          <t>BCIO:010027</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4693,33 +4633,37 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>embedded in participants’ community</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>vocational education teacher</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a source who is known and working to deliver intervention in own community.</t>
-        </is>
-      </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A teaching professional that teaches or instructs vocational or occupational subjects in adult and further education institutions and to senior students in secondary schools and colleges.</t>
         </is>
       </c>
       <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
-      <c r="R112" t="inlineStr"/>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>Automotive technology instructor, Cosmetology instructor, Vocational education teacher</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BCIO:010103</t>
+          <t>BCIO:010028</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4729,33 +4673,37 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>employer</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>secondary education teacher</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person which hires the services of the participant.</t>
-        </is>
-      </c>
-      <c r="O113" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A teaching professional that teaches one or more subjects at secondary education level.</t>
         </is>
       </c>
       <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr"/>
-      <c r="R113" t="inlineStr"/>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>Secondary school teacher, High school teacher</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BCIO:010104</t>
+          <t>BCIO:010033</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -4765,33 +4713,37 @@
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>peer</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>arts teacher</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is descried as matched to intervention recipients on the basis of ‘peerness’ – age, social status, gender, shared experience, shared health status etc.</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A teaching professional  that teaches students in the practice, theory and performance of dance, drama, visual and other arts (excluding music) in private or small group tuition or within mainstream educational institutions.</t>
         </is>
       </c>
       <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
-      <c r="R114" t="inlineStr"/>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>Dance teacher (private tuition), Drama teacher (private tuition), Painting teacher (private tuition), Sculpture teacher (private tuition)</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BCIO:010084</t>
+          <t>BCIO:010094</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -4799,12 +4751,12 @@
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>relatedness between person source and the target population</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
@@ -4812,22 +4764,22 @@
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
-        </is>
-      </c>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A personal role of source that is realised in some relationship to the characteristics of the intervention participants.</t>
         </is>
       </c>
       <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BCIO:010086</t>
+          <t>BCIO:010103</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4836,34 +4788,34 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>school student or trainee</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>employer</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning at a primary or secondary education level in an institutional, organised setting.</t>
-        </is>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A relatedness between person source and the target population that is a person which hires the services of the participant.</t>
         </is>
       </c>
       <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BCIO:010088</t>
+          <t>BCIO:010102</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4872,38 +4824,34 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>higher education student or trainee</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>colleague</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning on an advanced educational programme in a university, college or professional school.</t>
-        </is>
-      </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A relatedness between person source and the target population that is a person with whom the participant works in a profession or business.</t>
         </is>
       </c>
       <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr">
-        <is>
-          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
-        </is>
-      </c>
       <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BCIO:010090</t>
+          <t>BCIO:010105</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4915,7 +4863,7 @@
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>graduate student or trainee</t>
+          <t>embedded in participants’ community</t>
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
@@ -4924,26 +4872,22 @@
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
-          <t>A higher education student or trainee that has completed an undergraduate degree.</t>
-        </is>
-      </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A relatedness between person source and the target population that is a source who is known and working to deliver intervention in own community.</t>
         </is>
       </c>
       <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr">
-        <is>
-          <t>graduate student</t>
-        </is>
-      </c>
       <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BCIO:010091</t>
+          <t>BCIO:010104</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -4955,7 +4899,7 @@
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
-          <t>masters student or trainee</t>
+          <t>peer</t>
         </is>
       </c>
       <c r="J119" t="inlineStr"/>
@@ -4964,26 +4908,22 @@
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
-          <t>A higher education student or trainee that is currently studying for a Masters degree.</t>
-        </is>
-      </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A relatedness between person source and the target population that is descried as matched to intervention recipients on the basis of ‘peerness’ – age, social status, gender, shared experience, shared health status etc.</t>
         </is>
       </c>
       <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>MSc student, Masters student</t>
-        </is>
-      </c>
       <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BCIO:010092</t>
+          <t>BCIO:010100</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -4995,7 +4935,7 @@
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
-          <t>doctoral student or trainee</t>
+          <t>carer</t>
         </is>
       </c>
       <c r="J120" t="inlineStr"/>
@@ -5004,26 +4944,26 @@
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr">
         <is>
-          <t>A higher education student or trainee that is currently studying for a doctoral degree.</t>
-        </is>
-      </c>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A relatedness between person source and the target population that is an individual who cares, unpaid, for a friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
         </is>
       </c>
       <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>PhD student</t>
-        </is>
-      </c>
-      <c r="R120" t="inlineStr"/>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>carer</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BCIO:010089</t>
+          <t>BCIO:010101</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -5035,7 +4975,7 @@
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>undergraduate student or trainee</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -5044,26 +4984,22 @@
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr">
         <is>
-          <t>A higher education student or trainee that is currently studying for an undergraduate degree.</t>
-        </is>
-      </c>
-      <c r="O121" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A relatedness between person source and the target population that is a person whom the participant knows, likes and trusts, typically exclusive of sexual or family relations.</t>
         </is>
       </c>
       <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>undergraduate student</t>
-        </is>
-      </c>
       <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BCIO:010085</t>
+          <t>BCIO:010000</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -5071,12 +5007,12 @@
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>informal education student or trainee</t>
-        </is>
-      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>behaviour change intervention source</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
@@ -5084,22 +5020,22 @@
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning in a non-institutional setting.</t>
-        </is>
-      </c>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A role played by a person, population or organisation that provides a BCI.</t>
         </is>
       </c>
       <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BCIO:010087</t>
+          <t>BCIO:010001</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -5110,7 +5046,7 @@
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>vocational training student or trainee</t>
+          <t>person source role</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -5120,45 +5056,58 @@
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
-        </is>
-      </c>
-      <c r="O123" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A behaviour change intervention source role that inheres in a person.</t>
         </is>
       </c>
       <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BFO:0000016</t>
+          <t>BCIO:010138</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>disposition</t>
-        </is>
-      </c>
+      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>organisational source role</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>A BCI source role that is borne by an organisation.</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BCIO:010120</t>
+          <t>BCIO:010133</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -5166,12 +5115,12 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>expertise of person source</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>source role related to intervention</t>
+        </is>
+      </c>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
@@ -5179,22 +5128,22 @@
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr">
         <is>
-          <t>A disposition that is an expert skill or knowledge held by the source delivering the behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A BCI source whose occupational or voluntary role is focused on delivery of the behaviour change intervention.</t>
         </is>
       </c>
       <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BCIO:010121</t>
+          <t>BCIO:010134</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -5205,7 +5154,7 @@
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>knowledge or skill</t>
+          <t>source involved in development of intervention</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -5215,26 +5164,22 @@
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
-          <t>An expertise of person source that is knowledge or skills held in order to deliver the behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A BCI source that is involved in the development of intervention content.</t>
         </is>
       </c>
       <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>trained (if unclear whether pre-existing or acquired)</t>
-        </is>
-      </c>
       <c r="R126" t="inlineStr"/>
+      <c r="S126" t="inlineStr"/>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BCIO:010125</t>
+          <t>BCIO:010135</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -5246,7 +5191,7 @@
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>acquired knowledge or skill</t>
+          <t>source involved in co-production of intervention</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -5255,22 +5200,22 @@
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
-          <t>A knowledge or skill that is additional knowledge or skills supplied to the source to allow them to deliver the behaviour change intervention, including educational level and qualifications.</t>
-        </is>
-      </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A source involved in development of intervention that has developed the intervention content in collaboration with key stakeholders such as patients or community members.</t>
         </is>
       </c>
       <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr"/>
       <c r="R127" t="inlineStr"/>
+      <c r="S127" t="inlineStr"/>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BCIO:010122</t>
+          <t>BCIO:010084</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5278,39 +5223,35 @@
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
       <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>pre-existing knowledge or skill</t>
-        </is>
-      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr">
         <is>
-          <t>A knowledge or skill that is already possessed by the source which allows them to deliver the behaviour change intervention, including educational level and qualifications.</t>
-        </is>
-      </c>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
         </is>
       </c>
       <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr">
-        <is>
-          <t>Bachelor’s degree, certification, accredited, qualified</t>
-        </is>
-      </c>
       <c r="R128" t="inlineStr"/>
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BCIO:010127</t>
+          <t>BCIO:010087</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -5319,51 +5260,47 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>vocational training student or trainee</t>
+        </is>
+      </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>affiliation to a formal group or organisation</t>
-        </is>
-      </c>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
-          <t>A pre-existing knowledge or skill that is recognised through affiliation to a formal group or organisation.</t>
-        </is>
-      </c>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A student or trainee that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
         </is>
       </c>
       <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>member of British Psychological Society</t>
-        </is>
-      </c>
       <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr"/>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BCIO:010123</t>
+          <t>BCIO:010088</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>expertise discipline</t>
-        </is>
-      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>higher education student or trainee</t>
+        </is>
+      </c>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
@@ -5371,167 +5308,186 @@
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr">
         <is>
-          <t>An attribute that is a field of knowledge or practice.</t>
-        </is>
-      </c>
-      <c r="O130" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A student or trainee that is currently learning on an advanced educational programme in a university, college or professional school.</t>
         </is>
       </c>
       <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr">
-        <is>
-          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
-        </is>
-      </c>
-      <c r="R130" t="inlineStr"/>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>The division of expertise into different disciplines or fields is complex and depends on historical, social and structural factors.</t>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr"/>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BCIO:010124</t>
+          <t>BCIO:010091</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>discipline of pre-existing knowledge or skill</t>
-        </is>
-      </c>
+      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>masters student or trainee</t>
+        </is>
+      </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr">
         <is>
-          <t>The expertise discipline in which the person source has acquired their pre-existing knowledge and skills.</t>
-        </is>
-      </c>
-      <c r="O131" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A higher education student or trainee that is currently studying for a Masters degree.</t>
         </is>
       </c>
       <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr">
-        <is>
-          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
-        </is>
-      </c>
-      <c r="R131" t="inlineStr"/>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>MSc student, Masters student</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr"/>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BCIO:010093</t>
+          <t>BCIO:010092</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>discipline of current programme of study or training</t>
-        </is>
-      </c>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>doctoral student or trainee</t>
+        </is>
+      </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr">
         <is>
-          <t>An expertise discipline of the programme of study currently undertaken by the bearer of a student or trainee role.</t>
-        </is>
-      </c>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A higher education student or trainee that is currently studying for a doctoral degree.</t>
         </is>
       </c>
       <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr">
-        <is>
-          <t>psychology, medicine, hairdressing</t>
-        </is>
-      </c>
-      <c r="R132" t="inlineStr"/>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>PhD student</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr"/>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MF:0000030</t>
+          <t>BCIO:010089</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>representation</t>
-        </is>
-      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>undergraduate student or trainee</t>
+        </is>
+      </c>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr">
         <is>
-          <t>A dependent continuant which is about a portion of reality.</t>
+          <t>A higher education student or trainee that is currently studying for an undergraduate degree.</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr"/>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>undergraduate student</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr"/>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MF:0000031</t>
+          <t>BCIO:010090</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>cognitive representation</t>
-        </is>
-      </c>
+      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>graduate student or trainee</t>
+        </is>
+      </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr">
         <is>
-          <t>A representation which specifically depends on an anatomical structure in the cognitive system of an organism.</t>
+          <t>A higher education student or trainee that has completed an undergraduate degree.</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr"/>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>graduate student</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr"/>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ADDICTO:0000381</t>
+          <t>BCIO:010085</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -5539,12 +5495,12 @@
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>informal education student or trainee</t>
+        </is>
+      </c>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
@@ -5552,14 +5508,22 @@
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr">
         <is>
-          <t>A cognitive representation of themselves by a person or a group about themselves.</t>
+          <t>A student or trainee that is currently learning in a non-institutional setting.</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ADDICTO:0000399</t>
+          <t>BCIO:010086</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5570,7 +5534,7 @@
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
-          <t>self-identity</t>
+          <t>school student or trainee</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -5580,50 +5544,45 @@
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr">
         <is>
-          <t>An identity that a person has about themselves.</t>
+          <t>A student or trainee that is currently learning at a primary or secondary education level in an institutional, organised setting.</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr"/>
+      <c r="R136" t="inlineStr"/>
+      <c r="S136" t="inlineStr"/>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BCIO:015098</t>
+          <t>BFO:0000016</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>gender identity</t>
-        </is>
-      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
-        </is>
-      </c>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>Population</t>
-        </is>
-      </c>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr"/>
-      <c r="R137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BCIO:010111</t>
+          <t>BCIO:010120</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5631,39 +5590,35 @@
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>expertise of person source</t>
+        </is>
+      </c>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>female gender</t>
-        </is>
-      </c>
+      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr">
         <is>
-          <t>A gender identity as being female.</t>
-        </is>
-      </c>
-      <c r="O138" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A disposition that is an expert skill or knowledge held by the source delivering the behaviour change intervention.</t>
         </is>
       </c>
       <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>female, woman</t>
-        </is>
-      </c>
       <c r="R138" t="inlineStr"/>
+      <c r="S138" t="inlineStr"/>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BCIO:010112</t>
+          <t>BCIO:010121</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -5672,162 +5627,166 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>knowledge or skill</t>
+        </is>
+      </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>male gender</t>
-        </is>
-      </c>
+      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr">
         <is>
-          <t>A gender identity as being male.</t>
-        </is>
-      </c>
-      <c r="O139" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An expertise of person source that is knowledge or skills held in order to deliver the behaviour change intervention.</t>
         </is>
       </c>
       <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="inlineStr">
-        <is>
-          <t>male, man</t>
-        </is>
-      </c>
-      <c r="R139" t="inlineStr"/>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>trained (if unclear whether pre-existing or acquired)</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr"/>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BCIO:010108</t>
+          <t>BCIO:010125</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>socio demographic attribute of person source</t>
-        </is>
-      </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>acquired knowledge or skill</t>
+        </is>
+      </c>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr">
         <is>
-          <t>A social or demographic characteristic of a human being who is the bearer of a person source role.</t>
-        </is>
-      </c>
-      <c r="O140" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A knowledge or skill that is additional knowledge or skills supplied to the source to allow them to deliver the behaviour change intervention, including educational level and qualifications.</t>
         </is>
       </c>
       <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr"/>
+      <c r="S140" t="inlineStr"/>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BCIO:010119</t>
+          <t>BCIO:010122</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>psychological influence on intervention delivery of person source</t>
-        </is>
-      </c>
+      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>pre-existing knowledge or skill</t>
+        </is>
+      </c>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is their existing psychological attributes related to or potentially affecting the target behaviour.</t>
-        </is>
-      </c>
-      <c r="O141" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A knowledge or skill that is already possessed by the source which allows them to deliver the behaviour change intervention, including educational level and qualifications.</t>
         </is>
       </c>
       <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="inlineStr"/>
-      <c r="R141" t="inlineStr"/>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree, certification, accredited, qualified</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr"/>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BCIO:010110</t>
+          <t>BCIO:010127</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>gender of person source</t>
-        </is>
-      </c>
+      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>affiliation to a formal group or organisation</t>
+        </is>
+      </c>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is an individual's perception of having a particular gender, which may or may not correspond with their birth sex.</t>
-        </is>
-      </c>
-      <c r="O142" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A pre-existing knowledge or skill that is recognised through affiliation to a formal group or organisation.</t>
         </is>
       </c>
       <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>gender</t>
-        </is>
-      </c>
-      <c r="R142" t="inlineStr"/>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>member of British Psychological Society</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr"/>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BCIO:010113</t>
+          <t>BCIO:010108</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>socio demographic attribute of person source</t>
+        </is>
+      </c>
       <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>other gender</t>
-        </is>
-      </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
@@ -5836,26 +5795,22 @@
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr">
         <is>
-          <t>A gender of person source that reports not belonging to the cultural gender role distinctions of either male or female.</t>
-        </is>
-      </c>
-      <c r="O143" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A social or demographic characteristic of a human being who is the bearer of a person source role.</t>
         </is>
       </c>
       <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="inlineStr">
-        <is>
-          <t>non-binary, transexual</t>
-        </is>
-      </c>
       <c r="R143" t="inlineStr"/>
+      <c r="S143" t="inlineStr"/>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BCIO:010116</t>
+          <t>BCIO:010119</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -5864,7 +5819,7 @@
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>language proficiency of person source</t>
+          <t>psychological influence on intervention delivery of person source</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -5876,26 +5831,22 @@
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is an individual’s ability to speak or perform in the intervention language.</t>
-        </is>
-      </c>
-      <c r="O144" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A socio-demographic attribute of person source that is their existing psychological attributes related to or potentially affecting the target behaviour.</t>
         </is>
       </c>
       <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr">
-        <is>
-          <t>fluent, native</t>
-        </is>
-      </c>
       <c r="R144" t="inlineStr"/>
+      <c r="S144" t="inlineStr"/>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BCIO:010118</t>
+          <t>BCIO:010109</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -5904,7 +5855,7 @@
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>target behaviour of person source</t>
+          <t>age of person source</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -5916,26 +5867,22 @@
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is their amount or experience of the intervention’s target behaviour.</t>
-        </is>
-      </c>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A socio-demographic attribute of person source that is a time quality inhering in a bearer by virtue of how long the bearer has existed.</t>
         </is>
       </c>
       <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="inlineStr">
-        <is>
-          <t>source is highly physically active</t>
-        </is>
-      </c>
       <c r="R145" t="inlineStr"/>
+      <c r="S145" t="inlineStr"/>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BCIO:010109</t>
+          <t>BCIO:010118</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -5944,7 +5891,7 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>age of person source</t>
+          <t>target behaviour of person source</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -5956,22 +5903,26 @@
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is a time quality inhering in a bearer by virtue of how long the bearer has existed.</t>
-        </is>
-      </c>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A socio-demographic attribute of person source that is their amount or experience of the intervention’s target behaviour.</t>
         </is>
       </c>
       <c r="P146" t="inlineStr"/>
-      <c r="Q146" t="inlineStr"/>
-      <c r="R146" t="inlineStr"/>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>source is highly physically active</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BCIO:010114</t>
+          <t>BCIO:010115</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -5980,7 +5931,7 @@
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>ethnic group membership of person source</t>
+          <t>religious group membership of person source</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -5992,26 +5943,26 @@
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is the ethnic group to which an individual identifies as belonging, where an ethic group is a population whose members have a common heritage that is real or presumed such as common culture, language, religion, behaviour or biological trait.</t>
-        </is>
-      </c>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A socio-demographic attribute of person source that is a religious group to which an individual identifies as belonging, where a religious group is a group of people characterised by the practice of a common religion.</t>
         </is>
       </c>
       <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="inlineStr">
-        <is>
-          <t>black, white, Indian, Chinese, Somalian</t>
-        </is>
-      </c>
-      <c r="R147" t="inlineStr"/>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Muslim, Christian, Hindu, Sikh, Buddhist, Judaism</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr"/>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BCIO:010115</t>
+          <t>BCIO:010117</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -6020,7 +5971,7 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>religious group membership of person source</t>
+          <t>health status of person source</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -6032,26 +5983,26 @@
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is a religious group to which an individual identifies as belonging, where a religious group is a group of people characterised by the practice of a common religion.</t>
-        </is>
-      </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A socio-demographic attribute of person source that represents their mental or physical condition.</t>
         </is>
       </c>
       <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="inlineStr">
-        <is>
-          <t>Muslim, Christian, Hindu, Sikh, Buddhist, Judaism</t>
-        </is>
-      </c>
-      <c r="R148" t="inlineStr"/>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>diabetes, cancer, depression, obesity, overweight</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr"/>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BCIO:010117</t>
+          <t>BCIO:010114</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -6060,7 +6011,7 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>health status of person source</t>
+          <t>ethnic group membership of person source</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -6072,37 +6023,37 @@
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that represents their mental or physical condition.</t>
-        </is>
-      </c>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A socio-demographic attribute of person source that is the ethnic group to which an individual identifies as belonging, where an ethic group is a population whose members have a common heritage that is real or presumed such as common culture, language, religion, behaviour or biological trait.</t>
         </is>
       </c>
       <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>diabetes, cancer, depression, obesity, overweight</t>
-        </is>
-      </c>
-      <c r="R149" t="inlineStr"/>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>black, white, Indian, Chinese, Somalian</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr"/>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BFO:0000031</t>
+          <t>BCIO:010110</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>generically dependent continuant</t>
-        </is>
-      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>gender of person source</t>
+        </is>
+      </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
@@ -6112,26 +6063,38 @@
       <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr">
         <is>
-          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
+          <t>A socio-demographic attribute of person source that is an individual's perception of having a particular gender, which may or may not correspond with their birth sex.</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr"/>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr"/>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>IAO:0000030</t>
+          <t>BCIO:010113</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>information content entity</t>
-        </is>
-      </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>other gender</t>
+        </is>
+      </c>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
@@ -6140,14 +6103,26 @@
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr">
         <is>
-          <t>A generically dependent continuant that is about some thing.</t>
+          <t>A gender of person source that reports not belonging to the cultural gender role distinctions of either male or female.</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr"/>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>non-binary, transexual</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr"/>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>IAO:0000027</t>
+          <t>BCIO:010116</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -6156,7 +6131,7 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>language proficiency of person source</t>
         </is>
       </c>
       <c r="G152" t="inlineStr"/>
@@ -6168,26 +6143,38 @@
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
-          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
+          <t>A socio-demographic attribute of person source that is an individual’s ability to speak or perform in the intervention language.</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr"/>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>fluent, native</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr"/>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BCIO:010107</t>
+          <t>BCIO:010123</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>expertise discipline</t>
+        </is>
+      </c>
       <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>total number of people able to deliver intervention</t>
-        </is>
-      </c>
+      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
@@ -6196,34 +6183,43 @@
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr">
         <is>
-          <t>A count data item that is the total number of providers that are available and able to deliver the intervention.</t>
-        </is>
-      </c>
-      <c r="O153" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An attribute that is a field of knowledge or practice.</t>
         </is>
       </c>
       <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr"/>
-      <c r="R153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>The division of expertise into different disciplines or fields is complex and depends on historical, social and structural factors.</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr"/>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BCIO:010106</t>
+          <t>BCIO:010093</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>number of people delivering intervention to each participant</t>
-        </is>
-      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>discipline of current programme of study or training</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
@@ -6232,34 +6228,38 @@
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr">
         <is>
-          <t>A count data item that is the number of providers that an individual participant in the intervention encounters.</t>
-        </is>
-      </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An expertise discipline of the programme of study currently undertaken by the bearer of a student or trainee role.</t>
         </is>
       </c>
       <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="inlineStr"/>
-      <c r="R154" t="inlineStr"/>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>psychology, medicine, hairdressing</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr"/>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BCIO:010126</t>
+          <t>BCIO:010124</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>amount of experience</t>
-        </is>
-      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>discipline of pre-existing knowledge or skill</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
@@ -6268,21 +6268,21 @@
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr">
         <is>
-          <t>A knowledge or skill that is the duration of experience in related domain held by person source.</t>
-        </is>
-      </c>
-      <c r="O155" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>The expertise discipline in which the person source has acquired their pre-existing knowledge and skills.</t>
         </is>
       </c>
       <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="inlineStr">
-        <is>
-          <t>full-day, 6 years</t>
-        </is>
-      </c>
-      <c r="R155" t="inlineStr"/>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr"/>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6343,7 +6343,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BCIO:010129</t>
+          <t>BCIO:010130</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -6351,7 +6351,7 @@
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>volunteering of person source</t>
+          <t>payment of person source</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -6364,37 +6364,33 @@
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr">
         <is>
-          <t>A process in which a person source delivers the intervention on a voluntary basis without formal compensation.</t>
-        </is>
-      </c>
-      <c r="O158" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A process in which a person source is paid or compensated for delivering the intervention.</t>
         </is>
       </c>
       <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr">
-        <is>
-          <t>voluntary basis, volunteering</t>
-        </is>
-      </c>
       <c r="R158" t="inlineStr"/>
+      <c r="S158" t="inlineStr"/>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BCIO:010128</t>
+          <t>BCIO:010132</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>supervision of person source</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>non-monetary payment</t>
+        </is>
+      </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
@@ -6404,37 +6400,37 @@
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr">
         <is>
-          <t>A process in which a person source is formally provided, by an individual with appropriate expertise, with corrective and skill-enhancing feedback, regarding the person source’s performance in delivering the intervention.</t>
-        </is>
-      </c>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A payment of person source that is non-monetary compensation given to the source for delivering the intervention.</t>
         </is>
       </c>
       <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="inlineStr">
-        <is>
-          <t>supervised</t>
-        </is>
-      </c>
-      <c r="R159" t="inlineStr"/>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>course credit</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr"/>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BCIO:010130</t>
+          <t>BCIO:010131</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>payment of person source</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>monetary payment</t>
+        </is>
+      </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
@@ -6444,33 +6440,37 @@
       <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr">
         <is>
-          <t>A process in which a person source is paid or compensated for delivering the intervention.</t>
-        </is>
-      </c>
-      <c r="O160" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A payment of person source that is money, vouchers or valued objects given to the source for delivering the intervention.</t>
         </is>
       </c>
       <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr"/>
-      <c r="R160" t="inlineStr"/>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>paid in cash, vouchers</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr"/>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BCIO:010131</t>
+          <t>BCIO:010129</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>monetary payment</t>
-        </is>
-      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>volunteering of person source</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
@@ -6480,37 +6480,37 @@
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr">
         <is>
-          <t>A payment of person source that is money, vouchers or valued objects given to the source for delivering the intervention.</t>
-        </is>
-      </c>
-      <c r="O161" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A process in which a person source delivers the intervention on a voluntary basis without formal compensation.</t>
         </is>
       </c>
       <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr">
-        <is>
-          <t>paid in cash, vouchers</t>
-        </is>
-      </c>
-      <c r="R161" t="inlineStr"/>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>voluntary basis, volunteering</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr"/>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BCIO:010132</t>
+          <t>BCIO:010128</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>non-monetary payment</t>
-        </is>
-      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>supervision of person source</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
@@ -6520,21 +6520,21 @@
       <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr">
         <is>
-          <t>A payment of person source that is non-monetary compensation given to the source for delivering the intervention.</t>
-        </is>
-      </c>
-      <c r="O162" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A process in which a person source is formally provided, by an individual with appropriate expertise, with corrective and skill-enhancing feedback, regarding the person source’s performance in delivering the intervention.</t>
         </is>
       </c>
       <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>course credit</t>
-        </is>
-      </c>
-      <c r="R162" t="inlineStr"/>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>supervised</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr"/>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Source/BCIO-source-hierarchy.xlsx
+++ b/Source/BCIO-source-hierarchy.xlsx
@@ -445,32 +445,32 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>synonyms</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>subontology</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>crossreference</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>informaldefinition</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>synonyms</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>comment</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>examples</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>crossreference</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>subontology</t>
         </is>
       </c>
     </row>
@@ -533,13 +533,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BFO:0000002</t>
+          <t>BFO:0000003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>continuant</t>
+          <t>occurrent</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -554,21 +554,21 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
+          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BFO:0000004</t>
+          <t>BFO:0000015</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>independent continuant</t>
+          <t>process</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -582,14 +582,14 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
+          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BFO:0000040</t>
+          <t>BCIO:010128</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -597,7 +597,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>material entity</t>
+          <t>supervision of person source</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -610,25 +610,37 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+          <t>A process in which a person source is formally provided, by an individual with appropriate expertise, with corrective and skill-enhancing feedback, regarding the person source’s performance in delivering the intervention.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>supervised</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OBI:0000245</t>
+          <t>BCIO:010130</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>organization</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>payment of person source</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -638,22 +650,22 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>An entity that can bear roles, has members, and has a set of organization rules. Members of organizations are either organizations themselves or individual people. Members can bear specific organization member roles that are determined in the organization rules. The organization rules also determine how decisions are made on behalf of the organization by the organization members.</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
+          <t>A process in which a person source is paid or compensated for delivering the intervention.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OGMS:0000087</t>
+          <t>BCIO:010131</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -662,7 +674,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>extended organism</t>
+          <t>monetary payment</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -674,26 +686,38 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>An object aggregate consisting of an organism and all material entities located within the organism, overlapping the organism, or occupying sites formed in part by the organism.</t>
+          <t>A payment of person source that is money, vouchers or valued objects given to the source for delivering the intervention.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>paid in cash, vouchers</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MF:0000016</t>
+          <t>BCIO:010132</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>non-monetary payment</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -702,35 +726,39 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>An extended organism that is a member of the species Homo sapiens.</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A payment of person source that is non-monetary compensation given to the source for delivering the intervention.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>course credit</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:010002</t>
+          <t>BCIO:010129</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>volunteering of person source</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>person source</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -738,35 +766,39 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>A person who is the bearer of a behaviour change intervention source role.</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A process in which a person source delivers the intervention on a voluntary basis without formal compensation.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>voluntary basis, volunteering</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:010095</t>
+          <t>BFO:0000002</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>continuant</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>family member</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -774,142 +806,98 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>A person who is a member of a group of persons united by blood, or by marriage or other legal arrangement, or by self-identity as belonging to the same family.</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:010097</t>
+          <t>BFO:0000020</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>characteristic</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>spouse or partner</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>A family member that is an individual who is married or in a committed relationship with another individual.</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>boyfriend, girlfriend, partner, fiance, wife, husband</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A continuant that inheres in or is borne by other entities. Every instance of A requires some specific instance of B which must always be the same.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:010098</t>
+          <t>MF:0000030</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>representation</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>sibling relationship</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>A family member that is a family relationship between two persons with at least one shared parent.</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>brother, sister, step-brother, step-sister</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A dependent continuant which is about a portion of reality.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:010096</t>
+          <t>MF:0000031</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>cognitive representation</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>parent or guardian</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>A family member that is a mother, father or legal carer of a child.</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>mother, father, step-mother, step-father, guardian</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A representation which specifically depends on an anatomical structure in the cognitive system of an organism.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:010099</t>
+          <t>ADDICTO:0000381</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -917,39 +905,27 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>child relationship</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>A family member that is an offspring relationship from a person to their parent.</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>daughter, son, step-daughter, step-son</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A cognitive representation of themselves by a person or a group about themselves.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:050842</t>
+          <t>ADDICTO:0000399</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -960,7 +936,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>role model for a person</t>
+          <t>self-identity</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -970,130 +946,141 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>A &lt;person&gt; that influences a recipient by being perceived to be similar or admired.</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>This class lies at the intersection between a person and their environment and is defined from the perspective of the person.</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An identity that a person has about themselves.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:010139</t>
+          <t>BCIO:015098</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>organisation source</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>gender identity</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>An organisation that is the bearer of a behaviour change intervention source role, such as voluntary, public or commercial organisations delivering a behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
+          <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BFO:0000031</t>
+          <t>BCIO:010111</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>generically dependent continuant</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>female gender</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
+          <t>A gender identity as being female.</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>female, woman</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IAO:0000030</t>
+          <t>BCIO:010112</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>information content entity</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>male gender</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>A generically dependent continuant that is about some thing.</t>
+          <t>A gender identity as being male.</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>male, man</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IAO:0000027</t>
+          <t>BFO:0000017</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>realizable entity</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1103,50 +1090,37 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
+          <t>A specifically dependent continuant  that inheres in continuant  entities and are not exhibited in full at every time in which it inheres in an entity or group of entities. The exhibition or actualization of a realizable entity is a particular manifestation, functioning or process that occurs under certain circumstances.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:010106</t>
+          <t>BFO:0000016</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>number of people delivering intervention to each participant</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>A count data item that is the number of providers that an individual participant in the intervention encounters.</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:010126</t>
+          <t>BCIO:010120</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1156,7 +1130,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>amount of experience</t>
+          <t>expertise of person source</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -1167,26 +1141,22 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>A knowledge or skill that is the duration of experience in related domain held by person source.</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>full-day, 6 years</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A disposition that is an expert skill or knowledge held by the source delivering the behaviour change intervention.</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:010107</t>
+          <t>BCIO:010121</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1194,12 +1164,12 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>total number of people able to deliver intervention</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>knowledge or skill</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1207,118 +1177,154 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>A count data item that is the total number of providers that are available and able to deliver the intervention.</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An expertise of person source that is knowledge or skills held in order to deliver the behaviour change intervention.</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>trained (if unclear whether pre-existing or acquired)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BFO:0000020</t>
+          <t>BCIO:010125</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>specifically dependent continuant</t>
-        </is>
-      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>acquired knowledge or skill</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>b is a relational specifically dependent continuant = Def. b is a specifically dependent continuant and there are n &amp;gt; 1 independent continuants c1, … cn which are not spatial regions are such that for all 1  i &amp;lt; j  n, ci  and cj share no common parts, are such that for each 1  i  n, b s-depends_on ci at every time t during the course of b’s existence (axiom label in BFO2 Reference: [131-004])</t>
-        </is>
-      </c>
+          <t>A knowledge or skill that is additional knowledge or skills supplied to the source to allow them to deliver the behaviour change intervention, including educational level and qualifications.</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MF:0000030</t>
+          <t>BCIO:010122</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>representation</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>pre-existing knowledge or skill</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>A dependent continuant which is about a portion of reality.</t>
+          <t>A knowledge or skill that is already possessed by the source which allows them to deliver the behaviour change intervention, including educational level and qualifications.</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree, certification, accredited, qualified</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MF:0000031</t>
+          <t>BCIO:010127</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>cognitive representation</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>affiliation to a formal group or organisation</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>A representation which specifically depends on an anatomical structure in the cognitive system of an organism.</t>
+          <t>A pre-existing knowledge or skill that is recognised through affiliation to a formal group or organisation.</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>member of British Psychological Society</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ADDICTO:0000381</t>
+          <t>BFO:0000023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
@@ -1327,14 +1333,14 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>A cognitive representation of themselves by a person or a group about themselves.</t>
+          <t>A realizable entity  the manifestation of which brings about some result or end that is not essential to a continuant  in virtue of the kind of thing that it is but that can be served or participated in by that kind of continuant  in some kinds of natural, social or institutional contexts.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ADDICTO:0000399</t>
+          <t>BCIO:010084</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1342,12 +1348,12 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>self-identity</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -1355,14 +1361,22 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>An identity that a person has about themselves.</t>
-        </is>
-      </c>
+          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:015098</t>
+          <t>BCIO:010085</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1371,34 +1385,34 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>gender identity</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>informal education student or trainee</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr"/>
+          <t>A student or trainee that is currently learning in a non-institutional setting.</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Population</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:010111</t>
+          <t>BCIO:010088</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1407,38 +1421,38 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>higher education student or trainee</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>female gender</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>A gender identity as being female.</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr"/>
+          <t>A student or trainee that is currently learning on an advanced educational programme in a university, college or professional school.</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
-          <t>female, woman</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:010112</t>
+          <t>BCIO:010091</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1448,93 +1462,117 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>male gender</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>masters student or trainee</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>A gender identity as being male.</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr"/>
+          <t>A higher education student or trainee that is currently studying for a Masters degree.</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
-          <t>male, man</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>MSc student, Masters student</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BFO:0000017</t>
+          <t>BCIO:010092</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>realizable entity</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>doctoral student or trainee</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>A specifically dependent continuant  that inheres in continuant  entities and are not exhibited in full at every time in which it inheres in an entity or group of entities. The exhibition or actualization of a realizable entity is a particular manifestation, functioning or process that occurs under certain circumstances.</t>
+          <t>A higher education student or trainee that is currently studying for a doctoral degree.</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>PhD student</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BFO:0000023</t>
+          <t>BCIO:010090</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>graduate student or trainee</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>A realizable entity  the manifestation of which brings about some result or end that is not essential to a continuant  in virtue of the kind of thing that it is but that can be served or participated in by that kind of continuant  in some kinds of natural, social or institutional contexts.</t>
+          <t>A higher education student or trainee that has completed an undergraduate degree.</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>graduate student</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:010003</t>
+          <t>BCIO:010089</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1542,35 +1580,39 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>personal role of source</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>undergraduate student or trainee</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>A role that inheres in a person source.</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A higher education student or trainee that is currently studying for an undergraduate degree.</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>undergraduate student</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:010004</t>
+          <t>BCIO:010087</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1581,7 +1623,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>occupational role of source</t>
+          <t>vocational training student or trainee</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -1591,26 +1633,22 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>A personal role of source that is realised by doing a specified type of work or working in a specified way.</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>Interventionist, facilitator, study staff</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A student or trainee that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:010067</t>
+          <t>BCIO:010086</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1619,38 +1657,34 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>clerical support worker</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>school student or trainee</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>An occupational role that records, organizes, stores, computes and retrieves information, and performs a number of clerical duties in connection with money-handling operations, travel arrangements, requests for information, and appointments.</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>General and Keyboard Clerk, customers Services Clerk, Numerical and Material Recording Clerk</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A student or trainee that is currently learning at a primary or secondary education level in an institutional, organised setting.</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:010080</t>
+          <t>BCIO:010003</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1658,35 +1692,35 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>personal role of source</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>assembler</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>An occupational role that assembles products from component parts according to strict specifications and procedures.</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr"/>
+          <t>A role that inheres in a person source.</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:010079</t>
+          <t>BCIO:010094</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1695,38 +1729,34 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>plant and machine operator</t>
-        </is>
-      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>relatedness between person source and the target population</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>An occupational role that operates and monitors industrial and agricultural machinery and equipment on the spot or by remote control, or drives and operates trains, motor vehicles and mobile machinery and equipment.</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>Stationary Plant and Machine Operator, Driver, Mobile Plant Operator</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A personal role of source that is realised in some relationship to the characteristics of the intervention participants.</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:010081</t>
+          <t>BCIO:010100</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1738,7 +1768,7 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>elementary occupation</t>
+          <t>carer</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -1747,26 +1777,26 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>An occupational role that involves the performance of simple and routine tasks which may require the use of hand-held tools and considerable physical effort.</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr"/>
+          <t>A relatedness between person source and the target population that is an individual who cares, unpaid, for a friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Cleaner, Labourer, Food Preparation Assistant, Street and Related Services Worker, Street Vendor (excluding Food), Refuse Worker</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>carer</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:010083</t>
+          <t>BCIO:010101</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1778,7 +1808,7 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>researcher</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -1787,26 +1817,22 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>An occupational role that is a researcher but unclear what discipline.</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>researcher, research assistant, investigator</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A relatedness between person source and the target population that is a person whom the participant knows, likes and trusts, typically exclusive of sexual or family relations.</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:010078</t>
+          <t>BCIO:010105</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1818,7 +1844,7 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>craft and related trades worker</t>
+          <t>embedded in participants’ community</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -1827,26 +1853,22 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>An occupational role that applies specific technical and practical knowledge and skills to construct and maintain buildings, machinery, equipment or tools, carries out printing work, and produces or processes foodstuffs, textiles and wooden, metal and other articles, including handicraft goods.</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>Building Trade Worker, Metal Workers, Machinery Worker, Handicraft Worker, Printing Worker, Electrical Equipment Installers and Repairer, Electronics and Telecommunications Installer and Repairer, Food Processing Worker, Woodworker, Tobacco Product Maker</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A relatedness between person source and the target population that is a source who is known and working to deliver intervention in own community.</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:010077</t>
+          <t>BCIO:010103</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1858,7 +1880,7 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>skilled agricultural, forestry and fishery worker</t>
+          <t>employer</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
@@ -1867,26 +1889,22 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>An occupational role that grows and harvests plants or animals to provide food, shelter and income for themselves and their households.</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>Market gardener, Crop grower, Animal Producer, Mixed Crop and Animal Producer, Forestry worker, Fishery worker, Hunter. Subsistence Crop Farmer, Subsistence Livestock Farmer</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A relatedness between person source and the target population that is a person which hires the services of the participant.</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:010082</t>
+          <t>BCIO:010102</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1898,7 +1916,7 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>armed forces occupation</t>
+          <t>colleague</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -1907,26 +1925,22 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>An occupational role that includes all jobs held by members of the armed forces.</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>Admiral, Air commodore, Air marshal, Airman, Brigadier (army), Bombardier, Captain (air force), Captain (army), Captain (navy), Colonel (army), Corporal,  Field marshal, Flight lieutenant (air force), Flying officer (military), General (army), Gunner, Group captain, (air force), Lieutenant (army), Major (army), Midshipman, Naval officer (military) , Navy commander, Officer cadet (armed forces), Paratrooper, Rifleman, Sergeant (army), Second lieutenant (army), Seaman, Squadron leader, Sublieutenant (navy), Wing commander</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A relatedness between person source and the target population that is a person with whom the participant works in a profession or business.</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:010068</t>
+          <t>BCIO:010104</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1938,7 +1952,7 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>services and sales worker</t>
+          <t>peer</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -1947,22 +1961,22 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>An occupational role that provides personal or protective services related to travel, house-keeping, catering, personal care, protection against fire and unlawful acts, or sells goods in retail or markets.</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr"/>
+          <t>A relatedness between person source and the target population that is descried as matched to intervention recipients on the basis of ‘peerness’ – age, social status, gender, shared experience, shared health status etc.</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:010071</t>
+          <t>BCIO:010004</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1971,38 +1985,38 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>occupational role of source</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>personal care worker</t>
-        </is>
-      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>A services and sales worker that provides care, supervision and assistance for children, patients and elderly, convalescent or disabled persons in institutional and residential settings.</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr"/>
+          <t>A personal role of source that is realised by doing a specified type of work or working in a specified way.</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Personal carer</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Interventionist, facilitator, study staff</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:010074</t>
+          <t>BCIO:010080</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2012,37 +2026,33 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>assembler</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>health care assistant</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>A personal care worker that provides direct personal care and assistance with activities of daily living to patients and residents in a variety of health care settings, working  in implementation of established care plans and practices, and under the direct supervision of medical, nursing or other health professionals or associate professionals.</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>Nursing aide (clinic or hospital), Patient care assistant, Psychiatric aid</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>An occupational role that assembles products from component parts according to strict specifications and procedures.</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:010073</t>
+          <t>BCIO:010079</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2052,37 +2062,37 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>plant and machine operator</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teachers’ aide</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>A personal care worker that performs non-teaching duties to assist teaching staff, and provides care and supervision for children in schools and pre-schools.</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr"/>
+          <t>An occupational role that operates and monitors industrial and agricultural machinery and equipment on the spot or by remote control, or drives and operates trains, motor vehicles and mobile machinery and equipment.</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Pre-school assistant, Teacher’s assistant</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Stationary Plant and Machine Operator, Driver, Mobile Plant Operator</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:010075</t>
+          <t>BCIO:010068</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2092,37 +2102,33 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>services and sales worker</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>home-based personal care worker</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>A personal care worker that provide routine personal care and assistance with activities of daily living to persons who are in need of such care due to effects of ageing, illness, injury, or other physical or mental conditions, in private homes and other independent residential settings.</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>Home birth assistant, Home care aide, Nursing aide (home), Personal care provider</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>An occupational role that provides personal or protective services related to travel, house-keeping, catering, personal care, protection against fire and unlawful acts, or sells goods in retail or markets.</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:010072</t>
+          <t>BCIO:010076</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2133,29 +2139,29 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>child care worker</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>protective services worker</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>A personal care worker that provides care and supervision for children in non-domestic settings.</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr"/>
+          <t>A services and sales worker that protects individuals and property against fire and other hazards, maintain law and order and enforce laws and regulations.</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Babysitter, Child care worker, Creche ayah, Family day care worker, Nanny, Out of school hours care worker</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Firefighter, Police officer, Prison guard, Security guard, Offender manager</t>
         </is>
       </c>
     </row>
@@ -2186,23 +2192,23 @@
           <t>A services and sales worker that provides personal services related to travel, housekeeping, catering and hospitality, hairdressing and beauty treatment, animal care grooming and training, companionship and other services of a personal nature.</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
           <t>Travel Attendant, Conductor, Guide, Cook, Waiter, Bartender, Hairdresser, Beautician, Housekeeping Supervisor, Astrologer, Fortune-teller, Valet, Undertaker, Embalmer, Pet Groomer, Animal Care Worker</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:010076</t>
+          <t>BCIO:010070</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2215,7 +2221,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>protective services worker</t>
+          <t>sales worker</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -2223,26 +2229,26 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>A services and sales worker that protects individuals and property against fire and other hazards, maintain law and order and enforce laws and regulations.</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr"/>
+          <t>A services and sales worker that demonstrates goods in wholesale or retail shops, at stalls and markets, door to door, via telephone or customer contact centres. They may record and accept payment for goods and services purchased, and may operate small retail outlets.</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Firefighter, Police officer, Prison guard, Security guard, Offender manager</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Street Salesperson, Market Salesperson, Shop Salesperson, Cashier, Ticket Clerk, Model, Sales Demonstrator, Door-to-door Salesperson, Contact Centre Salesperson, Service Station Attendant, Food Service Counter Attendant</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:010070</t>
+          <t>BCIO:010071</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2255,7 +2261,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>sales worker</t>
+          <t>personal care worker</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -2263,26 +2269,26 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>A services and sales worker that demonstrates goods in wholesale or retail shops, at stalls and markets, door to door, via telephone or customer contact centres. They may record and accept payment for goods and services purchased, and may operate small retail outlets.</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr"/>
+          <t>A services and sales worker that provides care, supervision and assistance for children, patients and elderly, convalescent or disabled persons in institutional and residential settings.</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Street Salesperson, Market Salesperson, Shop Salesperson, Cashier, Ticket Clerk, Model, Sales Demonstrator, Door-to-door Salesperson, Contact Centre Salesperson, Service Station Attendant, Food Service Counter Attendant</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Personal carer</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:010005</t>
+          <t>BCIO:010074</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2292,37 +2298,37 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>manager</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>health care assistant</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>An occupational role of source that manages, plans and coordinates the overall activities of enterprises, governments and other organisations.</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr"/>
+          <t>A personal care worker that provides direct personal care and assistance with activities of daily living to patients and residents in a variety of health care settings, working  in implementation of established care plans and practices, and under the direct supervision of medical, nursing or other health professionals or associate professionals.</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Chief Executive Officers; Administrative Managers;  Commercial Managers</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Nursing aide (clinic or hospital), Patient care assistant, Psychiatric aid</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:010006</t>
+          <t>BCIO:010072</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2332,33 +2338,37 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>professional</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>child care worker</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>An occupational role that works in knowledge building activities, applies scientific or artistic concepts and theories or teaches about the foregoing in a systematic manner.</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A personal care worker that provides care and supervision for children in non-domestic settings.</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Babysitter, Child care worker, Creche ayah, Family day care worker, Nanny, Out of school hours care worker</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:010007</t>
+          <t>BCIO:010075</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2369,36 +2379,36 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>science and engineering professional</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>home-based personal care worker</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>A professional that conducts research, improves or develops concepts, theories and operational methods or applies scientific knowledge.</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr"/>
+          <t>A personal care worker that provide routine personal care and assistance with activities of daily living to persons who are in need of such care due to effects of ageing, illness, injury, or other physical or mental conditions, in private homes and other independent residential settings.</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Science Professional, Mathematician, Actuary, Statistician, Life Science Professional, Engineering Professional, Electrotechnology Engineer, Architect, Planner, Surveyor, Designer</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Home birth assistant, Home care aide, Nursing aide (home), Personal care provider</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:010008</t>
+          <t>BCIO:010073</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2409,36 +2419,36 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>health professional</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teachers’ aide</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>A professional that improves or develops concepts, theories and operational method, and applied scientific knowledge relating to medicine, nursing, dentistry, veterinary medicine, pharmacy, and promotion of health.</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr"/>
+          <t>A personal care worker that performs non-teaching duties to assist teaching staff, and provides care and supervision for children in schools and pre-schools.</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Health professional; Arts therapist, Chiropractor, Dance and movement therapist, Occupational therapist, Osteopath, Podiatrist, Recreational therapist, Health staff, Clinic staff</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Pre-school assistant, Teacher’s assistant</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:010017</t>
+          <t>BCIO:010077</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2448,37 +2458,37 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>skilled agricultural, forestry and fishery worker</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>veterinarian</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>A health professional that diagnoses, prevents and treats diseases, injuries and dysfunctions of animals.</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr"/>
+          <t>An occupational role that grows and harvests plants or animals to provide food, shelter and income for themselves and their households.</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Animal pathologist, Veterinarian, Veterinary epidemiologist, Veterinary intern, Veterinary surgeon</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Market gardener, Crop grower, Animal Producer, Mixed Crop and Animal Producer, Forestry worker, Fishery worker, Hunter. Subsistence Crop Farmer, Subsistence Livestock Farmer</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:010012</t>
+          <t>BCIO:010006</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2488,33 +2498,33 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>professional</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>nursing and midwifery professional</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>A health professional that provides treatment and care services for people who are physically or mentally ill, disabled or infirm, and those with potential risks to health including before, during and after childbirth. They assume responsibility for the planning, management and evaluation of the care of patients, including the supervision of other health care workers, working autonomously or in teams with medical doctors and others in the practical application of preventive and curative measures.</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr"/>
+          <t>An occupational role that works in knowledge building activities, applies scientific or artistic concepts and theories or teaches about the foregoing in a systematic manner.</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:010021</t>
+          <t>BCIO:010044</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2525,36 +2535,32 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>physiotherapist</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>technician and associate professional</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>A health professional  that assesses, plans and implements rehabilitative programmes that improve or restore human motor functions, maximize movement ability, relieve pain syndromes, and treat or prevent physical challenges associated with injuries, diseases and other impairments.</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>Geriatric physical therapist, Manipulative therapist, Orthopaedic physical therapist, Paediatric physical therapist, Physical therapist, Physiotherapist</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A professional that performs technical and related tasks connected with research and the application of scientific or artistic concepts and operational methods, and government or business regulations.</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:010013</t>
+          <t>BCIO:010058</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2568,33 +2574,33 @@
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>nursing professional</t>
+          <t>legal and related associate professional</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>A health professional that provides treatment, support and care services for people who are in need of nursing care due to the effects of ageing, injury, illness or other physical or mental impairment, or potential risks to health.</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr"/>
+          <t>A technician and associate professional that performs support functions in courts of law or in law offices, provide services related to such legal matters as insurance contracts, the transferring of property and the granting of loans and other financial transactions, or conduct investigations for clients.</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Clinical nurse consultant, District nurse, Nurse anaesthetist, Nurse educator, Nurse practitioner, Operating theatre nurse, Professional nurse, Public health nurse, Specialist nurse, Nursing Counsellor, Study Nurse</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Bailiff, Judge’s clerk, Conveyancing clerk, Court clerk, Justice of the peace, Law clerk, Legal assistant, Paralegal, Private detective, Title searcher</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:010023</t>
+          <t>BCIO:010061</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2608,33 +2614,33 @@
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>audiologist and speech therapist</t>
+          <t>sport and fitness worker</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>A health professional  that evaluates, manages and treats physical disorders affecting human hearing, speech, communication and swallowing.</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr"/>
+          <t>A technician and associate professional that prepares for and competes in sporting events for financial gain, trains amateur and professional sportsmen and women to enhance performance, promotes participation and standards in sport, organises and officiates sporting events, or provides instruction, training and supervision for various forms of exercise and other recreational activities.</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Audiologist, Language therapist, Speech pathologist, Speech therapist</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>physical activity professional, exercise physiologist, exercise therapist, exercise specialist</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:010020</t>
+          <t>BCIO:010063</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2646,35 +2652,35 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>environmental and occupational health and hygiene professional</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>sports coach, instructor and official</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>A health professional that assesses, plans and implements programmes to recognize, monitor and control environmental factors that can potentially affect human health, to ensure safe and healthy working conditions and to prevent disease or injury caused by chemical, physical, radiological and biological agents or ergonomic factors.</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr"/>
+          <t>A sport and fitness worker that works with amateur and professional sportspersons to enhance performance and encourage greater participation in sport, and organizes and officiates in sporting events according to established rules.</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
         <is>
-          <t>Environmental health officer, Occupational health and safety adviser, Occupational hygienist, Radiation protection expert</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Referee, Ski instructor, Sports coach, Sports official, Swimming instructor</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:010009</t>
+          <t>BCIO:010062</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2686,35 +2692,35 @@
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>medical doctor</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>athlete and sports player</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>A health professional that studies, diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans through the application of modern medicine. They plan, supervise and evaluate the implementation of care and treatment plans by other health care providers, and conduct medical education and research activities.</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr"/>
+          <t>A sport and fitness worker that participates in competitive sporting events. They train and compete, either individually or as part of a team, in their chosen sport.</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
         <is>
-          <t>District medical doctor-therapist, family medical practitioner, general practitioner, medical doctor (general), medical officer (general), physician (general), primary health care physician, resident medical officer specializing in general practice</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Athlete, Bicycle racer, Boxer, Chess player , Footballer, Golfer, Hockey player, Jockey, Poker player, Racing driver, Skier, Tennis player, Wrestler</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:010010</t>
+          <t>BCIO:010064</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2729,32 +2735,32 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>generalist medical practitioner</t>
+          <t>fitness and recreation instructor and programme leader</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments and maintains general health in humans through application of modern medicine. They do not limit their practice to certain disease categories or methods of treatment, and may assume responsibility for the provision of continuing and comprehensive medical care to individuals, families and communities.</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr"/>
+          <t>A sport and fitness worker that leads, guides and instructs groups and individuals in recreational, fitness or outdoor adventure activities.</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Primary care physician, family doctor, GP</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Aerobics instructor, Fitness instructor, Horse riding instructor, Outdoor adventure guide, Personal trainer, Sailing instructor, Underwater diving instructor</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:010011</t>
+          <t>BCIO:010059</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2766,35 +2772,35 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>specialist medical practitioner</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>social work associate professional</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans, using specialized testing, diagnostic, medical, surgical, physical and psychiatric techniques through application of the principles and procedures of modern medicine. They specialize in certain disease categories, types of patient or methods of treatment and may conduct medical education and research in their chosen areas of specialization.</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr"/>
+          <t>A technician and associate professional that implements social assistance programmes and community services and assist clients to deal with personal and social problems.</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Anaesthetist, Cardiologist, Emergency medicine specialist, Gynaecologist, Obstetrician, Ophthalmologist, Paediatrician, Pathologist, Preventive medicine specialist, Psychiatrist, Radiation oncologist, Radiologist, Resident medical officer in specialist training, Specialist medical practitioner (public health), Specialist physician (internal medicine), Specialist physician (nuclear medicine), Surgeon</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Community development worker, Community services worker, Crisis intervention worker, Disability services worker, Family services worker, Life skills instructor, Mental health support worker, Welfare support worker, Women’s shelter supervisor, Youth services worker</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:010019</t>
+          <t>BCIO:010066</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2808,33 +2814,33 @@
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>pharmacist</t>
+          <t>information and communications technician</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>A health professional that stores, preserves, compounds and dispenses medicinal products and counsel on the proper use and adverse effects of drugs and medicines following prescriptions issued by medical doctors and other health professionals.</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr"/>
+          <t>A technician and associate professional that provides support for the day to day running of computer systems, communication systems and networks, broadcast images and sound, telecommunication signals on land, sea or in aircraft.</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr">
         <is>
-          <t>Dispensing chemist, Hospital pharmacist, Industrial pharmacist, Retail pharmacist</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Information and Communications Technology Operations and User Support Technician, Telecommunications and Broadcasting Technician</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:010016</t>
+          <t>BCIO:010045</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2848,33 +2854,33 @@
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>paramedical practitioner</t>
+          <t>health associate professional</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>A health professional that provides advisory, diagnostic, curative and preventive medical services more limited in scope and complexity than those carried out by medical doctors. They work autonomously or with limited supervision of medical doctors, and apply advanced clinical procedures for treating and preventing diseases, injuries and other physical or mental impairments common to specific communities.</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr"/>
+          <t>A technician and associate professional that performs technical and practical tasks to support diagnosis and treatment of illness, disease, injuries and impairments in humans or animals, and supports the implementation of health care usually established by medical, veterinary, nursing and other health professionals.</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Advanced care paramedic, Clinical officer (paramedical), Feldscher, Primary care paramedic, Surgical technician</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Veterinary Technician</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:010024</t>
+          <t>BCIO:010047</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2886,35 +2892,35 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>optometrist and ophthalmic optician</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>nursing and midwifery associate professional</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>A health professional  that provides diagnosis, management and treatment services for disorders of the eyes and visual system.</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr"/>
+          <t>A health associate professional that provides basic nursing and personal care for people who are physically or mentally ill, disabled or infirm, and for others in need of care due to potential risks to health including before, during and after childbirth. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing, midwifery and other health professionals.</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Ophthalmic optician , Optometrist, Orthoptist</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Practice assistant, Quit Smoking Counsellor, Health educator, Dispensing Optician, Information Technician</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:010015</t>
+          <t>BCIO:010048</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2926,35 +2932,35 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>traditional and complementary medicine professional</t>
-        </is>
-      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>nursing associate professional</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>A health professional that examines patients, prevents and treats illness, disease, injury and other physical and mental impairments and maintains general health in humans. They do this by applying knowledge, skills and practices acquired through extensive study of the theories, beliefs and experiences originating in specific cultures.</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr"/>
+          <t>A nursing and midwifery associate professional that provides basic nursing and personal care for people in need of such care due to effects of ageing, illness, injury, or other physical or mental impairment. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing and other health professionals.</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr">
         <is>
-          <t>Acupuncturist, Ayurvedic practitioner,  Chinese herbal medicine practitioner, Homeopath, Naturopath, Unani practitioner</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Assistant nurse, Associate professional nurse, Enrolled nurse, Practical nurse</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:010022</t>
+          <t>BCIO:010049</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2966,35 +2972,35 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>dietician and nutritionist</t>
-        </is>
-      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>midwifery associate professional</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>A health professional  that assesses, plans and implements programmes to enhance the impact of food and nutrition on human health.</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr"/>
+          <t>A nursing and midwifery associate professional that provides basic health care and advice before, during and after pregnancy and childbirth. They implement care, treatment and referral plans usually established by medical, midwifery and other health professionals.</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr">
         <is>
-          <t>Clinical dietician, Food service dietician, Nutritionist, Public health nutritionist, Sports nutritionist</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Assistant midwife, Traditional midwife</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCIO:010018</t>
+          <t>BCIO:010056</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3006,35 +3012,35 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>dentist</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>ambulance worker</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>A health professional that diagnoses treats and prevents diseases, injuries and abnormalities of the teeth, mouth, jaws and associated tissues by applying the principles and procedures of modern dentistry.</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr"/>
+          <t>A health associate professional that provides emergency health care to patients who are injured, sick, infirm or otherwise physically or mentally impaired prior to and during transport to medical facilities.</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
-          <t>Dental practitioner, Dental surgeon, Dentist, Endodontist, Oral and maxillofacial surgeon, Oral pathologist, Orthodontist, Paedodontist, Periodontist, Prosthodontist, Stomatologist</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Ambulance officer, Ambulance paramedic, Emergency medical technician, Emergency paramedic</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIO:010014</t>
+          <t>BCIO:010051</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3046,35 +3052,35 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>midwifery professional</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>dental assistant and therapist</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>A health professional that plans, manages, provides and evaluates midwifery care services before, during and after pregnancy and childbirth. They provide delivery care for reducing health risks to women and newborn children, working autonomously or in teams with other health care providers.</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr"/>
+          <t>A health associate professional that provides basic dental care services for the prevention and treatment of diseases and disorders of the teeth and mouth, according to care plans and procedures established by a dentist or other oral health professional.</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
-          <t>Midwife</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Dental assistant, Dental hygienist , Dental therapist</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BCIO:010034</t>
+          <t>BCIO:010054</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3085,32 +3091,36 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>legal, social and cultural professional</t>
-        </is>
-      </c>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>medical assistant</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>A professional that conducts research, improves or develops concepts, theories and operational methods, or applies knowledge relating to the law, social or cultural studies.</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health associate professional that performs basic clinical and administrative tasks to support patient care under the direct supervision of a medical practitioner or other health professional.</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Clinical assistant, Medical assistant, Ophthalmic assistant</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BCIO:010043</t>
+          <t>BCIO:010055</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3122,35 +3132,36 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>creative and performing artist</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>environmental and occupational health inspector and associate</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that communicates ideas, impressions and facts in a wide range of media to achieve particular effects, interprets a composition such as a musical score or a script to perform or direct the performance, and hosts the presentation of such performance and other media events.</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr"/>
+          <t>A health associate professional that investigates the implementation of rules and regulations relating to environmental factors that may affect human health, safety in the 
+workplace, and safety of processes for the production of goods and services. They may implement and evaluate programmes to restore or improve safety and sanitary conditions under the supervision of a health professional.</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Visual artist, Musician, Singer, Composer, Dancer, Choreographer, Director, Producer, Actor, Announcer on radio, television and other media</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Food sanitation and safety inspector, Health inspector, Occupational health and safety inspector, Pollution inspector, Product safety inspector, Sanitarian, Sanitary inspector</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BCIO:010040</t>
+          <t>BCIO:010050</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3162,35 +3173,35 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>religious professional</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>traditional and complementary medicine associate professional</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that functions  as a perpetuator of sacred traditions, practices and beliefs. They conduct religious services, celebrate or administer the rites of a religious faith or denomination, provide spiritual and moral guidance and perform other functions associated with the practice of a religion.</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr"/>
+          <t>A health associate professional that prevents and treats human physical and mental illnesses, disorders and injuries using herbal and other therapies based on theories, beliefs and experiences originating in specific cultures. They administer treatments using traditional techniques and medicaments, either acting independently or according to therapeutic care plans established by a traditional medicine or other health professional.</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Bonze, Imam, Minister of religion, Poojari, Priest, Rabbi</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Acupuncture technician, Ayurvedic technician, Bonesetter, Herbalist , Homeopathy technician, Scraping and cupping therapist, Village healer, Witch doctor</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BCIO:010036</t>
+          <t>BCIO:010046</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3202,35 +3213,35 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>librarian, archivist and curator</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>medical and pharmaceutical technician</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that develops and maintains collections of archives, libraries, museums, art galleries and similar establishments.</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr"/>
+          <t>A health associate professional that performs technical tasks to assist in diagnosis and treatment of illness, disease, injuries and impairments.</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
-          <t>Librarian, Archivist,  Curator</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Medical imaging and therapeutic equipment technician, Medical and Pathology laboratory technician, Pharmaceutical technician, Medical and dental prosthetic technician</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BCIO:010035</t>
+          <t>BCIO:010053</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3242,35 +3253,35 @@
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>legal professional</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>physiotherapy technician and assistant</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conducts research on legal problems, advises clients on legal aspects of problems, pleads cases or conducts prosecutions in courts of law, presides over judicial proceedings in courts of law and draft laws and regulations.</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr"/>
+          <t>A health associate professional that provides physical therapeutic treatments to patients in circumstances where functional movement is threatened by injury, disease or impairment. Therapies are usually provided according to rehabilitative plans established by a physiotherapist or other health professional.</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
-          <t>Lawyer, Judge, Coroner</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Acupressure therapist, Electrotherapist, Hydrotherapist, Massage therapist, Physical rehabilitation technician, Physiotherapy technician, Shiatsu therapist</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BCIO:010037</t>
+          <t>BCIO:010052</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3282,35 +3293,35 @@
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>social professional</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>community health worker</t>
+        </is>
+      </c>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conducts research, improves or develops concepts, theories and operational methods or applies knowledge relating to psychology, sociology, philosophy, politics, economics, sociology, anthropology, history and other social sciences, or provides social services to meet the needs of individuals and families in a community.</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr"/>
+          <t>A health associate professional that provides health education, referral and follow-up, case management, basic preventive health care and home visiting services to specific communities. They provide support and assistance to individuals and families in navigating the health and social services system.</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Economist, Sociologist, Anthropologist, Philosopher, Historian, Political Scientist</t>
-        </is>
-      </c>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Community health aide, Community health promoter, Community health worker, Village health worker, outreach worker, health worker</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCIO:010038</t>
+          <t>BCIO:010060</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3322,35 +3333,35 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>psychologist</t>
-        </is>
-      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>religious associate professional</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>A social professional that studies the mental processes and behaviour of human beings as individuals or in groups, and applies this knowledge to promote personal, social, educational or occupational adjustment and development.</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr"/>
+          <t>A technician and associate professional that provides support to ministers of religion or to a religious community, undertake religious works, preach and propagate the teachings of a particular religion and endeavour to improve well-being through the power of faith and spiritual advice.</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr">
         <is>
-          <t>Clinical psychologist, Counselling psychologist, Educational psychologist, Forensic psychologist, Health psychologist, Neuropsychologist, Organizational psychologist, Psychotherapist, Sport and exercise psychologist</t>
-        </is>
-      </c>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Faith healer, Lay preacher, Monk, Nun</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIO:010039</t>
+          <t>BCIO:010057</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3362,35 +3373,35 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>social work and counselling professional</t>
-        </is>
-      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>business and administration associate professional</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>A social professional that provides advice and guidance to individuals, families, groups, communities and organizations in response to social and personal difficulties. They assist clients to develop skills and access resources and support services needed to respond to issues arising from unemployment, poverty, disability, addiction, criminal and delinquent behaviour, marital and other problems.</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr"/>
+          <t>A technician and associate professional that performs mostly technical tasks connected with the practical application of knowledge relating to financial accounting and transaction matters, mathematical calculations, human resource development, selling and buying financial instruments, specialized secretarial tasks and enforcing or applying government rules.</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr">
         <is>
-          <t>Counsellor, Addictions counsellor, Bereavement counsellor, Child and youth counsellor, District social welfare officer, Family counsellor, Marriage counsellor, Parole officer, Probation officer, Sexual assault counsellor, Social worker, Women’s welfare organizer</t>
-        </is>
-      </c>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Financial and Mathematical associate professional, Sales and purchasing agent, Broker, Business Services Agent, Administrative and Specialized Secretary, Government regulatory associate professional, Medical secretary</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BCIO:010042</t>
+          <t>BCIO:010065</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3404,33 +3415,33 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>linguist</t>
+          <t>artistic, cultural and culinary associate professional</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that translates or interprets from one language into another.</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr"/>
+          <t>A technician and associate professional that combines creative skills and technical and cultural knowledge in creative media or food.</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
-          <t>Interpretator; other linguist</t>
-        </is>
-      </c>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Photographer, Interior designers and decorator, Gallery, museum and library technician, Chef</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BCIO:010041</t>
+          <t>BCIO:010025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3441,36 +3452,36 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>author and journalist</t>
-        </is>
-      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>teaching professional</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conceives and creates literary works, and interprets and communicates news and public affairs through the media.</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr"/>
+          <t>A professional that teaches the theory and practice of one or more disciplines at different educational levels.</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr">
         <is>
-          <t>Author, Writer, Journalist, Translator, News anchor</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Education Methods Specialist, Other Language Teacher, Information Technology Teacher, Private Tutor, School Counsellor, Student Advisor</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BCIO:010044</t>
+          <t>BCIO:010027</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3481,32 +3492,36 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>technician and associate professional</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>vocational education teacher</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>A professional that performs technical and related tasks connected with research and the application of scientific or artistic concepts and operational methods, and government or business regulations.</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A teaching professional that teaches or instructs vocational or occupational subjects in adult and further education institutions and to senior students in secondary schools and colleges.</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Automotive technology instructor, Cosmetology instructor, Vocational education teacher</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BCIO:010057</t>
+          <t>BCIO:010026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3520,33 +3535,33 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>business and administration associate professional</t>
+          <t>university and higher education teacher</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs mostly technical tasks connected with the practical application of knowledge relating to financial accounting and transaction matters, mathematical calculations, human resource development, selling and buying financial instruments, specialized secretarial tasks and enforcing or applying government rules.</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr"/>
+          <t>A teaching professional that prepares and delivers lectures and conduct tutorials in one or more subjects within a prescribed course of study at a university or other higher educational institution. They conduct research, and prepare scholarly papers and books.</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
         <is>
-          <t>Financial and Mathematical associate professional, Sales and purchasing agent, Broker, Business Services Agent, Administrative and Specialized Secretary, Government regulatory associate professional, Medical secretary</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Higher education lecturer, Professor, University lecturer, University tutor</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BCIO:010065</t>
+          <t>BCIO:010033</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3560,33 +3575,33 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>artistic, cultural and culinary associate professional</t>
+          <t>arts teacher</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
-          <t>A technician and associate professional that combines creative skills and technical and cultural knowledge in creative media or food.</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr"/>
+          <t>A teaching professional  that teaches students in the practice, theory and performance of dance, drama, visual and other arts (excluding music) in private or small group tuition or within mainstream educational institutions.</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr">
         <is>
-          <t>Photographer, Interior designers and decorator, Gallery, museum and library technician, Chef</t>
-        </is>
-      </c>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Dance teacher (private tuition), Drama teacher (private tuition), Painting teacher (private tuition), Sculpture teacher (private tuition)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BCIO:010059</t>
+          <t>BCIO:010028</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3600,33 +3615,33 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>social work associate professional</t>
+          <t>secondary education teacher</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
-          <t>A technician and associate professional that implements social assistance programmes and community services and assist clients to deal with personal and social problems.</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr"/>
+          <t>A teaching professional that teaches one or more subjects at secondary education level.</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr">
         <is>
-          <t>Community development worker, Community services worker, Crisis intervention worker, Disability services worker, Family services worker, Life skills instructor, Mental health support worker, Welfare support worker, Women’s shelter supervisor, Youth services worker</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Secondary school teacher, High school teacher</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BCIO:010061</t>
+          <t>BCIO:010032</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3640,33 +3655,33 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>sport and fitness worker</t>
+          <t>music teacher</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
-          <t>A technician and associate professional that prepares for and competes in sporting events for financial gain, trains amateur and professional sportsmen and women to enhance performance, promotes participation and standards in sport, organises and officiates sporting events, or provides instruction, training and supervision for various forms of exercise and other recreational activities.</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr"/>
+          <t>A teaching professional that teaches students in the practice, theory and performance of music in private or small group tuition or within mainstream educational institutions.</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr">
         <is>
-          <t>physical activity professional, exercise physiologist, exercise therapist, exercise specialist</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Guitar teacher (private tuition), Piano teacher (private tuition), Singing teacher (private tuition), Violin teacher (private tuition)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BCIO:010064</t>
+          <t>BCIO:010031</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3678,35 +3693,35 @@
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>fitness and recreation instructor and programme leader</t>
-        </is>
-      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>special needs teacher</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that leads, guides and instructs groups and individuals in recreational, fitness or outdoor adventure activities.</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr"/>
+          <t>A teaching professional that teaches children, young persons or adults with physical or intellectual special needs.</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
         <is>
-          <t>Aerobics instructor, Fitness instructor, Horse riding instructor, Outdoor adventure guide, Personal trainer, Sailing instructor, Underwater diving instructor</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Learning disabilities special education teacher, Learning support teacher, Remedial teacher, Teacher of gifted children, Teacher of the hearing impaired, Teacher of the sight impaired</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BCIO:010063</t>
+          <t>BCIO:010029</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3718,35 +3733,31 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>sports coach, instructor and official</t>
-        </is>
-      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>primary school teacher</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that works with amateur and professional sportspersons to enhance performance and encourage greater participation in sport, and organizes and officiates in sporting events according to established rules.</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr"/>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>Referee, Ski instructor, Sports coach, Sports official, Swimming instructor</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A teaching professional that teaches teach a range of subjects at the primary education level.</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BCIO:010062</t>
+          <t>BCIO:010030</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3758,35 +3769,35 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>athlete and sports player</t>
-        </is>
-      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>early childhood educator</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that participates in competitive sporting events. They train and compete, either individually or as part of a team, in their chosen sport.</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr"/>
+          <t>A teaching professional that promotes the social, physical, and intellectual development of children below primary school age through the provision of educational and play activities.</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr">
         <is>
-          <t>Athlete, Bicycle racer, Boxer, Chess player , Footballer, Golfer, Hockey player, Jockey, Poker player, Racing driver, Skier, Tennis player, Wrestler</t>
-        </is>
-      </c>
-      <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Early childhood educator, Pre-school teacher</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BCIO:010066</t>
+          <t>BCIO:010007</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3797,36 +3808,36 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>information and communications technician</t>
-        </is>
-      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>science and engineering professional</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>A technician and associate professional that provides support for the day to day running of computer systems, communication systems and networks, broadcast images and sound, telecommunication signals on land, sea or in aircraft.</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr"/>
+          <t>A professional that conducts research, improves or develops concepts, theories and operational methods or applies scientific knowledge.</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr">
         <is>
-          <t>Information and Communications Technology Operations and User Support Technician, Telecommunications and Broadcasting Technician</t>
-        </is>
-      </c>
-      <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Science Professional, Mathematician, Actuary, Statistician, Life Science Professional, Engineering Professional, Electrotechnology Engineer, Architect, Planner, Surveyor, Designer</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BCIO:010060</t>
+          <t>BCIO:010034</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3837,36 +3848,32 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>religious associate professional</t>
-        </is>
-      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>legal, social and cultural professional</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>A technician and associate professional that provides support to ministers of religion or to a religious community, undertake religious works, preach and propagate the teachings of a particular religion and endeavour to improve well-being through the power of faith and spiritual advice.</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr"/>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>Faith healer, Lay preacher, Monk, Nun</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A professional that conducts research, improves or develops concepts, theories and operational methods, or applies knowledge relating to the law, social or cultural studies.</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BCIO:010045</t>
+          <t>BCIO:010036</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3880,33 +3887,33 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>health associate professional</t>
+          <t>librarian, archivist and curator</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs technical and practical tasks to support diagnosis and treatment of illness, disease, injuries and impairments in humans or animals, and supports the implementation of health care usually established by medical, veterinary, nursing and other health professionals.</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr"/>
+          <t>A legal, social and cultural professional that develops and maintains collections of archives, libraries, museums, art galleries and similar establishments.</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Veterinary Technician</t>
-        </is>
-      </c>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Librarian, Archivist,  Curator</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BCIO:010046</t>
+          <t>BCIO:010043</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -3918,35 +3925,35 @@
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>medical and pharmaceutical technician</t>
-        </is>
-      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>creative and performing artist</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
-          <t>A health associate professional that performs technical tasks to assist in diagnosis and treatment of illness, disease, injuries and impairments.</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr"/>
+          <t>A legal, social and cultural professional that communicates ideas, impressions and facts in a wide range of media to achieve particular effects, interprets a composition such as a musical score or a script to perform or direct the performance, and hosts the presentation of such performance and other media events.</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Medical imaging and therapeutic equipment technician, Medical and Pathology laboratory technician, Pharmaceutical technician, Medical and dental prosthetic technician</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr"/>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Visual artist, Musician, Singer, Composer, Dancer, Choreographer, Director, Producer, Actor, Announcer on radio, television and other media</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BCIO:010050</t>
+          <t>BCIO:010040</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3958,35 +3965,35 @@
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>traditional and complementary medicine associate professional</t>
-        </is>
-      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>religious professional</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
-          <t>A health associate professional that prevents and treats human physical and mental illnesses, disorders and injuries using herbal and other therapies based on theories, beliefs and experiences originating in specific cultures. They administer treatments using traditional techniques and medicaments, either acting independently or according to therapeutic care plans established by a traditional medicine or other health professional.</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr"/>
+          <t>A legal, social and cultural professional that functions  as a perpetuator of sacred traditions, practices and beliefs. They conduct religious services, celebrate or administer the rites of a religious faith or denomination, provide spiritual and moral guidance and perform other functions associated with the practice of a religion.</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Acupuncture technician, Ayurvedic technician, Bonesetter, Herbalist , Homeopathy technician, Scraping and cupping therapist, Village healer, Witch doctor</t>
-        </is>
-      </c>
-      <c r="S95" t="inlineStr"/>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Bonze, Imam, Minister of religion, Poojari, Priest, Rabbi</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BCIO:010054</t>
+          <t>BCIO:010042</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -3998,35 +4005,35 @@
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>medical assistant</t>
-        </is>
-      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>linguist</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
-          <t>A health associate professional that performs basic clinical and administrative tasks to support patient care under the direct supervision of a medical practitioner or other health professional.</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr"/>
+          <t>A legal, social and cultural professional that translates or interprets from one language into another.</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr">
         <is>
-          <t>Clinical assistant, Medical assistant, Ophthalmic assistant</t>
-        </is>
-      </c>
-      <c r="S96" t="inlineStr"/>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Interpretator; other linguist</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BCIO:010053</t>
+          <t>BCIO:010035</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -4038,35 +4045,35 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>physiotherapy technician and assistant</t>
-        </is>
-      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>legal professional</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
-          <t>A health associate professional that provides physical therapeutic treatments to patients in circumstances where functional movement is threatened by injury, disease or impairment. Therapies are usually provided according to rehabilitative plans established by a physiotherapist or other health professional.</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr"/>
+          <t>A legal, social and cultural professional that conducts research on legal problems, advises clients on legal aspects of problems, pleads cases or conducts prosecutions in courts of law, presides over judicial proceedings in courts of law and draft laws and regulations.</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Acupressure therapist, Electrotherapist, Hydrotherapist, Massage therapist, Physical rehabilitation technician, Physiotherapy technician, Shiatsu therapist</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr"/>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Lawyer, Judge, Coroner</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BCIO:010047</t>
+          <t>BCIO:010041</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4078,35 +4085,35 @@
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>nursing and midwifery associate professional</t>
-        </is>
-      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>author and journalist</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>A health associate professional that provides basic nursing and personal care for people who are physically or mentally ill, disabled or infirm, and for others in need of care due to potential risks to health including before, during and after childbirth. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing, midwifery and other health professionals.</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr"/>
+          <t>A legal, social and cultural professional that conceives and creates literary works, and interprets and communicates news and public affairs through the media.</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Practice assistant, Quit Smoking Counsellor, Health educator, Dispensing Optician, Information Technician</t>
-        </is>
-      </c>
-      <c r="S98" t="inlineStr"/>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Author, Writer, Journalist, Translator, News anchor</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BCIO:010049</t>
+          <t>BCIO:010037</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4118,35 +4125,35 @@
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>social professional</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>midwifery associate professional</t>
-        </is>
-      </c>
+      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
-          <t>A nursing and midwifery associate professional that provides basic health care and advice before, during and after pregnancy and childbirth. They implement care, treatment and referral plans usually established by medical, midwifery and other health professionals.</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr"/>
+          <t>A legal, social and cultural professional that conducts research, improves or develops concepts, theories and operational methods or applies knowledge relating to psychology, sociology, philosophy, politics, economics, sociology, anthropology, history and other social sciences, or provides social services to meet the needs of individuals and families in a community.</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Assistant midwife, Traditional midwife</t>
-        </is>
-      </c>
-      <c r="S99" t="inlineStr"/>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Economist, Sociologist, Anthropologist, Philosopher, Historian, Political Scientist</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BCIO:010048</t>
+          <t>BCIO:010039</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4159,34 +4166,34 @@
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>nursing associate professional</t>
-        </is>
-      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>social work and counselling professional</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
-          <t>A nursing and midwifery associate professional that provides basic nursing and personal care for people in need of such care due to effects of ageing, illness, injury, or other physical or mental impairment. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing and other health professionals.</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr"/>
+          <t>A social professional that provides advice and guidance to individuals, families, groups, communities and organizations in response to social and personal difficulties. They assist clients to develop skills and access resources and support services needed to respond to issues arising from unemployment, poverty, disability, addiction, criminal and delinquent behaviour, marital and other problems.</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Assistant nurse, Associate professional nurse, Enrolled nurse, Practical nurse</t>
-        </is>
-      </c>
-      <c r="S100" t="inlineStr"/>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Counsellor, Addictions counsellor, Bereavement counsellor, Child and youth counsellor, District social welfare officer, Family counsellor, Marriage counsellor, Parole officer, Probation officer, Sexual assault counsellor, Social worker, Women’s welfare organizer</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BCIO:010056</t>
+          <t>BCIO:010038</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4201,32 +4208,32 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>ambulance worker</t>
+          <t>psychologist</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
-          <t>A health associate professional that provides emergency health care to patients who are injured, sick, infirm or otherwise physically or mentally impaired prior to and during transport to medical facilities.</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr"/>
+          <t>A social professional that studies the mental processes and behaviour of human beings as individuals or in groups, and applies this knowledge to promote personal, social, educational or occupational adjustment and development.</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr">
         <is>
-          <t>Ambulance officer, Ambulance paramedic, Emergency medical technician, Emergency paramedic</t>
-        </is>
-      </c>
-      <c r="S101" t="inlineStr"/>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Clinical psychologist, Counselling psychologist, Educational psychologist, Forensic psychologist, Health psychologist, Neuropsychologist, Organizational psychologist, Psychotherapist, Sport and exercise psychologist</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BCIO:010052</t>
+          <t>BCIO:010008</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4237,36 +4244,36 @@
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>health professional</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>community health worker</t>
-        </is>
-      </c>
+      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
-          <t>A health associate professional that provides health education, referral and follow-up, case management, basic preventive health care and home visiting services to specific communities. They provide support and assistance to individuals and families in navigating the health and social services system.</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr"/>
+          <t>A professional that improves or develops concepts, theories and operational method, and applied scientific knowledge relating to medicine, nursing, dentistry, veterinary medicine, pharmacy, and promotion of health.</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr">
         <is>
-          <t>Community health aide, Community health promoter, Community health worker, Village health worker, outreach worker, health worker</t>
-        </is>
-      </c>
-      <c r="S102" t="inlineStr"/>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Health professional; Arts therapist, Chiropractor, Dance and movement therapist, Occupational therapist, Osteopath, Podiatrist, Recreational therapist, Health staff, Clinic staff</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BCIO:010055</t>
+          <t>BCIO:010020</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4278,36 +4285,35 @@
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>environmental and occupational health inspector and associate</t>
-        </is>
-      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>environmental and occupational health and hygiene professional</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
-          <t>A health associate professional that investigates the implementation of rules and regulations relating to environmental factors that may affect human health, safety in the 
-workplace, and safety of processes for the production of goods and services. They may implement and evaluate programmes to restore or improve safety and sanitary conditions under the supervision of a health professional.</t>
-        </is>
-      </c>
-      <c r="P103" t="inlineStr"/>
+          <t>A health professional that assesses, plans and implements programmes to recognize, monitor and control environmental factors that can potentially affect human health, to ensure safe and healthy working conditions and to prevent disease or injury caused by chemical, physical, radiological and biological agents or ergonomic factors.</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Food sanitation and safety inspector, Health inspector, Occupational health and safety inspector, Pollution inspector, Product safety inspector, Sanitarian, Sanitary inspector</t>
-        </is>
-      </c>
-      <c r="S103" t="inlineStr"/>
-      <c r="T103" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Environmental health officer, Occupational health and safety adviser, Occupational hygienist, Radiation protection expert</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BCIO:010051</t>
+          <t>BCIO:010019</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4319,35 +4325,35 @@
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>dental assistant and therapist</t>
-        </is>
-      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>pharmacist</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t>A health associate professional that provides basic dental care services for the prevention and treatment of diseases and disorders of the teeth and mouth, according to care plans and procedures established by a dentist or other oral health professional.</t>
-        </is>
-      </c>
-      <c r="P104" t="inlineStr"/>
+          <t>A health professional that stores, preserves, compounds and dispenses medicinal products and counsel on the proper use and adverse effects of drugs and medicines following prescriptions issued by medical doctors and other health professionals.</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Dental assistant, Dental hygienist , Dental therapist</t>
-        </is>
-      </c>
-      <c r="S104" t="inlineStr"/>
-      <c r="T104" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Dispensing chemist, Hospital pharmacist, Industrial pharmacist, Retail pharmacist</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BCIO:010058</t>
+          <t>BCIO:010024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4361,33 +4367,33 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>legal and related associate professional</t>
+          <t>optometrist and ophthalmic optician</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs support functions in courts of law or in law offices, provide services related to such legal matters as insurance contracts, the transferring of property and the granting of loans and other financial transactions, or conduct investigations for clients.</t>
-        </is>
-      </c>
-      <c r="P105" t="inlineStr"/>
+          <t>A health professional  that provides diagnosis, management and treatment services for disorders of the eyes and visual system.</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr">
         <is>
-          <t>Bailiff, Judge’s clerk, Conveyancing clerk, Court clerk, Justice of the peace, Law clerk, Legal assistant, Paralegal, Private detective, Title searcher</t>
-        </is>
-      </c>
-      <c r="S105" t="inlineStr"/>
-      <c r="T105" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Ophthalmic optician , Optometrist, Orthoptist</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BCIO:010025</t>
+          <t>BCIO:010022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4398,36 +4404,36 @@
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>teaching professional</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>dietician and nutritionist</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
-          <t>A professional that teaches the theory and practice of one or more disciplines at different educational levels.</t>
-        </is>
-      </c>
-      <c r="P106" t="inlineStr"/>
+          <t>A health professional  that assesses, plans and implements programmes to enhance the impact of food and nutrition on human health.</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr">
         <is>
-          <t>Education Methods Specialist, Other Language Teacher, Information Technology Teacher, Private Tutor, School Counsellor, Student Advisor</t>
-        </is>
-      </c>
-      <c r="S106" t="inlineStr"/>
-      <c r="T106" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Clinical dietician, Food service dietician, Nutritionist, Public health nutritionist, Sports nutritionist</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BCIO:010032</t>
+          <t>BCIO:010017</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4441,33 +4447,33 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>music teacher</t>
+          <t>veterinarian</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches students in the practice, theory and performance of music in private or small group tuition or within mainstream educational institutions.</t>
-        </is>
-      </c>
-      <c r="P107" t="inlineStr"/>
+          <t>A health professional that diagnoses, prevents and treats diseases, injuries and dysfunctions of animals.</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr">
         <is>
-          <t>Guitar teacher (private tuition), Piano teacher (private tuition), Singing teacher (private tuition), Violin teacher (private tuition)</t>
-        </is>
-      </c>
-      <c r="S107" t="inlineStr"/>
-      <c r="T107" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Animal pathologist, Veterinarian, Veterinary epidemiologist, Veterinary intern, Veterinary surgeon</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BCIO:010029</t>
+          <t>BCIO:010012</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4481,29 +4487,29 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>primary school teacher</t>
+          <t>nursing and midwifery professional</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches teach a range of subjects at the primary education level.</t>
-        </is>
-      </c>
-      <c r="P108" t="inlineStr"/>
+          <t>A health professional that provides treatment and care services for people who are physically or mentally ill, disabled or infirm, and those with potential risks to health including before, during and after childbirth. They assume responsibility for the planning, management and evaluation of the care of patients, including the supervision of other health care workers, working autonomously or in teams with medical doctors and others in the practical application of preventive and curative measures.</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr"/>
-      <c r="T108" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BCIO:010026</t>
+          <t>BCIO:010009</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4517,33 +4523,33 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>university and higher education teacher</t>
+          <t>medical doctor</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
-          <t>A teaching professional that prepares and delivers lectures and conduct tutorials in one or more subjects within a prescribed course of study at a university or other higher educational institution. They conduct research, and prepare scholarly papers and books.</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr"/>
+          <t>A health professional that studies, diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans through the application of modern medicine. They plan, supervise and evaluate the implementation of care and treatment plans by other health care providers, and conduct medical education and research activities.</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr">
         <is>
-          <t>Higher education lecturer, Professor, University lecturer, University tutor</t>
-        </is>
-      </c>
-      <c r="S109" t="inlineStr"/>
-      <c r="T109" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>District medical doctor-therapist, family medical practitioner, general practitioner, medical doctor (general), medical officer (general), physician (general), primary health care physician, resident medical officer specializing in general practice</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BCIO:010031</t>
+          <t>BCIO:010010</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4555,35 +4561,35 @@
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>special needs teacher</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>generalist medical practitioner</t>
+        </is>
+      </c>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches children, young persons or adults with physical or intellectual special needs.</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr"/>
+          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments and maintains general health in humans through application of modern medicine. They do not limit their practice to certain disease categories or methods of treatment, and may assume responsibility for the provision of continuing and comprehensive medical care to individuals, families and communities.</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr">
         <is>
-          <t>Learning disabilities special education teacher, Learning support teacher, Remedial teacher, Teacher of gifted children, Teacher of the hearing impaired, Teacher of the sight impaired</t>
-        </is>
-      </c>
-      <c r="S110" t="inlineStr"/>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Primary care physician, family doctor, GP</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BCIO:010030</t>
+          <t>BCIO:010011</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4595,35 +4601,35 @@
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>early childhood educator</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>specialist medical practitioner</t>
+        </is>
+      </c>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
-          <t>A teaching professional that promotes the social, physical, and intellectual development of children below primary school age through the provision of educational and play activities.</t>
-        </is>
-      </c>
-      <c r="P111" t="inlineStr"/>
+          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans, using specialized testing, diagnostic, medical, surgical, physical and psychiatric techniques through application of the principles and procedures of modern medicine. They specialize in certain disease categories, types of patient or methods of treatment and may conduct medical education and research in their chosen areas of specialization.</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr">
         <is>
-          <t>Early childhood educator, Pre-school teacher</t>
-        </is>
-      </c>
-      <c r="S111" t="inlineStr"/>
-      <c r="T111" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Anaesthetist, Cardiologist, Emergency medicine specialist, Gynaecologist, Obstetrician, Ophthalmologist, Paediatrician, Pathologist, Preventive medicine specialist, Psychiatrist, Radiation oncologist, Radiologist, Resident medical officer in specialist training, Specialist medical practitioner (public health), Specialist physician (internal medicine), Specialist physician (nuclear medicine), Surgeon</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BCIO:010027</t>
+          <t>BCIO:010014</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4637,33 +4643,33 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>vocational education teacher</t>
+          <t>midwifery professional</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches or instructs vocational or occupational subjects in adult and further education institutions and to senior students in secondary schools and colleges.</t>
-        </is>
-      </c>
-      <c r="P112" t="inlineStr"/>
+          <t>A health professional that plans, manages, provides and evaluates midwifery care services before, during and after pregnancy and childbirth. They provide delivery care for reducing health risks to women and newborn children, working autonomously or in teams with other health care providers.</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr">
         <is>
-          <t>Automotive technology instructor, Cosmetology instructor, Vocational education teacher</t>
-        </is>
-      </c>
-      <c r="S112" t="inlineStr"/>
-      <c r="T112" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Midwife</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BCIO:010028</t>
+          <t>BCIO:010015</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4677,33 +4683,33 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>secondary education teacher</t>
+          <t>traditional and complementary medicine professional</t>
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches one or more subjects at secondary education level.</t>
-        </is>
-      </c>
-      <c r="P113" t="inlineStr"/>
+          <t>A health professional that examines patients, prevents and treats illness, disease, injury and other physical and mental impairments and maintains general health in humans. They do this by applying knowledge, skills and practices acquired through extensive study of the theories, beliefs and experiences originating in specific cultures.</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr">
         <is>
-          <t>Secondary school teacher, High school teacher</t>
-        </is>
-      </c>
-      <c r="S113" t="inlineStr"/>
-      <c r="T113" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Acupuncturist, Ayurvedic practitioner,  Chinese herbal medicine practitioner, Homeopath, Naturopath, Unani practitioner</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BCIO:010033</t>
+          <t>BCIO:010023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -4717,33 +4723,33 @@
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>arts teacher</t>
+          <t>audiologist and speech therapist</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
-          <t>A teaching professional  that teaches students in the practice, theory and performance of dance, drama, visual and other arts (excluding music) in private or small group tuition or within mainstream educational institutions.</t>
-        </is>
-      </c>
-      <c r="P114" t="inlineStr"/>
+          <t>A health professional  that evaluates, manages and treats physical disorders affecting human hearing, speech, communication and swallowing.</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr">
         <is>
-          <t>Dance teacher (private tuition), Drama teacher (private tuition), Painting teacher (private tuition), Sculpture teacher (private tuition)</t>
-        </is>
-      </c>
-      <c r="S114" t="inlineStr"/>
-      <c r="T114" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Audiologist, Language therapist, Speech pathologist, Speech therapist</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BCIO:010094</t>
+          <t>BCIO:010021</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -4752,34 +4758,38 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>relatedness between person source and the target population</t>
-        </is>
-      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>physiotherapist</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
-          <t>A personal role of source that is realised in some relationship to the characteristics of the intervention participants.</t>
-        </is>
-      </c>
-      <c r="P115" t="inlineStr"/>
-      <c r="R115" t="inlineStr"/>
-      <c r="S115" t="inlineStr"/>
-      <c r="T115" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional  that assesses, plans and implements rehabilitative programmes that improve or restore human motor functions, maximize movement ability, relieve pain syndromes, and treat or prevent physical challenges associated with injuries, diseases and other impairments.</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>Geriatric physical therapist, Manipulative therapist, Orthopaedic physical therapist, Paediatric physical therapist, Physical therapist, Physiotherapist</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BCIO:010103</t>
+          <t>BCIO:010016</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4789,33 +4799,37 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>employer</t>
-        </is>
-      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>paramedical practitioner</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person which hires the services of the participant.</t>
-        </is>
-      </c>
-      <c r="P116" t="inlineStr"/>
-      <c r="R116" t="inlineStr"/>
-      <c r="S116" t="inlineStr"/>
-      <c r="T116" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that provides advisory, diagnostic, curative and preventive medical services more limited in scope and complexity than those carried out by medical doctors. They work autonomously or with limited supervision of medical doctors, and apply advanced clinical procedures for treating and preventing diseases, injuries and other physical or mental impairments common to specific communities.</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>Advanced care paramedic, Clinical officer (paramedical), Feldscher, Primary care paramedic, Surgical technician</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BCIO:010102</t>
+          <t>BCIO:010018</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4825,33 +4839,37 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>colleague</t>
-        </is>
-      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>dentist</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person with whom the participant works in a profession or business.</t>
-        </is>
-      </c>
-      <c r="P117" t="inlineStr"/>
-      <c r="R117" t="inlineStr"/>
-      <c r="S117" t="inlineStr"/>
-      <c r="T117" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that diagnoses treats and prevents diseases, injuries and abnormalities of the teeth, mouth, jaws and associated tissues by applying the principles and procedures of modern dentistry.</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>Dental practitioner, Dental surgeon, Dentist, Endodontist, Oral and maxillofacial surgeon, Oral pathologist, Orthodontist, Paedodontist, Periodontist, Prosthodontist, Stomatologist</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BCIO:010105</t>
+          <t>BCIO:010013</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4861,33 +4879,37 @@
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>embedded in participants’ community</t>
-        </is>
-      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>nursing professional</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a source who is known and working to deliver intervention in own community.</t>
-        </is>
-      </c>
-      <c r="P118" t="inlineStr"/>
-      <c r="R118" t="inlineStr"/>
-      <c r="S118" t="inlineStr"/>
-      <c r="T118" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A health professional that provides treatment, support and care services for people who are in need of nursing care due to the effects of ageing, injury, illness or other physical or mental impairment, or potential risks to health.</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>Clinical nurse consultant, District nurse, Nurse anaesthetist, Nurse educator, Nurse practitioner, Operating theatre nurse, Professional nurse, Public health nurse, Specialist nurse, Nursing Counsellor, Study Nurse</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BCIO:010104</t>
+          <t>BCIO:010067</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -4899,7 +4921,7 @@
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
-          <t>peer</t>
+          <t>clerical support worker</t>
         </is>
       </c>
       <c r="J119" t="inlineStr"/>
@@ -4908,22 +4930,26 @@
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is descried as matched to intervention recipients on the basis of ‘peerness’ – age, social status, gender, shared experience, shared health status etc.</t>
-        </is>
-      </c>
-      <c r="P119" t="inlineStr"/>
-      <c r="R119" t="inlineStr"/>
-      <c r="S119" t="inlineStr"/>
-      <c r="T119" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role that records, organizes, stores, computes and retrieves information, and performs a number of clerical duties in connection with money-handling operations, travel arrangements, requests for information, and appointments.</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>General and Keyboard Clerk, customers Services Clerk, Numerical and Material Recording Clerk</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BCIO:010100</t>
+          <t>BCIO:010082</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -4935,7 +4961,7 @@
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
-          <t>carer</t>
+          <t>armed forces occupation</t>
         </is>
       </c>
       <c r="J120" t="inlineStr"/>
@@ -4944,26 +4970,26 @@
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is an individual who cares, unpaid, for a friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
-        </is>
-      </c>
-      <c r="P120" t="inlineStr"/>
+          <t>An occupational role that includes all jobs held by members of the armed forces.</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr">
         <is>
-          <t>carer</t>
-        </is>
-      </c>
-      <c r="S120" t="inlineStr"/>
-      <c r="T120" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Admiral, Air commodore, Air marshal, Airman, Brigadier (army), Bombardier, Captain (air force), Captain (army), Captain (navy), Colonel (army), Corporal,  Field marshal, Flight lieutenant (air force), Flying officer (military), General (army), Gunner, Group captain, (air force), Lieutenant (army), Major (army), Midshipman, Naval officer (military) , Navy commander, Officer cadet (armed forces), Paratrooper, Rifleman, Sergeant (army), Second lieutenant (army), Seaman, Squadron leader, Sublieutenant (navy), Wing commander</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BCIO:010101</t>
+          <t>BCIO:010078</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -4975,7 +5001,7 @@
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>friend</t>
+          <t>craft and related trades worker</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -4984,22 +5010,26 @@
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person whom the participant knows, likes and trusts, typically exclusive of sexual or family relations.</t>
-        </is>
-      </c>
-      <c r="P121" t="inlineStr"/>
-      <c r="R121" t="inlineStr"/>
-      <c r="S121" t="inlineStr"/>
-      <c r="T121" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role that applies specific technical and practical knowledge and skills to construct and maintain buildings, machinery, equipment or tools, carries out printing work, and produces or processes foodstuffs, textiles and wooden, metal and other articles, including handicraft goods.</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>Building Trade Worker, Metal Workers, Machinery Worker, Handicraft Worker, Printing Worker, Electrical Equipment Installers and Repairer, Electronics and Telecommunications Installer and Repairer, Food Processing Worker, Woodworker, Tobacco Product Maker</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BCIO:010000</t>
+          <t>BCIO:010005</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -5007,35 +5037,39 @@
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>behaviour change intervention source</t>
-        </is>
-      </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr">
         <is>
-          <t>A role played by a person, population or organisation that provides a BCI.</t>
-        </is>
-      </c>
-      <c r="P122" t="inlineStr"/>
-      <c r="R122" t="inlineStr"/>
-      <c r="S122" t="inlineStr"/>
-      <c r="T122" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role of source that manages, plans and coordinates the overall activities of enterprises, governments and other organisations.</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>Chief Executive Officers; Administrative Managers;  Commercial Managers</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BCIO:010001</t>
+          <t>BCIO:010081</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -5044,34 +5078,38 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>person source role</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>elementary occupation</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr">
         <is>
-          <t>A behaviour change intervention source role that inheres in a person.</t>
-        </is>
-      </c>
-      <c r="P123" t="inlineStr"/>
-      <c r="R123" t="inlineStr"/>
-      <c r="S123" t="inlineStr"/>
-      <c r="T123" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role that involves the performance of simple and routine tasks which may require the use of hand-held tools and considerable physical effort.</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>Cleaner, Labourer, Food Preparation Assistant, Street and Related Services Worker, Street Vendor (excluding Food), Refuse Worker</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BCIO:010138</t>
+          <t>BCIO:010083</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -5080,34 +5118,38 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>organisational source role</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>researcher</t>
+        </is>
+      </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr">
         <is>
-          <t>A BCI source role that is borne by an organisation.</t>
-        </is>
-      </c>
-      <c r="P124" t="inlineStr"/>
-      <c r="R124" t="inlineStr"/>
-      <c r="S124" t="inlineStr"/>
-      <c r="T124" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An occupational role that is a researcher but unclear what discipline.</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>researcher, research assistant, investigator</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BCIO:010133</t>
+          <t>BCIO:010000</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -5115,12 +5157,12 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>source role related to intervention</t>
-        </is>
-      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>behaviour change intervention source</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
@@ -5128,22 +5170,22 @@
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr">
         <is>
-          <t>A BCI source whose occupational or voluntary role is focused on delivery of the behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="P125" t="inlineStr"/>
+          <t>A role played by a person, population or organisation that provides a BCI.</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
-      <c r="S125" t="inlineStr"/>
-      <c r="T125" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BCIO:010134</t>
+          <t>BCIO:010133</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -5154,7 +5196,7 @@
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>source involved in development of intervention</t>
+          <t>source role related to intervention</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -5164,22 +5206,22 @@
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
-          <t>A BCI source that is involved in the development of intervention content.</t>
-        </is>
-      </c>
-      <c r="P126" t="inlineStr"/>
+          <t>A BCI source whose occupational or voluntary role is focused on delivery of the behaviour change intervention.</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr"/>
-      <c r="S126" t="inlineStr"/>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BCIO:010135</t>
+          <t>BCIO:010138</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -5188,34 +5230,34 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>source involved in co-production of intervention</t>
-        </is>
-      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>organisational source role</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
-          <t>A source involved in development of intervention that has developed the intervention content in collaboration with key stakeholders such as patients or community members.</t>
-        </is>
-      </c>
-      <c r="P127" t="inlineStr"/>
+          <t>A BCI source role that is borne by an organisation.</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr"/>
       <c r="R127" t="inlineStr"/>
-      <c r="S127" t="inlineStr"/>
-      <c r="T127" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BCIO:010084</t>
+          <t>BCIO:010134</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5223,12 +5265,12 @@
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>source involved in development of intervention</t>
+        </is>
+      </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
@@ -5236,22 +5278,22 @@
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
-        </is>
-      </c>
-      <c r="P128" t="inlineStr"/>
+          <t>A BCI source that is involved in the development of intervention content.</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr"/>
-      <c r="S128" t="inlineStr"/>
-      <c r="T128" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BCIO:010087</t>
+          <t>BCIO:010135</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -5260,34 +5302,34 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>vocational training student or trainee</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>source involved in co-production of intervention</t>
+        </is>
+      </c>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
-        </is>
-      </c>
-      <c r="P129" t="inlineStr"/>
+          <t>A source involved in development of intervention that has developed the intervention content in collaboration with key stakeholders such as patients or community members.</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr"/>
-      <c r="S129" t="inlineStr"/>
-      <c r="T129" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BCIO:010088</t>
+          <t>BCIO:010001</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5298,7 +5340,7 @@
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
-          <t>higher education student or trainee</t>
+          <t>person source role</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -5308,199 +5350,196 @@
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning on an advanced educational programme in a university, college or professional school.</t>
-        </is>
-      </c>
-      <c r="P130" t="inlineStr"/>
-      <c r="R130" t="inlineStr">
-        <is>
-          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
-        </is>
-      </c>
-      <c r="S130" t="inlineStr"/>
-      <c r="T130" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A behaviour change intervention source role that inheres in a person.</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BCIO:010091</t>
+          <t>BCIO:010123</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>expertise discipline</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>masters student or trainee</t>
-        </is>
-      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr">
         <is>
-          <t>A higher education student or trainee that is currently studying for a Masters degree.</t>
-        </is>
-      </c>
-      <c r="P131" t="inlineStr"/>
+          <t>An attribute that is a field of knowledge or practice.</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr">
         <is>
-          <t>MSc student, Masters student</t>
-        </is>
-      </c>
-      <c r="S131" t="inlineStr"/>
+          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
+        </is>
+      </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>The division of expertise into different disciplines or fields is complex and depends on historical, social and structural factors.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BCIO:010092</t>
+          <t>BCIO:010124</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>discipline of pre-existing knowledge or skill</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>doctoral student or trainee</t>
-        </is>
-      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr">
         <is>
-          <t>A higher education student or trainee that is currently studying for a doctoral degree.</t>
-        </is>
-      </c>
-      <c r="P132" t="inlineStr"/>
+          <t>The expertise discipline in which the person source has acquired their pre-existing knowledge and skills.</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr">
         <is>
-          <t>PhD student</t>
-        </is>
-      </c>
-      <c r="S132" t="inlineStr"/>
-      <c r="T132" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BCIO:010089</t>
+          <t>BCIO:010093</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>discipline of current programme of study or training</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>undergraduate student or trainee</t>
-        </is>
-      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr">
         <is>
-          <t>A higher education student or trainee that is currently studying for an undergraduate degree.</t>
-        </is>
-      </c>
-      <c r="P133" t="inlineStr"/>
+          <t>An expertise discipline of the programme of study currently undertaken by the bearer of a student or trainee role.</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr">
         <is>
-          <t>undergraduate student</t>
-        </is>
-      </c>
-      <c r="S133" t="inlineStr"/>
-      <c r="T133" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>psychology, medicine, hairdressing</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BCIO:010090</t>
+          <t>BCIO:010108</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>socio demographic attribute of person source</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>graduate student or trainee</t>
-        </is>
-      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr">
         <is>
-          <t>A higher education student or trainee that has completed an undergraduate degree.</t>
-        </is>
-      </c>
-      <c r="P134" t="inlineStr"/>
-      <c r="R134" t="inlineStr">
-        <is>
-          <t>graduate student</t>
-        </is>
-      </c>
-      <c r="S134" t="inlineStr"/>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A social or demographic characteristic of a human being who is the bearer of a person source role.</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BCIO:010085</t>
+          <t>BCIO:010115</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>religious group membership of person source</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>informal education student or trainee</t>
-        </is>
-      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
@@ -5508,35 +5547,39 @@
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning in a non-institutional setting.</t>
-        </is>
-      </c>
-      <c r="P135" t="inlineStr"/>
-      <c r="R135" t="inlineStr"/>
-      <c r="S135" t="inlineStr"/>
-      <c r="T135" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A socio-demographic attribute of person source that is a religious group to which an individual identifies as belonging, where a religious group is a group of people characterised by the practice of a common religion.</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>Muslim, Christian, Hindu, Sikh, Buddhist, Judaism</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BCIO:010086</t>
+          <t>BCIO:010119</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>psychological influence on intervention delivery of person source</t>
+        </is>
+      </c>
       <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>school student or trainee</t>
-        </is>
-      </c>
+      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
@@ -5544,22 +5587,22 @@
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning at a primary or secondary education level in an institutional, organised setting.</t>
-        </is>
-      </c>
-      <c r="P136" t="inlineStr"/>
+          <t>A socio-demographic attribute of person source that is their existing psychological attributes related to or potentially affecting the target behaviour.</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr"/>
-      <c r="T136" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BFO:0000016</t>
+          <t>BCIO:010109</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5568,7 +5611,7 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>disposition</t>
+          <t>age of person source</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -5578,23 +5621,36 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>A socio-demographic attribute of person source that is a time quality inhering in a bearer by virtue of how long the bearer has existed.</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BCIO:010120</t>
+          <t>BCIO:010118</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>expertise of person source</t>
-        </is>
-      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>target behaviour of person source</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
@@ -5603,35 +5659,39 @@
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr">
         <is>
-          <t>A disposition that is an expert skill or knowledge held by the source delivering the behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="P138" t="inlineStr"/>
-      <c r="R138" t="inlineStr"/>
-      <c r="S138" t="inlineStr"/>
-      <c r="T138" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A socio-demographic attribute of person source that is their amount or experience of the intervention’s target behaviour.</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>source is highly physically active</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BCIO:010121</t>
+          <t>BCIO:010110</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>gender of person source</t>
+        </is>
+      </c>
       <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>knowledge or skill</t>
-        </is>
-      </c>
+      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
@@ -5639,26 +5699,26 @@
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr">
         <is>
-          <t>An expertise of person source that is knowledge or skills held in order to deliver the behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="P139" t="inlineStr"/>
+          <t>A socio-demographic attribute of person source that is an individual's perception of having a particular gender, which may or may not correspond with their birth sex.</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr">
         <is>
-          <t>trained (if unclear whether pre-existing or acquired)</t>
-        </is>
-      </c>
-      <c r="S139" t="inlineStr"/>
-      <c r="T139" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>gender</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BCIO:010125</t>
+          <t>BCIO:010113</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5666,126 +5726,130 @@
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>other gender</t>
+        </is>
+      </c>
       <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>acquired knowledge or skill</t>
-        </is>
-      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr">
         <is>
-          <t>A knowledge or skill that is additional knowledge or skills supplied to the source to allow them to deliver the behaviour change intervention, including educational level and qualifications.</t>
-        </is>
-      </c>
-      <c r="P140" t="inlineStr"/>
-      <c r="R140" t="inlineStr"/>
-      <c r="S140" t="inlineStr"/>
-      <c r="T140" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A gender of person source that reports not belonging to the cultural gender role distinctions of either male or female.</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>non-binary, transexual</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BCIO:010122</t>
+          <t>BCIO:010117</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>health status of person source</t>
+        </is>
+      </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>pre-existing knowledge or skill</t>
-        </is>
-      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr">
         <is>
-          <t>A knowledge or skill that is already possessed by the source which allows them to deliver the behaviour change intervention, including educational level and qualifications.</t>
-        </is>
-      </c>
-      <c r="P141" t="inlineStr"/>
+          <t>A socio-demographic attribute of person source that represents their mental or physical condition.</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr">
         <is>
-          <t>Bachelor’s degree, certification, accredited, qualified</t>
-        </is>
-      </c>
-      <c r="S141" t="inlineStr"/>
-      <c r="T141" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>diabetes, cancer, depression, obesity, overweight</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BCIO:010127</t>
+          <t>BCIO:010114</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>ethnic group membership of person source</t>
+        </is>
+      </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>affiliation to a formal group or organisation</t>
-        </is>
-      </c>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr">
         <is>
-          <t>A pre-existing knowledge or skill that is recognised through affiliation to a formal group or organisation.</t>
-        </is>
-      </c>
-      <c r="P142" t="inlineStr"/>
+          <t>A socio-demographic attribute of person source that is the ethnic group to which an individual identifies as belonging, where an ethic group is a population whose members have a common heritage that is real or presumed such as common culture, language, religion, behaviour or biological trait.</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr">
         <is>
-          <t>member of British Psychological Society</t>
-        </is>
-      </c>
-      <c r="S142" t="inlineStr"/>
-      <c r="T142" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>black, white, Indian, Chinese, Somalian</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BCIO:010108</t>
+          <t>BCIO:010116</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>socio demographic attribute of person source</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>language proficiency of person source</t>
+        </is>
+      </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
@@ -5795,33 +5859,37 @@
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr">
         <is>
-          <t>A social or demographic characteristic of a human being who is the bearer of a person source role.</t>
-        </is>
-      </c>
-      <c r="P143" t="inlineStr"/>
-      <c r="R143" t="inlineStr"/>
-      <c r="S143" t="inlineStr"/>
-      <c r="T143" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A socio-demographic attribute of person source that is an individual’s ability to speak or perform in the intervention language.</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>fluent, native</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BCIO:010119</t>
+          <t>BFO:0000031</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>generically dependent continuant</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>psychological influence on intervention delivery of person source</t>
-        </is>
-      </c>
+      <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
@@ -5831,33 +5899,25 @@
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is their existing psychological attributes related to or potentially affecting the target behaviour.</t>
-        </is>
-      </c>
-      <c r="P144" t="inlineStr"/>
-      <c r="R144" t="inlineStr"/>
-      <c r="S144" t="inlineStr"/>
-      <c r="T144" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BCIO:010109</t>
+          <t>IAO:0000030</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>age of person source</t>
-        </is>
-      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>information content entity</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
@@ -5867,22 +5927,14 @@
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is a time quality inhering in a bearer by virtue of how long the bearer has existed.</t>
-        </is>
-      </c>
-      <c r="P145" t="inlineStr"/>
-      <c r="R145" t="inlineStr"/>
-      <c r="S145" t="inlineStr"/>
-      <c r="T145" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A generically dependent continuant that is about some thing.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BCIO:010118</t>
+          <t>IAO:0000027</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -5891,7 +5943,7 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>target behaviour of person source</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -5903,38 +5955,26 @@
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is their amount or experience of the intervention’s target behaviour.</t>
-        </is>
-      </c>
-      <c r="P146" t="inlineStr"/>
-      <c r="R146" t="inlineStr">
-        <is>
-          <t>source is highly physically active</t>
-        </is>
-      </c>
-      <c r="S146" t="inlineStr"/>
-      <c r="T146" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BCIO:010115</t>
+          <t>BCIO:010126</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>religious group membership of person source</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>amount of experience</t>
+        </is>
+      </c>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
@@ -5943,38 +5983,38 @@
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is a religious group to which an individual identifies as belonging, where a religious group is a group of people characterised by the practice of a common religion.</t>
-        </is>
-      </c>
-      <c r="P147" t="inlineStr"/>
+          <t>A knowledge or skill that is the duration of experience in related domain held by person source.</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr">
         <is>
-          <t>Muslim, Christian, Hindu, Sikh, Buddhist, Judaism</t>
-        </is>
-      </c>
-      <c r="S147" t="inlineStr"/>
-      <c r="T147" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>full-day, 6 years</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BCIO:010117</t>
+          <t>BCIO:010106</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>health status of person source</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>number of people delivering intervention to each participant</t>
+        </is>
+      </c>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
@@ -5983,38 +6023,34 @@
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that represents their mental or physical condition.</t>
-        </is>
-      </c>
-      <c r="P148" t="inlineStr"/>
-      <c r="R148" t="inlineStr">
-        <is>
-          <t>diabetes, cancer, depression, obesity, overweight</t>
-        </is>
-      </c>
-      <c r="S148" t="inlineStr"/>
-      <c r="T148" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A count data item that is the number of providers that an individual participant in the intervention encounters.</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BCIO:010114</t>
+          <t>BCIO:010107</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>ethnic group membership of person source</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>total number of people able to deliver intervention</t>
+        </is>
+      </c>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
@@ -6023,37 +6059,33 @@
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is the ethnic group to which an individual identifies as belonging, where an ethic group is a population whose members have a common heritage that is real or presumed such as common culture, language, religion, behaviour or biological trait.</t>
-        </is>
-      </c>
-      <c r="P149" t="inlineStr"/>
-      <c r="R149" t="inlineStr">
-        <is>
-          <t>black, white, Indian, Chinese, Somalian</t>
-        </is>
-      </c>
-      <c r="S149" t="inlineStr"/>
-      <c r="T149" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A count data item that is the total number of providers that are available and able to deliver the intervention.</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BCIO:010110</t>
+          <t>BFO:0000004</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>independent continuant</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>gender of person source</t>
-        </is>
-      </c>
+      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
@@ -6063,38 +6095,26 @@
       <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is an individual's perception of having a particular gender, which may or may not correspond with their birth sex.</t>
-        </is>
-      </c>
-      <c r="P150" t="inlineStr"/>
-      <c r="R150" t="inlineStr">
-        <is>
-          <t>gender</t>
-        </is>
-      </c>
-      <c r="S150" t="inlineStr"/>
-      <c r="T150" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A continuant that is a bearer of quality and realizable entity entities, in which other entities inhere and which itself cannot inhere in anything.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BCIO:010113</t>
+          <t>BFO:0000040</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>other gender</t>
-        </is>
-      </c>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
@@ -6103,26 +6123,14 @@
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr">
         <is>
-          <t>A gender of person source that reports not belonging to the cultural gender role distinctions of either male or female.</t>
-        </is>
-      </c>
-      <c r="P151" t="inlineStr"/>
-      <c r="R151" t="inlineStr">
-        <is>
-          <t>non-binary, transexual</t>
-        </is>
-      </c>
-      <c r="S151" t="inlineStr"/>
-      <c r="T151" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An &lt;independent continuant&gt; that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BCIO:010116</t>
+          <t>OGMS:0000087</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -6131,7 +6139,7 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>language proficiency of person source</t>
+          <t>extended organism</t>
         </is>
       </c>
       <c r="G152" t="inlineStr"/>
@@ -6143,38 +6151,26 @@
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is an individual’s ability to speak or perform in the intervention language.</t>
-        </is>
-      </c>
-      <c r="P152" t="inlineStr"/>
-      <c r="R152" t="inlineStr">
-        <is>
-          <t>fluent, native</t>
-        </is>
-      </c>
-      <c r="S152" t="inlineStr"/>
-      <c r="T152" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>An object aggregate consisting of an organism and all material entities located within the organism, overlapping the organism, or occupying sites formed in part by the organism.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BCIO:010123</t>
+          <t>MF:0000016</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>expertise discipline</t>
-        </is>
-      </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>human being</t>
+        </is>
+      </c>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
@@ -6183,44 +6179,35 @@
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr">
         <is>
-          <t>An attribute that is a field of knowledge or practice.</t>
-        </is>
-      </c>
-      <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>The division of expertise into different disciplines or fields is complex and depends on historical, social and structural factors.</t>
-        </is>
-      </c>
-      <c r="R153" t="inlineStr">
-        <is>
-          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
-        </is>
-      </c>
-      <c r="S153" t="inlineStr"/>
-      <c r="T153" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>An extended organism that is a member of the species Homo sapiens.</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BCIO:010093</t>
+          <t>BCIO:010002</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>discipline of current programme of study or training</t>
-        </is>
-      </c>
+      <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>person source</t>
+        </is>
+      </c>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
@@ -6228,39 +6215,35 @@
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr">
         <is>
-          <t>An expertise discipline of the programme of study currently undertaken by the bearer of a student or trainee role.</t>
-        </is>
-      </c>
-      <c r="P154" t="inlineStr"/>
-      <c r="R154" t="inlineStr">
-        <is>
-          <t>psychology, medicine, hairdressing</t>
-        </is>
-      </c>
-      <c r="S154" t="inlineStr"/>
-      <c r="T154" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A person who is the bearer of a behaviour change intervention source role.</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BCIO:010124</t>
+          <t>BCIO:010095</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>discipline of pre-existing knowledge or skill</t>
-        </is>
-      </c>
+      <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>family member</t>
+        </is>
+      </c>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
@@ -6268,171 +6251,195 @@
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr">
         <is>
-          <t>The expertise discipline in which the person source has acquired their pre-existing knowledge and skills.</t>
-        </is>
-      </c>
-      <c r="P155" t="inlineStr"/>
-      <c r="R155" t="inlineStr">
-        <is>
-          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
-        </is>
-      </c>
-      <c r="S155" t="inlineStr"/>
-      <c r="T155" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A person who is a member of a group of persons united by blood, or by marriage or other legal arrangement, or by self-identity as belonging to the same family.</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BFO:0000003</t>
+          <t>BCIO:010097</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>occurrent</t>
-        </is>
-      </c>
+      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>spouse or partner</t>
+        </is>
+      </c>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr">
         <is>
-          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
+          <t>A family member that is an individual who is married or in a committed relationship with another individual.</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>boyfriend, girlfriend, partner, fiance, wife, husband</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BFO:0000015</t>
+          <t>BCIO:010098</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>process</t>
-        </is>
-      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>sibling relationship</t>
+        </is>
+      </c>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr">
         <is>
-          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
+          <t>A family member that is a family relationship between two persons with at least one shared parent.</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>brother, sister, step-brother, step-sister</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BCIO:010130</t>
+          <t>BCIO:010099</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>payment of person source</t>
-        </is>
-      </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>child relationship</t>
+        </is>
+      </c>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr">
         <is>
-          <t>A process in which a person source is paid or compensated for delivering the intervention.</t>
-        </is>
-      </c>
-      <c r="P158" t="inlineStr"/>
-      <c r="R158" t="inlineStr"/>
-      <c r="S158" t="inlineStr"/>
-      <c r="T158" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>A family member that is an offspring relationship from a person to their parent.</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>daughter, son, step-daughter, step-son</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BCIO:010132</t>
+          <t>BCIO:010096</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>non-monetary payment</t>
-        </is>
-      </c>
+      <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>parent or guardian</t>
+        </is>
+      </c>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr">
         <is>
-          <t>A payment of person source that is non-monetary compensation given to the source for delivering the intervention.</t>
-        </is>
-      </c>
-      <c r="P159" t="inlineStr"/>
+          <t>A family member that is a mother, father or legal carer of a child.</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr">
         <is>
-          <t>course credit</t>
-        </is>
-      </c>
-      <c r="S159" t="inlineStr"/>
-      <c r="T159" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>mother, father, step-mother, step-father, guardian</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BCIO:010131</t>
+          <t>BCIO:050842</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>monetary payment</t>
-        </is>
-      </c>
+      <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>role model for a person</t>
+        </is>
+      </c>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
@@ -6440,37 +6447,38 @@
       <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr">
         <is>
-          <t>A payment of person source that is money, vouchers or valued objects given to the source for delivering the intervention.</t>
-        </is>
-      </c>
-      <c r="P160" t="inlineStr"/>
-      <c r="R160" t="inlineStr">
-        <is>
-          <t>paid in cash, vouchers</t>
-        </is>
-      </c>
-      <c r="S160" t="inlineStr"/>
+          <t>A &lt;person&gt; that influences a recipient by being perceived to be similar or admired.</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr"/>
       <c r="T160" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>This class lies at the intersection between a person and their environment and is defined from the perspective of the person.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BCIO:010129</t>
+          <t>OBI:0000245</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>volunteering of person source</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>organisation</t>
+        </is>
+      </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
@@ -6480,37 +6488,33 @@
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr">
         <is>
-          <t>A process in which a person source delivers the intervention on a voluntary basis without formal compensation.</t>
-        </is>
-      </c>
-      <c r="P161" t="inlineStr"/>
-      <c r="R161" t="inlineStr">
-        <is>
-          <t>voluntary basis, volunteering</t>
-        </is>
-      </c>
-      <c r="S161" t="inlineStr"/>
-      <c r="T161" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>An entity that can bear roles, has members, and has a set of organization rules. Members of organizations are either organizations themselves or individual people. Members can bear specific organization member roles that are determined in the organization rules. The organization rules also determine how decisions are made on behalf of the organization by the organization members.</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BCIO:010128</t>
+          <t>BCIO:010139</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>supervision of person source</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>organisation source</t>
+        </is>
+      </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
@@ -6520,21 +6524,17 @@
       <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr">
         <is>
-          <t>A process in which a person source is formally provided, by an individual with appropriate expertise, with corrective and skill-enhancing feedback, regarding the person source’s performance in delivering the intervention.</t>
-        </is>
-      </c>
-      <c r="P162" t="inlineStr"/>
-      <c r="R162" t="inlineStr">
-        <is>
-          <t>supervised</t>
-        </is>
-      </c>
-      <c r="S162" t="inlineStr"/>
-      <c r="T162" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>An organisation that is the bearer of a behaviour change intervention source role, such as voluntary, public or commercial organisations delivering a behaviour change intervention.</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Source/BCIO-source-hierarchy.xlsx
+++ b/Source/BCIO-source-hierarchy.xlsx
@@ -445,27 +445,27 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>crossreference</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>subontology</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>crossreference</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>examples</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
@@ -533,13 +533,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BFO:0000003</t>
+          <t>BFO:0000002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>occurrent</t>
+          <t>continuant</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -554,21 +554,21 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
+          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BFO:0000015</t>
+          <t>BFO:0000004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>independent continuant</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -582,14 +582,14 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
+          <t>A continuant that is a bearer of quality and realizable entity entities, in which other entities inhere and which itself cannot inhere in anything.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCIO:010128</t>
+          <t>BFO:0000040</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -597,7 +597,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>supervision of person source</t>
+          <t>material entity</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -610,37 +610,25 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>A process in which a person source is formally provided, by an individual with appropriate expertise, with corrective and skill-enhancing feedback, regarding the person source’s performance in delivering the intervention.</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>supervised</t>
+          <t>An &lt;independent continuant&gt; that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCIO:010130</t>
+          <t>OGMS:0000087</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>payment of person source</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>extended organism</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -650,34 +638,26 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>A process in which a person source is paid or compensated for delivering the intervention.</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+          <t>An object aggregate consisting of an organism and all material entities located within the organism, overlapping the organism, or occupying sites formed in part by the organism.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:010131</t>
+          <t>MF:0000016</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>monetary payment</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>human being</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -686,39 +666,35 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>A payment of person source that is money, vouchers or valued objects given to the source for delivering the intervention.</t>
+          <t>An extended organism that is a member of the species Homo sapiens.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>paid in cash, vouchers</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:010132</t>
+          <t>BCIO:010002</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>non-monetary payment</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>person source</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -726,39 +702,35 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>A payment of person source that is non-monetary compensation given to the source for delivering the intervention.</t>
+          <t>A person who is the bearer of a behaviour change intervention source role.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>course credit</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:010129</t>
+          <t>BCIO:010095</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>volunteering of person source</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>family member</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -766,138 +738,182 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>A process in which a person source delivers the intervention on a voluntary basis without formal compensation.</t>
+          <t>A person who is a member of a group of persons united by blood, or by marriage or other legal arrangement, or by self-identity as belonging to the same family.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>voluntary basis, volunteering</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BFO:0000002</t>
+          <t>BCIO:010098</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>continuant</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>sibling relationship</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
+          <t>A family member that is a family relationship between two persons with at least one shared parent.</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>brother, sister, step-brother, step-sister</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BFO:0000020</t>
+          <t>BCIO:010097</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>characteristic</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>spouse or partner</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>A continuant that inheres in or is borne by other entities. Every instance of A requires some specific instance of B which must always be the same.</t>
+          <t>A family member that is an individual who is married or in a committed relationship with another individual.</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>boyfriend, girlfriend, partner, fiance, wife, husband</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MF:0000030</t>
+          <t>BCIO:010096</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>representation</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>parent or guardian</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>A dependent continuant which is about a portion of reality.</t>
+          <t>A family member that is a mother, father or legal carer of a child.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>mother, father, step-mother, step-father, guardian</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MF:0000031</t>
+          <t>BCIO:010099</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>cognitive representation</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>child relationship</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>A representation which specifically depends on an anatomical structure in the cognitive system of an organism.</t>
+          <t>A family member that is an offspring relationship from a person to their parent.</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>daughter, son, step-daughter, step-son</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ADDICTO:0000381</t>
+          <t>BCIO:050842</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -905,12 +921,12 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>role model for a person</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -918,27 +934,40 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>A cognitive representation of themselves by a person or a group about themselves.</t>
+          <t>A &lt;person&gt; that influences a recipient by being perceived to be similar or admired.</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>This class lies at the intersection between a person and their environment and is defined from the perspective of the person.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ADDICTO:0000399</t>
+          <t>BCIO:010139</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>organisation source</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>self-identity</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -946,141 +975,133 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>An identity that a person has about themselves.</t>
-        </is>
-      </c>
+          <t>An organisation that is the bearer of a behaviour change intervention source role, such as voluntary, public or commercial organisations delivering a behaviour change intervention.</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:015098</t>
+          <t>OBI:0000245</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>organization</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>gender identity</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
+          <t>An entity that can bear roles, has members, and has a set of organization rules. Members of organizations are either organizations themselves or individual people. Members can bear specific organization member roles that are determined in the organization rules. The organization rules also determine how decisions are made on behalf of the organization by the organization members.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Population</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:010111</t>
+          <t>BFO:0000020</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>characteristic</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>female gender</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>A gender identity as being female.</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>female, woman</t>
+          <t>b is a specifically dependent continuant = Def. b is a continuant &amp; there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:010112</t>
+          <t>BCIO:010108</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>socio demographic attribute of person source</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>male gender</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>A gender identity as being male.</t>
+          <t>A social or demographic characteristic of a human being who is the bearer of a person source role.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>male, man</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BFO:0000017</t>
+          <t>BCIO:010119</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>realizable entity</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>psychological influence on intervention delivery of person source</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1090,14 +1111,22 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>A specifically dependent continuant  that inheres in continuant  entities and are not exhibited in full at every time in which it inheres in an entity or group of entities. The exhibition or actualization of a realizable entity is a particular manifestation, functioning or process that occurs under certain circumstances.</t>
-        </is>
-      </c>
+          <t>A socio-demographic attribute of person source that is their existing psychological attributes related to or potentially affecting the target behaviour.</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BFO:0000016</t>
+          <t>BCIO:010109</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1106,7 +1135,7 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>disposition</t>
+          <t>age of person source</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1116,23 +1145,36 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>A socio-demographic attribute of person source that is a time quality inhering in a bearer by virtue of how long the bearer has existed.</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:010120</t>
+          <t>BCIO:010110</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>expertise of person source</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>gender of person source</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -1141,22 +1183,26 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>A disposition that is an expert skill or knowledge held by the source delivering the behaviour change intervention.</t>
+          <t>A socio-demographic attribute of person source that is an individual's perception of having a particular gender, which may or may not correspond with their birth sex.</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:010121</t>
+          <t>BCIO:010113</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1164,12 +1210,12 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>knowledge or skill</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>other gender</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1177,142 +1223,146 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>An expertise of person source that is knowledge or skills held in order to deliver the behaviour change intervention.</t>
+          <t>A gender of person source that reports not belonging to the cultural gender role distinctions of either male or female.</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
-          <t>trained (if unclear whether pre-existing or acquired)</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>non-binary, transexual</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:010125</t>
+          <t>BCIO:010117</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>health status of person source</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>acquired knowledge or skill</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>A knowledge or skill that is additional knowledge or skills supplied to the source to allow them to deliver the behaviour change intervention, including educational level and qualifications.</t>
+          <t>A socio-demographic attribute of person source that represents their mental or physical condition.</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>diabetes, cancer, depression, obesity, overweight</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:010122</t>
+          <t>BCIO:010115</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>religious group membership of person source</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>pre-existing knowledge or skill</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>A knowledge or skill that is already possessed by the source which allows them to deliver the behaviour change intervention, including educational level and qualifications.</t>
+          <t>A socio-demographic attribute of person source that is a religious group to which an individual identifies as belonging, where a religious group is a group of people characterised by the practice of a common religion.</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Bachelor’s degree, certification, accredited, qualified</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Muslim, Christian, Hindu, Sikh, Buddhist, Judaism</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:010127</t>
+          <t>BCIO:010114</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ethnic group membership of person source</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>affiliation to a formal group or organisation</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>A pre-existing knowledge or skill that is recognised through affiliation to a formal group or organisation.</t>
+          <t>A socio-demographic attribute of person source that is the ethnic group to which an individual identifies as belonging, where an ethic group is a population whose members have a common heritage that is real or presumed such as common culture, language, religion, behaviour or biological trait.</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>member of British Psychological Society</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>black, white, Indian, Chinese, Somalian</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BFO:0000023</t>
+          <t>BCIO:010118</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1321,7 +1371,7 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>target behaviour of person source</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1333,26 +1383,38 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>A realizable entity  the manifestation of which brings about some result or end that is not essential to a continuant  in virtue of the kind of thing that it is but that can be served or participated in by that kind of continuant  in some kinds of natural, social or institutional contexts.</t>
+          <t>A socio-demographic attribute of person source that is their amount or experience of the intervention’s target behaviour.</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>source is highly physically active</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:010084</t>
+          <t>BCIO:010116</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>language proficiency of person source</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
@@ -1361,35 +1423,39 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
+          <t>A socio-demographic attribute of person source that is an individual’s ability to speak or perform in the intervention language.</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>fluent, native</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:010085</t>
+          <t>MF:0000030</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>representation</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>informal education student or trainee</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -1397,35 +1463,27 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning in a non-institutional setting.</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+          <t>A dependent continuant which is about a portion of reality.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:010088</t>
+          <t>MF:0000031</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>cognitive representation</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>higher education student or trainee</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -1433,26 +1491,14 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning on an advanced educational programme in a university, college or professional school.</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
+          <t>A representation which specifically depends on an anatomical structure in the cognitive system of an organism.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:010091</t>
+          <t>ADDICTO:0000381</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1460,39 +1506,27 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>masters student or trainee</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>A higher education student or trainee that is currently studying for a Masters degree.</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>MSc student, Masters student</t>
+          <t>A cognitive representation of themselves by a person or a group about themselves.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:010092</t>
+          <t>ADDICTO:0000399</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1501,38 +1535,26 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>doctoral student or trainee</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>self-identity</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>A higher education student or trainee that is currently studying for a doctoral degree.</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>PhD student</t>
+          <t>An identity that a person has about themselves.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:010090</t>
+          <t>BCIO:015098</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1544,7 +1566,7 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>graduate student or trainee</t>
+          <t>gender identity</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -1553,26 +1575,22 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>A higher education student or trainee that has completed an undergraduate degree.</t>
+          <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
         </is>
       </c>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>graduate student</t>
-        </is>
-      </c>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:010089</t>
+          <t>BCIO:010111</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1582,37 +1600,37 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>undergraduate student or trainee</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>female gender</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>A higher education student or trainee that is currently studying for an undergraduate degree.</t>
+          <t>A gender identity as being female.</t>
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>undergraduate student</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>female, woman</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:010087</t>
+          <t>BCIO:010112</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1621,47 +1639,51 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>vocational training student or trainee</t>
-        </is>
-      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>male gender</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
+          <t>A gender identity as being male.</t>
         </is>
       </c>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>male, man</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:010086</t>
+          <t>BCIO:010123</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>expertise discipline</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>school student or trainee</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -1669,34 +1691,43 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning at a primary or secondary education level in an institutional, organised setting.</t>
+          <t>An attribute that is a field of knowledge or practice.</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>The division of expertise into different disciplines or fields is complex and depends on historical, social and structural factors.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:010003</t>
+          <t>BCIO:010093</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>personal role of source</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>discipline of current programme of study or training</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -1705,35 +1736,39 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>A role that inheres in a person source.</t>
+          <t>An expertise discipline of the programme of study currently undertaken by the bearer of a student or trainee role.</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>psychology, medicine, hairdressing</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:010094</t>
+          <t>BCIO:010124</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>discipline of pre-existing knowledge or skill</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>relatedness between person source and the target population</t>
-        </is>
-      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
@@ -1741,98 +1776,82 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>A personal role of source that is realised in some relationship to the characteristics of the intervention participants.</t>
+          <t>The expertise discipline in which the person source has acquired their pre-existing knowledge and skills.</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:010100</t>
+          <t>BFO:0000017</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>realizable</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>carer</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is an individual who cares, unpaid, for a friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>carer</t>
+          <t>A specifically dependent continuant  that inheres in continuant  entities and are not exhibited in full at every time in which it inheres in an entity or group of entities. The exhibition or actualization of a realizable entity is a particular manifestation, functioning or process that occurs under certain circumstances.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:010101</t>
+          <t>BFO:0000023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>friend</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person whom the participant knows, likes and trusts, typically exclusive of sexual or family relations.</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
+          <t>A realizable entity  the manifestation of which brings about some result or end that is not essential to a continuant  in virtue of the kind of thing that it is but that can be served or participated in by that kind of continuant  in some kinds of natural, social or institutional contexts.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:010105</t>
+          <t>BCIO:010084</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1840,35 +1859,35 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>embedded in participants’ community</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a source who is known and working to deliver intervention in own community.</t>
+          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:010103</t>
+          <t>BCIO:010088</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1877,34 +1896,38 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>employer</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>higher education student or trainee</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person which hires the services of the participant.</t>
+          <t>A student or trainee that is currently learning on an advanced educational programme in a university, college or professional school.</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:010102</t>
+          <t>BCIO:010089</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1916,7 +1939,7 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>colleague</t>
+          <t>undergraduate student or trainee</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -1925,22 +1948,26 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person with whom the participant works in a profession or business.</t>
+          <t>A higher education student or trainee that is currently studying for an undergraduate degree.</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>undergraduate student</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:010104</t>
+          <t>BCIO:010091</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1952,7 +1979,7 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>peer</t>
+          <t>masters student or trainee</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -1961,22 +1988,26 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is descried as matched to intervention recipients on the basis of ‘peerness’ – age, social status, gender, shared experience, shared health status etc.</t>
+          <t>A higher education student or trainee that is currently studying for a Masters degree.</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>MSc student, Masters student</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:010004</t>
+          <t>BCIO:010090</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1985,38 +2016,38 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>occupational role of source</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>graduate student or trainee</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>A personal role of source that is realised by doing a specified type of work or working in a specified way.</t>
+          <t>A higher education student or trainee that has completed an undergraduate degree.</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Interventionist, facilitator, study staff</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>graduate student</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:010080</t>
+          <t>BCIO:010092</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2028,7 +2059,7 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>assembler</t>
+          <t>doctoral student or trainee</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -2037,22 +2068,26 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>An occupational role that assembles products from component parts according to strict specifications and procedures.</t>
+          <t>A higher education student or trainee that is currently studying for a doctoral degree.</t>
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>PhD student</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:010079</t>
+          <t>BCIO:010085</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2061,38 +2096,34 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>plant and machine operator</t>
-        </is>
-      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>informal education student or trainee</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>An occupational role that operates and monitors industrial and agricultural machinery and equipment on the spot or by remote control, or drives and operates trains, motor vehicles and mobile machinery and equipment.</t>
+          <t>A student or trainee that is currently learning in a non-institutional setting.</t>
         </is>
       </c>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Stationary Plant and Machine Operator, Driver, Mobile Plant Operator</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:010068</t>
+          <t>BCIO:010086</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2101,34 +2132,34 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>services and sales worker</t>
-        </is>
-      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>school student or trainee</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>An occupational role that provides personal or protective services related to travel, house-keeping, catering, personal care, protection against fire and unlawful acts, or sells goods in retail or markets.</t>
+          <t>A student or trainee that is currently learning at a primary or secondary education level in an institutional, organised setting.</t>
         </is>
       </c>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:010076</t>
+          <t>BCIO:010087</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2137,38 +2168,34 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>vocational training student or trainee</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>protective services worker</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>A services and sales worker that protects individuals and property against fire and other hazards, maintain law and order and enforce laws and regulations.</t>
+          <t>A student or trainee that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
         </is>
       </c>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Firefighter, Police officer, Prison guard, Security guard, Offender manager</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:010069</t>
+          <t>BCIO:010000</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2176,39 +2203,35 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>behaviour change intervention source</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>personal services worker</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>A services and sales worker that provides personal services related to travel, housekeeping, catering and hospitality, hairdressing and beauty treatment, animal care grooming and training, companionship and other services of a personal nature.</t>
+          <t>A role played by a person, population or organisation that provides a BCI.</t>
         </is>
       </c>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Travel Attendant, Conductor, Guide, Cook, Waiter, Bartender, Hairdresser, Beautician, Housekeeping Supervisor, Astrologer, Fortune-teller, Valet, Undertaker, Embalmer, Pet Groomer, Animal Care Worker</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:010070</t>
+          <t>BCIO:010138</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2217,38 +2240,34 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>organisational source role</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>sales worker</t>
-        </is>
-      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>A services and sales worker that demonstrates goods in wholesale or retail shops, at stalls and markets, door to door, via telephone or customer contact centres. They may record and accept payment for goods and services purchased, and may operate small retail outlets.</t>
+          <t>A BCI source role that is borne by an organisation.</t>
         </is>
       </c>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Street Salesperson, Market Salesperson, Shop Salesperson, Cashier, Ticket Clerk, Model, Sales Demonstrator, Door-to-door Salesperson, Contact Centre Salesperson, Service Station Attendant, Food Service Counter Attendant</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:010071</t>
+          <t>BCIO:010133</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2257,38 +2276,34 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>source role related to intervention</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>personal care worker</t>
-        </is>
-      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>A services and sales worker that provides care, supervision and assistance for children, patients and elderly, convalescent or disabled persons in institutional and residential settings.</t>
+          <t>A BCI source whose occupational or voluntary role is focused on delivery of the behaviour change intervention.</t>
         </is>
       </c>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Personal carer</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:010074</t>
+          <t>BCIO:010134</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2297,38 +2312,34 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>source involved in development of intervention</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>health care assistant</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>A personal care worker that provides direct personal care and assistance with activities of daily living to patients and residents in a variety of health care settings, working  in implementation of established care plans and practices, and under the direct supervision of medical, nursing or other health professionals or associate professionals.</t>
+          <t>A BCI source that is involved in the development of intervention content.</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Nursing aide (clinic or hospital), Patient care assistant, Psychiatric aid</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:010072</t>
+          <t>BCIO:010135</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2338,37 +2349,33 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>source involved in co-production of intervention</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>child care worker</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>A personal care worker that provides care and supervision for children in non-domestic settings.</t>
+          <t>A source involved in development of intervention that has developed the intervention content in collaboration with key stakeholders such as patients or community members.</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Babysitter, Child care worker, Creche ayah, Family day care worker, Nanny, Out of school hours care worker</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:010075</t>
+          <t>BCIO:010001</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2377,38 +2384,34 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>person source role</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>home-based personal care worker</t>
-        </is>
-      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>A personal care worker that provide routine personal care and assistance with activities of daily living to persons who are in need of such care due to effects of ageing, illness, injury, or other physical or mental conditions, in private homes and other independent residential settings.</t>
+          <t>A behaviour change intervention source role that inheres in a person.</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Home birth assistant, Home care aide, Nursing aide (home), Personal care provider</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:010073</t>
+          <t>BCIO:010003</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2416,39 +2419,35 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>personal role of source</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>teachers’ aide</t>
-        </is>
-      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>A personal care worker that performs non-teaching duties to assist teaching staff, and provides care and supervision for children in schools and pre-schools.</t>
+          <t>A role that inheres in a person source.</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Pre-school assistant, Teacher’s assistant</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:010077</t>
+          <t>BCIO:010094</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2457,38 +2456,34 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>skilled agricultural, forestry and fishery worker</t>
-        </is>
-      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>relatedness between person source and the target population</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>An occupational role that grows and harvests plants or animals to provide food, shelter and income for themselves and their households.</t>
+          <t>A personal role of source that is realised in some relationship to the characteristics of the intervention participants.</t>
         </is>
       </c>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Market gardener, Crop grower, Animal Producer, Mixed Crop and Animal Producer, Forestry worker, Fishery worker, Hunter. Subsistence Crop Farmer, Subsistence Livestock Farmer</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:010006</t>
+          <t>BCIO:010105</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2500,7 +2495,7 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>professional</t>
+          <t>embedded in participants’ community</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
@@ -2509,22 +2504,22 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>An occupational role that works in knowledge building activities, applies scientific or artistic concepts and theories or teaches about the foregoing in a systematic manner.</t>
+          <t>A relatedness between person source and the target population that is a source who is known and working to deliver intervention in own community.</t>
         </is>
       </c>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:010044</t>
+          <t>BCIO:010103</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2534,33 +2529,33 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>technician and associate professional</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>employer</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>A professional that performs technical and related tasks connected with research and the application of scientific or artistic concepts and operational methods, and government or business regulations.</t>
+          <t>A relatedness between person source and the target population that is a person which hires the services of the participant.</t>
         </is>
       </c>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:010058</t>
+          <t>BCIO:010100</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2570,37 +2565,37 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>carer</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>legal and related associate professional</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs support functions in courts of law or in law offices, provide services related to such legal matters as insurance contracts, the transferring of property and the granting of loans and other financial transactions, or conduct investigations for clients.</t>
+          <t>A relatedness between person source and the target population that is an individual who cares, unpaid, for a friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
         </is>
       </c>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Bailiff, Judge’s clerk, Conveyancing clerk, Court clerk, Justice of the peace, Law clerk, Legal assistant, Paralegal, Private detective, Title searcher</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>carer</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:010061</t>
+          <t>BCIO:010102</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2610,37 +2605,33 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>colleague</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>sport and fitness worker</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>A technician and associate professional that prepares for and competes in sporting events for financial gain, trains amateur and professional sportsmen and women to enhance performance, promotes participation and standards in sport, organises and officiates sporting events, or provides instruction, training and supervision for various forms of exercise and other recreational activities.</t>
+          <t>A relatedness between person source and the target population that is a person with whom the participant works in a profession or business.</t>
         </is>
       </c>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
       <c r="R61" t="inlineStr">
         <is>
-          <t>physical activity professional, exercise physiologist, exercise therapist, exercise specialist</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:010063</t>
+          <t>BCIO:010104</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2650,37 +2641,33 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>peer</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>sports coach, instructor and official</t>
-        </is>
-      </c>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that works with amateur and professional sportspersons to enhance performance and encourage greater participation in sport, and organizes and officiates in sporting events according to established rules.</t>
+          <t>A relatedness between person source and the target population that is descried as matched to intervention recipients on the basis of ‘peerness’ – age, social status, gender, shared experience, shared health status etc.</t>
         </is>
       </c>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
         <is>
-          <t>Referee, Ski instructor, Sports coach, Sports official, Swimming instructor</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:010062</t>
+          <t>BCIO:010101</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2690,37 +2677,33 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>athlete and sports player</t>
-        </is>
-      </c>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that participates in competitive sporting events. They train and compete, either individually or as part of a team, in their chosen sport.</t>
+          <t>A relatedness between person source and the target population that is a person whom the participant knows, likes and trusts, typically exclusive of sexual or family relations.</t>
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Athlete, Bicycle racer, Boxer, Chess player , Footballer, Golfer, Hockey player, Jockey, Poker player, Racing driver, Skier, Tennis player, Wrestler</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:010064</t>
+          <t>BCIO:010004</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2729,38 +2712,38 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>occupational role of source</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>fitness and recreation instructor and programme leader</t>
-        </is>
-      </c>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that leads, guides and instructs groups and individuals in recreational, fitness or outdoor adventure activities.</t>
+          <t>A personal role of source that is realised by doing a specified type of work or working in a specified way.</t>
         </is>
       </c>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Aerobics instructor, Fitness instructor, Horse riding instructor, Outdoor adventure guide, Personal trainer, Sailing instructor, Underwater diving instructor</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Interventionist, facilitator, study staff</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:010059</t>
+          <t>BCIO:010081</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2770,37 +2753,37 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>elementary occupation</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>social work associate professional</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>A technician and associate professional that implements social assistance programmes and community services and assist clients to deal with personal and social problems.</t>
+          <t>An occupational role that involves the performance of simple and routine tasks which may require the use of hand-held tools and considerable physical effort.</t>
         </is>
       </c>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Community development worker, Community services worker, Crisis intervention worker, Disability services worker, Family services worker, Life skills instructor, Mental health support worker, Welfare support worker, Women’s shelter supervisor, Youth services worker</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Cleaner, Labourer, Food Preparation Assistant, Street and Related Services Worker, Street Vendor (excluding Food), Refuse Worker</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:010066</t>
+          <t>BCIO:010083</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2810,37 +2793,37 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>researcher</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>information and communications technician</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>A technician and associate professional that provides support for the day to day running of computer systems, communication systems and networks, broadcast images and sound, telecommunication signals on land, sea or in aircraft.</t>
+          <t>An occupational role that is a researcher but unclear what discipline.</t>
         </is>
       </c>
       <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
       <c r="R66" t="inlineStr">
         <is>
-          <t>Information and Communications Technology Operations and User Support Technician, Telecommunications and Broadcasting Technician</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>researcher, research assistant, investigator</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:010045</t>
+          <t>BCIO:010080</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2850,37 +2833,33 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>assembler</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>health associate professional</t>
-        </is>
-      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs technical and practical tasks to support diagnosis and treatment of illness, disease, injuries and impairments in humans or animals, and supports the implementation of health care usually established by medical, veterinary, nursing and other health professionals.</t>
+          <t>An occupational role that assembles products from component parts according to strict specifications and procedures.</t>
         </is>
       </c>
       <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Veterinary Technician</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:010047</t>
+          <t>BCIO:010067</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2890,37 +2869,37 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>clerical support worker</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>nursing and midwifery associate professional</t>
-        </is>
-      </c>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>A health associate professional that provides basic nursing and personal care for people who are physically or mentally ill, disabled or infirm, and for others in need of care due to potential risks to health including before, during and after childbirth. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing, midwifery and other health professionals.</t>
+          <t>An occupational role that records, organizes, stores, computes and retrieves information, and performs a number of clerical duties in connection with money-handling operations, travel arrangements, requests for information, and appointments.</t>
         </is>
       </c>
       <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Practice assistant, Quit Smoking Counsellor, Health educator, Dispensing Optician, Information Technician</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>General and Keyboard Clerk, customers Services Clerk, Numerical and Material Recording Clerk</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:010048</t>
+          <t>BCIO:010068</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2930,37 +2909,33 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>services and sales worker</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>nursing associate professional</t>
-        </is>
-      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>A nursing and midwifery associate professional that provides basic nursing and personal care for people in need of such care due to effects of ageing, illness, injury, or other physical or mental impairment. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing and other health professionals.</t>
+          <t>An occupational role that provides personal or protective services related to travel, house-keeping, catering, personal care, protection against fire and unlawful acts, or sells goods in retail or markets.</t>
         </is>
       </c>
       <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
       <c r="R69" t="inlineStr">
         <is>
-          <t>Assistant nurse, Associate professional nurse, Enrolled nurse, Practical nurse</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:010049</t>
+          <t>BCIO:010076</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2971,36 +2946,36 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>protective services worker</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>midwifery associate professional</t>
-        </is>
-      </c>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>A nursing and midwifery associate professional that provides basic health care and advice before, during and after pregnancy and childbirth. They implement care, treatment and referral plans usually established by medical, midwifery and other health professionals.</t>
+          <t>A services and sales worker that protects individuals and property against fire and other hazards, maintain law and order and enforce laws and regulations.</t>
         </is>
       </c>
       <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
       <c r="R70" t="inlineStr">
         <is>
-          <t>Assistant midwife, Traditional midwife</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Firefighter, Police officer, Prison guard, Security guard, Offender manager</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCIO:010056</t>
+          <t>BCIO:010069</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3011,36 +2986,36 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>personal services worker</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>ambulance worker</t>
-        </is>
-      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>A health associate professional that provides emergency health care to patients who are injured, sick, infirm or otherwise physically or mentally impaired prior to and during transport to medical facilities.</t>
+          <t>A services and sales worker that provides personal services related to travel, housekeeping, catering and hospitality, hairdressing and beauty treatment, animal care grooming and training, companionship and other services of a personal nature.</t>
         </is>
       </c>
       <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
-          <t>Ambulance officer, Ambulance paramedic, Emergency medical technician, Emergency paramedic</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Travel Attendant, Conductor, Guide, Cook, Waiter, Bartender, Hairdresser, Beautician, Housekeeping Supervisor, Astrologer, Fortune-teller, Valet, Undertaker, Embalmer, Pet Groomer, Animal Care Worker</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIO:010051</t>
+          <t>BCIO:010070</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3051,36 +3026,36 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>sales worker</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>dental assistant and therapist</t>
-        </is>
-      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>A health associate professional that provides basic dental care services for the prevention and treatment of diseases and disorders of the teeth and mouth, according to care plans and procedures established by a dentist or other oral health professional.</t>
+          <t>A services and sales worker that demonstrates goods in wholesale or retail shops, at stalls and markets, door to door, via telephone or customer contact centres. They may record and accept payment for goods and services purchased, and may operate small retail outlets.</t>
         </is>
       </c>
       <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
-          <t>Dental assistant, Dental hygienist , Dental therapist</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Street Salesperson, Market Salesperson, Shop Salesperson, Cashier, Ticket Clerk, Model, Sales Demonstrator, Door-to-door Salesperson, Contact Centre Salesperson, Service Station Attendant, Food Service Counter Attendant</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BCIO:010054</t>
+          <t>BCIO:010071</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3091,36 +3066,36 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>personal care worker</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>medical assistant</t>
-        </is>
-      </c>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>A health associate professional that performs basic clinical and administrative tasks to support patient care under the direct supervision of a medical practitioner or other health professional.</t>
+          <t>A services and sales worker that provides care, supervision and assistance for children, patients and elderly, convalescent or disabled persons in institutional and residential settings.</t>
         </is>
       </c>
       <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
-          <t>Clinical assistant, Medical assistant, Ophthalmic assistant</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Personal carer</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BCIO:010055</t>
+          <t>BCIO:010073</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3132,36 +3107,35 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>environmental and occupational health inspector and associate</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>teachers’ aide</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>A health associate professional that investigates the implementation of rules and regulations relating to environmental factors that may affect human health, safety in the 
-workplace, and safety of processes for the production of goods and services. They may implement and evaluate programmes to restore or improve safety and sanitary conditions under the supervision of a health professional.</t>
+          <t>A personal care worker that performs non-teaching duties to assist teaching staff, and provides care and supervision for children in schools and pre-schools.</t>
         </is>
       </c>
       <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Food sanitation and safety inspector, Health inspector, Occupational health and safety inspector, Pollution inspector, Product safety inspector, Sanitarian, Sanitary inspector</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Pre-school assistant, Teacher’s assistant</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BCIO:010050</t>
+          <t>BCIO:010072</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3173,35 +3147,35 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>traditional and complementary medicine associate professional</t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>child care worker</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>A health associate professional that prevents and treats human physical and mental illnesses, disorders and injuries using herbal and other therapies based on theories, beliefs and experiences originating in specific cultures. They administer treatments using traditional techniques and medicaments, either acting independently or according to therapeutic care plans established by a traditional medicine or other health professional.</t>
+          <t>A personal care worker that provides care and supervision for children in non-domestic settings.</t>
         </is>
       </c>
       <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Acupuncture technician, Ayurvedic technician, Bonesetter, Herbalist , Homeopathy technician, Scraping and cupping therapist, Village healer, Witch doctor</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Babysitter, Child care worker, Creche ayah, Family day care worker, Nanny, Out of school hours care worker</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BCIO:010046</t>
+          <t>BCIO:010075</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3213,35 +3187,35 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>medical and pharmaceutical technician</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>home-based personal care worker</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>A health associate professional that performs technical tasks to assist in diagnosis and treatment of illness, disease, injuries and impairments.</t>
+          <t>A personal care worker that provide routine personal care and assistance with activities of daily living to persons who are in need of such care due to effects of ageing, illness, injury, or other physical or mental conditions, in private homes and other independent residential settings.</t>
         </is>
       </c>
       <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
-          <t>Medical imaging and therapeutic equipment technician, Medical and Pathology laboratory technician, Pharmaceutical technician, Medical and dental prosthetic technician</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Home birth assistant, Home care aide, Nursing aide (home), Personal care provider</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BCIO:010053</t>
+          <t>BCIO:010074</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3253,35 +3227,35 @@
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>physiotherapy technician and assistant</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>health care assistant</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>A health associate professional that provides physical therapeutic treatments to patients in circumstances where functional movement is threatened by injury, disease or impairment. Therapies are usually provided according to rehabilitative plans established by a physiotherapist or other health professional.</t>
+          <t>A personal care worker that provides direct personal care and assistance with activities of daily living to patients and residents in a variety of health care settings, working  in implementation of established care plans and practices, and under the direct supervision of medical, nursing or other health professionals or associate professionals.</t>
         </is>
       </c>
       <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
-          <t>Acupressure therapist, Electrotherapist, Hydrotherapist, Massage therapist, Physical rehabilitation technician, Physiotherapy technician, Shiatsu therapist</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Nursing aide (clinic or hospital), Patient care assistant, Psychiatric aid</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BCIO:010052</t>
+          <t>BCIO:010077</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3291,37 +3265,37 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>skilled agricultural, forestry and fishery worker</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>community health worker</t>
-        </is>
-      </c>
+      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>A health associate professional that provides health education, referral and follow-up, case management, basic preventive health care and home visiting services to specific communities. They provide support and assistance to individuals and families in navigating the health and social services system.</t>
+          <t>An occupational role that grows and harvests plants or animals to provide food, shelter and income for themselves and their households.</t>
         </is>
       </c>
       <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Community health aide, Community health promoter, Community health worker, Village health worker, outreach worker, health worker</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Market gardener, Crop grower, Animal Producer, Mixed Crop and Animal Producer, Forestry worker, Fishery worker, Hunter. Subsistence Crop Farmer, Subsistence Livestock Farmer</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCIO:010060</t>
+          <t>BCIO:010006</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3331,37 +3305,33 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>professional</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>religious associate professional</t>
-        </is>
-      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>A technician and associate professional that provides support to ministers of religion or to a religious community, undertake religious works, preach and propagate the teachings of a particular religion and endeavour to improve well-being through the power of faith and spiritual advice.</t>
+          <t>An occupational role that works in knowledge building activities, applies scientific or artistic concepts and theories or teaches about the foregoing in a systematic manner.</t>
         </is>
       </c>
       <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
       <c r="R79" t="inlineStr">
         <is>
-          <t>Faith healer, Lay preacher, Monk, Nun</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIO:010057</t>
+          <t>BCIO:010007</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3372,36 +3342,36 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>business and administration associate professional</t>
-        </is>
-      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>science and engineering professional</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs mostly technical tasks connected with the practical application of knowledge relating to financial accounting and transaction matters, mathematical calculations, human resource development, selling and buying financial instruments, specialized secretarial tasks and enforcing or applying government rules.</t>
+          <t>A professional that conducts research, improves or develops concepts, theories and operational methods or applies scientific knowledge.</t>
         </is>
       </c>
       <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
       <c r="R80" t="inlineStr">
         <is>
-          <t>Financial and Mathematical associate professional, Sales and purchasing agent, Broker, Business Services Agent, Administrative and Specialized Secretary, Government regulatory associate professional, Medical secretary</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Science Professional, Mathematician, Actuary, Statistician, Life Science Professional, Engineering Professional, Electrotechnology Engineer, Architect, Planner, Surveyor, Designer</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BCIO:010065</t>
+          <t>BCIO:010008</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3412,36 +3382,36 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>artistic, cultural and culinary associate professional</t>
-        </is>
-      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>health professional</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>A technician and associate professional that combines creative skills and technical and cultural knowledge in creative media or food.</t>
+          <t>A professional that improves or develops concepts, theories and operational method, and applied scientific knowledge relating to medicine, nursing, dentistry, veterinary medicine, pharmacy, and promotion of health.</t>
         </is>
       </c>
       <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
-          <t>Photographer, Interior designers and decorator, Gallery, museum and library technician, Chef</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Health professional; Arts therapist, Chiropractor, Dance and movement therapist, Occupational therapist, Osteopath, Podiatrist, Recreational therapist, Health staff, Clinic staff</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BCIO:010025</t>
+          <t>BCIO:010024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3452,36 +3422,36 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>teaching professional</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>optometrist and ophthalmic optician</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
-          <t>A professional that teaches the theory and practice of one or more disciplines at different educational levels.</t>
+          <t>A health professional  that provides diagnosis, management and treatment services for disorders of the eyes and visual system.</t>
         </is>
       </c>
       <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
       <c r="R82" t="inlineStr">
         <is>
-          <t>Education Methods Specialist, Other Language Teacher, Information Technology Teacher, Private Tutor, School Counsellor, Student Advisor</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Ophthalmic optician , Optometrist, Orthoptist</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BCIO:010027</t>
+          <t>BCIO:010013</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3495,33 +3465,33 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>vocational education teacher</t>
+          <t>nursing professional</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches or instructs vocational or occupational subjects in adult and further education institutions and to senior students in secondary schools and colleges.</t>
+          <t>A health professional that provides treatment, support and care services for people who are in need of nursing care due to the effects of ageing, injury, illness or other physical or mental impairment, or potential risks to health.</t>
         </is>
       </c>
       <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Automotive technology instructor, Cosmetology instructor, Vocational education teacher</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Clinical nurse consultant, District nurse, Nurse anaesthetist, Nurse educator, Nurse practitioner, Operating theatre nurse, Professional nurse, Public health nurse, Specialist nurse, Nursing Counsellor, Study Nurse</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BCIO:010026</t>
+          <t>BCIO:010017</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3535,33 +3505,33 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>university and higher education teacher</t>
+          <t>veterinarian</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
-          <t>A teaching professional that prepares and delivers lectures and conduct tutorials in one or more subjects within a prescribed course of study at a university or other higher educational institution. They conduct research, and prepare scholarly papers and books.</t>
+          <t>A health professional that diagnoses, prevents and treats diseases, injuries and dysfunctions of animals.</t>
         </is>
       </c>
       <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
         <is>
-          <t>Higher education lecturer, Professor, University lecturer, University tutor</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Animal pathologist, Veterinarian, Veterinary epidemiologist, Veterinary intern, Veterinary surgeon</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BCIO:010033</t>
+          <t>BCIO:010021</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3575,33 +3545,33 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>arts teacher</t>
+          <t>physiotherapist</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
-          <t>A teaching professional  that teaches students in the practice, theory and performance of dance, drama, visual and other arts (excluding music) in private or small group tuition or within mainstream educational institutions.</t>
+          <t>A health professional  that assesses, plans and implements rehabilitative programmes that improve or restore human motor functions, maximize movement ability, relieve pain syndromes, and treat or prevent physical challenges associated with injuries, diseases and other impairments.</t>
         </is>
       </c>
       <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
       <c r="R85" t="inlineStr">
         <is>
-          <t>Dance teacher (private tuition), Drama teacher (private tuition), Painting teacher (private tuition), Sculpture teacher (private tuition)</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>Geriatric physical therapist, Manipulative therapist, Orthopaedic physical therapist, Paediatric physical therapist, Physical therapist, Physiotherapist</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BCIO:010028</t>
+          <t>BCIO:010016</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3615,33 +3585,33 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>secondary education teacher</t>
+          <t>paramedical practitioner</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches one or more subjects at secondary education level.</t>
+          <t>A health professional that provides advisory, diagnostic, curative and preventive medical services more limited in scope and complexity than those carried out by medical doctors. They work autonomously or with limited supervision of medical doctors, and apply advanced clinical procedures for treating and preventing diseases, injuries and other physical or mental impairments common to specific communities.</t>
         </is>
       </c>
       <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
       <c r="R86" t="inlineStr">
         <is>
-          <t>Secondary school teacher, High school teacher</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Advanced care paramedic, Clinical officer (paramedical), Feldscher, Primary care paramedic, Surgical technician</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BCIO:010032</t>
+          <t>BCIO:010009</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3655,33 +3625,33 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>music teacher</t>
+          <t>medical doctor</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches students in the practice, theory and performance of music in private or small group tuition or within mainstream educational institutions.</t>
+          <t>A health professional that studies, diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans through the application of modern medicine. They plan, supervise and evaluate the implementation of care and treatment plans by other health care providers, and conduct medical education and research activities.</t>
         </is>
       </c>
       <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
       <c r="R87" t="inlineStr">
         <is>
-          <t>Guitar teacher (private tuition), Piano teacher (private tuition), Singing teacher (private tuition), Violin teacher (private tuition)</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>District medical doctor-therapist, family medical practitioner, general practitioner, medical doctor (general), medical officer (general), physician (general), primary health care physician, resident medical officer specializing in general practice</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BCIO:010031</t>
+          <t>BCIO:010011</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3693,35 +3663,35 @@
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>special needs teacher</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>specialist medical practitioner</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches children, young persons or adults with physical or intellectual special needs.</t>
+          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans, using specialized testing, diagnostic, medical, surgical, physical and psychiatric techniques through application of the principles and procedures of modern medicine. They specialize in certain disease categories, types of patient or methods of treatment and may conduct medical education and research in their chosen areas of specialization.</t>
         </is>
       </c>
       <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
         <is>
-          <t>Learning disabilities special education teacher, Learning support teacher, Remedial teacher, Teacher of gifted children, Teacher of the hearing impaired, Teacher of the sight impaired</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Anaesthetist, Cardiologist, Emergency medicine specialist, Gynaecologist, Obstetrician, Ophthalmologist, Paediatrician, Pathologist, Preventive medicine specialist, Psychiatrist, Radiation oncologist, Radiologist, Resident medical officer in specialist training, Specialist medical practitioner (public health), Specialist physician (internal medicine), Specialist physician (nuclear medicine), Surgeon</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BCIO:010029</t>
+          <t>BCIO:010010</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3733,31 +3703,35 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>primary school teacher</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>generalist medical practitioner</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches teach a range of subjects at the primary education level.</t>
+          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments and maintains general health in humans through application of modern medicine. They do not limit their practice to certain disease categories or methods of treatment, and may assume responsibility for the provision of continuing and comprehensive medical care to individuals, families and communities.</t>
         </is>
       </c>
       <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Primary care physician, family doctor, GP</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BCIO:010030</t>
+          <t>BCIO:010015</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3771,33 +3745,33 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>early childhood educator</t>
+          <t>traditional and complementary medicine professional</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>A teaching professional that promotes the social, physical, and intellectual development of children below primary school age through the provision of educational and play activities.</t>
+          <t>A health professional that examines patients, prevents and treats illness, disease, injury and other physical and mental impairments and maintains general health in humans. They do this by applying knowledge, skills and practices acquired through extensive study of the theories, beliefs and experiences originating in specific cultures.</t>
         </is>
       </c>
       <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
       <c r="R90" t="inlineStr">
         <is>
-          <t>Early childhood educator, Pre-school teacher</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Acupuncturist, Ayurvedic practitioner,  Chinese herbal medicine practitioner, Homeopath, Naturopath, Unani practitioner</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BCIO:010007</t>
+          <t>BCIO:010018</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3808,36 +3782,36 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>science and engineering professional</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>dentist</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>A professional that conducts research, improves or develops concepts, theories and operational methods or applies scientific knowledge.</t>
+          <t>A health professional that diagnoses treats and prevents diseases, injuries and abnormalities of the teeth, mouth, jaws and associated tissues by applying the principles and procedures of modern dentistry.</t>
         </is>
       </c>
       <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
       <c r="R91" t="inlineStr">
         <is>
-          <t>Science Professional, Mathematician, Actuary, Statistician, Life Science Professional, Engineering Professional, Electrotechnology Engineer, Architect, Planner, Surveyor, Designer</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Dental practitioner, Dental surgeon, Dentist, Endodontist, Oral and maxillofacial surgeon, Oral pathologist, Orthodontist, Paedodontist, Periodontist, Prosthodontist, Stomatologist</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BCIO:010034</t>
+          <t>BCIO:010020</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3848,32 +3822,36 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>legal, social and cultural professional</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>environmental and occupational health and hygiene professional</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>A professional that conducts research, improves or develops concepts, theories and operational methods, or applies knowledge relating to the law, social or cultural studies.</t>
+          <t>A health professional that assesses, plans and implements programmes to recognize, monitor and control environmental factors that can potentially affect human health, to ensure safe and healthy working conditions and to prevent disease or injury caused by chemical, physical, radiological and biological agents or ergonomic factors.</t>
         </is>
       </c>
       <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Environmental health officer, Occupational health and safety adviser, Occupational hygienist, Radiation protection expert</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BCIO:010036</t>
+          <t>BCIO:010014</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3887,33 +3865,33 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>librarian, archivist and curator</t>
+          <t>midwifery professional</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that develops and maintains collections of archives, libraries, museums, art galleries and similar establishments.</t>
+          <t>A health professional that plans, manages, provides and evaluates midwifery care services before, during and after pregnancy and childbirth. They provide delivery care for reducing health risks to women and newborn children, working autonomously or in teams with other health care providers.</t>
         </is>
       </c>
       <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Librarian, Archivist,  Curator</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Midwife</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BCIO:010043</t>
+          <t>BCIO:010019</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -3927,33 +3905,33 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>creative and performing artist</t>
+          <t>pharmacist</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that communicates ideas, impressions and facts in a wide range of media to achieve particular effects, interprets a composition such as a musical score or a script to perform or direct the performance, and hosts the presentation of such performance and other media events.</t>
+          <t>A health professional that stores, preserves, compounds and dispenses medicinal products and counsel on the proper use and adverse effects of drugs and medicines following prescriptions issued by medical doctors and other health professionals.</t>
         </is>
       </c>
       <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Visual artist, Musician, Singer, Composer, Dancer, Choreographer, Director, Producer, Actor, Announcer on radio, television and other media</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Dispensing chemist, Hospital pharmacist, Industrial pharmacist, Retail pharmacist</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BCIO:010040</t>
+          <t>BCIO:010023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3967,33 +3945,33 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>religious professional</t>
+          <t>audiologist and speech therapist</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that functions  as a perpetuator of sacred traditions, practices and beliefs. They conduct religious services, celebrate or administer the rites of a religious faith or denomination, provide spiritual and moral guidance and perform other functions associated with the practice of a religion.</t>
+          <t>A health professional  that evaluates, manages and treats physical disorders affecting human hearing, speech, communication and swallowing.</t>
         </is>
       </c>
       <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Bonze, Imam, Minister of religion, Poojari, Priest, Rabbi</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Audiologist, Language therapist, Speech pathologist, Speech therapist</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BCIO:010042</t>
+          <t>BCIO:010012</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -4007,33 +3985,29 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>linguist</t>
+          <t>nursing and midwifery professional</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that translates or interprets from one language into another.</t>
+          <t>A health professional that provides treatment and care services for people who are physically or mentally ill, disabled or infirm, and those with potential risks to health including before, during and after childbirth. They assume responsibility for the planning, management and evaluation of the care of patients, including the supervision of other health care workers, working autonomously or in teams with medical doctors and others in the practical application of preventive and curative measures.</t>
         </is>
       </c>
       <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
       <c r="R96" t="inlineStr">
         <is>
-          <t>Interpretator; other linguist</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BCIO:010035</t>
+          <t>BCIO:010022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -4047,33 +4021,33 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>legal professional</t>
+          <t>dietician and nutritionist</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conducts research on legal problems, advises clients on legal aspects of problems, pleads cases or conducts prosecutions in courts of law, presides over judicial proceedings in courts of law and draft laws and regulations.</t>
+          <t>A health professional  that assesses, plans and implements programmes to enhance the impact of food and nutrition on human health.</t>
         </is>
       </c>
       <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Lawyer, Judge, Coroner</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>Clinical dietician, Food service dietician, Nutritionist, Public health nutritionist, Sports nutritionist</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BCIO:010041</t>
+          <t>BCIO:010025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4084,36 +4058,36 @@
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>author and journalist</t>
-        </is>
-      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>teaching professional</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conceives and creates literary works, and interprets and communicates news and public affairs through the media.</t>
+          <t>A professional that teaches the theory and practice of one or more disciplines at different educational levels.</t>
         </is>
       </c>
       <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Author, Writer, Journalist, Translator, News anchor</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Education Methods Specialist, Other Language Teacher, Information Technology Teacher, Private Tutor, School Counsellor, Student Advisor</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BCIO:010037</t>
+          <t>BCIO:010029</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4127,33 +4101,29 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>social professional</t>
+          <t>primary school teacher</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conducts research, improves or develops concepts, theories and operational methods or applies knowledge relating to psychology, sociology, philosophy, politics, economics, sociology, anthropology, history and other social sciences, or provides social services to meet the needs of individuals and families in a community.</t>
+          <t>A teaching professional that teaches teach a range of subjects at the primary education level.</t>
         </is>
       </c>
       <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Economist, Sociologist, Anthropologist, Philosopher, Historian, Political Scientist</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BCIO:010039</t>
+          <t>BCIO:010028</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4165,35 +4135,35 @@
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>social work and counselling professional</t>
-        </is>
-      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>secondary education teacher</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
-          <t>A social professional that provides advice and guidance to individuals, families, groups, communities and organizations in response to social and personal difficulties. They assist clients to develop skills and access resources and support services needed to respond to issues arising from unemployment, poverty, disability, addiction, criminal and delinquent behaviour, marital and other problems.</t>
+          <t>A teaching professional that teaches one or more subjects at secondary education level.</t>
         </is>
       </c>
       <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Counsellor, Addictions counsellor, Bereavement counsellor, Child and youth counsellor, District social welfare officer, Family counsellor, Marriage counsellor, Parole officer, Probation officer, Sexual assault counsellor, Social worker, Women’s welfare organizer</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Secondary school teacher, High school teacher</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BCIO:010038</t>
+          <t>BCIO:010031</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4205,35 +4175,35 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>psychologist</t>
-        </is>
-      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>special needs teacher</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
-          <t>A social professional that studies the mental processes and behaviour of human beings as individuals or in groups, and applies this knowledge to promote personal, social, educational or occupational adjustment and development.</t>
+          <t>A teaching professional that teaches children, young persons or adults with physical or intellectual special needs.</t>
         </is>
       </c>
       <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
       <c r="R101" t="inlineStr">
         <is>
-          <t>Clinical psychologist, Counselling psychologist, Educational psychologist, Forensic psychologist, Health psychologist, Neuropsychologist, Organizational psychologist, Psychotherapist, Sport and exercise psychologist</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Learning disabilities special education teacher, Learning support teacher, Remedial teacher, Teacher of gifted children, Teacher of the hearing impaired, Teacher of the sight impaired</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BCIO:010008</t>
+          <t>BCIO:010027</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4244,36 +4214,36 @@
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>health professional</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>vocational education teacher</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
-          <t>A professional that improves or develops concepts, theories and operational method, and applied scientific knowledge relating to medicine, nursing, dentistry, veterinary medicine, pharmacy, and promotion of health.</t>
+          <t>A teaching professional that teaches or instructs vocational or occupational subjects in adult and further education institutions and to senior students in secondary schools and colleges.</t>
         </is>
       </c>
       <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
       <c r="R102" t="inlineStr">
         <is>
-          <t>Health professional; Arts therapist, Chiropractor, Dance and movement therapist, Occupational therapist, Osteopath, Podiatrist, Recreational therapist, Health staff, Clinic staff</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>Automotive technology instructor, Cosmetology instructor, Vocational education teacher</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BCIO:010020</t>
+          <t>BCIO:010032</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4287,33 +4257,33 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>environmental and occupational health and hygiene professional</t>
+          <t>music teacher</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
-          <t>A health professional that assesses, plans and implements programmes to recognize, monitor and control environmental factors that can potentially affect human health, to ensure safe and healthy working conditions and to prevent disease or injury caused by chemical, physical, radiological and biological agents or ergonomic factors.</t>
+          <t>A teaching professional that teaches students in the practice, theory and performance of music in private or small group tuition or within mainstream educational institutions.</t>
         </is>
       </c>
       <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Environmental health officer, Occupational health and safety adviser, Occupational hygienist, Radiation protection expert</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Guitar teacher (private tuition), Piano teacher (private tuition), Singing teacher (private tuition), Violin teacher (private tuition)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BCIO:010019</t>
+          <t>BCIO:010026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4327,33 +4297,33 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>pharmacist</t>
+          <t>university and higher education teacher</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t>A health professional that stores, preserves, compounds and dispenses medicinal products and counsel on the proper use and adverse effects of drugs and medicines following prescriptions issued by medical doctors and other health professionals.</t>
+          <t>A teaching professional that prepares and delivers lectures and conduct tutorials in one or more subjects within a prescribed course of study at a university or other higher educational institution. They conduct research, and prepare scholarly papers and books.</t>
         </is>
       </c>
       <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Dispensing chemist, Hospital pharmacist, Industrial pharmacist, Retail pharmacist</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>Higher education lecturer, Professor, University lecturer, University tutor</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BCIO:010024</t>
+          <t>BCIO:010030</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4367,33 +4337,33 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>optometrist and ophthalmic optician</t>
+          <t>early childhood educator</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
-          <t>A health professional  that provides diagnosis, management and treatment services for disorders of the eyes and visual system.</t>
+          <t>A teaching professional that promotes the social, physical, and intellectual development of children below primary school age through the provision of educational and play activities.</t>
         </is>
       </c>
       <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
       <c r="R105" t="inlineStr">
         <is>
-          <t>Ophthalmic optician , Optometrist, Orthoptist</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>Early childhood educator, Pre-school teacher</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BCIO:010022</t>
+          <t>BCIO:010033</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4407,33 +4377,33 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>dietician and nutritionist</t>
+          <t>arts teacher</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
-          <t>A health professional  that assesses, plans and implements programmes to enhance the impact of food and nutrition on human health.</t>
+          <t>A teaching professional  that teaches students in the practice, theory and performance of dance, drama, visual and other arts (excluding music) in private or small group tuition or within mainstream educational institutions.</t>
         </is>
       </c>
       <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
       <c r="R106" t="inlineStr">
         <is>
-          <t>Clinical dietician, Food service dietician, Nutritionist, Public health nutritionist, Sports nutritionist</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>Dance teacher (private tuition), Drama teacher (private tuition), Painting teacher (private tuition), Sculpture teacher (private tuition)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BCIO:010017</t>
+          <t>BCIO:010044</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4444,36 +4414,32 @@
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>veterinarian</t>
-        </is>
-      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>technician and associate professional</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
-          <t>A health professional that diagnoses, prevents and treats diseases, injuries and dysfunctions of animals.</t>
+          <t>A professional that performs technical and related tasks connected with research and the application of scientific or artistic concepts and operational methods, and government or business regulations.</t>
         </is>
       </c>
       <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
       <c r="R107" t="inlineStr">
         <is>
-          <t>Animal pathologist, Veterinarian, Veterinary epidemiologist, Veterinary intern, Veterinary surgeon</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BCIO:010012</t>
+          <t>BCIO:010065</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4487,29 +4453,33 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>nursing and midwifery professional</t>
+          <t>artistic, cultural and culinary associate professional</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
-          <t>A health professional that provides treatment and care services for people who are physically or mentally ill, disabled or infirm, and those with potential risks to health including before, during and after childbirth. They assume responsibility for the planning, management and evaluation of the care of patients, including the supervision of other health care workers, working autonomously or in teams with medical doctors and others in the practical application of preventive and curative measures.</t>
+          <t>A technician and associate professional that combines creative skills and technical and cultural knowledge in creative media or food.</t>
         </is>
       </c>
       <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q108" t="inlineStr"/>
-      <c r="R108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>Photographer, Interior designers and decorator, Gallery, museum and library technician, Chef</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BCIO:010009</t>
+          <t>BCIO:010061</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4523,33 +4493,33 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>medical doctor</t>
+          <t>sport and fitness worker</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
-          <t>A health professional that studies, diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans through the application of modern medicine. They plan, supervise and evaluate the implementation of care and treatment plans by other health care providers, and conduct medical education and research activities.</t>
+          <t>A technician and associate professional that prepares for and competes in sporting events for financial gain, trains amateur and professional sportsmen and women to enhance performance, promotes participation and standards in sport, organises and officiates sporting events, or provides instruction, training and supervision for various forms of exercise and other recreational activities.</t>
         </is>
       </c>
       <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
       <c r="R109" t="inlineStr">
         <is>
-          <t>District medical doctor-therapist, family medical practitioner, general practitioner, medical doctor (general), medical officer (general), physician (general), primary health care physician, resident medical officer specializing in general practice</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>physical activity professional, exercise physiologist, exercise therapist, exercise specialist</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BCIO:010010</t>
+          <t>BCIO:010064</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4564,32 +4534,32 @@
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>generalist medical practitioner</t>
+          <t>fitness and recreation instructor and programme leader</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
-          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments and maintains general health in humans through application of modern medicine. They do not limit their practice to certain disease categories or methods of treatment, and may assume responsibility for the provision of continuing and comprehensive medical care to individuals, families and communities.</t>
+          <t>A sport and fitness worker that leads, guides and instructs groups and individuals in recreational, fitness or outdoor adventure activities.</t>
         </is>
       </c>
       <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
       <c r="R110" t="inlineStr">
         <is>
-          <t>Primary care physician, family doctor, GP</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>Aerobics instructor, Fitness instructor, Horse riding instructor, Outdoor adventure guide, Personal trainer, Sailing instructor, Underwater diving instructor</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BCIO:010011</t>
+          <t>BCIO:010062</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4604,32 +4574,32 @@
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>specialist medical practitioner</t>
+          <t>athlete and sports player</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
-          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans, using specialized testing, diagnostic, medical, surgical, physical and psychiatric techniques through application of the principles and procedures of modern medicine. They specialize in certain disease categories, types of patient or methods of treatment and may conduct medical education and research in their chosen areas of specialization.</t>
+          <t>A sport and fitness worker that participates in competitive sporting events. They train and compete, either individually or as part of a team, in their chosen sport.</t>
         </is>
       </c>
       <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
       <c r="R111" t="inlineStr">
         <is>
-          <t>Anaesthetist, Cardiologist, Emergency medicine specialist, Gynaecologist, Obstetrician, Ophthalmologist, Paediatrician, Pathologist, Preventive medicine specialist, Psychiatrist, Radiation oncologist, Radiologist, Resident medical officer in specialist training, Specialist medical practitioner (public health), Specialist physician (internal medicine), Specialist physician (nuclear medicine), Surgeon</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>Athlete, Bicycle racer, Boxer, Chess player , Footballer, Golfer, Hockey player, Jockey, Poker player, Racing driver, Skier, Tennis player, Wrestler</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BCIO:010014</t>
+          <t>BCIO:010063</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4641,35 +4611,35 @@
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>midwifery professional</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>sports coach, instructor and official</t>
+        </is>
+      </c>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr">
         <is>
-          <t>A health professional that plans, manages, provides and evaluates midwifery care services before, during and after pregnancy and childbirth. They provide delivery care for reducing health risks to women and newborn children, working autonomously or in teams with other health care providers.</t>
+          <t>A sport and fitness worker that works with amateur and professional sportspersons to enhance performance and encourage greater participation in sport, and organizes and officiates in sporting events according to established rules.</t>
         </is>
       </c>
       <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
       <c r="R112" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>Referee, Ski instructor, Sports coach, Sports official, Swimming instructor</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BCIO:010015</t>
+          <t>BCIO:010058</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4683,33 +4653,33 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>traditional and complementary medicine professional</t>
+          <t>legal and related associate professional</t>
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
-          <t>A health professional that examines patients, prevents and treats illness, disease, injury and other physical and mental impairments and maintains general health in humans. They do this by applying knowledge, skills and practices acquired through extensive study of the theories, beliefs and experiences originating in specific cultures.</t>
+          <t>A technician and associate professional that performs support functions in courts of law or in law offices, provide services related to such legal matters as insurance contracts, the transferring of property and the granting of loans and other financial transactions, or conduct investigations for clients.</t>
         </is>
       </c>
       <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
       <c r="R113" t="inlineStr">
         <is>
-          <t>Acupuncturist, Ayurvedic practitioner,  Chinese herbal medicine practitioner, Homeopath, Naturopath, Unani practitioner</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>Bailiff, Judge’s clerk, Conveyancing clerk, Court clerk, Justice of the peace, Law clerk, Legal assistant, Paralegal, Private detective, Title searcher</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BCIO:010023</t>
+          <t>BCIO:010060</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -4723,33 +4693,33 @@
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>audiologist and speech therapist</t>
+          <t>religious associate professional</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
-          <t>A health professional  that evaluates, manages and treats physical disorders affecting human hearing, speech, communication and swallowing.</t>
+          <t>A technician and associate professional that provides support to ministers of religion or to a religious community, undertake religious works, preach and propagate the teachings of a particular religion and endeavour to improve well-being through the power of faith and spiritual advice.</t>
         </is>
       </c>
       <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
       <c r="R114" t="inlineStr">
         <is>
-          <t>Audiologist, Language therapist, Speech pathologist, Speech therapist</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>Faith healer, Lay preacher, Monk, Nun</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BCIO:010021</t>
+          <t>BCIO:010057</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -4763,33 +4733,33 @@
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>physiotherapist</t>
+          <t>business and administration associate professional</t>
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
-          <t>A health professional  that assesses, plans and implements rehabilitative programmes that improve or restore human motor functions, maximize movement ability, relieve pain syndromes, and treat or prevent physical challenges associated with injuries, diseases and other impairments.</t>
+          <t>A technician and associate professional that performs mostly technical tasks connected with the practical application of knowledge relating to financial accounting and transaction matters, mathematical calculations, human resource development, selling and buying financial instruments, specialized secretarial tasks and enforcing or applying government rules.</t>
         </is>
       </c>
       <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
       <c r="R115" t="inlineStr">
         <is>
-          <t>Geriatric physical therapist, Manipulative therapist, Orthopaedic physical therapist, Paediatric physical therapist, Physical therapist, Physiotherapist</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>Financial and Mathematical associate professional, Sales and purchasing agent, Broker, Business Services Agent, Administrative and Specialized Secretary, Government regulatory associate professional, Medical secretary</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BCIO:010016</t>
+          <t>BCIO:010045</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4803,33 +4773,33 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>paramedical practitioner</t>
+          <t>health associate professional</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
-          <t>A health professional that provides advisory, diagnostic, curative and preventive medical services more limited in scope and complexity than those carried out by medical doctors. They work autonomously or with limited supervision of medical doctors, and apply advanced clinical procedures for treating and preventing diseases, injuries and other physical or mental impairments common to specific communities.</t>
+          <t>A technician and associate professional that performs technical and practical tasks to support diagnosis and treatment of illness, disease, injuries and impairments in humans or animals, and supports the implementation of health care usually established by medical, veterinary, nursing and other health professionals.</t>
         </is>
       </c>
       <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
       <c r="R116" t="inlineStr">
         <is>
-          <t>Advanced care paramedic, Clinical officer (paramedical), Feldscher, Primary care paramedic, Surgical technician</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>Veterinary Technician</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BCIO:010018</t>
+          <t>BCIO:010051</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4841,35 +4811,35 @@
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>dentist</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>dental assistant and therapist</t>
+        </is>
+      </c>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
-          <t>A health professional that diagnoses treats and prevents diseases, injuries and abnormalities of the teeth, mouth, jaws and associated tissues by applying the principles and procedures of modern dentistry.</t>
+          <t>A health associate professional that provides basic dental care services for the prevention and treatment of diseases and disorders of the teeth and mouth, according to care plans and procedures established by a dentist or other oral health professional.</t>
         </is>
       </c>
       <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
       <c r="R117" t="inlineStr">
         <is>
-          <t>Dental practitioner, Dental surgeon, Dentist, Endodontist, Oral and maxillofacial surgeon, Oral pathologist, Orthodontist, Paedodontist, Periodontist, Prosthodontist, Stomatologist</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>Dental assistant, Dental hygienist , Dental therapist</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BCIO:010013</t>
+          <t>BCIO:010056</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4881,35 +4851,35 @@
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>nursing professional</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>ambulance worker</t>
+        </is>
+      </c>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
-          <t>A health professional that provides treatment, support and care services for people who are in need of nursing care due to the effects of ageing, injury, illness or other physical or mental impairment, or potential risks to health.</t>
+          <t>A health associate professional that provides emergency health care to patients who are injured, sick, infirm or otherwise physically or mentally impaired prior to and during transport to medical facilities.</t>
         </is>
       </c>
       <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
       <c r="R118" t="inlineStr">
         <is>
-          <t>Clinical nurse consultant, District nurse, Nurse anaesthetist, Nurse educator, Nurse practitioner, Operating theatre nurse, Professional nurse, Public health nurse, Specialist nurse, Nursing Counsellor, Study Nurse</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>Ambulance officer, Ambulance paramedic, Emergency medical technician, Emergency paramedic</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BCIO:010067</t>
+          <t>BCIO:010050</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -4919,37 +4889,37 @@
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>clerical support worker</t>
-        </is>
-      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>traditional and complementary medicine associate professional</t>
+        </is>
+      </c>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
-          <t>An occupational role that records, organizes, stores, computes and retrieves information, and performs a number of clerical duties in connection with money-handling operations, travel arrangements, requests for information, and appointments.</t>
+          <t>A health associate professional that prevents and treats human physical and mental illnesses, disorders and injuries using herbal and other therapies based on theories, beliefs and experiences originating in specific cultures. They administer treatments using traditional techniques and medicaments, either acting independently or according to therapeutic care plans established by a traditional medicine or other health professional.</t>
         </is>
       </c>
       <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
       <c r="R119" t="inlineStr">
         <is>
-          <t>General and Keyboard Clerk, customers Services Clerk, Numerical and Material Recording Clerk</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>Acupuncture technician, Ayurvedic technician, Bonesetter, Herbalist , Homeopathy technician, Scraping and cupping therapist, Village healer, Witch doctor</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BCIO:010082</t>
+          <t>BCIO:010053</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -4959,37 +4929,37 @@
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>armed forces occupation</t>
-        </is>
-      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>physiotherapy technician and assistant</t>
+        </is>
+      </c>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr">
         <is>
-          <t>An occupational role that includes all jobs held by members of the armed forces.</t>
+          <t>A health associate professional that provides physical therapeutic treatments to patients in circumstances where functional movement is threatened by injury, disease or impairment. Therapies are usually provided according to rehabilitative plans established by a physiotherapist or other health professional.</t>
         </is>
       </c>
       <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
       <c r="R120" t="inlineStr">
         <is>
-          <t>Admiral, Air commodore, Air marshal, Airman, Brigadier (army), Bombardier, Captain (air force), Captain (army), Captain (navy), Colonel (army), Corporal,  Field marshal, Flight lieutenant (air force), Flying officer (military), General (army), Gunner, Group captain, (air force), Lieutenant (army), Major (army), Midshipman, Naval officer (military) , Navy commander, Officer cadet (armed forces), Paratrooper, Rifleman, Sergeant (army), Second lieutenant (army), Seaman, Squadron leader, Sublieutenant (navy), Wing commander</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>Acupressure therapist, Electrotherapist, Hydrotherapist, Massage therapist, Physical rehabilitation technician, Physiotherapy technician, Shiatsu therapist</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BCIO:010078</t>
+          <t>BCIO:010047</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -4999,37 +4969,37 @@
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>craft and related trades worker</t>
-        </is>
-      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>nursing and midwifery associate professional</t>
+        </is>
+      </c>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr">
         <is>
-          <t>An occupational role that applies specific technical and practical knowledge and skills to construct and maintain buildings, machinery, equipment or tools, carries out printing work, and produces or processes foodstuffs, textiles and wooden, metal and other articles, including handicraft goods.</t>
+          <t>A health associate professional that provides basic nursing and personal care for people who are physically or mentally ill, disabled or infirm, and for others in need of care due to potential risks to health including before, during and after childbirth. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing, midwifery and other health professionals.</t>
         </is>
       </c>
       <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
       <c r="R121" t="inlineStr">
         <is>
-          <t>Building Trade Worker, Metal Workers, Machinery Worker, Handicraft Worker, Printing Worker, Electrical Equipment Installers and Repairer, Electronics and Telecommunications Installer and Repairer, Food Processing Worker, Woodworker, Tobacco Product Maker</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>Practice assistant, Quit Smoking Counsellor, Health educator, Dispensing Optician, Information Technician</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BCIO:010005</t>
+          <t>BCIO:010048</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -5039,37 +5009,37 @@
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>manager</t>
-        </is>
-      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>nursing associate professional</t>
+        </is>
+      </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>An occupational role of source that manages, plans and coordinates the overall activities of enterprises, governments and other organisations.</t>
+          <t>A nursing and midwifery associate professional that provides basic nursing and personal care for people in need of such care due to effects of ageing, illness, injury, or other physical or mental impairment. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing and other health professionals.</t>
         </is>
       </c>
       <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
       <c r="R122" t="inlineStr">
         <is>
-          <t>Chief Executive Officers; Administrative Managers;  Commercial Managers</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>Assistant nurse, Associate professional nurse, Enrolled nurse, Practical nurse</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BCIO:010081</t>
+          <t>BCIO:010049</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -5079,37 +5049,37 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>elementary occupation</t>
-        </is>
-      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>midwifery associate professional</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>An occupational role that involves the performance of simple and routine tasks which may require the use of hand-held tools and considerable physical effort.</t>
+          <t>A nursing and midwifery associate professional that provides basic health care and advice before, during and after pregnancy and childbirth. They implement care, treatment and referral plans usually established by medical, midwifery and other health professionals.</t>
         </is>
       </c>
       <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
       <c r="R123" t="inlineStr">
         <is>
-          <t>Cleaner, Labourer, Food Preparation Assistant, Street and Related Services Worker, Street Vendor (excluding Food), Refuse Worker</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>Assistant midwife, Traditional midwife</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BCIO:010083</t>
+          <t>BCIO:010052</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -5119,37 +5089,37 @@
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>researcher</t>
-        </is>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>community health worker</t>
+        </is>
+      </c>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr">
         <is>
-          <t>An occupational role that is a researcher but unclear what discipline.</t>
+          <t>A health associate professional that provides health education, referral and follow-up, case management, basic preventive health care and home visiting services to specific communities. They provide support and assistance to individuals and families in navigating the health and social services system.</t>
         </is>
       </c>
       <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
       <c r="R124" t="inlineStr">
         <is>
-          <t>researcher, research assistant, investigator</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>Community health aide, Community health promoter, Community health worker, Village health worker, outreach worker, health worker</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BCIO:010000</t>
+          <t>BCIO:010046</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -5157,35 +5127,39 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>behaviour change intervention source</t>
-        </is>
-      </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>medical and pharmaceutical technician</t>
+        </is>
+      </c>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr">
         <is>
-          <t>A role played by a person, population or organisation that provides a BCI.</t>
+          <t>A health associate professional that performs technical tasks to assist in diagnosis and treatment of illness, disease, injuries and impairments.</t>
         </is>
       </c>
       <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q125" t="inlineStr"/>
-      <c r="R125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>Medical imaging and therapeutic equipment technician, Medical and Pathology laboratory technician, Pharmaceutical technician, Medical and dental prosthetic technician</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BCIO:010133</t>
+          <t>BCIO:010055</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -5194,34 +5168,39 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>source role related to intervention</t>
-        </is>
-      </c>
+      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>environmental and occupational health inspector and associate</t>
+        </is>
+      </c>
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
-          <t>A BCI source whose occupational or voluntary role is focused on delivery of the behaviour change intervention.</t>
+          <t>A health associate professional that investigates the implementation of rules and regulations relating to environmental factors that may affect human health, safety in the 
+workplace, and safety of processes for the production of goods and services. They may implement and evaluate programmes to restore or improve safety and sanitary conditions under the supervision of a health professional.</t>
         </is>
       </c>
       <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q126" t="inlineStr"/>
-      <c r="R126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>Food sanitation and safety inspector, Health inspector, Occupational health and safety inspector, Pollution inspector, Product safety inspector, Sanitarian, Sanitary inspector</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BCIO:010138</t>
+          <t>BCIO:010054</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -5230,34 +5209,38 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>organisational source role</t>
-        </is>
-      </c>
+      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>medical assistant</t>
+        </is>
+      </c>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
-          <t>A BCI source role that is borne by an organisation.</t>
+          <t>A health associate professional that performs basic clinical and administrative tasks to support patient care under the direct supervision of a medical practitioner or other health professional.</t>
         </is>
       </c>
       <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q127" t="inlineStr"/>
-      <c r="R127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>Clinical assistant, Medical assistant, Ophthalmic assistant</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BCIO:010134</t>
+          <t>BCIO:010059</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5266,34 +5249,38 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>source involved in development of intervention</t>
-        </is>
-      </c>
+      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>social work associate professional</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr">
         <is>
-          <t>A BCI source that is involved in the development of intervention content.</t>
+          <t>A technician and associate professional that implements social assistance programmes and community services and assist clients to deal with personal and social problems.</t>
         </is>
       </c>
       <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q128" t="inlineStr"/>
-      <c r="R128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>Community development worker, Community services worker, Crisis intervention worker, Disability services worker, Family services worker, Life skills instructor, Mental health support worker, Welfare support worker, Women’s shelter supervisor, Youth services worker</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BCIO:010135</t>
+          <t>BCIO:010066</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -5303,33 +5290,37 @@
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>source involved in co-production of intervention</t>
-        </is>
-      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>information and communications technician</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
-          <t>A source involved in development of intervention that has developed the intervention content in collaboration with key stakeholders such as patients or community members.</t>
+          <t>A technician and associate professional that provides support for the day to day running of computer systems, communication systems and networks, broadcast images and sound, telecommunication signals on land, sea or in aircraft.</t>
         </is>
       </c>
       <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q129" t="inlineStr"/>
-      <c r="R129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>Information and Communications Technology Operations and User Support Technician, Telecommunications and Broadcasting Technician</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BCIO:010001</t>
+          <t>BCIO:010034</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5338,387 +5329,394 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>person source role</t>
-        </is>
-      </c>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>legal, social and cultural professional</t>
+        </is>
+      </c>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr">
         <is>
-          <t>A behaviour change intervention source role that inheres in a person.</t>
+          <t>A professional that conducts research, improves or develops concepts, theories and operational methods, or applies knowledge relating to the law, social or cultural studies.</t>
         </is>
       </c>
       <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q130" t="inlineStr"/>
-      <c r="R130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BCIO:010123</t>
+          <t>BCIO:010041</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>expertise discipline</t>
-        </is>
-      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>author and journalist</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr">
         <is>
-          <t>An attribute that is a field of knowledge or practice.</t>
+          <t>A legal, social and cultural professional that conceives and creates literary works, and interprets and communicates news and public affairs through the media.</t>
         </is>
       </c>
       <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
       <c r="R131" t="inlineStr">
         <is>
-          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
-        </is>
-      </c>
-      <c r="T131" t="inlineStr">
-        <is>
-          <t>The division of expertise into different disciplines or fields is complex and depends on historical, social and structural factors.</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>Author, Writer, Journalist, Translator, News anchor</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BCIO:010124</t>
+          <t>BCIO:010042</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>discipline of pre-existing knowledge or skill</t>
-        </is>
-      </c>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>linguist</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr">
         <is>
-          <t>The expertise discipline in which the person source has acquired their pre-existing knowledge and skills.</t>
+          <t>A legal, social and cultural professional that translates or interprets from one language into another.</t>
         </is>
       </c>
       <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
       <c r="R132" t="inlineStr">
         <is>
-          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>Interpretator; other linguist</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BCIO:010093</t>
+          <t>BCIO:010036</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>discipline of current programme of study or training</t>
-        </is>
-      </c>
+      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>librarian, archivist and curator</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr">
         <is>
-          <t>An expertise discipline of the programme of study currently undertaken by the bearer of a student or trainee role.</t>
+          <t>A legal, social and cultural professional that develops and maintains collections of archives, libraries, museums, art galleries and similar establishments.</t>
         </is>
       </c>
       <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
       <c r="R133" t="inlineStr">
         <is>
-          <t>psychology, medicine, hairdressing</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>Librarian, Archivist,  Curator</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BCIO:010108</t>
+          <t>BCIO:010035</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>socio demographic attribute of person source</t>
-        </is>
-      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>legal professional</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr">
         <is>
-          <t>A social or demographic characteristic of a human being who is the bearer of a person source role.</t>
+          <t>A legal, social and cultural professional that conducts research on legal problems, advises clients on legal aspects of problems, pleads cases or conducts prosecutions in courts of law, presides over judicial proceedings in courts of law and draft laws and regulations.</t>
         </is>
       </c>
       <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q134" t="inlineStr"/>
-      <c r="R134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>Lawyer, Judge, Coroner</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BCIO:010115</t>
+          <t>BCIO:010040</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>religious group membership of person source</t>
-        </is>
-      </c>
+      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>religious professional</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is a religious group to which an individual identifies as belonging, where a religious group is a group of people characterised by the practice of a common religion.</t>
+          <t>A legal, social and cultural professional that functions  as a perpetuator of sacred traditions, practices and beliefs. They conduct religious services, celebrate or administer the rites of a religious faith or denomination, provide spiritual and moral guidance and perform other functions associated with the practice of a religion.</t>
         </is>
       </c>
       <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
       <c r="R135" t="inlineStr">
         <is>
-          <t>Muslim, Christian, Hindu, Sikh, Buddhist, Judaism</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>Bonze, Imam, Minister of religion, Poojari, Priest, Rabbi</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BCIO:010119</t>
+          <t>BCIO:010037</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>psychological influence on intervention delivery of person source</t>
-        </is>
-      </c>
+      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>social professional</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is their existing psychological attributes related to or potentially affecting the target behaviour.</t>
+          <t>A legal, social and cultural professional that conducts research, improves or develops concepts, theories and operational methods or applies knowledge relating to psychology, sociology, philosophy, politics, economics, sociology, anthropology, history and other social sciences, or provides social services to meet the needs of individuals and families in a community.</t>
         </is>
       </c>
       <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q136" t="inlineStr"/>
-      <c r="R136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>Economist, Sociologist, Anthropologist, Philosopher, Historian, Political Scientist</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BCIO:010109</t>
+          <t>BCIO:010038</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>age of person source</t>
-        </is>
-      </c>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>psychologist</t>
+        </is>
+      </c>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is a time quality inhering in a bearer by virtue of how long the bearer has existed.</t>
+          <t>A social professional that studies the mental processes and behaviour of human beings as individuals or in groups, and applies this knowledge to promote personal, social, educational or occupational adjustment and development.</t>
         </is>
       </c>
       <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q137" t="inlineStr"/>
-      <c r="R137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>Clinical psychologist, Counselling psychologist, Educational psychologist, Forensic psychologist, Health psychologist, Neuropsychologist, Organizational psychologist, Psychotherapist, Sport and exercise psychologist</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BCIO:010118</t>
+          <t>BCIO:010039</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>target behaviour of person source</t>
-        </is>
-      </c>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>social work and counselling professional</t>
+        </is>
+      </c>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is their amount or experience of the intervention’s target behaviour.</t>
+          <t>A social professional that provides advice and guidance to individuals, families, groups, communities and organizations in response to social and personal difficulties. They assist clients to develop skills and access resources and support services needed to respond to issues arising from unemployment, poverty, disability, addiction, criminal and delinquent behaviour, marital and other problems.</t>
         </is>
       </c>
       <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
       <c r="R138" t="inlineStr">
         <is>
-          <t>source is highly physically active</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>Counsellor, Addictions counsellor, Bereavement counsellor, Child and youth counsellor, District social welfare officer, Family counsellor, Marriage counsellor, Parole officer, Probation officer, Sexual assault counsellor, Social worker, Women’s welfare organizer</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BCIO:010110</t>
+          <t>BCIO:010043</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>gender of person source</t>
-        </is>
-      </c>
+      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>creative and performing artist</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is an individual's perception of having a particular gender, which may or may not correspond with their birth sex.</t>
+          <t>A legal, social and cultural professional that communicates ideas, impressions and facts in a wide range of media to achieve particular effects, interprets a composition such as a musical score or a script to perform or direct the performance, and hosts the presentation of such performance and other media events.</t>
         </is>
       </c>
       <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
       <c r="R139" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>Visual artist, Musician, Singer, Composer, Dancer, Choreographer, Director, Producer, Actor, Announcer on radio, television and other media</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BCIO:010113</t>
+          <t>BCIO:010005</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5726,170 +5724,170 @@
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>other gender</t>
-        </is>
-      </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr">
         <is>
-          <t>A gender of person source that reports not belonging to the cultural gender role distinctions of either male or female.</t>
+          <t>An occupational role of source that manages, plans and coordinates the overall activities of enterprises, governments and other organisations.</t>
         </is>
       </c>
       <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
       <c r="R140" t="inlineStr">
         <is>
-          <t>non-binary, transexual</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>Chief Executive Officers; Administrative Managers;  Commercial Managers</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BCIO:010117</t>
+          <t>BCIO:010082</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>health status of person source</t>
-        </is>
-      </c>
+      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>armed forces occupation</t>
+        </is>
+      </c>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that represents their mental or physical condition.</t>
+          <t>An occupational role that includes all jobs held by members of the armed forces.</t>
         </is>
       </c>
       <c r="O141" t="inlineStr"/>
-      <c r="P141" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
       <c r="R141" t="inlineStr">
         <is>
-          <t>diabetes, cancer, depression, obesity, overweight</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>Admiral, Air commodore, Air marshal, Airman, Brigadier (army), Bombardier, Captain (air force), Captain (army), Captain (navy), Colonel (army), Corporal,  Field marshal, Flight lieutenant (air force), Flying officer (military), General (army), Gunner, Group captain, (air force), Lieutenant (army), Major (army), Midshipman, Naval officer (military) , Navy commander, Officer cadet (armed forces), Paratrooper, Rifleman, Sergeant (army), Second lieutenant (army), Seaman, Squadron leader, Sublieutenant (navy), Wing commander</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BCIO:010114</t>
+          <t>BCIO:010079</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>ethnic group membership of person source</t>
-        </is>
-      </c>
+      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>plant and machine operator</t>
+        </is>
+      </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is the ethnic group to which an individual identifies as belonging, where an ethic group is a population whose members have a common heritage that is real or presumed such as common culture, language, religion, behaviour or biological trait.</t>
+          <t>An occupational role that operates and monitors industrial and agricultural machinery and equipment on the spot or by remote control, or drives and operates trains, motor vehicles and mobile machinery and equipment.</t>
         </is>
       </c>
       <c r="O142" t="inlineStr"/>
-      <c r="P142" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
       <c r="R142" t="inlineStr">
         <is>
-          <t>black, white, Indian, Chinese, Somalian</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>Stationary Plant and Machine Operator, Driver, Mobile Plant Operator</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BCIO:010116</t>
+          <t>BCIO:010078</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>language proficiency of person source</t>
-        </is>
-      </c>
+      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>craft and related trades worker</t>
+        </is>
+      </c>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is an individual’s ability to speak or perform in the intervention language.</t>
+          <t>An occupational role that applies specific technical and practical knowledge and skills to construct and maintain buildings, machinery, equipment or tools, carries out printing work, and produces or processes foodstuffs, textiles and wooden, metal and other articles, including handicraft goods.</t>
         </is>
       </c>
       <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
       <c r="R143" t="inlineStr">
         <is>
-          <t>fluent, native</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>Building Trade Worker, Metal Workers, Machinery Worker, Handicraft Worker, Printing Worker, Electrical Equipment Installers and Repairer, Electronics and Telecommunications Installer and Repairer, Food Processing Worker, Woodworker, Tobacco Product Maker</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BFO:0000031</t>
+          <t>BFO:0000016</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>generically dependent continuant</t>
-        </is>
-      </c>
+      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
@@ -5897,28 +5895,23 @@
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr">
-        <is>
-          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>IAO:0000030</t>
+          <t>BCIO:010120</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>information content entity</t>
-        </is>
-      </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>expertise of person source</t>
+        </is>
+      </c>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
@@ -5927,27 +5920,35 @@
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr">
         <is>
-          <t>A generically dependent continuant that is about some thing.</t>
-        </is>
-      </c>
+          <t>A disposition that is an expert skill or knowledge held by the source delivering the behaviour change intervention.</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>IAO:0000027</t>
+          <t>BCIO:010121</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>knowledge or skill</t>
+        </is>
+      </c>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
@@ -5955,14 +5956,26 @@
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr">
         <is>
-          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
+          <t>An expertise of person source that is knowledge or skills held in order to deliver the behaviour change intervention.</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>trained (if unclear whether pre-existing or acquired)</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BCIO:010126</t>
+          <t>BCIO:010125</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -5970,39 +5983,35 @@
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>amount of experience</t>
-        </is>
-      </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>acquired knowledge or skill</t>
+        </is>
+      </c>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr">
         <is>
-          <t>A knowledge or skill that is the duration of experience in related domain held by person source.</t>
+          <t>A knowledge or skill that is additional knowledge or skills supplied to the source to allow them to deliver the behaviour change intervention, including educational level and qualifications.</t>
         </is>
       </c>
       <c r="O147" t="inlineStr"/>
-      <c r="P147" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
       <c r="R147" t="inlineStr">
         <is>
-          <t>full-day, 6 years</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BCIO:010106</t>
+          <t>BCIO:010122</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -6010,35 +6019,39 @@
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>number of people delivering intervention to each participant</t>
-        </is>
-      </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>pre-existing knowledge or skill</t>
+        </is>
+      </c>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr">
         <is>
-          <t>A count data item that is the number of providers that an individual participant in the intervention encounters.</t>
+          <t>A knowledge or skill that is already possessed by the source which allows them to deliver the behaviour change intervention, including educational level and qualifications.</t>
         </is>
       </c>
       <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q148" t="inlineStr"/>
-      <c r="R148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree, certification, accredited, qualified</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BCIO:010107</t>
+          <t>BCIO:010127</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -6046,42 +6059,46 @@
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>total number of people able to deliver intervention</t>
-        </is>
-      </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>affiliation to a formal group or organisation</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr">
         <is>
-          <t>A count data item that is the total number of providers that are available and able to deliver the intervention.</t>
+          <t>A pre-existing knowledge or skill that is recognised through affiliation to a formal group or organisation.</t>
         </is>
       </c>
       <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q149" t="inlineStr"/>
-      <c r="R149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>member of British Psychological Society</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BFO:0000004</t>
+          <t>BFO:0000031</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>independent continuant</t>
+          <t>generically dependent continuant</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -6095,14 +6112,14 @@
       <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr">
         <is>
-          <t>A continuant that is a bearer of quality and realizable entity entities, in which other entities inhere and which itself cannot inhere in anything.</t>
+          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BFO:0000040</t>
+          <t>IAO:0000030</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -6110,7 +6127,7 @@
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>material entity</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
@@ -6123,14 +6140,14 @@
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr">
         <is>
-          <t>An &lt;independent continuant&gt; that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+          <t>A generically dependent continuant that is about some thing.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>OGMS:0000087</t>
+          <t>IAO:0000027</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -6139,7 +6156,7 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>extended organism</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="G152" t="inlineStr"/>
@@ -6151,14 +6168,14 @@
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
-          <t>An object aggregate consisting of an organism and all material entities located within the organism, overlapping the organism, or occupying sites formed in part by the organism.</t>
+          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MF:0000016</t>
+          <t>BCIO:010107</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -6168,7 +6185,7 @@
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>human being</t>
+          <t>total number of people able to deliver intervention</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
@@ -6179,22 +6196,22 @@
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr">
         <is>
-          <t>An extended organism that is a member of the species Homo sapiens.</t>
+          <t>A count data item that is the total number of providers that are available and able to deliver the intervention.</t>
         </is>
       </c>
       <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q153" t="inlineStr"/>
-      <c r="R153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BCIO:010002</t>
+          <t>BCIO:010126</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -6202,12 +6219,12 @@
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>person source</t>
-        </is>
-      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>amount of experience</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
@@ -6215,22 +6232,26 @@
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr">
         <is>
-          <t>A person who is the bearer of a behaviour change intervention source role.</t>
+          <t>A knowledge or skill that is the duration of experience in related domain held by person source.</t>
         </is>
       </c>
       <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q154" t="inlineStr"/>
-      <c r="R154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>full-day, 6 years</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BCIO:010095</t>
+          <t>BCIO:010106</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -6238,12 +6259,12 @@
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>family member</t>
-        </is>
-      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>number of people delivering intervention to each participant</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
@@ -6251,195 +6272,167 @@
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr">
         <is>
-          <t>A person who is a member of a group of persons united by blood, or by marriage or other legal arrangement, or by self-identity as belonging to the same family.</t>
+          <t>A count data item that is the number of providers that an individual participant in the intervention encounters.</t>
         </is>
       </c>
       <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q155" t="inlineStr"/>
-      <c r="R155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BCIO:010097</t>
+          <t>BFO:0000003</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
-      <c r="C156" t="inlineStr"/>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>occurrent</t>
+        </is>
+      </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>spouse or partner</t>
-        </is>
-      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr">
         <is>
-          <t>A family member that is an individual who is married or in a committed relationship with another individual.</t>
-        </is>
-      </c>
-      <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q156" t="inlineStr"/>
-      <c r="R156" t="inlineStr">
-        <is>
-          <t>boyfriend, girlfriend, partner, fiance, wife, husband</t>
+          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BCIO:010098</t>
+          <t>BFO:0000015</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>sibling relationship</t>
-        </is>
-      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr">
         <is>
-          <t>A family member that is a family relationship between two persons with at least one shared parent.</t>
-        </is>
-      </c>
-      <c r="O157" t="inlineStr"/>
-      <c r="P157" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q157" t="inlineStr"/>
-      <c r="R157" t="inlineStr">
-        <is>
-          <t>brother, sister, step-brother, step-sister</t>
+          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BCIO:010099</t>
+          <t>BCIO:010130</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>payment of person source</t>
+        </is>
+      </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>child relationship</t>
-        </is>
-      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr">
         <is>
-          <t>A family member that is an offspring relationship from a person to their parent.</t>
+          <t>A process in which a person source is paid or compensated for delivering the intervention.</t>
         </is>
       </c>
       <c r="O158" t="inlineStr"/>
-      <c r="P158" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
       <c r="R158" t="inlineStr">
         <is>
-          <t>daughter, son, step-daughter, step-son</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BCIO:010096</t>
+          <t>BCIO:010132</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>non-monetary payment</t>
+        </is>
+      </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>parent or guardian</t>
-        </is>
-      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr">
         <is>
-          <t>A family member that is a mother, father or legal carer of a child.</t>
+          <t>A payment of person source that is non-monetary compensation given to the source for delivering the intervention.</t>
         </is>
       </c>
       <c r="O159" t="inlineStr"/>
-      <c r="P159" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
       <c r="R159" t="inlineStr">
         <is>
-          <t>mother, father, step-mother, step-father, guardian</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>course credit</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BCIO:050842</t>
+          <t>BCIO:010131</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>monetary payment</t>
+        </is>
+      </c>
       <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>role model for a person</t>
-        </is>
-      </c>
+      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
@@ -6447,38 +6440,37 @@
       <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr">
         <is>
-          <t>A &lt;person&gt; that influences a recipient by being perceived to be similar or admired.</t>
+          <t>A payment of person source that is money, vouchers or valued objects given to the source for delivering the intervention.</t>
         </is>
       </c>
       <c r="O160" t="inlineStr"/>
-      <c r="P160" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q160" t="inlineStr"/>
-      <c r="R160" t="inlineStr"/>
-      <c r="T160" t="inlineStr">
-        <is>
-          <t>This class lies at the intersection between a person and their environment and is defined from the perspective of the person.</t>
+      <c r="P160" t="inlineStr"/>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>paid in cash, vouchers</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>OBI:0000245</t>
+          <t>BCIO:010129</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>organisation</t>
-        </is>
-      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>volunteering of person source</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
@@ -6488,33 +6480,37 @@
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr">
         <is>
-          <t>An entity that can bear roles, has members, and has a set of organization rules. Members of organizations are either organizations themselves or individual people. Members can bear specific organization member roles that are determined in the organization rules. The organization rules also determine how decisions are made on behalf of the organization by the organization members.</t>
+          <t>A process in which a person source delivers the intervention on a voluntary basis without formal compensation.</t>
         </is>
       </c>
       <c r="O161" t="inlineStr"/>
-      <c r="P161" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q161" t="inlineStr"/>
-      <c r="R161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>voluntary basis, volunteering</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BCIO:010139</t>
+          <t>BCIO:010128</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>organisation source</t>
-        </is>
-      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>supervision of person source</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
@@ -6524,17 +6520,21 @@
       <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr">
         <is>
-          <t>An organisation that is the bearer of a behaviour change intervention source role, such as voluntary, public or commercial organisations delivering a behaviour change intervention.</t>
+          <t>A process in which a person source is formally provided, by an individual with appropriate expertise, with corrective and skill-enhancing feedback, regarding the person source’s performance in delivering the intervention.</t>
         </is>
       </c>
       <c r="O162" t="inlineStr"/>
-      <c r="P162" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="Q162" t="inlineStr"/>
-      <c r="R162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>supervised</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Source/BCIO-source-hierarchy.xlsx
+++ b/Source/BCIO-source-hierarchy.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T162"/>
+  <dimension ref="A1:T163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,32 +445,32 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>crossreference</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>subontology</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
         <is>
           <t>synonyms</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>subontology</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>examples</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>comment</t>
         </is>
       </c>
     </row>
@@ -561,14 +561,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BFO:0000004</t>
+          <t>BFO:0000020</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>independent continuant</t>
+          <t>specifically dependent continuant</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -582,14 +582,14 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>A continuant that is a bearer of quality and realizable entity entities, in which other entities inhere and which itself cannot inhere in anything.</t>
+          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BFO:0000040</t>
+          <t>BCIO:010123</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -597,7 +597,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>material entity</t>
+          <t>expertise discipline</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -610,14 +610,31 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>An &lt;independent continuant&gt; that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
-        </is>
-      </c>
+          <t>An attribute that is a field of knowledge or practice.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>The division of expertise into different disciplines or fields is complex and depends on historical, social and structural factors.</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OGMS:0000087</t>
+          <t>BCIO:010093</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -626,7 +643,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>extended organism</t>
+          <t>discipline of current programme of study or training</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -638,26 +655,38 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>An object aggregate consisting of an organism and all material entities located within the organism, overlapping the organism, or occupying sites formed in part by the organism.</t>
-        </is>
-      </c>
+          <t>An expertise discipline of the programme of study currently undertaken by the bearer of a student or trainee role.</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>psychology, medicine, hairdressing</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MF:0000016</t>
+          <t>BCIO:010124</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>human being</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>discipline of pre-existing knowledge or skill</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -666,35 +695,39 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>An extended organism that is a member of the species Homo sapiens.</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>The expertise discipline in which the person source has acquired their pre-existing knowledge and skills.</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:010002</t>
+          <t>BFO:0000017</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>realizable</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>person source</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -702,35 +735,27 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>A person who is the bearer of a behaviour change intervention source role.</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr"/>
+          <t>A specifically dependent continuant  that inheres in continuant  entities and are not exhibited in full at every time in which it inheres in an entity or group of entities. The exhibition or actualization of a realizable entity is a particular manifestation, functioning or process that occurs under certain circumstances.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:010095</t>
+          <t>BFO:0000023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>family member</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -738,22 +763,14 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>A person who is a member of a group of persons united by blood, or by marriage or other legal arrangement, or by self-identity as belonging to the same family.</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr"/>
+          <t>A realizable entity  the manifestation of which brings about some result or end that is not essential to a continuant  in virtue of the kind of thing that it is but that can be served or participated in by that kind of continuant  in some kinds of natural, social or institutional contexts.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:010098</t>
+          <t>BCIO:010003</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -761,39 +778,35 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>personal role of source</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>sibling relationship</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>A family member that is a family relationship between two persons with at least one shared parent.</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
+          <t>A role that inheres in a person source.</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>brother, sister, step-brother, step-sister</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:010097</t>
+          <t>BCIO:010004</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -802,38 +815,38 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>spouse or partner</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>occupational role of source</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>A family member that is an individual who is married or in a committed relationship with another individual.</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
+          <t>A personal role of source that is realised by doing a specified type of work or working in a specified way.</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Interventionist, facilitator, study staff</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>boyfriend, girlfriend, partner, fiance, wife, husband</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:010096</t>
+          <t>BCIO:010005</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -845,7 +858,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>parent or guardian</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -854,26 +867,26 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>A family member that is a mother, father or legal carer of a child.</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
+          <t>An occupational role of source that manages, plans and coordinates the overall activities of enterprises, governments and other organisations.</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Chief Executive Officers; Administrative Managers;  Commercial Managers</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>mother, father, step-mother, step-father, guardian</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:010099</t>
+          <t>BCIO:010067</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -885,7 +898,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>child relationship</t>
+          <t>clerical support worker</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -894,26 +907,26 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>A family member that is an offspring relationship from a person to their parent.</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
+          <t>An occupational role that records, organizes, stores, computes and retrieves information, and performs a number of clerical duties in connection with money-handling operations, travel arrangements, requests for information, and appointments.</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>General and Keyboard Clerk, customers Services Clerk, Numerical and Material Recording Clerk</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>daughter, son, step-daughter, step-son</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:050842</t>
+          <t>BCIO:010077</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -922,287 +935,314 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>role model for a person</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>skilled agricultural, forestry and fishery worker</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>A &lt;person&gt; that influences a recipient by being perceived to be similar or admired.</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
+          <t>An occupational role that grows and harvests plants or animals to provide food, shelter and income for themselves and their households.</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>This class lies at the intersection between a person and their environment and is defined from the perspective of the person.</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Market gardener, Crop grower, Animal Producer, Mixed Crop and Animal Producer, Forestry worker, Fishery worker, Hunter. Subsistence Crop Farmer, Subsistence Livestock Farmer</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:010139</t>
+          <t>BCIO:010068</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>organisation source</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>services and sales worker</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>An organisation that is the bearer of a behaviour change intervention source role, such as voluntary, public or commercial organisations delivering a behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+          <t>An occupational role that provides personal or protective services related to travel, house-keeping, catering, personal care, protection against fire and unlawful acts, or sells goods in retail or markets.</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OBI:0000245</t>
+          <t>BCIO:010071</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>organization</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>personal care worker</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>An entity that can bear roles, has members, and has a set of organization rules. Members of organizations are either organizations themselves or individual people. Members can bear specific organization member roles that are determined in the organization rules. The organization rules also determine how decisions are made on behalf of the organization by the organization members.</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>A services and sales worker that provides care, supervision and assistance for children, patients and elderly, convalescent or disabled persons in institutional and residential settings.</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Personal carer</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BFO:0000020</t>
+          <t>BCIO:010075</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>characteristic</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>home-based personal care worker</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>b is a specifically dependent continuant = Def. b is a continuant &amp; there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
-        </is>
-      </c>
+          <t>A personal care worker that provide routine personal care and assistance with activities of daily living to persons who are in need of such care due to effects of ageing, illness, injury, or other physical or mental conditions, in private homes and other independent residential settings.</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Home birth assistant, Home care aide, Nursing aide (home), Personal care provider</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:010108</t>
+          <t>BCIO:010072</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>socio demographic attribute of person source</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>child care worker</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>A social or demographic characteristic of a human being who is the bearer of a person source role.</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
+          <t>A personal care worker that provides care and supervision for children in non-domestic settings.</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Babysitter, Child care worker, Creche ayah, Family day care worker, Nanny, Out of school hours care worker</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:010119</t>
+          <t>BCIO:010073</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>psychological influence on intervention delivery of person source</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teachers’ aide</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is their existing psychological attributes related to or potentially affecting the target behaviour.</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>A personal care worker that performs non-teaching duties to assist teaching staff, and provides care and supervision for children in schools and pre-schools.</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Pre-school assistant, Teacher’s assistant</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:010109</t>
+          <t>BCIO:010074</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>age of person source</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>health care assistant</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is a time quality inhering in a bearer by virtue of how long the bearer has existed.</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
+          <t>A personal care worker that provides direct personal care and assistance with activities of daily living to patients and residents in a variety of health care settings, working  in implementation of established care plans and practices, and under the direct supervision of medical, nursing or other health professionals or associate professionals.</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Nursing aide (clinic or hospital), Patient care assistant, Psychiatric aid</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:010110</t>
+          <t>BCIO:010076</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>gender of person source</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>protective services worker</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is an individual's perception of having a particular gender, which may or may not correspond with their birth sex.</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>A services and sales worker that protects individuals and property against fire and other hazards, maintain law and order and enforce laws and regulations.</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Firefighter, Police officer, Prison guard, Security guard, Offender manager</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>gender</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:010113</t>
+          <t>BCIO:010069</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1210,295 +1250,306 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>other gender</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>personal services worker</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>A gender of person source that reports not belonging to the cultural gender role distinctions of either male or female.</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>A services and sales worker that provides personal services related to travel, housekeeping, catering and hospitality, hairdressing and beauty treatment, animal care grooming and training, companionship and other services of a personal nature.</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Travel Attendant, Conductor, Guide, Cook, Waiter, Bartender, Hairdresser, Beautician, Housekeeping Supervisor, Astrologer, Fortune-teller, Valet, Undertaker, Embalmer, Pet Groomer, Animal Care Worker</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>non-binary, transexual</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:010117</t>
+          <t>BCIO:010070</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>health status of person source</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>sales worker</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that represents their mental or physical condition.</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>A services and sales worker that demonstrates goods in wholesale or retail shops, at stalls and markets, door to door, via telephone or customer contact centres. They may record and accept payment for goods and services purchased, and may operate small retail outlets.</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Street Salesperson, Market Salesperson, Shop Salesperson, Cashier, Ticket Clerk, Model, Sales Demonstrator, Door-to-door Salesperson, Contact Centre Salesperson, Service Station Attendant, Food Service Counter Attendant</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>diabetes, cancer, depression, obesity, overweight</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:010115</t>
+          <t>BCIO:010082</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>religious group membership of person source</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>armed forces occupation</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is a religious group to which an individual identifies as belonging, where a religious group is a group of people characterised by the practice of a common religion.</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
+          <t>An occupational role that includes all jobs held by members of the armed forces.</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Admiral, Air commodore, Air marshal, Airman, Brigadier (army), Bombardier, Captain (air force), Captain (army), Captain (navy), Colonel (army), Corporal,  Field marshal, Flight lieutenant (air force), Flying officer (military), General (army), Gunner, Group captain, (air force), Lieutenant (army), Major (army), Midshipman, Naval officer (military) , Navy commander, Officer cadet (armed forces), Paratrooper, Rifleman, Sergeant (army), Second lieutenant (army), Seaman, Squadron leader, Sublieutenant (navy), Wing commander</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Muslim, Christian, Hindu, Sikh, Buddhist, Judaism</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:010114</t>
+          <t>BCIO:010083</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ethnic group membership of person source</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>researcher</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is the ethnic group to which an individual identifies as belonging, where an ethic group is a population whose members have a common heritage that is real or presumed such as common culture, language, religion, behaviour or biological trait.</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+          <t>A occupational role played by a person that contributes substantively to production or reporting of a research study</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>researcher, research assistant, investigator</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>black, white, Indian, Chinese, Somalian</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:010118</t>
+          <t>BCIO:030000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>target behaviour of person source</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>behaviour change intervention study investigator role</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is their amount or experience of the intervention’s target behaviour.</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+          <t>A researcher role played by a person that contributes substantively to production or reporting of a BCI evaluation study.</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>source is highly physically active</t>
-        </is>
-      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:010116</t>
+          <t>BCIO:010079</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>language proficiency of person source</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>plant and machine operator</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is an individual’s ability to speak or perform in the intervention language.</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
+          <t>An occupational role that operates and monitors industrial and agricultural machinery and equipment on the spot or by remote control, or drives and operates trains, motor vehicles and mobile machinery and equipment.</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Stationary Plant and Machine Operator, Driver, Mobile Plant Operator</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>fluent, native</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MF:0000030</t>
+          <t>BCIO:010078</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>representation</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>craft and related trades worker</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>A dependent continuant which is about a portion of reality.</t>
-        </is>
-      </c>
+          <t>An occupational role that applies specific technical and practical knowledge and skills to construct and maintain buildings, machinery, equipment or tools, carries out printing work, and produces or processes foodstuffs, textiles and wooden, metal and other articles, including handicraft goods.</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Building Trade Worker, Metal Workers, Machinery Worker, Handicraft Worker, Printing Worker, Electrical Equipment Installers and Repairer, Electronics and Telecommunications Installer and Repairer, Food Processing Worker, Woodworker, Tobacco Product Maker</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MF:0000031</t>
+          <t>BCIO:010080</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>cognitive representation</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>assembler</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>A representation which specifically depends on an anatomical structure in the cognitive system of an organism.</t>
-        </is>
-      </c>
+          <t>An occupational role that assembles products from component parts according to strict specifications and procedures.</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ADDICTO:0000381</t>
+          <t>BCIO:010081</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1506,27 +1557,39 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>elementary occupation</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>A cognitive representation of themselves by a person or a group about themselves.</t>
-        </is>
-      </c>
+          <t>An occupational role that involves the performance of simple and routine tasks which may require the use of hand-held tools and considerable physical effort.</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Cleaner, Labourer, Food Preparation Assistant, Street and Related Services Worker, Street Vendor (excluding Food), Refuse Worker</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ADDICTO:0000399</t>
+          <t>BCIO:010006</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1535,26 +1598,34 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>self-identity</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>professional</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>An identity that a person has about themselves.</t>
-        </is>
-      </c>
+          <t>An occupational role that works in knowledge building activities, applies scientific or artistic concepts and theories or teaches about the foregoing in a systematic manner.</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:015098</t>
+          <t>BCIO:010007</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1564,33 +1635,37 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>gender identity</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>science and engineering professional</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
+          <t>A professional that conducts research, improves or develops concepts, theories and operational methods or applies scientific knowledge.</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>Population</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Science Professional, Mathematician, Actuary, Statistician, Life Science Professional, Engineering Professional, Electrotechnology Engineer, Architect, Planner, Surveyor, Designer</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:010111</t>
+          <t>BCIO:010044</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1603,7 +1678,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>female gender</t>
+          <t>technician and associate professional</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -1611,26 +1686,22 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>A gender identity as being female.</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
+          <t>A professional that performs technical and related tasks connected with research and the application of scientific or artistic concepts and operational methods, and government or business regulations.</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr"/>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>female, woman</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:010112</t>
+          <t>BCIO:010065</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1641,217 +1712,237 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>male gender</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>artistic, cultural and culinary associate professional</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>A gender identity as being male.</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr"/>
+          <t>A technician and associate professional that combines creative skills and technical and cultural knowledge in creative media or food.</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Photographer, Interior designers and decorator, Gallery, museum and library technician, Chef</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>male, man</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:010123</t>
+          <t>BCIO:010045</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>expertise discipline</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>health associate professional</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>An attribute that is a field of knowledge or practice.</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr"/>
+          <t>A technician and associate professional that performs technical and practical tasks to support diagnosis and treatment of illness, disease, injuries and impairments in humans or animals, and supports the implementation of health care usually established by medical, veterinary, nursing and other health professionals.</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Veterinary Technician</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>The division of expertise into different disciplines or fields is complex and depends on historical, social and structural factors.</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:010093</t>
+          <t>BCIO:010050</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>discipline of current programme of study or training</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>traditional and complementary medicine associate professional</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>An expertise discipline of the programme of study currently undertaken by the bearer of a student or trainee role.</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
+          <t>A health associate professional that prevents and treats human physical and mental illnesses, disorders and injuries using herbal and other therapies based on theories, beliefs and experiences originating in specific cultures. They administer treatments using traditional techniques and medicaments, either acting independently or according to therapeutic care plans established by a traditional medicine or other health professional.</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr"/>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Acupuncture technician, Ayurvedic technician, Bonesetter, Herbalist , Homeopathy technician, Scraping and cupping therapist, Village healer, Witch doctor</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>psychology, medicine, hairdressing</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:010124</t>
+          <t>BCIO:010051</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>discipline of pre-existing knowledge or skill</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>dental assistant and therapist</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>The expertise discipline in which the person source has acquired their pre-existing knowledge and skills.</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr"/>
+          <t>A health associate professional that provides basic dental care services for the prevention and treatment of diseases and disorders of the teeth and mouth, according to care plans and procedures established by a dentist or other oral health professional.</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Dental assistant, Dental hygienist , Dental therapist</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BFO:0000017</t>
+          <t>BCIO:010055</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>realizable</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>environmental and occupational health inspector and associate</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>A specifically dependent continuant  that inheres in continuant  entities and are not exhibited in full at every time in which it inheres in an entity or group of entities. The exhibition or actualization of a realizable entity is a particular manifestation, functioning or process that occurs under certain circumstances.</t>
-        </is>
-      </c>
+          <t>A health associate professional that investigates the implementation of rules and regulations relating to environmental factors that may affect human health, safety in the 
+workplace, and safety of processes for the production of goods and services. They may implement and evaluate programmes to restore or improve safety and sanitary conditions under the supervision of a health professional.</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Food sanitation and safety inspector, Health inspector, Occupational health and safety inspector, Pollution inspector, Product safety inspector, Sanitarian, Sanitary inspector</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BFO:0000023</t>
+          <t>BCIO:010054</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>medical assistant</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>A realizable entity  the manifestation of which brings about some result or end that is not essential to a continuant  in virtue of the kind of thing that it is but that can be served or participated in by that kind of continuant  in some kinds of natural, social or institutional contexts.</t>
-        </is>
-      </c>
+          <t>A health associate professional that performs basic clinical and administrative tasks to support patient care under the direct supervision of a medical practitioner or other health professional.</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Clinical assistant, Medical assistant, Ophthalmic assistant</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:010084</t>
+          <t>BCIO:010056</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1859,35 +1950,39 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>ambulance worker</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr"/>
+          <t>A health associate professional that provides emergency health care to patients who are injured, sick, infirm or otherwise physically or mentally impaired prior to and during transport to medical facilities.</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr"/>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Ambulance officer, Ambulance paramedic, Emergency medical technician, Emergency paramedic</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:010088</t>
+          <t>BCIO:010052</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1896,38 +1991,38 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>higher education student or trainee</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>community health worker</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning on an advanced educational programme in a university, college or professional school.</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
+          <t>A health associate professional that provides health education, referral and follow-up, case management, basic preventive health care and home visiting services to specific communities. They provide support and assistance to individuals and families in navigating the health and social services system.</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr"/>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Community health aide, Community health promoter, Community health worker, Village health worker, outreach worker, health worker</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:010089</t>
+          <t>BCIO:010053</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1937,37 +2032,37 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>undergraduate student or trainee</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>physiotherapy technician and assistant</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>A higher education student or trainee that is currently studying for an undergraduate degree.</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr"/>
+          <t>A health associate professional that provides physical therapeutic treatments to patients in circumstances where functional movement is threatened by injury, disease or impairment. Therapies are usually provided according to rehabilitative plans established by a physiotherapist or other health professional.</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr"/>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Acupressure therapist, Electrotherapist, Hydrotherapist, Massage therapist, Physical rehabilitation technician, Physiotherapy technician, Shiatsu therapist</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>undergraduate student</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:010091</t>
+          <t>BCIO:010047</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1977,37 +2072,37 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>masters student or trainee</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>nursing and midwifery associate professional</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>A higher education student or trainee that is currently studying for a Masters degree.</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr"/>
+          <t>A health associate professional that provides basic nursing and personal care for people who are physically or mentally ill, disabled or infirm, and for others in need of care due to potential risks to health including before, during and after childbirth. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing, midwifery and other health professionals.</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr"/>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Practice assistant, Quit Smoking Counsellor, Health educator, Dispensing Optician, Information Technician</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>MSc student, Masters student</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:010090</t>
+          <t>BCIO:010049</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2017,37 +2112,37 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>graduate student or trainee</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>midwifery associate professional</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>A higher education student or trainee that has completed an undergraduate degree.</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr"/>
+          <t>A nursing and midwifery associate professional that provides basic health care and advice before, during and after pregnancy and childbirth. They implement care, treatment and referral plans usually established by medical, midwifery and other health professionals.</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr"/>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Assistant midwife, Traditional midwife</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>graduate student</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:010092</t>
+          <t>BCIO:010048</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2057,37 +2152,37 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>doctoral student or trainee</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>nursing associate professional</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>A higher education student or trainee that is currently studying for a doctoral degree.</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr"/>
+          <t>A nursing and midwifery associate professional that provides basic nursing and personal care for people in need of such care due to effects of ageing, illness, injury, or other physical or mental impairment. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing and other health professionals.</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr"/>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Assistant nurse, Associate professional nurse, Enrolled nurse, Practical nurse</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>PhD student</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:010085</t>
+          <t>BCIO:010046</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2096,34 +2191,38 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>informal education student or trainee</t>
-        </is>
-      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>medical and pharmaceutical technician</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning in a non-institutional setting.</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
+          <t>A health associate professional that performs technical tasks to assist in diagnosis and treatment of illness, disease, injuries and impairments.</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr"/>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Medical imaging and therapeutic equipment technician, Medical and Pathology laboratory technician, Pharmaceutical technician, Medical and dental prosthetic technician</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:010086</t>
+          <t>BCIO:010061</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2132,34 +2231,38 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>school student or trainee</t>
-        </is>
-      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>sport and fitness worker</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning at a primary or secondary education level in an institutional, organised setting.</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
+          <t>A technician and associate professional that prepares for and competes in sporting events for financial gain, trains amateur and professional sportsmen and women to enhance performance, promotes participation and standards in sport, organises and officiates sporting events, or provides instruction, training and supervision for various forms of exercise and other recreational activities.</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr"/>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>physical activity professional, exercise physiologist, exercise therapist, exercise specialist</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:010087</t>
+          <t>BCIO:010064</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2168,34 +2271,38 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>vocational training student or trainee</t>
-        </is>
-      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>fitness and recreation instructor and programme leader</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
+          <t>A sport and fitness worker that leads, guides and instructs groups and individuals in recreational, fitness or outdoor adventure activities.</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr"/>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Aerobics instructor, Fitness instructor, Horse riding instructor, Outdoor adventure guide, Personal trainer, Sailing instructor, Underwater diving instructor</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:010000</t>
+          <t>BCIO:010062</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2203,35 +2310,39 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>behaviour change intervention source</t>
-        </is>
-      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>athlete and sports player</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>A role played by a person, population or organisation that provides a BCI.</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
+          <t>A sport and fitness worker that participates in competitive sporting events. They train and compete, either individually or as part of a team, in their chosen sport.</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr"/>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Athlete, Bicycle racer, Boxer, Chess player , Footballer, Golfer, Hockey player, Jockey, Poker player, Racing driver, Skier, Tennis player, Wrestler</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:010138</t>
+          <t>BCIO:010063</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2240,34 +2351,38 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>organisational source role</t>
-        </is>
-      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>sports coach, instructor and official</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>A BCI source role that is borne by an organisation.</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr"/>
+          <t>A sport and fitness worker that works with amateur and professional sportspersons to enhance performance and encourage greater participation in sport, and organizes and officiates in sporting events according to established rules.</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr"/>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Referee, Ski instructor, Sports coach, Sports official, Swimming instructor</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:010133</t>
+          <t>BCIO:010058</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2276,34 +2391,38 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>source role related to intervention</t>
-        </is>
-      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>legal and related associate professional</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>A BCI source whose occupational or voluntary role is focused on delivery of the behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr"/>
+          <t>A technician and associate professional that performs support functions in courts of law or in law offices, provide services related to such legal matters as insurance contracts, the transferring of property and the granting of loans and other financial transactions, or conduct investigations for clients.</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr"/>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Bailiff, Judge’s clerk, Conveyancing clerk, Court clerk, Justice of the peace, Law clerk, Legal assistant, Paralegal, Private detective, Title searcher</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:010134</t>
+          <t>BCIO:010057</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2312,34 +2431,38 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>source involved in development of intervention</t>
-        </is>
-      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>business and administration associate professional</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>A BCI source that is involved in the development of intervention content.</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr"/>
+          <t>A technician and associate professional that performs mostly technical tasks connected with the practical application of knowledge relating to financial accounting and transaction matters, mathematical calculations, human resource development, selling and buying financial instruments, specialized secretarial tasks and enforcing or applying government rules.</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr"/>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Financial and Mathematical associate professional, Sales and purchasing agent, Broker, Business Services Agent, Administrative and Specialized Secretary, Government regulatory associate professional, Medical secretary</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:010135</t>
+          <t>BCIO:010059</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2349,33 +2472,37 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>source involved in co-production of intervention</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>social work associate professional</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>A source involved in development of intervention that has developed the intervention content in collaboration with key stakeholders such as patients or community members.</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr"/>
+          <t>A technician and associate professional that implements social assistance programmes and community services and assist clients to deal with personal and social problems.</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr"/>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Community development worker, Community services worker, Crisis intervention worker, Disability services worker, Family services worker, Life skills instructor, Mental health support worker, Welfare support worker, Women’s shelter supervisor, Youth services worker</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:010001</t>
+          <t>BCIO:010066</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2384,34 +2511,38 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>person source role</t>
-        </is>
-      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>information and communications technician</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>A behaviour change intervention source role that inheres in a person.</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr"/>
+          <t>A technician and associate professional that provides support for the day to day running of computer systems, communication systems and networks, broadcast images and sound, telecommunication signals on land, sea or in aircraft.</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr"/>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Information and Communications Technology Operations and User Support Technician, Telecommunications and Broadcasting Technician</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:010003</t>
+          <t>BCIO:010060</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2419,35 +2550,39 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>personal role of source</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>religious associate professional</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>A role that inheres in a person source.</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr"/>
+          <t>A technician and associate professional that provides support to ministers of religion or to a religious community, undertake religious works, preach and propagate the teachings of a particular religion and endeavour to improve well-being through the power of faith and spiritual advice.</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr"/>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Faith healer, Lay preacher, Monk, Nun</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:010094</t>
+          <t>BCIO:010008</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2456,34 +2591,38 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>relatedness between person source and the target population</t>
-        </is>
-      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>health professional</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>A personal role of source that is realised in some relationship to the characteristics of the intervention participants.</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr"/>
+          <t>A professional that improves or develops concepts, theories and operational method, and applied scientific knowledge relating to medicine, nursing, dentistry, veterinary medicine, pharmacy, and promotion of health.</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr"/>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Health professional; Arts therapist, Chiropractor, Dance and movement therapist, Occupational therapist, Osteopath, Podiatrist, Recreational therapist, Health staff, Clinic staff</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:010105</t>
+          <t>BCIO:010015</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2493,33 +2632,37 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>embedded in participants’ community</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>traditional and complementary medicine professional</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a source who is known and working to deliver intervention in own community.</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr"/>
+          <t>A health professional that examines patients, prevents and treats illness, disease, injury and other physical and mental impairments and maintains general health in humans. They do this by applying knowledge, skills and practices acquired through extensive study of the theories, beliefs and experiences originating in specific cultures.</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr"/>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Acupuncturist, Ayurvedic practitioner,  Chinese herbal medicine practitioner, Homeopath, Naturopath, Unani practitioner</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:010103</t>
+          <t>BCIO:010009</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2529,33 +2672,37 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>employer</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>medical doctor</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person which hires the services of the participant.</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr"/>
+          <t>A health professional that studies, diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans through the application of modern medicine. They plan, supervise and evaluate the implementation of care and treatment plans by other health care providers, and conduct medical education and research activities.</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr"/>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>District medical doctor-therapist, family medical practitioner, general practitioner, medical doctor (general), medical officer (general), physician (general), primary health care physician, resident medical officer specializing in general practice</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:010100</t>
+          <t>BCIO:010010</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2565,37 +2712,37 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>carer</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>generalist medical practitioner</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is an individual who cares, unpaid, for a friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr"/>
+          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments and maintains general health in humans through application of modern medicine. They do not limit their practice to certain disease categories or methods of treatment, and may assume responsibility for the provision of continuing and comprehensive medical care to individuals, families and communities.</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr"/>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Primary care physician, family doctor, GP</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>carer</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:010102</t>
+          <t>BCIO:010011</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2605,33 +2752,37 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>colleague</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>specialist medical practitioner</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person with whom the participant works in a profession or business.</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr"/>
+          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans, using specialized testing, diagnostic, medical, surgical, physical and psychiatric techniques through application of the principles and procedures of modern medicine. They specialize in certain disease categories, types of patient or methods of treatment and may conduct medical education and research in their chosen areas of specialization.</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr"/>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Anaesthetist, Cardiologist, Emergency medicine specialist, Gynaecologist, Obstetrician, Ophthalmologist, Paediatrician, Pathologist, Preventive medicine specialist, Psychiatrist, Radiation oncologist, Radiologist, Resident medical officer in specialist training, Specialist medical practitioner (public health), Specialist physician (internal medicine), Specialist physician (nuclear medicine), Surgeon</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:010104</t>
+          <t>BCIO:010023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2641,33 +2792,37 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>peer</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>audiologist and speech therapist</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is descried as matched to intervention recipients on the basis of ‘peerness’ – age, social status, gender, shared experience, shared health status etc.</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr"/>
+          <t>A health professional  that evaluates, manages and treats physical disorders affecting human hearing, speech, communication and swallowing.</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr"/>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Audiologist, Language therapist, Speech pathologist, Speech therapist</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:010101</t>
+          <t>BCIO:010024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2677,33 +2832,37 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>friend</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>optometrist and ophthalmic optician</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person whom the participant knows, likes and trusts, typically exclusive of sexual or family relations.</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr"/>
+          <t>A health professional  that provides diagnosis, management and treatment services for disorders of the eyes and visual system.</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr"/>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Ophthalmic optician , Optometrist, Orthoptist</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:010004</t>
+          <t>BCIO:010018</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2712,38 +2871,38 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>occupational role of source</t>
-        </is>
-      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>dentist</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>A personal role of source that is realised by doing a specified type of work or working in a specified way.</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr"/>
+          <t>A health professional that diagnoses treats and prevents diseases, injuries and abnormalities of the teeth, mouth, jaws and associated tissues by applying the principles and procedures of modern dentistry.</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr"/>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Dental practitioner, Dental surgeon, Dentist, Endodontist, Oral and maxillofacial surgeon, Oral pathologist, Orthodontist, Paedodontist, Periodontist, Prosthodontist, Stomatologist</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>Interventionist, facilitator, study staff</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:010081</t>
+          <t>BCIO:010012</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2753,37 +2912,33 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>elementary occupation</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>nursing and midwifery professional</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>An occupational role that involves the performance of simple and routine tasks which may require the use of hand-held tools and considerable physical effort.</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr"/>
+          <t>A health professional that provides treatment and care services for people who are physically or mentally ill, disabled or infirm, and those with potential risks to health including before, during and after childbirth. They assume responsibility for the planning, management and evaluation of the care of patients, including the supervision of other health care workers, working autonomously or in teams with medical doctors and others in the practical application of preventive and curative measures.</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr"/>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
-          <t>Cleaner, Labourer, Food Preparation Assistant, Street and Related Services Worker, Street Vendor (excluding Food), Refuse Worker</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:010083</t>
+          <t>BCIO:010019</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2793,37 +2948,37 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>researcher</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>pharmacist</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>An occupational role that is a researcher but unclear what discipline.</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr"/>
+          <t>A health professional that stores, preserves, compounds and dispenses medicinal products and counsel on the proper use and adverse effects of drugs and medicines following prescriptions issued by medical doctors and other health professionals.</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr"/>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Dispensing chemist, Hospital pharmacist, Industrial pharmacist, Retail pharmacist</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>researcher, research assistant, investigator</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:010080</t>
+          <t>BCIO:010016</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2833,33 +2988,37 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>assembler</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>paramedical practitioner</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>An occupational role that assembles products from component parts according to strict specifications and procedures.</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr"/>
+          <t>A health professional that provides advisory, diagnostic, curative and preventive medical services more limited in scope and complexity than those carried out by medical doctors. They work autonomously or with limited supervision of medical doctors, and apply advanced clinical procedures for treating and preventing diseases, injuries and other physical or mental impairments common to specific communities.</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr"/>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Advanced care paramedic, Clinical officer (paramedical), Feldscher, Primary care paramedic, Surgical technician</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:010067</t>
+          <t>BCIO:010021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2869,37 +3028,37 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>clerical support worker</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>physiotherapist</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>An occupational role that records, organizes, stores, computes and retrieves information, and performs a number of clerical duties in connection with money-handling operations, travel arrangements, requests for information, and appointments.</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr"/>
+          <t>A health professional  that assesses, plans and implements rehabilitative programmes that improve or restore human motor functions, maximize movement ability, relieve pain syndromes, and treat or prevent physical challenges associated with injuries, diseases and other impairments.</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr"/>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Geriatric physical therapist, Manipulative therapist, Orthopaedic physical therapist, Paediatric physical therapist, Physical therapist, Physiotherapist</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>General and Keyboard Clerk, customers Services Clerk, Numerical and Material Recording Clerk</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:010068</t>
+          <t>BCIO:010014</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2909,33 +3068,37 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>services and sales worker</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>midwifery professional</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>An occupational role that provides personal or protective services related to travel, house-keeping, catering, personal care, protection against fire and unlawful acts, or sells goods in retail or markets.</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr"/>
+          <t>A health professional that plans, manages, provides and evaluates midwifery care services before, during and after pregnancy and childbirth. They provide delivery care for reducing health risks to women and newborn children, working autonomously or in teams with other health care providers.</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr"/>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Midwife</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:010076</t>
+          <t>BCIO:010020</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2946,36 +3109,36 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>protective services worker</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>environmental and occupational health and hygiene professional</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>A services and sales worker that protects individuals and property against fire and other hazards, maintain law and order and enforce laws and regulations.</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr"/>
+          <t>A health professional that assesses, plans and implements programmes to recognize, monitor and control environmental factors that can potentially affect human health, to ensure safe and healthy working conditions and to prevent disease or injury caused by chemical, physical, radiological and biological agents or ergonomic factors.</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr"/>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Environmental health officer, Occupational health and safety adviser, Occupational hygienist, Radiation protection expert</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Firefighter, Police officer, Prison guard, Security guard, Offender manager</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCIO:010069</t>
+          <t>BCIO:010022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2986,36 +3149,36 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>personal services worker</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>dietician and nutritionist</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>A services and sales worker that provides personal services related to travel, housekeeping, catering and hospitality, hairdressing and beauty treatment, animal care grooming and training, companionship and other services of a personal nature.</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr"/>
+          <t>A health professional  that assesses, plans and implements programmes to enhance the impact of food and nutrition on human health.</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr"/>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Clinical dietician, Food service dietician, Nutritionist, Public health nutritionist, Sports nutritionist</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>Travel Attendant, Conductor, Guide, Cook, Waiter, Bartender, Hairdresser, Beautician, Housekeeping Supervisor, Astrologer, Fortune-teller, Valet, Undertaker, Embalmer, Pet Groomer, Animal Care Worker</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIO:010070</t>
+          <t>BCIO:010017</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3026,36 +3189,36 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>sales worker</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>veterinarian</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>A services and sales worker that demonstrates goods in wholesale or retail shops, at stalls and markets, door to door, via telephone or customer contact centres. They may record and accept payment for goods and services purchased, and may operate small retail outlets.</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr"/>
+          <t>A health professional that diagnoses, prevents and treats diseases, injuries and dysfunctions of animals.</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr"/>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Animal pathologist, Veterinarian, Veterinary epidemiologist, Veterinary intern, Veterinary surgeon</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>Street Salesperson, Market Salesperson, Shop Salesperson, Cashier, Ticket Clerk, Model, Sales Demonstrator, Door-to-door Salesperson, Contact Centre Salesperson, Service Station Attendant, Food Service Counter Attendant</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BCIO:010071</t>
+          <t>BCIO:010013</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3066,36 +3229,36 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>personal care worker</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>nursing professional</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>A services and sales worker that provides care, supervision and assistance for children, patients and elderly, convalescent or disabled persons in institutional and residential settings.</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr"/>
+          <t>A health professional that provides treatment, support and care services for people who are in need of nursing care due to the effects of ageing, injury, illness or other physical or mental impairment, or potential risks to health.</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr"/>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Clinical nurse consultant, District nurse, Nurse anaesthetist, Nurse educator, Nurse practitioner, Operating theatre nurse, Professional nurse, Public health nurse, Specialist nurse, Nursing Counsellor, Study Nurse</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>Personal carer</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BCIO:010073</t>
+          <t>BCIO:010025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3106,36 +3269,36 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>teachers’ aide</t>
-        </is>
-      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>teaching professional</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>A personal care worker that performs non-teaching duties to assist teaching staff, and provides care and supervision for children in schools and pre-schools.</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr"/>
+          <t>A professional that teaches the theory and practice of one or more disciplines at different educational levels.</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr"/>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Education Methods Specialist, Other Language Teacher, Information Technology Teacher, Private Tutor, School Counsellor, Student Advisor</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>Pre-school assistant, Teacher’s assistant</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BCIO:010072</t>
+          <t>BCIO:010027</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3149,33 +3312,33 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>child care worker</t>
+          <t>vocational education teacher</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>A personal care worker that provides care and supervision for children in non-domestic settings.</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr"/>
+          <t>A teaching professional that teaches or instructs vocational or occupational subjects in adult and further education institutions and to senior students in secondary schools and colleges.</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr"/>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Automotive technology instructor, Cosmetology instructor, Vocational education teacher</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>Babysitter, Child care worker, Creche ayah, Family day care worker, Nanny, Out of school hours care worker</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BCIO:010075</t>
+          <t>BCIO:010029</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3189,33 +3352,29 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>home-based personal care worker</t>
+          <t>primary school teacher</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>A personal care worker that provide routine personal care and assistance with activities of daily living to persons who are in need of such care due to effects of ageing, illness, injury, or other physical or mental conditions, in private homes and other independent residential settings.</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr"/>
+          <t>A teaching professional that teaches teach a range of subjects at the primary education level.</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr"/>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Home birth assistant, Home care aide, Nursing aide (home), Personal care provider</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BCIO:010074</t>
+          <t>BCIO:010028</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3229,33 +3388,33 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>health care assistant</t>
+          <t>secondary education teacher</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>A personal care worker that provides direct personal care and assistance with activities of daily living to patients and residents in a variety of health care settings, working  in implementation of established care plans and practices, and under the direct supervision of medical, nursing or other health professionals or associate professionals.</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr"/>
+          <t>A teaching professional that teaches one or more subjects at secondary education level.</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr"/>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Secondary school teacher, High school teacher</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>Nursing aide (clinic or hospital), Patient care assistant, Psychiatric aid</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BCIO:010077</t>
+          <t>BCIO:010026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3265,37 +3424,37 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>skilled agricultural, forestry and fishery worker</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>university and higher education teacher</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>An occupational role that grows and harvests plants or animals to provide food, shelter and income for themselves and their households.</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr"/>
+          <t>A teaching professional that prepares and delivers lectures and conduct tutorials in one or more subjects within a prescribed course of study at a university or other higher educational institution. They conduct research, and prepare scholarly papers and books.</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr"/>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Higher education lecturer, Professor, University lecturer, University tutor</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>Market gardener, Crop grower, Animal Producer, Mixed Crop and Animal Producer, Forestry worker, Fishery worker, Hunter. Subsistence Crop Farmer, Subsistence Livestock Farmer</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCIO:010006</t>
+          <t>BCIO:010031</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3305,33 +3464,37 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>professional</t>
-        </is>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>special needs teacher</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>An occupational role that works in knowledge building activities, applies scientific or artistic concepts and theories or teaches about the foregoing in a systematic manner.</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr"/>
+          <t>A teaching professional that teaches children, young persons or adults with physical or intellectual special needs.</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr"/>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Learning disabilities special education teacher, Learning support teacher, Remedial teacher, Teacher of gifted children, Teacher of the hearing impaired, Teacher of the sight impaired</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIO:010007</t>
+          <t>BCIO:010033</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3342,36 +3505,36 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>science and engineering professional</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>arts teacher</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>A professional that conducts research, improves or develops concepts, theories and operational methods or applies scientific knowledge.</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr"/>
+          <t>A teaching professional  that teaches students in the practice, theory and performance of dance, drama, visual and other arts (excluding music) in private or small group tuition or within mainstream educational institutions.</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr"/>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Dance teacher (private tuition), Drama teacher (private tuition), Painting teacher (private tuition), Sculpture teacher (private tuition)</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Science Professional, Mathematician, Actuary, Statistician, Life Science Professional, Engineering Professional, Electrotechnology Engineer, Architect, Planner, Surveyor, Designer</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BCIO:010008</t>
+          <t>BCIO:010032</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3382,36 +3545,36 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>health professional</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>music teacher</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>A professional that improves or develops concepts, theories and operational method, and applied scientific knowledge relating to medicine, nursing, dentistry, veterinary medicine, pharmacy, and promotion of health.</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr"/>
+          <t>A teaching professional that teaches students in the practice, theory and performance of music in private or small group tuition or within mainstream educational institutions.</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr"/>
-      <c r="R81" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Guitar teacher (private tuition), Piano teacher (private tuition), Singing teacher (private tuition), Violin teacher (private tuition)</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>Health professional; Arts therapist, Chiropractor, Dance and movement therapist, Occupational therapist, Osteopath, Podiatrist, Recreational therapist, Health staff, Clinic staff</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BCIO:010024</t>
+          <t>BCIO:010030</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3425,33 +3588,33 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>optometrist and ophthalmic optician</t>
+          <t>early childhood educator</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
-          <t>A health professional  that provides diagnosis, management and treatment services for disorders of the eyes and visual system.</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr"/>
+          <t>A teaching professional that promotes the social, physical, and intellectual development of children below primary school age through the provision of educational and play activities.</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr"/>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Early childhood educator, Pre-school teacher</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>Ophthalmic optician , Optometrist, Orthoptist</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BCIO:010013</t>
+          <t>BCIO:010034</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3462,36 +3625,32 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>nursing professional</t>
-        </is>
-      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>legal, social and cultural professional</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>A health professional that provides treatment, support and care services for people who are in need of nursing care due to the effects of ageing, injury, illness or other physical or mental impairment, or potential risks to health.</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr"/>
+          <t>A professional that conducts research, improves or develops concepts, theories and operational methods, or applies knowledge relating to the law, social or cultural studies.</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr"/>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
-          <t>Clinical nurse consultant, District nurse, Nurse anaesthetist, Nurse educator, Nurse practitioner, Operating theatre nurse, Professional nurse, Public health nurse, Specialist nurse, Nursing Counsellor, Study Nurse</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BCIO:010017</t>
+          <t>BCIO:010042</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3505,33 +3664,33 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>veterinarian</t>
+          <t>linguist</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
-          <t>A health professional that diagnoses, prevents and treats diseases, injuries and dysfunctions of animals.</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr"/>
+          <t>A legal, social and cultural professional that translates or interprets from one language into another.</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr"/>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Interpretator; other linguist</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>Animal pathologist, Veterinarian, Veterinary epidemiologist, Veterinary intern, Veterinary surgeon</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BCIO:010021</t>
+          <t>BCIO:010036</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3545,33 +3704,33 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>physiotherapist</t>
+          <t>librarian, archivist and curator</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
-          <t>A health professional  that assesses, plans and implements rehabilitative programmes that improve or restore human motor functions, maximize movement ability, relieve pain syndromes, and treat or prevent physical challenges associated with injuries, diseases and other impairments.</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr"/>
+          <t>A legal, social and cultural professional that develops and maintains collections of archives, libraries, museums, art galleries and similar establishments.</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr"/>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>Librarian, Archivist,  Curator</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>Geriatric physical therapist, Manipulative therapist, Orthopaedic physical therapist, Paediatric physical therapist, Physical therapist, Physiotherapist</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BCIO:010016</t>
+          <t>BCIO:010037</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3585,33 +3744,33 @@
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>paramedical practitioner</t>
+          <t>social professional</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
-          <t>A health professional that provides advisory, diagnostic, curative and preventive medical services more limited in scope and complexity than those carried out by medical doctors. They work autonomously or with limited supervision of medical doctors, and apply advanced clinical procedures for treating and preventing diseases, injuries and other physical or mental impairments common to specific communities.</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr"/>
+          <t>A legal, social and cultural professional that conducts research, improves or develops concepts, theories and operational methods or applies knowledge relating to psychology, sociology, philosophy, politics, economics, sociology, anthropology, history and other social sciences, or provides social services to meet the needs of individuals and families in a community.</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr"/>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Economist, Sociologist, Anthropologist, Philosopher, Historian, Political Scientist</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>Advanced care paramedic, Clinical officer (paramedical), Feldscher, Primary care paramedic, Surgical technician</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BCIO:010009</t>
+          <t>BCIO:010039</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3623,35 +3782,35 @@
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>medical doctor</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>social work and counselling professional</t>
+        </is>
+      </c>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
-          <t>A health professional that studies, diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans through the application of modern medicine. They plan, supervise and evaluate the implementation of care and treatment plans by other health care providers, and conduct medical education and research activities.</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr"/>
+          <t>A social professional that provides advice and guidance to individuals, families, groups, communities and organizations in response to social and personal difficulties. They assist clients to develop skills and access resources and support services needed to respond to issues arising from unemployment, poverty, disability, addiction, criminal and delinquent behaviour, marital and other problems.</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr"/>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Counsellor, Addictions counsellor, Bereavement counsellor, Child and youth counsellor, District social welfare officer, Family counsellor, Marriage counsellor, Parole officer, Probation officer, Sexual assault counsellor, Social worker, Women’s welfare organizer</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>District medical doctor-therapist, family medical practitioner, general practitioner, medical doctor (general), medical officer (general), physician (general), primary health care physician, resident medical officer specializing in general practice</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BCIO:010011</t>
+          <t>BCIO:010038</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3666,32 +3825,32 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>specialist medical practitioner</t>
+          <t>psychologist</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
-          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans, using specialized testing, diagnostic, medical, surgical, physical and psychiatric techniques through application of the principles and procedures of modern medicine. They specialize in certain disease categories, types of patient or methods of treatment and may conduct medical education and research in their chosen areas of specialization.</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr"/>
+          <t>A social professional that studies the mental processes and behaviour of human beings as individuals or in groups, and applies this knowledge to promote personal, social, educational or occupational adjustment and development.</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr"/>
-      <c r="R88" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Clinical psychologist, Counselling psychologist, Educational psychologist, Forensic psychologist, Health psychologist, Neuropsychologist, Organizational psychologist, Psychotherapist, Sport and exercise psychologist</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>Anaesthetist, Cardiologist, Emergency medicine specialist, Gynaecologist, Obstetrician, Ophthalmologist, Paediatrician, Pathologist, Preventive medicine specialist, Psychiatrist, Radiation oncologist, Radiologist, Resident medical officer in specialist training, Specialist medical practitioner (public health), Specialist physician (internal medicine), Specialist physician (nuclear medicine), Surgeon</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BCIO:010010</t>
+          <t>BCIO:010035</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3703,35 +3862,35 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>generalist medical practitioner</t>
-        </is>
-      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>legal professional</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments and maintains general health in humans through application of modern medicine. They do not limit their practice to certain disease categories or methods of treatment, and may assume responsibility for the provision of continuing and comprehensive medical care to individuals, families and communities.</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr"/>
+          <t>A legal, social and cultural professional that conducts research on legal problems, advises clients on legal aspects of problems, pleads cases or conducts prosecutions in courts of law, presides over judicial proceedings in courts of law and draft laws and regulations.</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr"/>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Lawyer, Judge, Coroner</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>Primary care physician, family doctor, GP</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BCIO:010015</t>
+          <t>BCIO:010041</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3745,33 +3904,33 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>traditional and complementary medicine professional</t>
+          <t>author and journalist</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>A health professional that examines patients, prevents and treats illness, disease, injury and other physical and mental impairments and maintains general health in humans. They do this by applying knowledge, skills and practices acquired through extensive study of the theories, beliefs and experiences originating in specific cultures.</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr"/>
+          <t>A legal, social and cultural professional that conceives and creates literary works, and interprets and communicates news and public affairs through the media.</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr"/>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Author, Writer, Journalist, Translator, News anchor</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>Acupuncturist, Ayurvedic practitioner,  Chinese herbal medicine practitioner, Homeopath, Naturopath, Unani practitioner</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BCIO:010018</t>
+          <t>BCIO:010043</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3785,33 +3944,33 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>dentist</t>
+          <t>creative and performing artist</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>A health professional that diagnoses treats and prevents diseases, injuries and abnormalities of the teeth, mouth, jaws and associated tissues by applying the principles and procedures of modern dentistry.</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr"/>
+          <t>A legal, social and cultural professional that communicates ideas, impressions and facts in a wide range of media to achieve particular effects, interprets a composition such as a musical score or a script to perform or direct the performance, and hosts the presentation of such performance and other media events.</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr"/>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Visual artist, Musician, Singer, Composer, Dancer, Choreographer, Director, Producer, Actor, Announcer on radio, television and other media</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>Dental practitioner, Dental surgeon, Dentist, Endodontist, Oral and maxillofacial surgeon, Oral pathologist, Orthodontist, Paedodontist, Periodontist, Prosthodontist, Stomatologist</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BCIO:010020</t>
+          <t>BCIO:010040</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3825,33 +3984,33 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>environmental and occupational health and hygiene professional</t>
+          <t>religious professional</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>A health professional that assesses, plans and implements programmes to recognize, monitor and control environmental factors that can potentially affect human health, to ensure safe and healthy working conditions and to prevent disease or injury caused by chemical, physical, radiological and biological agents or ergonomic factors.</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr"/>
+          <t>A legal, social and cultural professional that functions  as a perpetuator of sacred traditions, practices and beliefs. They conduct religious services, celebrate or administer the rites of a religious faith or denomination, provide spiritual and moral guidance and perform other functions associated with the practice of a religion.</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr"/>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Bonze, Imam, Minister of religion, Poojari, Priest, Rabbi</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>Environmental health officer, Occupational health and safety adviser, Occupational hygienist, Radiation protection expert</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BCIO:010014</t>
+          <t>BCIO:010094</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3860,38 +4019,34 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>relatedness between person source and the target population</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>midwifery professional</t>
-        </is>
-      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>A health professional that plans, manages, provides and evaluates midwifery care services before, during and after pregnancy and childbirth. They provide delivery care for reducing health risks to women and newborn children, working autonomously or in teams with other health care providers.</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr"/>
+          <t>A personal role of source that is realised in some relationship to the characteristics of the intervention participants.</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr"/>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
-          <t>Midwife</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BCIO:010019</t>
+          <t>BCIO:010102</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -3901,37 +4056,33 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>colleague</t>
+        </is>
+      </c>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>pharmacist</t>
-        </is>
-      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
-          <t>A health professional that stores, preserves, compounds and dispenses medicinal products and counsel on the proper use and adverse effects of drugs and medicines following prescriptions issued by medical doctors and other health professionals.</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr"/>
+          <t>A relatedness between person source and the target population that is a person with whom the participant works in a profession or business.</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr"/>
-      <c r="R94" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
-          <t>Dispensing chemist, Hospital pharmacist, Industrial pharmacist, Retail pharmacist</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BCIO:010023</t>
+          <t>BCIO:010101</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3941,37 +4092,33 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>audiologist and speech therapist</t>
-        </is>
-      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
-          <t>A health professional  that evaluates, manages and treats physical disorders affecting human hearing, speech, communication and swallowing.</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr"/>
+          <t>A relatedness between person source and the target population that is a person whom the participant knows, likes and trusts, typically exclusive of sexual or family relations.</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr"/>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
-          <t>Audiologist, Language therapist, Speech pathologist, Speech therapist</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BCIO:010012</t>
+          <t>BCIO:010105</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -3981,33 +4128,33 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>embedded in participants’ community</t>
+        </is>
+      </c>
       <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>nursing and midwifery professional</t>
-        </is>
-      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
-          <t>A health professional that provides treatment and care services for people who are physically or mentally ill, disabled or infirm, and those with potential risks to health including before, during and after childbirth. They assume responsibility for the planning, management and evaluation of the care of patients, including the supervision of other health care workers, working autonomously or in teams with medical doctors and others in the practical application of preventive and curative measures.</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr"/>
+          <t>A relatedness between person source and the target population that is a source who is known and working to deliver intervention in own community.</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr"/>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BCIO:010022</t>
+          <t>BCIO:010103</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -4017,37 +4164,33 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>employer</t>
+        </is>
+      </c>
       <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>dietician and nutritionist</t>
-        </is>
-      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
-          <t>A health professional  that assesses, plans and implements programmes to enhance the impact of food and nutrition on human health.</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr"/>
+          <t>A relatedness between person source and the target population that is a person which hires the services of the participant.</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr"/>
-      <c r="R97" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
-          <t>Clinical dietician, Food service dietician, Nutritionist, Public health nutritionist, Sports nutritionist</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BCIO:010025</t>
+          <t>BCIO:010100</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4057,37 +4200,37 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>teaching professional</t>
-        </is>
-      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>carer</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>A professional that teaches the theory and practice of one or more disciplines at different educational levels.</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr"/>
+          <t>A relatedness between person source and the target population that is an individual who cares, unpaid, for a friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr"/>
-      <c r="R98" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>carer</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>Education Methods Specialist, Other Language Teacher, Information Technology Teacher, Private Tutor, School Counsellor, Student Advisor</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BCIO:010029</t>
+          <t>BCIO:010104</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4097,33 +4240,33 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>peer</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>primary school teacher</t>
-        </is>
-      </c>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches teach a range of subjects at the primary education level.</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr"/>
+          <t>A relatedness between person source and the target population that is descried as matched to intervention recipients on the basis of ‘peerness’ – age, social status, gender, shared experience, shared health status etc.</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr"/>
-      <c r="R99" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BCIO:010028</t>
+          <t>BCIO:010084</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4131,39 +4274,35 @@
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>secondary education teacher</t>
-        </is>
-      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches one or more subjects at secondary education level.</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr"/>
+          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr"/>
-      <c r="R100" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
-          <t>Secondary school teacher, High school teacher</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BCIO:010031</t>
+          <t>BCIO:010087</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4172,38 +4311,34 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>trainee role</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>special needs teacher</t>
-        </is>
-      </c>
+      <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches children, young persons or adults with physical or intellectual special needs.</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr"/>
+          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr"/>
-      <c r="R101" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
-          <t>Learning disabilities special education teacher, Learning support teacher, Remedial teacher, Teacher of gifted children, Teacher of the hearing impaired, Teacher of the sight impaired</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BCIO:010027</t>
+          <t>BCIO:010085</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4212,38 +4347,34 @@
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>informal education student role</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>vocational education teacher</t>
-        </is>
-      </c>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches or instructs vocational or occupational subjects in adult and further education institutions and to senior students in secondary schools and colleges.</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr"/>
+          <t>A student or trainee that is currently learning in a non-institutional setting.</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr"/>
-      <c r="R102" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
-          <t>Automotive technology instructor, Cosmetology instructor, Vocational education teacher</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BCIO:010032</t>
+          <t>BCIO:010088</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4252,38 +4383,38 @@
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>higher education student role</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>music teacher</t>
-        </is>
-      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches students in the practice, theory and performance of music in private or small group tuition or within mainstream educational institutions.</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr"/>
+          <t>A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school.</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr"/>
-      <c r="R103" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>Guitar teacher (private tuition), Piano teacher (private tuition), Singing teacher (private tuition), Violin teacher (private tuition)</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BCIO:010026</t>
+          <t>BCIO:010092</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4293,37 +4424,37 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>doctoral student role</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>university and higher education teacher</t>
-        </is>
-      </c>
+      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t>A teaching professional that prepares and delivers lectures and conduct tutorials in one or more subjects within a prescribed course of study at a university or other higher educational institution. They conduct research, and prepare scholarly papers and books.</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr"/>
+          <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr"/>
-      <c r="R104" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>PhD student</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>Higher education lecturer, Professor, University lecturer, University tutor</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BCIO:010030</t>
+          <t>BCIO:010090</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4333,37 +4464,37 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>graduate student role</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>early childhood educator</t>
-        </is>
-      </c>
+      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
-          <t>A teaching professional that promotes the social, physical, and intellectual development of children below primary school age through the provision of educational and play activities.</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr"/>
+          <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr"/>
-      <c r="R105" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>graduate student</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>Early childhood educator, Pre-school teacher</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BCIO:010033</t>
+          <t>BCIO:010089</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4373,37 +4504,37 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>undergraduate student role</t>
+        </is>
+      </c>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>arts teacher</t>
-        </is>
-      </c>
+      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
-          <t>A teaching professional  that teaches students in the practice, theory and performance of dance, drama, visual and other arts (excluding music) in private or small group tuition or within mainstream educational institutions.</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr"/>
+          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr"/>
-      <c r="R106" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>undergraduate student</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>Dance teacher (private tuition), Drama teacher (private tuition), Painting teacher (private tuition), Sculpture teacher (private tuition)</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BCIO:010044</t>
+          <t>BCIO:010091</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4413,33 +4544,37 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>technician and associate professional</t>
-        </is>
-      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>masters student role</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
-          <t>A professional that performs technical and related tasks connected with research and the application of scientific or artistic concepts and operational methods, and government or business regulations.</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr"/>
+          <t>A higher education student  role realised by currently studying for a masters degree.</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr"/>
-      <c r="R107" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>MSc student, Masters student</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BCIO:010065</t>
+          <t>BCIO:010086</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4448,38 +4583,34 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>school student role</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>artistic, cultural and culinary associate professional</t>
-        </is>
-      </c>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
-          <t>A technician and associate professional that combines creative skills and technical and cultural knowledge in creative media or food.</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr"/>
+          <t>A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting.</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr"/>
-      <c r="R108" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
-          <t>Photographer, Interior designers and decorator, Gallery, museum and library technician, Chef</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BCIO:010061</t>
+          <t>BCIO:010000</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4487,39 +4618,35 @@
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>behaviour change intervention source</t>
+        </is>
+      </c>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>sport and fitness worker</t>
-        </is>
-      </c>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
-          <t>A technician and associate professional that prepares for and competes in sporting events for financial gain, trains amateur and professional sportsmen and women to enhance performance, promotes participation and standards in sport, organises and officiates sporting events, or provides instruction, training and supervision for various forms of exercise and other recreational activities.</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr"/>
+          <t>A role played by a person, population or organisation that provides a BCI.</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr"/>
-      <c r="R109" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
-          <t>physical activity professional, exercise physiologist, exercise therapist, exercise specialist</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BCIO:010064</t>
+          <t>BCIO:010001</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4528,38 +4655,34 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>person source role</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>fitness and recreation instructor and programme leader</t>
-        </is>
-      </c>
+      <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that leads, guides and instructs groups and individuals in recreational, fitness or outdoor adventure activities.</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr"/>
+          <t>A behaviour change intervention source role that inheres in a person.</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr"/>
-      <c r="R110" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
-          <t>Aerobics instructor, Fitness instructor, Horse riding instructor, Outdoor adventure guide, Personal trainer, Sailing instructor, Underwater diving instructor</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BCIO:010062</t>
+          <t>BCIO:010134</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4568,38 +4691,34 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>source involved in development of intervention</t>
+        </is>
+      </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>athlete and sports player</t>
-        </is>
-      </c>
+      <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that participates in competitive sporting events. They train and compete, either individually or as part of a team, in their chosen sport.</t>
-        </is>
-      </c>
-      <c r="O111" t="inlineStr"/>
+          <t>A BCI source that is involved in the development of intervention content.</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr"/>
-      <c r="R111" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
-          <t>Athlete, Bicycle racer, Boxer, Chess player , Footballer, Golfer, Hockey player, Jockey, Poker player, Racing driver, Skier, Tennis player, Wrestler</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BCIO:010063</t>
+          <t>BCIO:010135</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4609,37 +4728,33 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>source involved in co-production of intervention</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>sports coach, instructor and official</t>
-        </is>
-      </c>
+      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that works with amateur and professional sportspersons to enhance performance and encourage greater participation in sport, and organizes and officiates in sporting events according to established rules.</t>
-        </is>
-      </c>
-      <c r="O112" t="inlineStr"/>
+          <t>A source involved in development of intervention that has developed the intervention content in collaboration with key stakeholders such as patients or community members.</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr"/>
-      <c r="R112" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
-          <t>Referee, Ski instructor, Sports coach, Sports official, Swimming instructor</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BCIO:010058</t>
+          <t>BCIO:010138</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4648,38 +4763,34 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>organisational source role</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>legal and related associate professional</t>
-        </is>
-      </c>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs support functions in courts of law or in law offices, provide services related to such legal matters as insurance contracts, the transferring of property and the granting of loans and other financial transactions, or conduct investigations for clients.</t>
-        </is>
-      </c>
-      <c r="O113" t="inlineStr"/>
+          <t>A BCI source role that is borne by an organisation.</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr"/>
-      <c r="R113" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
-          <t>Bailiff, Judge’s clerk, Conveyancing clerk, Court clerk, Justice of the peace, Law clerk, Legal assistant, Paralegal, Private detective, Title searcher</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BCIO:010060</t>
+          <t>BCIO:010133</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -4688,78 +4799,57 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>source role related to intervention</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>religious associate professional</t>
-        </is>
-      </c>
+      <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
-          <t>A technician and associate professional that provides support to ministers of religion or to a religious community, undertake religious works, preach and propagate the teachings of a particular religion and endeavour to improve well-being through the power of faith and spiritual advice.</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr"/>
+          <t>A BCI source whose occupational or voluntary role is focused on delivery of the behaviour change intervention.</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr"/>
-      <c r="R114" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
-          <t>Faith healer, Lay preacher, Monk, Nun</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BCIO:010057</t>
+          <t>BFO:0000016</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>business and administration associate professional</t>
-        </is>
-      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>A technician and associate professional that performs mostly technical tasks connected with the practical application of knowledge relating to financial accounting and transaction matters, mathematical calculations, human resource development, selling and buying financial instruments, specialized secretarial tasks and enforcing or applying government rules.</t>
-        </is>
-      </c>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="R115" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>Financial and Mathematical associate professional, Sales and purchasing agent, Broker, Business Services Agent, Administrative and Specialized Secretary, Government regulatory associate professional, Medical secretary</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BCIO:010045</t>
+          <t>BCIO:010120</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4767,39 +4857,35 @@
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>expertise of person source</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>health associate professional</t>
-        </is>
-      </c>
+      <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs technical and practical tasks to support diagnosis and treatment of illness, disease, injuries and impairments in humans or animals, and supports the implementation of health care usually established by medical, veterinary, nursing and other health professionals.</t>
-        </is>
-      </c>
-      <c r="O116" t="inlineStr"/>
+          <t>A disposition that is an expert skill or knowledge held by the source delivering the behaviour change intervention.</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr"/>
-      <c r="R116" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
-          <t>Veterinary Technician</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BCIO:010051</t>
+          <t>BCIO:010121</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4808,38 +4894,38 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>knowledge or skill</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>dental assistant and therapist</t>
-        </is>
-      </c>
+      <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
-          <t>A health associate professional that provides basic dental care services for the prevention and treatment of diseases and disorders of the teeth and mouth, according to care plans and procedures established by a dentist or other oral health professional.</t>
-        </is>
-      </c>
-      <c r="O117" t="inlineStr"/>
+          <t>An expertise of person source that is knowledge or skills held in order to deliver the behaviour change intervention.</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr"/>
-      <c r="R117" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>trained (if unclear whether pre-existing or acquired)</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>Dental assistant, Dental hygienist , Dental therapist</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BCIO:010056</t>
+          <t>BCIO:010125</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4849,37 +4935,33 @@
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>acquired knowledge or skill</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>ambulance worker</t>
-        </is>
-      </c>
+      <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
-          <t>A health associate professional that provides emergency health care to patients who are injured, sick, infirm or otherwise physically or mentally impaired prior to and during transport to medical facilities.</t>
-        </is>
-      </c>
-      <c r="O118" t="inlineStr"/>
+          <t>A knowledge or skill that is additional knowledge or skills supplied to the source to allow them to deliver the behaviour change intervention, including educational level and qualifications.</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr"/>
-      <c r="R118" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
-          <t>Ambulance officer, Ambulance paramedic, Emergency medical technician, Emergency paramedic</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BCIO:010050</t>
+          <t>BCIO:010122</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -4889,37 +4971,37 @@
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>pre-existing knowledge or skill</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>traditional and complementary medicine associate professional</t>
-        </is>
-      </c>
+      <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
-          <t>A health associate professional that prevents and treats human physical and mental illnesses, disorders and injuries using herbal and other therapies based on theories, beliefs and experiences originating in specific cultures. They administer treatments using traditional techniques and medicaments, either acting independently or according to therapeutic care plans established by a traditional medicine or other health professional.</t>
-        </is>
-      </c>
-      <c r="O119" t="inlineStr"/>
+          <t>A knowledge or skill that is already possessed by the source which allows them to deliver the behaviour change intervention, including educational level and qualifications.</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr"/>
-      <c r="R119" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree, certification, accredited, qualified</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>Acupuncture technician, Ayurvedic technician, Bonesetter, Herbalist , Homeopathy technician, Scraping and cupping therapist, Village healer, Witch doctor</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BCIO:010053</t>
+          <t>BCIO:010127</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -4930,116 +5012,92 @@
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>affiliation to a formal group or organisation</t>
+        </is>
+      </c>
       <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>physiotherapy technician and assistant</t>
-        </is>
-      </c>
+      <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr">
         <is>
-          <t>A health associate professional that provides physical therapeutic treatments to patients in circumstances where functional movement is threatened by injury, disease or impairment. Therapies are usually provided according to rehabilitative plans established by a physiotherapist or other health professional.</t>
-        </is>
-      </c>
-      <c r="O120" t="inlineStr"/>
+          <t>A pre-existing knowledge or skill that is recognised through affiliation to a formal group or organisation.</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr"/>
-      <c r="R120" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>member of British Psychological Society</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>Acupressure therapist, Electrotherapist, Hydrotherapist, Massage therapist, Physical rehabilitation technician, Physiotherapy technician, Shiatsu therapist</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BCIO:010047</t>
+          <t>MF:0000030</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>representation</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>nursing and midwifery associate professional</t>
-        </is>
-      </c>
+      <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr">
         <is>
-          <t>A health associate professional that provides basic nursing and personal care for people who are physically or mentally ill, disabled or infirm, and for others in need of care due to potential risks to health including before, during and after childbirth. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing, midwifery and other health professionals.</t>
-        </is>
-      </c>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="R121" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>Practice assistant, Quit Smoking Counsellor, Health educator, Dispensing Optician, Information Technician</t>
+          <t>A dependent continuant which is about a portion of reality.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BCIO:010048</t>
+          <t>MF:0000031</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>cognitive representation</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>nursing associate professional</t>
-        </is>
-      </c>
+      <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr">
         <is>
-          <t>A nursing and midwifery associate professional that provides basic nursing and personal care for people in need of such care due to effects of ageing, illness, injury, or other physical or mental impairment. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing and other health professionals.</t>
-        </is>
-      </c>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-      <c r="R122" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>Assistant nurse, Associate professional nurse, Enrolled nurse, Practical nurse</t>
+          <t>A representation which specifically depends on an anatomical structure in the cognitive system of an organism.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BCIO:010049</t>
+          <t>ADDICTO:0000381</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -5047,39 +5105,27 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>midwifery associate professional</t>
-        </is>
-      </c>
+      <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr">
         <is>
-          <t>A nursing and midwifery associate professional that provides basic health care and advice before, during and after pregnancy and childbirth. They implement care, treatment and referral plans usually established by medical, midwifery and other health professionals.</t>
-        </is>
-      </c>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="R123" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>Assistant midwife, Traditional midwife</t>
+          <t>A cognitive representation of themselves by a person or a group about themselves.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BCIO:010052</t>
+          <t>ADDICTO:0000399</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -5088,38 +5134,26 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>self-identity</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>community health worker</t>
-        </is>
-      </c>
+      <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr">
         <is>
-          <t>A health associate professional that provides health education, referral and follow-up, case management, basic preventive health care and home visiting services to specific communities. They provide support and assistance to individuals and families in navigating the health and social services system.</t>
-        </is>
-      </c>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-      <c r="R124" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>Community health aide, Community health promoter, Community health worker, Village health worker, outreach worker, health worker</t>
+          <t>An identity that a person has about themselves.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BCIO:010046</t>
+          <t>BCIO:015098</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -5129,37 +5163,33 @@
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>gender identity</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>medical and pharmaceutical technician</t>
-        </is>
-      </c>
+      <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr">
         <is>
-          <t>A health associate professional that performs technical tasks to assist in diagnosis and treatment of illness, disease, injuries and impairments.</t>
-        </is>
-      </c>
-      <c r="O125" t="inlineStr"/>
+          <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr"/>
-      <c r="R125" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
-          <t>Medical imaging and therapeutic equipment technician, Medical and Pathology laboratory technician, Pharmaceutical technician, Medical and dental prosthetic technician</t>
-        </is>
-      </c>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BCIO:010055</t>
+          <t>BCIO:010111</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -5170,37 +5200,36 @@
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>female gender</t>
+        </is>
+      </c>
       <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>environmental and occupational health inspector and associate</t>
-        </is>
-      </c>
+      <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
-          <t>A health associate professional that investigates the implementation of rules and regulations relating to environmental factors that may affect human health, safety in the 
-workplace, and safety of processes for the production of goods and services. They may implement and evaluate programmes to restore or improve safety and sanitary conditions under the supervision of a health professional.</t>
-        </is>
-      </c>
-      <c r="O126" t="inlineStr"/>
+          <t>A gender identity as being female.</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr"/>
-      <c r="R126" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>female, woman</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>Food sanitation and safety inspector, Health inspector, Occupational health and safety inspector, Pollution inspector, Product safety inspector, Sanitarian, Sanitary inspector</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BCIO:010054</t>
+          <t>BCIO:010112</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -5211,272 +5240,268 @@
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>male gender</t>
+        </is>
+      </c>
       <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>medical assistant</t>
-        </is>
-      </c>
+      <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
-          <t>A health associate professional that performs basic clinical and administrative tasks to support patient care under the direct supervision of a medical practitioner or other health professional.</t>
-        </is>
-      </c>
-      <c r="O127" t="inlineStr"/>
+          <t>A gender identity as being male.</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr"/>
-      <c r="R127" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>male, man</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>Clinical assistant, Medical assistant, Ophthalmic assistant</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BCIO:010059</t>
+          <t>BCIO:010108</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>socio demographic attribute of person source</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>social work associate professional</t>
-        </is>
-      </c>
+      <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr">
         <is>
-          <t>A technician and associate professional that implements social assistance programmes and community services and assist clients to deal with personal and social problems.</t>
-        </is>
-      </c>
-      <c r="O128" t="inlineStr"/>
+          <t>A social or demographic characteristic of a human being who is the bearer of a person source role.</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr"/>
-      <c r="R128" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
-          <t>Community development worker, Community services worker, Crisis intervention worker, Disability services worker, Family services worker, Life skills instructor, Mental health support worker, Welfare support worker, Women’s shelter supervisor, Youth services worker</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BCIO:010066</t>
+          <t>BCIO:010116</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>language proficiency of person source</t>
+        </is>
+      </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>information and communications technician</t>
-        </is>
-      </c>
+      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
-          <t>A technician and associate professional that provides support for the day to day running of computer systems, communication systems and networks, broadcast images and sound, telecommunication signals on land, sea or in aircraft.</t>
-        </is>
-      </c>
-      <c r="O129" t="inlineStr"/>
+          <t>A socio-demographic attribute of person source that is an individual’s ability to speak or perform in the intervention language.</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr"/>
-      <c r="R129" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>fluent, native</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>Information and Communications Technology Operations and User Support Technician, Telecommunications and Broadcasting Technician</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BCIO:010034</t>
+          <t>BCIO:010117</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>health status of person source</t>
+        </is>
+      </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>legal, social and cultural professional</t>
-        </is>
-      </c>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr">
         <is>
-          <t>A professional that conducts research, improves or develops concepts, theories and operational methods, or applies knowledge relating to the law, social or cultural studies.</t>
-        </is>
-      </c>
-      <c r="O130" t="inlineStr"/>
+          <t>A socio-demographic attribute of person source that represents their mental or physical condition.</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr"/>
-      <c r="R130" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>diabetes, cancer, depression, obesity, overweight</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BCIO:010041</t>
+          <t>BCIO:010109</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>age of person source</t>
+        </is>
+      </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>author and journalist</t>
-        </is>
-      </c>
+      <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conceives and creates literary works, and interprets and communicates news and public affairs through the media.</t>
-        </is>
-      </c>
-      <c r="O131" t="inlineStr"/>
+          <t>A socio-demographic attribute of person source that is a time quality inhering in a bearer by virtue of how long the bearer has existed.</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr"/>
-      <c r="R131" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
-          <t>Author, Writer, Journalist, Translator, News anchor</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BCIO:010042</t>
+          <t>BCIO:010114</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>ethnic group membership of person source</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>linguist</t>
-        </is>
-      </c>
+      <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that translates or interprets from one language into another.</t>
-        </is>
-      </c>
-      <c r="O132" t="inlineStr"/>
+          <t>A socio-demographic attribute of person source that is the ethnic group to which an individual identifies as belonging, where an ethic group is a population whose members have a common heritage that is real or presumed such as common culture, language, religion, behaviour or biological trait.</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr"/>
-      <c r="R132" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>black, white, Indian, Chinese, Somalian</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>Interpretator; other linguist</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BCIO:010036</t>
+          <t>BCIO:010110</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>gender of person source</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>librarian, archivist and curator</t>
-        </is>
-      </c>
+      <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that develops and maintains collections of archives, libraries, museums, art galleries and similar establishments.</t>
-        </is>
-      </c>
-      <c r="O133" t="inlineStr"/>
+          <t>A socio-demographic attribute of person source that is an individual's perception of having a particular gender, which may or may not correspond with their birth sex.</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr"/>
-      <c r="R133" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>gender</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>Librarian, Archivist,  Curator</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BCIO:010035</t>
+          <t>BCIO:010113</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5484,164 +5509,164 @@
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>other gender</t>
+        </is>
+      </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>legal professional</t>
-        </is>
-      </c>
+      <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conducts research on legal problems, advises clients on legal aspects of problems, pleads cases or conducts prosecutions in courts of law, presides over judicial proceedings in courts of law and draft laws and regulations.</t>
-        </is>
-      </c>
-      <c r="O134" t="inlineStr"/>
+          <t>A gender of person source that reports not belonging to the cultural gender role distinctions of either male or female.</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr"/>
-      <c r="R134" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>non-binary, transexual</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>Lawyer, Judge, Coroner</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BCIO:010040</t>
+          <t>BCIO:010119</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>psychological influence on intervention delivery of person source</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>religious professional</t>
-        </is>
-      </c>
+      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that functions  as a perpetuator of sacred traditions, practices and beliefs. They conduct religious services, celebrate or administer the rites of a religious faith or denomination, provide spiritual and moral guidance and perform other functions associated with the practice of a religion.</t>
-        </is>
-      </c>
-      <c r="O135" t="inlineStr"/>
+          <t>A socio-demographic attribute of person source that is their existing psychological attributes related to or potentially affecting the target behaviour.</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr"/>
-      <c r="R135" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
-          <t>Bonze, Imam, Minister of religion, Poojari, Priest, Rabbi</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BCIO:010037</t>
+          <t>BCIO:010115</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>religious group membership of person source</t>
+        </is>
+      </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>social professional</t>
-        </is>
-      </c>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conducts research, improves or develops concepts, theories and operational methods or applies knowledge relating to psychology, sociology, philosophy, politics, economics, sociology, anthropology, history and other social sciences, or provides social services to meet the needs of individuals and families in a community.</t>
-        </is>
-      </c>
-      <c r="O136" t="inlineStr"/>
+          <t>A socio-demographic attribute of person source that is a religious group to which an individual identifies as belonging, where a religious group is a group of people characterised by the practice of a common religion.</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr"/>
-      <c r="R136" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>Muslim, Christian, Hindu, Sikh, Buddhist, Judaism</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>Economist, Sociologist, Anthropologist, Philosopher, Historian, Political Scientist</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BCIO:010038</t>
+          <t>BCIO:010118</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>target behaviour of person source</t>
+        </is>
+      </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>psychologist</t>
-        </is>
-      </c>
+      <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr">
         <is>
-          <t>A social professional that studies the mental processes and behaviour of human beings as individuals or in groups, and applies this knowledge to promote personal, social, educational or occupational adjustment and development.</t>
-        </is>
-      </c>
-      <c r="O137" t="inlineStr"/>
+          <t>A socio-demographic attribute of person source that is their amount or experience of the intervention’s target behaviour.</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr"/>
-      <c r="R137" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>source is highly physically active</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>Clinical psychologist, Counselling psychologist, Educational psychologist, Forensic psychologist, Health psychologist, Neuropsychologist, Organizational psychologist, Psychotherapist, Sport and exercise psychologist</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BCIO:010039</t>
+          <t>BFO:0000031</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>generically dependent continuant</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
@@ -5649,114 +5674,74 @@
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>social work and counselling professional</t>
-        </is>
-      </c>
+      <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr">
         <is>
-          <t>A social professional that provides advice and guidance to individuals, families, groups, communities and organizations in response to social and personal difficulties. They assist clients to develop skills and access resources and support services needed to respond to issues arising from unemployment, poverty, disability, addiction, criminal and delinquent behaviour, marital and other problems.</t>
-        </is>
-      </c>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
-      <c r="R138" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>Counsellor, Addictions counsellor, Bereavement counsellor, Child and youth counsellor, District social welfare officer, Family counsellor, Marriage counsellor, Parole officer, Probation officer, Sexual assault counsellor, Social worker, Women’s welfare organizer</t>
+          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BCIO:010043</t>
+          <t>IAO:0000030</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>information content entity</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>creative and performing artist</t>
-        </is>
-      </c>
+      <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that communicates ideas, impressions and facts in a wide range of media to achieve particular effects, interprets a composition such as a musical score or a script to perform or direct the performance, and hosts the presentation of such performance and other media events.</t>
-        </is>
-      </c>
-      <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
-      <c r="R139" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>Visual artist, Musician, Singer, Composer, Dancer, Choreographer, Director, Producer, Actor, Announcer on radio, television and other media</t>
+          <t>A generically dependent continuant that is about some thing.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BCIO:010005</t>
+          <t>IAO:0000027</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>manager</t>
-        </is>
-      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr">
         <is>
-          <t>An occupational role of source that manages, plans and coordinates the overall activities of enterprises, governments and other organisations.</t>
-        </is>
-      </c>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
-      <c r="R140" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>Chief Executive Officers; Administrative Managers;  Commercial Managers</t>
+          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BCIO:010082</t>
+          <t>BCIO:010107</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -5764,39 +5749,35 @@
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>total number of people able to deliver intervention</t>
+        </is>
+      </c>
       <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>armed forces occupation</t>
-        </is>
-      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr">
         <is>
-          <t>An occupational role that includes all jobs held by members of the armed forces.</t>
-        </is>
-      </c>
-      <c r="O141" t="inlineStr"/>
+          <t>A count data item that is the total number of providers that are available and able to deliver the intervention.</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr"/>
-      <c r="R141" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
-          <t>Admiral, Air commodore, Air marshal, Airman, Brigadier (army), Bombardier, Captain (air force), Captain (army), Captain (navy), Colonel (army), Corporal,  Field marshal, Flight lieutenant (air force), Flying officer (military), General (army), Gunner, Group captain, (air force), Lieutenant (army), Major (army), Midshipman, Naval officer (military) , Navy commander, Officer cadet (armed forces), Paratrooper, Rifleman, Sergeant (army), Second lieutenant (army), Seaman, Squadron leader, Sublieutenant (navy), Wing commander</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BCIO:010079</t>
+          <t>BCIO:010106</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -5804,39 +5785,35 @@
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>number of people delivering intervention to each participant</t>
+        </is>
+      </c>
       <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>plant and machine operator</t>
-        </is>
-      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr">
         <is>
-          <t>An occupational role that operates and monitors industrial and agricultural machinery and equipment on the spot or by remote control, or drives and operates trains, motor vehicles and mobile machinery and equipment.</t>
-        </is>
-      </c>
-      <c r="O142" t="inlineStr"/>
+          <t>A count data item that is the number of providers that an individual participant in the intervention encounters.</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr"/>
-      <c r="R142" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
-          <t>Stationary Plant and Machine Operator, Driver, Mobile Plant Operator</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BCIO:010078</t>
+          <t>BCIO:010126</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -5844,50 +5821,50 @@
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>amount of experience</t>
+        </is>
+      </c>
       <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>craft and related trades worker</t>
-        </is>
-      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr">
         <is>
-          <t>An occupational role that applies specific technical and practical knowledge and skills to construct and maintain buildings, machinery, equipment or tools, carries out printing work, and produces or processes foodstuffs, textiles and wooden, metal and other articles, including handicraft goods.</t>
-        </is>
-      </c>
-      <c r="O143" t="inlineStr"/>
+          <t>A knowledge or skill that is the duration of experience in related domain held by person source.</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr"/>
-      <c r="R143" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>full-day, 6 years</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>Building Trade Worker, Metal Workers, Machinery Worker, Handicraft Worker, Printing Worker, Electrical Equipment Installers and Repairer, Electronics and Telecommunications Installer and Repairer, Food Processing Worker, Woodworker, Tobacco Product Maker</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BFO:0000016</t>
+          <t>BFO:0000004</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>independent continuant</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>disposition</t>
-        </is>
-      </c>
+      <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
@@ -5895,23 +5872,28 @@
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BCIO:010120</t>
+          <t>BFO:0000040</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>expertise of person source</t>
-        </is>
-      </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
@@ -5920,35 +5902,27 @@
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr">
         <is>
-          <t>A disposition that is an expert skill or knowledge held by the source delivering the behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
-      <c r="R145" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S145" t="inlineStr"/>
+          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BCIO:010121</t>
+          <t>OGMS:0000087</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>extended organism</t>
+        </is>
+      </c>
       <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>knowledge or skill</t>
-        </is>
-      </c>
+      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
@@ -5956,26 +5930,14 @@
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr">
         <is>
-          <t>An expertise of person source that is knowledge or skills held in order to deliver the behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="O146" t="inlineStr"/>
-      <c r="P146" t="inlineStr"/>
-      <c r="R146" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>trained (if unclear whether pre-existing or acquired)</t>
+          <t>An object aggregate consisting of an organism and all material entities located within the organism, overlapping the organism, or occupying sites formed in part by the organism.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BCIO:010125</t>
+          <t>MF:0000016</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -5983,35 +5945,35 @@
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>human being</t>
+        </is>
+      </c>
       <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>acquired knowledge or skill</t>
-        </is>
-      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr">
         <is>
-          <t>A knowledge or skill that is additional knowledge or skills supplied to the source to allow them to deliver the behaviour change intervention, including educational level and qualifications.</t>
-        </is>
-      </c>
-      <c r="O147" t="inlineStr"/>
+          <t>An extended organism that is a member of the species Homo sapiens.</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr"/>
-      <c r="R147" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BCIO:010122</t>
+          <t>BCIO:010095</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -6020,38 +5982,34 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>pre-existing knowledge or skill</t>
-        </is>
-      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>family member</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr">
         <is>
-          <t>A knowledge or skill that is already possessed by the source which allows them to deliver the behaviour change intervention, including educational level and qualifications.</t>
-        </is>
-      </c>
-      <c r="O148" t="inlineStr"/>
+          <t>A person who is a member of a group of persons united by blood, or by marriage or other legal arrangement, or by self-identity as belonging to the same family.</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr"/>
-      <c r="R148" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q148" t="inlineStr"/>
       <c r="S148" t="inlineStr">
         <is>
-          <t>Bachelor’s degree, certification, accredited, qualified</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BCIO:010127</t>
+          <t>BCIO:010097</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -6061,121 +6019,157 @@
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>affiliation to a formal group or organisation</t>
-        </is>
-      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>spouse or partner</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr">
         <is>
-          <t>A pre-existing knowledge or skill that is recognised through affiliation to a formal group or organisation.</t>
-        </is>
-      </c>
-      <c r="O149" t="inlineStr"/>
+          <t>A family member that is an individual who is married or in a committed relationship with another individual.</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr"/>
-      <c r="R149" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>boyfriend, girlfriend, partner, fiance, wife, husband</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>member of British Psychological Society</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BFO:0000031</t>
+          <t>BCIO:010099</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>generically dependent continuant</t>
-        </is>
-      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>child relationship</t>
+        </is>
+      </c>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr">
         <is>
-          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
-        </is>
-      </c>
+          <t>A family member that is an offspring relationship from a person to their parent.</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>daughter, son, step-daughter, step-son</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>IAO:0000030</t>
+          <t>BCIO:010098</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>information content entity</t>
-        </is>
-      </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>sibling relationship</t>
+        </is>
+      </c>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr">
         <is>
-          <t>A generically dependent continuant that is about some thing.</t>
-        </is>
-      </c>
+          <t>A family member that is a family relationship between two persons with at least one shared parent.</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>brother, sister, step-brother, step-sister</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>IAO:0000027</t>
+          <t>BCIO:010096</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
+      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>parent or guardian</t>
+        </is>
+      </c>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
-          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
-        </is>
-      </c>
+          <t>A family member that is a mother, father or legal carer of a child.</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>mother, father, step-mother, step-father, guardian</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BCIO:010107</t>
+          <t>BCIO:010002</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -6183,12 +6177,12 @@
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>total number of people able to deliver intervention</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>person source</t>
+        </is>
+      </c>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
@@ -6196,22 +6190,22 @@
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr">
         <is>
-          <t>A count data item that is the total number of providers that are available and able to deliver the intervention.</t>
-        </is>
-      </c>
-      <c r="O153" t="inlineStr"/>
+          <t>A person who is the bearer of a behaviour change intervention source role.</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr"/>
-      <c r="R153" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BCIO:010126</t>
+          <t>BCIO:050842</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -6219,12 +6213,12 @@
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>amount of experience</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>role model for a person</t>
+        </is>
+      </c>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
@@ -6232,38 +6226,39 @@
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr">
         <is>
-          <t>A knowledge or skill that is the duration of experience in related domain held by person source.</t>
-        </is>
-      </c>
-      <c r="O154" t="inlineStr"/>
+          <t>A &lt;person&gt; that influences a recipient by being perceived to be similar or admired.</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>This class lies at the intersection between a person and their environment and is defined from the perspective of the person.</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr"/>
-      <c r="R154" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q154" t="inlineStr"/>
       <c r="S154" t="inlineStr">
         <is>
-          <t>full-day, 6 years</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BCIO:010106</t>
+          <t>BCIO:010139</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>number of people delivering intervention to each participant</t>
-        </is>
-      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>organisation source</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
@@ -6272,33 +6267,33 @@
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr">
         <is>
-          <t>A count data item that is the number of providers that an individual participant in the intervention encounters.</t>
-        </is>
-      </c>
-      <c r="O155" t="inlineStr"/>
+          <t>An organisation that is the bearer of a behaviour change intervention source role, such as voluntary, public or commercial organisations delivering a behaviour change intervention.</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr"/>
-      <c r="R155" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BFO:0000003</t>
+          <t>OBI:0000245</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>occurrent</t>
-        </is>
-      </c>
+      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>organisation</t>
+        </is>
+      </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
@@ -6308,23 +6303,31 @@
       <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr">
         <is>
-          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
-        </is>
-      </c>
+          <t>An entity that can bear roles, has members, and has a set of organization rules. Members of organizations are either organizations themselves or individual people. Members can bear specific organization member roles that are determined in the organization rules. The organization rules also determine how decisions are made on behalf of the organization by the organization members.</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BFO:0000015</t>
+          <t>BFO:0000003</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>process</t>
-        </is>
-      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>occurrent</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
@@ -6336,24 +6339,24 @@
       <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr">
         <is>
-          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
+          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BCIO:010130</t>
+          <t>BFO:0000015</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>payment of person source</t>
-        </is>
-      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
@@ -6364,33 +6367,25 @@
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr">
         <is>
-          <t>A process in which a person source is paid or compensated for delivering the intervention.</t>
-        </is>
-      </c>
-      <c r="O158" t="inlineStr"/>
-      <c r="P158" t="inlineStr"/>
-      <c r="R158" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S158" t="inlineStr"/>
+          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BCIO:010132</t>
+          <t>BCIO:010130</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>non-monetary payment</t>
-        </is>
-      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>payment of person source</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
@@ -6400,21 +6395,17 @@
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr">
         <is>
-          <t>A payment of person source that is non-monetary compensation given to the source for delivering the intervention.</t>
-        </is>
-      </c>
-      <c r="O159" t="inlineStr"/>
+          <t>A process in which a person source is paid or compensated for delivering the intervention.</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr"/>
-      <c r="R159" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="Q159" t="inlineStr"/>
       <c r="S159" t="inlineStr">
         <is>
-          <t>course credit</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6443,34 +6434,34 @@
           <t>A payment of person source that is money, vouchers or valued objects given to the source for delivering the intervention.</t>
         </is>
       </c>
-      <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr"/>
-      <c r="R160" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>paid in cash, vouchers</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>paid in cash, vouchers</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BCIO:010129</t>
+          <t>BCIO:010132</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>volunteering of person source</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>non-monetary payment</t>
+        </is>
+      </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
@@ -6480,26 +6471,26 @@
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr">
         <is>
-          <t>A process in which a person source delivers the intervention on a voluntary basis without formal compensation.</t>
-        </is>
-      </c>
-      <c r="O161" t="inlineStr"/>
+          <t>A payment of person source that is non-monetary compensation given to the source for delivering the intervention.</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr"/>
-      <c r="R161" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>course credit</t>
         </is>
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>voluntary basis, volunteering</t>
-        </is>
-      </c>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BCIO:010128</t>
+          <t>BCIO:010129</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -6507,7 +6498,7 @@
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>supervision of person source</t>
+          <t>volunteering of person source</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -6520,21 +6511,61 @@
       <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr">
         <is>
+          <t>A process in which a person source delivers the intervention on a voluntary basis without formal compensation.</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>voluntary basis, volunteering</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>BCIO:010128</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>supervision of person source</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr">
+        <is>
           <t>A process in which a person source is formally provided, by an individual with appropriate expertise, with corrective and skill-enhancing feedback, regarding the person source’s performance in delivering the intervention.</t>
         </is>
       </c>
-      <c r="O162" t="inlineStr"/>
-      <c r="P162" t="inlineStr"/>
-      <c r="R162" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="S162" t="inlineStr">
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr">
         <is>
           <t>supervised</t>
         </is>
       </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Source/BCIO-source-hierarchy.xlsx
+++ b/Source/BCIO-source-hierarchy.xlsx
@@ -450,27 +450,27 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>synonyms</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>subontology</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>crossreference</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>examples</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>subontology</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>synonyms</t>
         </is>
       </c>
     </row>
@@ -561,14 +561,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BFO:0000020</t>
+          <t>BFO:0000031</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>specifically dependent continuant</t>
+          <t>generically dependent continuant</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -582,14 +582,14 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>b is a specifically dependent continuant = Def. b is a continuant and there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
+          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCIO:010123</t>
+          <t>IAO:0000030</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -597,7 +597,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>expertise discipline</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -610,31 +610,14 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>An attribute that is a field of knowledge or practice.</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>The division of expertise into different disciplines or fields is complex and depends on historical, social and structural factors.</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>A generically dependent continuant that is about some thing.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCIO:010093</t>
+          <t>IAO:0000027</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -643,7 +626,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>discipline of current programme of study or training</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -655,38 +638,26 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>An expertise discipline of the programme of study currently undertaken by the bearer of a student or trainee role.</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>psychology, medicine, hairdressing</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
+          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:010124</t>
+          <t>BCIO:010126</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>discipline of pre-existing knowledge or skill</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>amount of experience</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -695,38 +666,38 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>The expertise discipline in which the person source has acquired their pre-existing knowledge and skills.</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
+          <t>A knowledge or skill that is the duration of experience in related domain held by person source.</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>full-day, 6 years</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BFO:0000017</t>
+          <t>BCIO:010106</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>realizable</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>number of people delivering intervention to each participant</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -735,26 +706,34 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>A specifically dependent continuant  that inheres in continuant  entities and are not exhibited in full at every time in which it inheres in an entity or group of entities. The exhibition or actualization of a realizable entity is a particular manifestation, functioning or process that occurs under certain circumstances.</t>
-        </is>
-      </c>
+          <t>A count data item that is the number of providers that an individual participant in the intervention encounters.</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BFO:0000023</t>
+          <t>BCIO:010107</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>total number of people able to deliver intervention</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -763,26 +742,34 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>A realizable entity  the manifestation of which brings about some result or end that is not essential to a continuant  in virtue of the kind of thing that it is but that can be served or participated in by that kind of continuant  in some kinds of natural, social or institutional contexts.</t>
-        </is>
-      </c>
+          <t>A count data item that is the total number of providers that are available and able to deliver the intervention.</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:010003</t>
+          <t>BFO:0000004</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>independent continuant</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>personal role of source</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -791,35 +778,27 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>A role that inheres in a person source.</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:010004</t>
+          <t>BFO:0000040</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>occupational role of source</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -827,66 +806,42 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>A personal role of source that is realised by doing a specified type of work or working in a specified way.</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Interventionist, facilitator, study staff</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
+          <t>An &lt;independent continuant&gt; that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:010005</t>
+          <t>OGMS:0000087</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>extended organism</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>manager</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>An occupational role of source that manages, plans and coordinates the overall activities of enterprises, governments and other organisations.</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Chief Executive Officers; Administrative Managers;  Commercial Managers</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
+          <t>An object aggregate consisting of an organism and all material entities located within the organism, overlapping the organism, or occupying sites formed in part by the organism.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:010067</t>
+          <t>MF:0000016</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -894,39 +849,35 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>human being</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>clerical support worker</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>An occupational role that records, organizes, stores, computes and retrieves information, and performs a number of clerical duties in connection with money-handling operations, travel arrangements, requests for information, and appointments.</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>General and Keyboard Clerk, customers Services Clerk, Numerical and Material Recording Clerk</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>An extended organism that is a member of the species Homo sapiens.</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:010077</t>
+          <t>BCIO:010002</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -935,38 +886,34 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>skilled agricultural, forestry and fishery worker</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>person source</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>An occupational role that grows and harvests plants or animals to provide food, shelter and income for themselves and their households.</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Market gardener, Crop grower, Animal Producer, Mixed Crop and Animal Producer, Forestry worker, Fishery worker, Hunter. Subsistence Crop Farmer, Subsistence Livestock Farmer</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A person who is the bearer of a behaviour change intervention source role.</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:010068</t>
+          <t>BCIO:010095</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -975,34 +922,34 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>services and sales worker</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>family member</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>An occupational role that provides personal or protective services related to travel, house-keeping, catering, personal care, protection against fire and unlawful acts, or sells goods in retail or markets.</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
+          <t>A person who is a member of a group of persons united by blood, or by marriage or other legal arrangement, or by self-identity as belonging to the same family.</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr"/>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:010071</t>
+          <t>BCIO:010099</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1012,37 +959,37 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>personal care worker</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>child relationship</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>A services and sales worker that provides care, supervision and assistance for children, patients and elderly, convalescent or disabled persons in institutional and residential settings.</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Personal carer</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>A family member that is an offspring relationship from a person to their parent.</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>daughter, son, step-daughter, step-son</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:010075</t>
+          <t>BCIO:010098</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1052,37 +999,37 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>sibling relationship</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>home-based personal care worker</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>A personal care worker that provide routine personal care and assistance with activities of daily living to persons who are in need of such care due to effects of ageing, illness, injury, or other physical or mental conditions, in private homes and other independent residential settings.</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Home birth assistant, Home care aide, Nursing aide (home), Personal care provider</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>A family member that is a family relationship between two persons with at least one shared parent.</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>brother, sister, step-brother, step-sister</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:010072</t>
+          <t>BCIO:010096</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1092,37 +1039,37 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>parent or guardian</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>child care worker</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>A personal care worker that provides care and supervision for children in non-domestic settings.</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Babysitter, Child care worker, Creche ayah, Family day care worker, Nanny, Out of school hours care worker</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
+          <t>A family member that is a mother, father or legal carer of a child.</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>mother, father, step-mother, step-father, guardian</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:010073</t>
+          <t>BCIO:010097</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1132,37 +1079,37 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>spouse or partner</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teachers’ aide</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>A personal care worker that performs non-teaching duties to assist teaching staff, and provides care and supervision for children in schools and pre-schools.</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Pre-school assistant, Teacher’s assistant</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
+          <t>A family member that is an individual who is married or in a committed relationship with another individual.</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>boyfriend, girlfriend, partner, fiance, wife, husband</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:010074</t>
+          <t>BCIO:050842</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1171,238 +1118,195 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>role model for a person</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>health care assistant</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>A personal care worker that provides direct personal care and assistance with activities of daily living to patients and residents in a variety of health care settings, working  in implementation of established care plans and practices, and under the direct supervision of medical, nursing or other health professionals or associate professionals.</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Nursing aide (clinic or hospital), Patient care assistant, Psychiatric aid</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A &lt;person&gt; that influences a recipient by being perceived to be similar or admired.</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>This class lies at the intersection between a person and their environment and is defined from the perspective of the person.</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:010076</t>
+          <t>BCIO:010139</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>organisation source</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>protective services worker</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>A services and sales worker that protects individuals and property against fire and other hazards, maintain law and order and enforce laws and regulations.</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Firefighter, Police officer, Prison guard, Security guard, Offender manager</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>An organisation that is the bearer of a behaviour change intervention source role, such as voluntary, public or commercial organisations delivering a behaviour change intervention.</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:010069</t>
+          <t>OBI:0000245</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>organization</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>personal services worker</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>A services and sales worker that provides personal services related to travel, housekeeping, catering and hospitality, hairdressing and beauty treatment, animal care grooming and training, companionship and other services of a personal nature.</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Travel Attendant, Conductor, Guide, Cook, Waiter, Bartender, Hairdresser, Beautician, Housekeeping Supervisor, Astrologer, Fortune-teller, Valet, Undertaker, Embalmer, Pet Groomer, Animal Care Worker</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>An entity that can bear roles, has members, and has a set of organization rules. Members of organizations are either organizations themselves or individual people. Members can bear specific organization member roles that are determined in the organization rules. The organization rules also determine how decisions are made on behalf of the organization by the organization members.</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:010070</t>
+          <t>BFO:0000020</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>characteristic</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>sales worker</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>A services and sales worker that demonstrates goods in wholesale or retail shops, at stalls and markets, door to door, via telephone or customer contact centres. They may record and accept payment for goods and services purchased, and may operate small retail outlets.</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Street Salesperson, Market Salesperson, Shop Salesperson, Cashier, Ticket Clerk, Model, Sales Demonstrator, Door-to-door Salesperson, Contact Centre Salesperson, Service Station Attendant, Food Service Counter Attendant</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
+          <t>b is a relational specifically dependent continuant = Def. b is a specifically dependent continuant and there are n &amp;gt; 1 independent continuants c1, … cn which are not spatial regions are such that for all 1  i &amp;lt; j  n, ci  and cj share no common parts, are such that for each 1  i  n, b s-depends_on ci at every time t during the course of b’s existence (axiom label in BFO2 Reference: [131-004])</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:010082</t>
+          <t>BFO:0000017</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>realizable</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>armed forces occupation</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>An occupational role that includes all jobs held by members of the armed forces.</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Admiral, Air commodore, Air marshal, Airman, Brigadier (army), Bombardier, Captain (air force), Captain (army), Captain (navy), Colonel (army), Corporal,  Field marshal, Flight lieutenant (air force), Flying officer (military), General (army), Gunner, Group captain, (air force), Lieutenant (army), Major (army), Midshipman, Naval officer (military) , Navy commander, Officer cadet (armed forces), Paratrooper, Rifleman, Sergeant (army), Second lieutenant (army), Seaman, Squadron leader, Sublieutenant (navy), Wing commander</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr"/>
+          <t>A specifically dependent continuant  that inheres in continuant  entities and are not exhibited in full at every time in which it inheres in an entity or group of entities. The exhibition or actualization of a realizable entity is a particular manifestation, functioning or process that occurs under certain circumstances.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:010083</t>
+          <t>BFO:0000023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>researcher</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>A occupational role played by a person that contributes substantively to production or reporting of a research study</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>researcher, research assistant, investigator</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
+          <t>A realizable entity  the manifestation of which brings about some result or end that is not essential to a continuant  in virtue of the kind of thing that it is but that can be served or participated in by that kind of continuant  in some kinds of natural, social or institutional contexts.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:030000</t>
+          <t>BCIO:010084</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1410,30 +1314,35 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>student or trainee role</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>behaviour change intervention study investigator role</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>A researcher role played by a person that contributes substantively to production or reporting of a BCI evaluation study.</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr"/>
+          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:010079</t>
+          <t>BCIO:010086</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1442,38 +1351,34 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>plant and machine operator</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>school student role</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>An occupational role that operates and monitors industrial and agricultural machinery and equipment on the spot or by remote control, or drives and operates trains, motor vehicles and mobile machinery and equipment.</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Stationary Plant and Machine Operator, Driver, Mobile Plant Operator</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting.</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:010078</t>
+          <t>BCIO:010087</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1482,38 +1387,34 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>craft and related trades worker</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>trainee role</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>An occupational role that applies specific technical and practical knowledge and skills to construct and maintain buildings, machinery, equipment or tools, carries out printing work, and produces or processes foodstuffs, textiles and wooden, metal and other articles, including handicraft goods.</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Building Trade Worker, Metal Workers, Machinery Worker, Handicraft Worker, Printing Worker, Electrical Equipment Installers and Repairer, Electronics and Telecommunications Installer and Repairer, Food Processing Worker, Woodworker, Tobacco Product Maker</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:010080</t>
+          <t>BCIO:010085</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1522,34 +1423,34 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>assembler</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>informal education student role</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>An occupational role that assembles products from component parts according to strict specifications and procedures.</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr"/>
+          <t>A student or trainee role that is currently learning in a non-institutional setting.</t>
+        </is>
+      </c>
       <c r="Q30" t="inlineStr"/>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:010081</t>
+          <t>BCIO:010088</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1558,38 +1459,38 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>elementary occupation</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>higher education student role</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>An occupational role that involves the performance of simple and routine tasks which may require the use of hand-held tools and considerable physical effort.</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Cleaner, Labourer, Food Preparation Assistant, Street and Related Services Worker, Street Vendor (excluding Food), Refuse Worker</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr"/>
+          <t>A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school.</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:010006</t>
+          <t>BCIO:010092</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1601,7 +1502,7 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>professional</t>
+          <t>doctoral student role</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -1610,22 +1511,26 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>An occupational role that works in knowledge building activities, applies scientific or artistic concepts and theories or teaches about the foregoing in a systematic manner.</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr"/>
+          <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
+        </is>
+      </c>
       <c r="Q32" t="inlineStr"/>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>PhD student</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:010007</t>
+          <t>BCIO:010090</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1635,37 +1540,37 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>science and engineering professional</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>graduate student role</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>A professional that conducts research, improves or develops concepts, theories and operational methods or applies scientific knowledge.</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Science Professional, Mathematician, Actuary, Statistician, Life Science Professional, Engineering Professional, Electrotechnology Engineer, Architect, Planner, Surveyor, Designer</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr"/>
+          <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>graduate student</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:010044</t>
+          <t>BCIO:010089</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1675,33 +1580,37 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>technician and associate professional</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>undergraduate student role</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>A professional that performs technical and related tasks connected with research and the application of scientific or artistic concepts and operational methods, and government or business regulations.</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr"/>
+          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
+        </is>
+      </c>
       <c r="Q34" t="inlineStr"/>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>undergraduate student</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:010065</t>
+          <t>BCIO:010091</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1711,37 +1620,37 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>masters student role</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>artistic, cultural and culinary associate professional</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>A technician and associate professional that combines creative skills and technical and cultural knowledge in creative media or food.</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Photographer, Interior designers and decorator, Gallery, museum and library technician, Chef</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr"/>
+          <t>A higher education student  role realised by currently studying for a masters degree.</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>MSc student, Masters student</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:010045</t>
+          <t>BCIO:006081</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1749,39 +1658,35 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>personal role</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>health associate professional</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs technical and practical tasks to support diagnosis and treatment of illness, disease, injuries and impairments in humans or animals, and supports the implementation of health care usually established by medical, veterinary, nursing and other health professionals.</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Veterinary Technician</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A role that inheres in a human being by virtue of their social and institutional circumstances.</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:010050</t>
+          <t>BCIO:051024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1790,38 +1695,29 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>certified professional role</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>traditional and complementary medicine associate professional</t>
-        </is>
-      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>A health associate professional that prevents and treats human physical and mental illnesses, disorders and injuries using herbal and other therapies based on theories, beliefs and experiences originating in specific cultures. They administer treatments using traditional techniques and medicaments, either acting independently or according to therapeutic care plans established by a traditional medicine or other health professional.</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Acupuncture technician, Ayurvedic technician, Bonesetter, Herbalist , Homeopathy technician, Scraping and cupping therapist, Village healer, Witch doctor</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A personal role that inheres in a human being by virtue of formal recognition of their competence by a professional or regulatory body.</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:010051</t>
+          <t>BCIO:010000</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1829,39 +1725,35 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>behaviour change intervention source</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>dental assistant and therapist</t>
-        </is>
-      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>A health associate professional that provides basic dental care services for the prevention and treatment of diseases and disorders of the teeth and mouth, according to care plans and procedures established by a dentist or other oral health professional.</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Dental assistant, Dental hygienist , Dental therapist</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A role played by a person, population or organisation that provides a BCI.</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:010055</t>
+          <t>BCIO:010133</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1870,39 +1762,34 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>source role related to intervention</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>environmental and occupational health inspector and associate</t>
-        </is>
-      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>A health associate professional that investigates the implementation of rules and regulations relating to environmental factors that may affect human health, safety in the 
-workplace, and safety of processes for the production of goods and services. They may implement and evaluate programmes to restore or improve safety and sanitary conditions under the supervision of a health professional.</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Food sanitation and safety inspector, Health inspector, Occupational health and safety inspector, Pollution inspector, Product safety inspector, Sanitarian, Sanitary inspector</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A BCI source whose occupational or voluntary role is focused on delivery of the behaviour change intervention.</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:010054</t>
+          <t>BCIO:010134</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1911,38 +1798,34 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>source involved in development of intervention</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>medical assistant</t>
-        </is>
-      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>A health associate professional that performs basic clinical and administrative tasks to support patient care under the direct supervision of a medical practitioner or other health professional.</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Clinical assistant, Medical assistant, Ophthalmic assistant</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A BCI source that is involved in the development of intervention content.</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:010056</t>
+          <t>BCIO:010135</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1952,37 +1835,33 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>source involved in co-production of intervention</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>ambulance worker</t>
-        </is>
-      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>A health associate professional that provides emergency health care to patients who are injured, sick, infirm or otherwise physically or mentally impaired prior to and during transport to medical facilities.</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Ambulance officer, Ambulance paramedic, Emergency medical technician, Emergency paramedic</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A source involved in development of intervention that has developed the intervention content in collaboration with key stakeholders such as patients or community members.</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:010052</t>
+          <t>BCIO:010138</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1991,38 +1870,34 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>organisational source role</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>community health worker</t>
-        </is>
-      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>A health associate professional that provides health education, referral and follow-up, case management, basic preventive health care and home visiting services to specific communities. They provide support and assistance to individuals and families in navigating the health and social services system.</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>Community health aide, Community health promoter, Community health worker, Village health worker, outreach worker, health worker</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A BCI source role that is borne by an organisation.</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:010053</t>
+          <t>BCIO:010001</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2031,38 +1906,34 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>person source role</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>physiotherapy technician and assistant</t>
-        </is>
-      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>A health associate professional that provides physical therapeutic treatments to patients in circumstances where functional movement is threatened by injury, disease or impairment. Therapies are usually provided according to rehabilitative plans established by a physiotherapist or other health professional.</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>Acupressure therapist, Electrotherapist, Hydrotherapist, Massage therapist, Physical rehabilitation technician, Physiotherapy technician, Shiatsu therapist</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A behaviour change intervention source role that inheres in a person.</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:010047</t>
+          <t>BCIO:010003</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2070,39 +1941,35 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>personal role of source</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>nursing and midwifery associate professional</t>
-        </is>
-      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>A health associate professional that provides basic nursing and personal care for people who are physically or mentally ill, disabled or infirm, and for others in need of care due to potential risks to health including before, during and after childbirth. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing, midwifery and other health professionals.</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>Practice assistant, Quit Smoking Counsellor, Health educator, Dispensing Optician, Information Technician</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A role that inheres in a person source.</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:010049</t>
+          <t>BCIO:010004</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2111,38 +1978,38 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>occupational role of source</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>midwifery associate professional</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>A nursing and midwifery associate professional that provides basic health care and advice before, during and after pregnancy and childbirth. They implement care, treatment and referral plans usually established by medical, midwifery and other health professionals.</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Assistant midwife, Traditional midwife</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr"/>
+          <t>A personal role of source that is realised by doing a specified type of work or working in a specified way.</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Interventionist, facilitator, study staff</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:010048</t>
+          <t>BCIO:010079</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2152,37 +2019,37 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>plant and machine operator</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>nursing associate professional</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>A nursing and midwifery associate professional that provides basic nursing and personal care for people in need of such care due to effects of ageing, illness, injury, or other physical or mental impairment. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing and other health professionals.</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>Assistant nurse, Associate professional nurse, Enrolled nurse, Practical nurse</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr"/>
+          <t>An occupational role that operates and monitors industrial and agricultural machinery and equipment on the spot or by remote control, or drives and operates trains, motor vehicles and mobile machinery and equipment.</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stationary Plant and Machine Operator, Driver, Mobile Plant Operator</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:010046</t>
+          <t>BCIO:010083</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2192,37 +2059,37 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>researcher role</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>medical and pharmaceutical technician</t>
-        </is>
-      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>A health associate professional that performs technical tasks to assist in diagnosis and treatment of illness, disease, injuries and impairments.</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>Medical imaging and therapeutic equipment technician, Medical and Pathology laboratory technician, Pharmaceutical technician, Medical and dental prosthetic technician</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr"/>
+          <t>A occupational role played by a person that contributes substantively to production or reporting of a research study.</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>researcher, research assistant, investigator</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:010061</t>
+          <t>BCIO:030000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2233,36 +2100,27 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>sport and fitness worker</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>behaviour change intervention study investigator role</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>A technician and associate professional that prepares for and competes in sporting events for financial gain, trains amateur and professional sportsmen and women to enhance performance, promotes participation and standards in sport, organises and officiates sporting events, or provides instruction, training and supervision for various forms of exercise and other recreational activities.</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>physical activity professional, exercise physiologist, exercise therapist, exercise specialist</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A researcher role played by a person that contributes substantively to production or reporting of a BCI evaluation study.</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:010064</t>
+          <t>BCIO:010006</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2272,37 +2130,33 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>professional</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>fitness and recreation instructor and programme leader</t>
-        </is>
-      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that leads, guides and instructs groups and individuals in recreational, fitness or outdoor adventure activities.</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>Aerobics instructor, Fitness instructor, Horse riding instructor, Outdoor adventure guide, Personal trainer, Sailing instructor, Underwater diving instructor</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>An occupational role that works in knowledge building activities, applies scientific or artistic concepts and theories or teaches about the foregoing in a systematic manner.</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:010062</t>
+          <t>BCIO:010025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2313,36 +2167,36 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>teaching professional</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>athlete and sports player</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that participates in competitive sporting events. They train and compete, either individually or as part of a team, in their chosen sport.</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>Athlete, Bicycle racer, Boxer, Chess player , Footballer, Golfer, Hockey player, Jockey, Poker player, Racing driver, Skier, Tennis player, Wrestler</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr"/>
+          <t>A professional that teaches the theory and practice of one or more disciplines at different educational levels.</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Education Methods Specialist, Other Language Teacher, Information Technology Teacher, Private Tutor, School Counsellor, Student Advisor</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:010063</t>
+          <t>BCIO:010032</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2354,35 +2208,35 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>sports coach, instructor and official</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>music teacher</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>A sport and fitness worker that works with amateur and professional sportspersons to enhance performance and encourage greater participation in sport, and organizes and officiates in sporting events according to established rules.</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>Referee, Ski instructor, Sports coach, Sports official, Swimming instructor</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr"/>
+          <t>A teaching professional that teaches students in the practice, theory and performance of music in private or small group tuition or within mainstream educational institutions.</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Guitar teacher (private tuition), Piano teacher (private tuition), Singing teacher (private tuition), Violin teacher (private tuition)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:010058</t>
+          <t>BCIO:010026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2396,33 +2250,33 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>legal and related associate professional</t>
+          <t>university and higher education teacher</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs support functions in courts of law or in law offices, provide services related to such legal matters as insurance contracts, the transferring of property and the granting of loans and other financial transactions, or conduct investigations for clients.</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>Bailiff, Judge’s clerk, Conveyancing clerk, Court clerk, Justice of the peace, Law clerk, Legal assistant, Paralegal, Private detective, Title searcher</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr"/>
+          <t>A teaching professional that prepares and delivers lectures and conduct tutorials in one or more subjects within a prescribed course of study at a university or other higher educational institution. They conduct research, and prepare scholarly papers and books.</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Higher education lecturer, Professor, University lecturer, University tutor</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:010057</t>
+          <t>BCIO:010027</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2436,33 +2290,33 @@
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>business and administration associate professional</t>
+          <t>vocational education teacher</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>A technician and associate professional that performs mostly technical tasks connected with the practical application of knowledge relating to financial accounting and transaction matters, mathematical calculations, human resource development, selling and buying financial instruments, specialized secretarial tasks and enforcing or applying government rules.</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>Financial and Mathematical associate professional, Sales and purchasing agent, Broker, Business Services Agent, Administrative and Specialized Secretary, Government regulatory associate professional, Medical secretary</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr"/>
+          <t>A teaching professional that teaches or instructs vocational or occupational subjects in adult and further education institutions and to senior students in secondary schools and colleges.</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Automotive technology instructor, Cosmetology instructor, Vocational education teacher</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:010059</t>
+          <t>BCIO:010031</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2476,33 +2330,33 @@
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>social work associate professional</t>
+          <t>special needs teacher</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>A technician and associate professional that implements social assistance programmes and community services and assist clients to deal with personal and social problems.</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>Community development worker, Community services worker, Crisis intervention worker, Disability services worker, Family services worker, Life skills instructor, Mental health support worker, Welfare support worker, Women’s shelter supervisor, Youth services worker</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr"/>
+          <t>A teaching professional that teaches children, young persons or adults with physical or intellectual special needs.</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Learning disabilities special education teacher, Learning support teacher, Remedial teacher, Teacher of gifted children, Teacher of the hearing impaired, Teacher of the sight impaired</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:010066</t>
+          <t>BCIO:010033</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2516,33 +2370,33 @@
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>information and communications technician</t>
+          <t>arts teacher</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>A technician and associate professional that provides support for the day to day running of computer systems, communication systems and networks, broadcast images and sound, telecommunication signals on land, sea or in aircraft.</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>Information and Communications Technology Operations and User Support Technician, Telecommunications and Broadcasting Technician</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr"/>
+          <t>A teaching professional  that teaches students in the practice, theory and performance of dance, drama, visual and other arts (excluding music) in private or small group tuition or within mainstream educational institutions.</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dance teacher (private tuition), Drama teacher (private tuition), Painting teacher (private tuition), Sculpture teacher (private tuition)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:010060</t>
+          <t>BCIO:010029</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2556,33 +2410,29 @@
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>religious associate professional</t>
+          <t>primary school teacher</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>A technician and associate professional that provides support to ministers of religion or to a religious community, undertake religious works, preach and propagate the teachings of a particular religion and endeavour to improve well-being through the power of faith and spiritual advice.</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>Faith healer, Lay preacher, Monk, Nun</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A teaching professional that teaches teach a range of subjects at the primary education level.</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:010008</t>
+          <t>BCIO:010028</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2593,36 +2443,36 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>health professional</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>secondary education teacher</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>A professional that improves or develops concepts, theories and operational method, and applied scientific knowledge relating to medicine, nursing, dentistry, veterinary medicine, pharmacy, and promotion of health.</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>Health professional; Arts therapist, Chiropractor, Dance and movement therapist, Occupational therapist, Osteopath, Podiatrist, Recreational therapist, Health staff, Clinic staff</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr"/>
+          <t>A teaching professional that teaches one or more subjects at secondary education level.</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Secondary school teacher, High school teacher</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:010015</t>
+          <t>BCIO:010030</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2636,33 +2486,33 @@
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>traditional and complementary medicine professional</t>
+          <t>early childhood educator</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>A health professional that examines patients, prevents and treats illness, disease, injury and other physical and mental impairments and maintains general health in humans. They do this by applying knowledge, skills and practices acquired through extensive study of the theories, beliefs and experiences originating in specific cultures.</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>Acupuncturist, Ayurvedic practitioner,  Chinese herbal medicine practitioner, Homeopath, Naturopath, Unani practitioner</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr"/>
+          <t>A teaching professional that promotes the social, physical, and intellectual development of children below primary school age through the provision of educational and play activities.</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Early childhood educator, Pre-school teacher</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:010009</t>
+          <t>BCIO:010007</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2673,36 +2523,36 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>medical doctor</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>science and engineering professional</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>A health professional that studies, diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans through the application of modern medicine. They plan, supervise and evaluate the implementation of care and treatment plans by other health care providers, and conduct medical education and research activities.</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>District medical doctor-therapist, family medical practitioner, general practitioner, medical doctor (general), medical officer (general), physician (general), primary health care physician, resident medical officer specializing in general practice</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr"/>
+          <t>A professional that conducts research, improves or develops concepts, theories and operational methods or applies scientific knowledge.</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Science Professional, Mathematician, Actuary, Statistician, Life Science Professional, Engineering Professional, Electrotechnology Engineer, Architect, Planner, Surveyor, Designer</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:010010</t>
+          <t>BCIO:010008</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2713,36 +2563,36 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>health professional</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>generalist medical practitioner</t>
-        </is>
-      </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments and maintains general health in humans through application of modern medicine. They do not limit their practice to certain disease categories or methods of treatment, and may assume responsibility for the provision of continuing and comprehensive medical care to individuals, families and communities.</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>Primary care physician, family doctor, GP</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr"/>
+          <t>A professional that improves or develops concepts, theories and operational method, and applied scientific knowledge relating to medicine, nursing, dentistry, veterinary medicine, pharmacy, and promotion of health.</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Health professional; Arts therapist, Chiropractor, Dance and movement therapist, Occupational therapist, Osteopath, Podiatrist, Recreational therapist, Health staff, Clinic staff</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:010011</t>
+          <t>BCIO:010013</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2754,35 +2604,35 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>specialist medical practitioner</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>nursing professional</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans, using specialized testing, diagnostic, medical, surgical, physical and psychiatric techniques through application of the principles and procedures of modern medicine. They specialize in certain disease categories, types of patient or methods of treatment and may conduct medical education and research in their chosen areas of specialization.</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>Anaesthetist, Cardiologist, Emergency medicine specialist, Gynaecologist, Obstetrician, Ophthalmologist, Paediatrician, Pathologist, Preventive medicine specialist, Psychiatrist, Radiation oncologist, Radiologist, Resident medical officer in specialist training, Specialist medical practitioner (public health), Specialist physician (internal medicine), Specialist physician (nuclear medicine), Surgeon</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr"/>
+          <t>A health professional that provides treatment, support and care services for people who are in need of nursing care due to the effects of ageing, injury, illness or other physical or mental impairment, or potential risks to health.</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Clinical nurse consultant, District nurse, Nurse anaesthetist, Nurse educator, Nurse practitioner, Operating theatre nurse, Professional nurse, Public health nurse, Specialist nurse, Nursing Counsellor, Study Nurse</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:010023</t>
+          <t>BCIO:010022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2796,33 +2646,33 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>audiologist and speech therapist</t>
+          <t>dietician and nutritionist</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>A health professional  that evaluates, manages and treats physical disorders affecting human hearing, speech, communication and swallowing.</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>Audiologist, Language therapist, Speech pathologist, Speech therapist</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr"/>
+          <t>A health professional  that assesses, plans and implements programmes to enhance the impact of food and nutrition on human health.</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Clinical dietician, Food service dietician, Nutritionist, Public health nutritionist, Sports nutritionist</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:010024</t>
+          <t>BCIO:010014</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2836,33 +2686,33 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>optometrist and ophthalmic optician</t>
+          <t>midwifery professional</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>A health professional  that provides diagnosis, management and treatment services for disorders of the eyes and visual system.</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Ophthalmic optician , Optometrist, Orthoptist</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr"/>
+          <t>A health professional that plans, manages, provides and evaluates midwifery care services before, during and after pregnancy and childbirth. They provide delivery care for reducing health risks to women and newborn children, working autonomously or in teams with other health care providers.</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Midwife</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:010018</t>
+          <t>BCIO:010015</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2876,33 +2726,33 @@
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>dentist</t>
+          <t>traditional and complementary medicine professional</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>A health professional that diagnoses treats and prevents diseases, injuries and abnormalities of the teeth, mouth, jaws and associated tissues by applying the principles and procedures of modern dentistry.</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>Dental practitioner, Dental surgeon, Dentist, Endodontist, Oral and maxillofacial surgeon, Oral pathologist, Orthodontist, Paedodontist, Periodontist, Prosthodontist, Stomatologist</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr"/>
+          <t>A health professional that examines patients, prevents and treats illness, disease, injury and other physical and mental impairments and maintains general health in humans. They do this by applying knowledge, skills and practices acquired through extensive study of the theories, beliefs and experiences originating in specific cultures.</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Acupuncturist, Ayurvedic practitioner,  Chinese herbal medicine practitioner, Homeopath, Naturopath, Unani practitioner</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:010012</t>
+          <t>BCIO:010020</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2916,29 +2766,33 @@
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>nursing and midwifery professional</t>
+          <t>environmental and occupational health and hygiene professional</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>A health professional that provides treatment and care services for people who are physically or mentally ill, disabled or infirm, and those with potential risks to health including before, during and after childbirth. They assume responsibility for the planning, management and evaluation of the care of patients, including the supervision of other health care workers, working autonomously or in teams with medical doctors and others in the practical application of preventive and curative measures.</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr"/>
+          <t>A health professional that assesses, plans and implements programmes to recognize, monitor and control environmental factors that can potentially affect human health, to ensure safe and healthy working conditions and to prevent disease or injury caused by chemical, physical, radiological and biological agents or ergonomic factors.</t>
+        </is>
+      </c>
       <c r="Q65" t="inlineStr"/>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Environmental health officer, Occupational health and safety adviser, Occupational hygienist, Radiation protection expert</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:010019</t>
+          <t>BCIO:010017</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2952,33 +2806,33 @@
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>pharmacist</t>
+          <t>veterinarian</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>A health professional that stores, preserves, compounds and dispenses medicinal products and counsel on the proper use and adverse effects of drugs and medicines following prescriptions issued by medical doctors and other health professionals.</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>Dispensing chemist, Hospital pharmacist, Industrial pharmacist, Retail pharmacist</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr"/>
+          <t>A health professional that diagnoses, prevents and treats diseases, injuries and dysfunctions of animals.</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Animal pathologist, Veterinarian, Veterinary epidemiologist, Veterinary intern, Veterinary surgeon</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:010016</t>
+          <t>BCIO:010021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2992,33 +2846,33 @@
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>paramedical practitioner</t>
+          <t>physiotherapist</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>A health professional that provides advisory, diagnostic, curative and preventive medical services more limited in scope and complexity than those carried out by medical doctors. They work autonomously or with limited supervision of medical doctors, and apply advanced clinical procedures for treating and preventing diseases, injuries and other physical or mental impairments common to specific communities.</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>Advanced care paramedic, Clinical officer (paramedical), Feldscher, Primary care paramedic, Surgical technician</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr"/>
+          <t>A health professional  that assesses, plans and implements rehabilitative programmes that improve or restore human motor functions, maximize movement ability, relieve pain syndromes, and treat or prevent physical challenges associated with injuries, diseases and other impairments.</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Geriatric physical therapist, Manipulative therapist, Orthopaedic physical therapist, Paediatric physical therapist, Physical therapist, Physiotherapist</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:010021</t>
+          <t>BCIO:010012</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -3032,33 +2886,29 @@
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>physiotherapist</t>
+          <t>nursing and midwifery professional</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>A health professional  that assesses, plans and implements rehabilitative programmes that improve or restore human motor functions, maximize movement ability, relieve pain syndromes, and treat or prevent physical challenges associated with injuries, diseases and other impairments.</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>Geriatric physical therapist, Manipulative therapist, Orthopaedic physical therapist, Paediatric physical therapist, Physical therapist, Physiotherapist</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A health professional that provides treatment and care services for people who are physically or mentally ill, disabled or infirm, and those with potential risks to health including before, during and after childbirth. They assume responsibility for the planning, management and evaluation of the care of patients, including the supervision of other health care workers, working autonomously or in teams with medical doctors and others in the practical application of preventive and curative measures.</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:010014</t>
+          <t>BCIO:010016</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -3072,33 +2922,33 @@
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>midwifery professional</t>
+          <t>paramedical practitioner</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>A health professional that plans, manages, provides and evaluates midwifery care services before, during and after pregnancy and childbirth. They provide delivery care for reducing health risks to women and newborn children, working autonomously or in teams with other health care providers.</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>Midwife</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr"/>
+          <t>A health professional that provides advisory, diagnostic, curative and preventive medical services more limited in scope and complexity than those carried out by medical doctors. They work autonomously or with limited supervision of medical doctors, and apply advanced clinical procedures for treating and preventing diseases, injuries and other physical or mental impairments common to specific communities.</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Advanced care paramedic, Clinical officer (paramedical), Feldscher, Primary care paramedic, Surgical technician</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:010020</t>
+          <t>BCIO:010024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -3112,33 +2962,33 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>environmental and occupational health and hygiene professional</t>
+          <t>optometrist and ophthalmic optician</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>A health professional that assesses, plans and implements programmes to recognize, monitor and control environmental factors that can potentially affect human health, to ensure safe and healthy working conditions and to prevent disease or injury caused by chemical, physical, radiological and biological agents or ergonomic factors.</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>Environmental health officer, Occupational health and safety adviser, Occupational hygienist, Radiation protection expert</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr"/>
+          <t>A health professional  that provides diagnosis, management and treatment services for disorders of the eyes and visual system.</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Ophthalmic optician , Optometrist, Orthoptist</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCIO:010022</t>
+          <t>BCIO:010023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3152,33 +3002,33 @@
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>dietician and nutritionist</t>
+          <t>audiologist and speech therapist</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>A health professional  that assesses, plans and implements programmes to enhance the impact of food and nutrition on human health.</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>Clinical dietician, Food service dietician, Nutritionist, Public health nutritionist, Sports nutritionist</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr"/>
+          <t>A health professional  that evaluates, manages and treats physical disorders affecting human hearing, speech, communication and swallowing.</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Audiologist, Language therapist, Speech pathologist, Speech therapist</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIO:010017</t>
+          <t>BCIO:010018</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3192,33 +3042,33 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>veterinarian</t>
+          <t>dentist</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>A health professional that diagnoses, prevents and treats diseases, injuries and dysfunctions of animals.</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>Animal pathologist, Veterinarian, Veterinary epidemiologist, Veterinary intern, Veterinary surgeon</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr"/>
+          <t>A health professional that diagnoses treats and prevents diseases, injuries and abnormalities of the teeth, mouth, jaws and associated tissues by applying the principles and procedures of modern dentistry.</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dental practitioner, Dental surgeon, Dentist, Endodontist, Oral and maxillofacial surgeon, Oral pathologist, Orthodontist, Paedodontist, Periodontist, Prosthodontist, Stomatologist</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BCIO:010013</t>
+          <t>BCIO:010009</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3232,33 +3082,33 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>nursing professional</t>
+          <t>medical doctor</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>A health professional that provides treatment, support and care services for people who are in need of nursing care due to the effects of ageing, injury, illness or other physical or mental impairment, or potential risks to health.</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>Clinical nurse consultant, District nurse, Nurse anaesthetist, Nurse educator, Nurse practitioner, Operating theatre nurse, Professional nurse, Public health nurse, Specialist nurse, Nursing Counsellor, Study Nurse</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T73" t="inlineStr"/>
+          <t>A health professional that studies, diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans through the application of modern medicine. They plan, supervise and evaluate the implementation of care and treatment plans by other health care providers, and conduct medical education and research activities.</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>District medical doctor-therapist, family medical practitioner, general practitioner, medical doctor (general), medical officer (general), physician (general), primary health care physician, resident medical officer specializing in general practice</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BCIO:010025</t>
+          <t>BCIO:010011</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3269,36 +3119,36 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>teaching professional</t>
-        </is>
-      </c>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>specialist medical practitioner</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>A professional that teaches the theory and practice of one or more disciplines at different educational levels.</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>Education Methods Specialist, Other Language Teacher, Information Technology Teacher, Private Tutor, School Counsellor, Student Advisor</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr"/>
+          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments in humans, using specialized testing, diagnostic, medical, surgical, physical and psychiatric techniques through application of the principles and procedures of modern medicine. They specialize in certain disease categories, types of patient or methods of treatment and may conduct medical education and research in their chosen areas of specialization.</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Anaesthetist, Cardiologist, Emergency medicine specialist, Gynaecologist, Obstetrician, Ophthalmologist, Paediatrician, Pathologist, Preventive medicine specialist, Psychiatrist, Radiation oncologist, Radiologist, Resident medical officer in specialist training, Specialist medical practitioner (public health), Specialist physician (internal medicine), Specialist physician (nuclear medicine), Surgeon</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BCIO:010027</t>
+          <t>BCIO:010010</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3310,35 +3160,35 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>vocational education teacher</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>generalist medical practitioner</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches or instructs vocational or occupational subjects in adult and further education institutions and to senior students in secondary schools and colleges.</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>Automotive technology instructor, Cosmetology instructor, Vocational education teacher</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr"/>
+          <t>A medical doctor that diagnoses, treats and prevents illness, disease, injury and other physical and mental impairments and maintains general health in humans through application of modern medicine. They do not limit their practice to certain disease categories or methods of treatment, and may assume responsibility for the provision of continuing and comprehensive medical care to individuals, families and communities.</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Primary care physician, family doctor, GP</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BCIO:010029</t>
+          <t>BCIO:010019</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3352,29 +3202,33 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>primary school teacher</t>
+          <t>pharmacist</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches teach a range of subjects at the primary education level.</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr"/>
+          <t>A health professional that stores, preserves, compounds and dispenses medicinal products and counsel on the proper use and adverse effects of drugs and medicines following prescriptions issued by medical doctors and other health professionals.</t>
+        </is>
+      </c>
       <c r="Q76" t="inlineStr"/>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dispensing chemist, Hospital pharmacist, Industrial pharmacist, Retail pharmacist</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BCIO:010028</t>
+          <t>BCIO:010044</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3385,36 +3239,32 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>secondary education teacher</t>
-        </is>
-      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>technician and associate professional</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches one or more subjects at secondary education level.</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>Secondary school teacher, High school teacher</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A professional that performs technical and related tasks connected with research and the application of scientific or artistic concepts and operational methods, and government or business regulations.</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BCIO:010026</t>
+          <t>BCIO:010045</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3428,33 +3278,33 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>university and higher education teacher</t>
+          <t>health associate professional</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>A teaching professional that prepares and delivers lectures and conduct tutorials in one or more subjects within a prescribed course of study at a university or other higher educational institution. They conduct research, and prepare scholarly papers and books.</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>Higher education lecturer, Professor, University lecturer, University tutor</t>
-        </is>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T78" t="inlineStr"/>
+          <t>A technician and associate professional that performs technical and practical tasks to support diagnosis and treatment of illness, disease, injuries and impairments in humans or animals, and supports the implementation of health care usually established by medical, veterinary, nursing and other health professionals.</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Veterinary Technician</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCIO:010031</t>
+          <t>BCIO:010047</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3466,35 +3316,35 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>special needs teacher</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>nursing and midwifery associate professional</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches children, young persons or adults with physical or intellectual special needs.</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>Learning disabilities special education teacher, Learning support teacher, Remedial teacher, Teacher of gifted children, Teacher of the hearing impaired, Teacher of the sight impaired</t>
-        </is>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T79" t="inlineStr"/>
+          <t>A health associate professional that provides basic nursing and personal care for people who are physically or mentally ill, disabled or infirm, and for others in need of care due to potential risks to health including before, during and after childbirth. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing, midwifery and other health professionals.</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Practice assistant, Quit Smoking Counsellor, Health educator, Dispensing Optician, Information Technician</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIO:010033</t>
+          <t>BCIO:010049</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3506,35 +3356,35 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>arts teacher</t>
-        </is>
-      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>midwifery associate professional</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>A teaching professional  that teaches students in the practice, theory and performance of dance, drama, visual and other arts (excluding music) in private or small group tuition or within mainstream educational institutions.</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>Dance teacher (private tuition), Drama teacher (private tuition), Painting teacher (private tuition), Sculpture teacher (private tuition)</t>
-        </is>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr"/>
+          <t>A nursing and midwifery associate professional that provides basic health care and advice before, during and after pregnancy and childbirth. They implement care, treatment and referral plans usually established by medical, midwifery and other health professionals.</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Assistant midwife, Traditional midwife</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BCIO:010032</t>
+          <t>BCIO:010048</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3546,35 +3396,35 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>music teacher</t>
-        </is>
-      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>nursing associate professional</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>A teaching professional that teaches students in the practice, theory and performance of music in private or small group tuition or within mainstream educational institutions.</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>Guitar teacher (private tuition), Piano teacher (private tuition), Singing teacher (private tuition), Violin teacher (private tuition)</t>
-        </is>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T81" t="inlineStr"/>
+          <t>A nursing and midwifery associate professional that provides basic nursing and personal care for people in need of such care due to effects of ageing, illness, injury, or other physical or mental impairment. They generally work under the supervision of, and in support of, implementation of health care, treatment and referrals plans established by medical, nursing and other health professionals.</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Assistant nurse, Associate professional nurse, Enrolled nurse, Practical nurse</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BCIO:010030</t>
+          <t>BCIO:010055</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3586,35 +3436,36 @@
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>early childhood educator</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>environmental and occupational health inspector and associate</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
-          <t>A teaching professional that promotes the social, physical, and intellectual development of children below primary school age through the provision of educational and play activities.</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>Early childhood educator, Pre-school teacher</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr"/>
+          <t>A health associate professional that investigates the implementation of rules and regulations relating to environmental factors that may affect human health, safety in the 
+workplace, and safety of processes for the production of goods and services. They may implement and evaluate programmes to restore or improve safety and sanitary conditions under the supervision of a health professional.</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Food sanitation and safety inspector, Health inspector, Occupational health and safety inspector, Pollution inspector, Product safety inspector, Sanitarian, Sanitary inspector</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BCIO:010034</t>
+          <t>BCIO:010051</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3625,32 +3476,36 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>legal, social and cultural professional</t>
-        </is>
-      </c>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>dental assistant and therapist</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>A professional that conducts research, improves or develops concepts, theories and operational methods, or applies knowledge relating to the law, social or cultural studies.</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr"/>
+          <t>A health associate professional that provides basic dental care services for the prevention and treatment of diseases and disorders of the teeth and mouth, according to care plans and procedures established by a dentist or other oral health professional.</t>
+        </is>
+      </c>
       <c r="Q83" t="inlineStr"/>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T83" t="inlineStr"/>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dental assistant, Dental hygienist , Dental therapist</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BCIO:010042</t>
+          <t>BCIO:010054</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3662,35 +3517,35 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>linguist</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>medical assistant</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that translates or interprets from one language into another.</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>Interpretator; other linguist</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T84" t="inlineStr"/>
+          <t>A health associate professional that performs basic clinical and administrative tasks to support patient care under the direct supervision of a medical practitioner or other health professional.</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Clinical assistant, Medical assistant, Ophthalmic assistant</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BCIO:010036</t>
+          <t>BCIO:010053</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3702,35 +3557,35 @@
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>librarian, archivist and curator</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>physiotherapy technician and assistant</t>
+        </is>
+      </c>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that develops and maintains collections of archives, libraries, museums, art galleries and similar establishments.</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>Librarian, Archivist,  Curator</t>
-        </is>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T85" t="inlineStr"/>
+          <t>A health associate professional that provides physical therapeutic treatments to patients in circumstances where functional movement is threatened by injury, disease or impairment. Therapies are usually provided according to rehabilitative plans established by a physiotherapist or other health professional.</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Acupressure therapist, Electrotherapist, Hydrotherapist, Massage therapist, Physical rehabilitation technician, Physiotherapy technician, Shiatsu therapist</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BCIO:010037</t>
+          <t>BCIO:010050</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3742,35 +3597,35 @@
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>social professional</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>traditional and complementary medicine associate professional</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conducts research, improves or develops concepts, theories and operational methods or applies knowledge relating to psychology, sociology, philosophy, politics, economics, sociology, anthropology, history and other social sciences, or provides social services to meet the needs of individuals and families in a community.</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>Economist, Sociologist, Anthropologist, Philosopher, Historian, Political Scientist</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T86" t="inlineStr"/>
+          <t>A health associate professional that prevents and treats human physical and mental illnesses, disorders and injuries using herbal and other therapies based on theories, beliefs and experiences originating in specific cultures. They administer treatments using traditional techniques and medicaments, either acting independently or according to therapeutic care plans established by a traditional medicine or other health professional.</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Acupuncture technician, Ayurvedic technician, Bonesetter, Herbalist , Homeopathy technician, Scraping and cupping therapist, Village healer, Witch doctor</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BCIO:010039</t>
+          <t>BCIO:010052</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3785,32 +3640,32 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>social work and counselling professional</t>
+          <t>community health worker</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
-          <t>A social professional that provides advice and guidance to individuals, families, groups, communities and organizations in response to social and personal difficulties. They assist clients to develop skills and access resources and support services needed to respond to issues arising from unemployment, poverty, disability, addiction, criminal and delinquent behaviour, marital and other problems.</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>Counsellor, Addictions counsellor, Bereavement counsellor, Child and youth counsellor, District social welfare officer, Family counsellor, Marriage counsellor, Parole officer, Probation officer, Sexual assault counsellor, Social worker, Women’s welfare organizer</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T87" t="inlineStr"/>
+          <t>A health associate professional that provides health education, referral and follow-up, case management, basic preventive health care and home visiting services to specific communities. They provide support and assistance to individuals and families in navigating the health and social services system.</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Community health aide, Community health promoter, Community health worker, Village health worker, outreach worker, health worker</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BCIO:010038</t>
+          <t>BCIO:010056</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3825,32 +3680,32 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>psychologist</t>
+          <t>ambulance worker</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
-          <t>A social professional that studies the mental processes and behaviour of human beings as individuals or in groups, and applies this knowledge to promote personal, social, educational or occupational adjustment and development.</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>Clinical psychologist, Counselling psychologist, Educational psychologist, Forensic psychologist, Health psychologist, Neuropsychologist, Organizational psychologist, Psychotherapist, Sport and exercise psychologist</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T88" t="inlineStr"/>
+          <t>A health associate professional that provides emergency health care to patients who are injured, sick, infirm or otherwise physically or mentally impaired prior to and during transport to medical facilities.</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Ambulance officer, Ambulance paramedic, Emergency medical technician, Emergency paramedic</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BCIO:010035</t>
+          <t>BCIO:010046</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3862,35 +3717,35 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>legal professional</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>medical and pharmaceutical technician</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conducts research on legal problems, advises clients on legal aspects of problems, pleads cases or conducts prosecutions in courts of law, presides over judicial proceedings in courts of law and draft laws and regulations.</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>Lawyer, Judge, Coroner</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T89" t="inlineStr"/>
+          <t>A health associate professional that performs technical tasks to assist in diagnosis and treatment of illness, disease, injuries and impairments.</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Medical imaging and therapeutic equipment technician, Medical and Pathology laboratory technician, Pharmaceutical technician, Medical and dental prosthetic technician</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BCIO:010041</t>
+          <t>BCIO:010057</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3904,33 +3759,33 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>author and journalist</t>
+          <t>business and administration associate professional</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that conceives and creates literary works, and interprets and communicates news and public affairs through the media.</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>Author, Writer, Journalist, Translator, News anchor</t>
-        </is>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T90" t="inlineStr"/>
+          <t>A technician and associate professional that performs mostly technical tasks connected with the practical application of knowledge relating to financial accounting and transaction matters, mathematical calculations, human resource development, selling and buying financial instruments, specialized secretarial tasks and enforcing or applying government rules.</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Financial and Mathematical associate professional, Sales and purchasing agent, Broker, Business Services Agent, Administrative and Specialized Secretary, Government regulatory associate professional, Medical secretary</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BCIO:010043</t>
+          <t>BCIO:010059</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3944,33 +3799,33 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>creative and performing artist</t>
+          <t>social work associate professional</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that communicates ideas, impressions and facts in a wide range of media to achieve particular effects, interprets a composition such as a musical score or a script to perform or direct the performance, and hosts the presentation of such performance and other media events.</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>Visual artist, Musician, Singer, Composer, Dancer, Choreographer, Director, Producer, Actor, Announcer on radio, television and other media</t>
-        </is>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T91" t="inlineStr"/>
+          <t>A technician and associate professional that implements social assistance programmes and community services and assist clients to deal with personal and social problems.</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Community development worker, Community services worker, Crisis intervention worker, Disability services worker, Family services worker, Life skills instructor, Mental health support worker, Welfare support worker, Women’s shelter supervisor, Youth services worker</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BCIO:010040</t>
+          <t>BCIO:010058</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3984,33 +3839,33 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>religious professional</t>
+          <t>legal and related associate professional</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t>A legal, social and cultural professional that functions  as a perpetuator of sacred traditions, practices and beliefs. They conduct religious services, celebrate or administer the rites of a religious faith or denomination, provide spiritual and moral guidance and perform other functions associated with the practice of a religion.</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>Bonze, Imam, Minister of religion, Poojari, Priest, Rabbi</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T92" t="inlineStr"/>
+          <t>A technician and associate professional that performs support functions in courts of law or in law offices, provide services related to such legal matters as insurance contracts, the transferring of property and the granting of loans and other financial transactions, or conduct investigations for clients.</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Bailiff, Judge’s clerk, Conveyancing clerk, Court clerk, Justice of the peace, Law clerk, Legal assistant, Paralegal, Private detective, Title searcher</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BCIO:010094</t>
+          <t>BCIO:010065</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -4019,34 +3874,38 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>relatedness between person source and the target population</t>
-        </is>
-      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>artistic, cultural and culinary associate professional</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>A personal role of source that is realised in some relationship to the characteristics of the intervention participants.</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr"/>
+          <t>A technician and associate professional that combines creative skills and technical and cultural knowledge in creative media or food.</t>
+        </is>
+      </c>
       <c r="Q93" t="inlineStr"/>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T93" t="inlineStr"/>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Photographer, Interior designers and decorator, Gallery, museum and library technician, Chef</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BCIO:010102</t>
+          <t>BCIO:010060</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -4056,33 +3915,37 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>colleague</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>religious associate professional</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person with whom the participant works in a profession or business.</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr"/>
+          <t>A technician and associate professional that provides support to ministers of religion or to a religious community, undertake religious works, preach and propagate the teachings of a particular religion and endeavour to improve well-being through the power of faith and spiritual advice.</t>
+        </is>
+      </c>
       <c r="Q94" t="inlineStr"/>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T94" t="inlineStr"/>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Faith healer, Lay preacher, Monk, Nun</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BCIO:010101</t>
+          <t>BCIO:010066</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -4092,33 +3955,37 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>friend</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>information and communications technician</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person whom the participant knows, likes and trusts, typically exclusive of sexual or family relations.</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr"/>
+          <t>A technician and associate professional that provides support for the day to day running of computer systems, communication systems and networks, broadcast images and sound, telecommunication signals on land, sea or in aircraft.</t>
+        </is>
+      </c>
       <c r="Q95" t="inlineStr"/>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T95" t="inlineStr"/>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Information and Communications Technology Operations and User Support Technician, Telecommunications and Broadcasting Technician</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BCIO:010105</t>
+          <t>BCIO:010061</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -4128,33 +3995,37 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>embedded in participants’ community</t>
-        </is>
-      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>sport and fitness worker</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a source who is known and working to deliver intervention in own community.</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr"/>
+          <t>A technician and associate professional that prepares for and competes in sporting events for financial gain, trains amateur and professional sportsmen and women to enhance performance, promotes participation and standards in sport, organises and officiates sporting events, or provides instruction, training and supervision for various forms of exercise and other recreational activities.</t>
+        </is>
+      </c>
       <c r="Q96" t="inlineStr"/>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T96" t="inlineStr"/>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>physical activity professional, exercise physiologist, exercise therapist, exercise specialist</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BCIO:010103</t>
+          <t>BCIO:010064</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -4164,33 +4035,37 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>employer</t>
-        </is>
-      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>fitness and recreation instructor and programme leader</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is a person which hires the services of the participant.</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr"/>
+          <t>A sport and fitness worker that leads, guides and instructs groups and individuals in recreational, fitness or outdoor adventure activities.</t>
+        </is>
+      </c>
       <c r="Q97" t="inlineStr"/>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T97" t="inlineStr"/>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Aerobics instructor, Fitness instructor, Horse riding instructor, Outdoor adventure guide, Personal trainer, Sailing instructor, Underwater diving instructor</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BCIO:010100</t>
+          <t>BCIO:010063</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4200,37 +4075,37 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>carer</t>
-        </is>
-      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>sports coach, instructor and official</t>
+        </is>
+      </c>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is an individual who cares, unpaid, for a friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>carer</t>
-        </is>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T98" t="inlineStr"/>
+          <t>A sport and fitness worker that works with amateur and professional sportspersons to enhance performance and encourage greater participation in sport, and organizes and officiates in sporting events according to established rules.</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Referee, Ski instructor, Sports coach, Sports official, Swimming instructor</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BCIO:010104</t>
+          <t>BCIO:010062</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4240,33 +4115,37 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>peer</t>
-        </is>
-      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>athlete and sports player</t>
+        </is>
+      </c>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
-          <t>A relatedness between person source and the target population that is descried as matched to intervention recipients on the basis of ‘peerness’ – age, social status, gender, shared experience, shared health status etc.</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr"/>
+          <t>A sport and fitness worker that participates in competitive sporting events. They train and compete, either individually or as part of a team, in their chosen sport.</t>
+        </is>
+      </c>
       <c r="Q99" t="inlineStr"/>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T99" t="inlineStr"/>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Athlete, Bicycle racer, Boxer, Chess player , Footballer, Golfer, Hockey player, Jockey, Poker player, Racing driver, Skier, Tennis player, Wrestler</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BCIO:010084</t>
+          <t>BCIO:010034</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4274,35 +4153,35 @@
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>student or trainee role</t>
-        </is>
-      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>legal, social and cultural professional</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr"/>
+          <t>A professional that conducts research, improves or develops concepts, theories and operational methods, or applies knowledge relating to the law, social or cultural studies.</t>
+        </is>
+      </c>
       <c r="Q100" t="inlineStr"/>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BCIO:010087</t>
+          <t>BCIO:010041</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4311,34 +4190,38 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>trainee role</t>
-        </is>
-      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>author and journalist</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
-          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr"/>
+          <t>A legal, social and cultural professional that conceives and creates literary works, and interprets and communicates news and public affairs through the media.</t>
+        </is>
+      </c>
       <c r="Q101" t="inlineStr"/>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T101" t="inlineStr"/>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Author, Writer, Journalist, Translator, News anchor</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BCIO:010085</t>
+          <t>BCIO:010036</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4347,34 +4230,38 @@
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>informal education student role</t>
-        </is>
-      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>librarian, archivist and curator</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
-          <t>A student or trainee that is currently learning in a non-institutional setting.</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr"/>
+          <t>A legal, social and cultural professional that develops and maintains collections of archives, libraries, museums, art galleries and similar establishments.</t>
+        </is>
+      </c>
       <c r="Q102" t="inlineStr"/>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T102" t="inlineStr"/>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Librarian, Archivist,  Curator</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BCIO:010088</t>
+          <t>BCIO:010037</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4383,38 +4270,38 @@
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>higher education student role</t>
-        </is>
-      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>social professional</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
-          <t>A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school.</t>
-        </is>
-      </c>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
-        </is>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T103" t="inlineStr"/>
+          <t>A legal, social and cultural professional that conducts research, improves or develops concepts, theories and operational methods or applies knowledge relating to psychology, sociology, philosophy, politics, economics, sociology, anthropology, history and other social sciences, or provides social services to meet the needs of individuals and families in a community.</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Economist, Sociologist, Anthropologist, Philosopher, Historian, Political Scientist</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BCIO:010092</t>
+          <t>BCIO:010038</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4424,37 +4311,37 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>doctoral student role</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>psychologist</t>
+        </is>
+      </c>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
-        </is>
-      </c>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>PhD student</t>
-        </is>
-      </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T104" t="inlineStr"/>
+          <t>A social professional that studies the mental processes and behaviour of human beings as individuals or in groups, and applies this knowledge to promote personal, social, educational or occupational adjustment and development.</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Clinical psychologist, Counselling psychologist, Educational psychologist, Forensic psychologist, Health psychologist, Neuropsychologist, Organizational psychologist, Psychotherapist, Sport and exercise psychologist</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BCIO:010090</t>
+          <t>BCIO:010039</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4464,37 +4351,37 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>graduate student role</t>
-        </is>
-      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>social work and counselling professional</t>
+        </is>
+      </c>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
-          <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
-        </is>
-      </c>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr">
-        <is>
-          <t>graduate student</t>
-        </is>
-      </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T105" t="inlineStr"/>
+          <t>A social professional that provides advice and guidance to individuals, families, groups, communities and organizations in response to social and personal difficulties. They assist clients to develop skills and access resources and support services needed to respond to issues arising from unemployment, poverty, disability, addiction, criminal and delinquent behaviour, marital and other problems.</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Counsellor, Addictions counsellor, Bereavement counsellor, Child and youth counsellor, District social welfare officer, Family counsellor, Marriage counsellor, Parole officer, Probation officer, Sexual assault counsellor, Social worker, Women’s welfare organizer</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BCIO:010089</t>
+          <t>BCIO:010042</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4504,37 +4391,37 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>undergraduate student role</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>linguist</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
-          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
-        </is>
-      </c>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>undergraduate student</t>
-        </is>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T106" t="inlineStr"/>
+          <t>A legal, social and cultural professional that translates or interprets from one language into another.</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Interpretator; other linguist</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BCIO:010091</t>
+          <t>BCIO:010035</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4544,37 +4431,37 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>masters student role</t>
-        </is>
-      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>legal professional</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
-          <t>A higher education student  role realised by currently studying for a masters degree.</t>
-        </is>
-      </c>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>MSc student, Masters student</t>
-        </is>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T107" t="inlineStr"/>
+          <t>A legal, social and cultural professional that conducts research on legal problems, advises clients on legal aspects of problems, pleads cases or conducts prosecutions in courts of law, presides over judicial proceedings in courts of law and draft laws and regulations.</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Lawyer, Judge, Coroner</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BCIO:010086</t>
+          <t>BCIO:010043</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4583,34 +4470,38 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>school student role</t>
-        </is>
-      </c>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>creative and performing artist</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
-          <t>A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting.</t>
-        </is>
-      </c>
-      <c r="P108" t="inlineStr"/>
+          <t>A legal, social and cultural professional that communicates ideas, impressions and facts in a wide range of media to achieve particular effects, interprets a composition such as a musical score or a script to perform or direct the performance, and hosts the presentation of such performance and other media events.</t>
+        </is>
+      </c>
       <c r="Q108" t="inlineStr"/>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T108" t="inlineStr"/>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Visual artist, Musician, Singer, Composer, Dancer, Choreographer, Director, Producer, Actor, Announcer on radio, television and other media</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BCIO:010000</t>
+          <t>BCIO:010040</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4618,35 +4509,39 @@
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>behaviour change intervention source</t>
-        </is>
-      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>religious professional</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
-          <t>A role played by a person, population or organisation that provides a BCI.</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr"/>
+          <t>A legal, social and cultural professional that functions  as a perpetuator of sacred traditions, practices and beliefs. They conduct religious services, celebrate or administer the rites of a religious faith or denomination, provide spiritual and moral guidance and perform other functions associated with the practice of a religion.</t>
+        </is>
+      </c>
       <c r="Q109" t="inlineStr"/>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T109" t="inlineStr"/>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Bonze, Imam, Minister of religion, Poojari, Priest, Rabbi</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BCIO:010001</t>
+          <t>BCIO:010081</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4655,34 +4550,38 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>person source role</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>elementary occupation</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
-          <t>A behaviour change intervention source role that inheres in a person.</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr"/>
+          <t>An occupational role that involves the performance of simple and routine tasks which may require the use of hand-held tools and considerable physical effort.</t>
+        </is>
+      </c>
       <c r="Q110" t="inlineStr"/>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T110" t="inlineStr"/>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Cleaner, Labourer, Food Preparation Assistant, Street and Related Services Worker, Street Vendor (excluding Food), Refuse Worker</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BCIO:010134</t>
+          <t>BCIO:010080</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4691,34 +4590,34 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>source involved in development of intervention</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>assembler</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
-          <t>A BCI source that is involved in the development of intervention content.</t>
-        </is>
-      </c>
-      <c r="P111" t="inlineStr"/>
+          <t>An occupational role that assembles products from component parts according to strict specifications and procedures.</t>
+        </is>
+      </c>
       <c r="Q111" t="inlineStr"/>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BCIO:010135</t>
+          <t>BCIO:010082</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4730,7 +4629,7 @@
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>source involved in co-production of intervention</t>
+          <t>armed forces occupation</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
@@ -4739,22 +4638,26 @@
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr">
         <is>
-          <t>A source involved in development of intervention that has developed the intervention content in collaboration with key stakeholders such as patients or community members.</t>
-        </is>
-      </c>
-      <c r="P112" t="inlineStr"/>
+          <t>An occupational role that includes all jobs held by members of the armed forces.</t>
+        </is>
+      </c>
       <c r="Q112" t="inlineStr"/>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T112" t="inlineStr"/>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Admiral, Air commodore, Air marshal, Airman, Brigadier (army), Bombardier, Captain (air force), Captain (army), Captain (navy), Colonel (army), Corporal,  Field marshal, Flight lieutenant (air force), Flying officer (military), General (army), Gunner, Group captain, (air force), Lieutenant (army), Major (army), Midshipman, Naval officer (military) , Navy commander, Officer cadet (armed forces), Paratrooper, Rifleman, Sergeant (army), Second lieutenant (army), Seaman, Squadron leader, Sublieutenant (navy), Wing commander</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BCIO:010138</t>
+          <t>BCIO:010078</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4763,34 +4666,38 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>organisational source role</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>craft and related trades worker</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
-          <t>A BCI source role that is borne by an organisation.</t>
-        </is>
-      </c>
-      <c r="P113" t="inlineStr"/>
+          <t>An occupational role that applies specific technical and practical knowledge and skills to construct and maintain buildings, machinery, equipment or tools, carries out printing work, and produces or processes foodstuffs, textiles and wooden, metal and other articles, including handicraft goods.</t>
+        </is>
+      </c>
       <c r="Q113" t="inlineStr"/>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T113" t="inlineStr"/>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Building Trade Worker, Metal Workers, Machinery Worker, Handicraft Worker, Printing Worker, Electrical Equipment Installers and Repairer, Electronics and Telecommunications Installer and Repairer, Food Processing Worker, Woodworker, Tobacco Product Maker</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BCIO:010133</t>
+          <t>BCIO:010068</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -4799,57 +4706,74 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>source role related to intervention</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>services and sales worker</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
-          <t>A BCI source whose occupational or voluntary role is focused on delivery of the behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="P114" t="inlineStr"/>
+          <t>An occupational role that provides personal or protective services related to travel, house-keeping, catering, personal care, protection against fire and unlawful acts, or sells goods in retail or markets.</t>
+        </is>
+      </c>
       <c r="Q114" t="inlineStr"/>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BFO:0000016</t>
+          <t>BCIO:010070</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>disposition</t>
-        </is>
-      </c>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>sales worker</t>
+        </is>
+      </c>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>A services and sales worker that demonstrates goods in wholesale or retail shops, at stalls and markets, door to door, via telephone or customer contact centres. They may record and accept payment for goods and services purchased, and may operate small retail outlets.</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Street Salesperson, Market Salesperson, Shop Salesperson, Cashier, Ticket Clerk, Model, Sales Demonstrator, Door-to-door Salesperson, Contact Centre Salesperson, Service Station Attendant, Food Service Counter Attendant</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BCIO:010120</t>
+          <t>BCIO:010071</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4857,35 +4781,39 @@
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>expertise of person source</t>
-        </is>
-      </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>personal care worker</t>
+        </is>
+      </c>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
-          <t>A disposition that is an expert skill or knowledge held by the source delivering the behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="P116" t="inlineStr"/>
+          <t>A services and sales worker that provides care, supervision and assistance for children, patients and elderly, convalescent or disabled persons in institutional and residential settings.</t>
+        </is>
+      </c>
       <c r="Q116" t="inlineStr"/>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T116" t="inlineStr"/>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Personal carer</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BCIO:010121</t>
+          <t>BCIO:010073</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4894,38 +4822,38 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>knowledge or skill</t>
-        </is>
-      </c>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>teachers’ aide</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
-          <t>An expertise of person source that is knowledge or skills held in order to deliver the behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr">
-        <is>
-          <t>trained (if unclear whether pre-existing or acquired)</t>
-        </is>
-      </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T117" t="inlineStr"/>
+          <t>A personal care worker that performs non-teaching duties to assist teaching staff, and provides care and supervision for children in schools and pre-schools.</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Pre-school assistant, Teacher’s assistant</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BCIO:010125</t>
+          <t>BCIO:010072</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4935,33 +4863,37 @@
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>acquired knowledge or skill</t>
-        </is>
-      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>child care worker</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
-          <t>A knowledge or skill that is additional knowledge or skills supplied to the source to allow them to deliver the behaviour change intervention, including educational level and qualifications.</t>
-        </is>
-      </c>
-      <c r="P118" t="inlineStr"/>
+          <t>A personal care worker that provides care and supervision for children in non-domestic settings.</t>
+        </is>
+      </c>
       <c r="Q118" t="inlineStr"/>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T118" t="inlineStr"/>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Babysitter, Child care worker, Creche ayah, Family day care worker, Nanny, Out of school hours care worker</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BCIO:010122</t>
+          <t>BCIO:010074</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -4971,37 +4903,37 @@
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>pre-existing knowledge or skill</t>
-        </is>
-      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>health care assistant</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
-          <t>A knowledge or skill that is already possessed by the source which allows them to deliver the behaviour change intervention, including educational level and qualifications.</t>
-        </is>
-      </c>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>Bachelor’s degree, certification, accredited, qualified</t>
-        </is>
-      </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T119" t="inlineStr"/>
+          <t>A personal care worker that provides direct personal care and assistance with activities of daily living to patients and residents in a variety of health care settings, working  in implementation of established care plans and practices, and under the direct supervision of medical, nursing or other health professionals or associate professionals.</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Nursing aide (clinic or hospital), Patient care assistant, Psychiatric aid</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BCIO:010127</t>
+          <t>BCIO:010075</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -5012,92 +4944,116 @@
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>affiliation to a formal group or organisation</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>home-based personal care worker</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr">
         <is>
-          <t>A pre-existing knowledge or skill that is recognised through affiliation to a formal group or organisation.</t>
-        </is>
-      </c>
-      <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>member of British Psychological Society</t>
-        </is>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T120" t="inlineStr"/>
+          <t>A personal care worker that provide routine personal care and assistance with activities of daily living to persons who are in need of such care due to effects of ageing, illness, injury, or other physical or mental conditions, in private homes and other independent residential settings.</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Home birth assistant, Home care aide, Nursing aide (home), Personal care provider</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MF:0000030</t>
+          <t>BCIO:010076</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>representation</t>
-        </is>
-      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>protective services worker</t>
+        </is>
+      </c>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr">
         <is>
-          <t>A dependent continuant which is about a portion of reality.</t>
+          <t>A services and sales worker that protects individuals and property against fire and other hazards, maintain law and order and enforce laws and regulations.</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Firefighter, Police officer, Prison guard, Security guard, Offender manager</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MF:0000031</t>
+          <t>BCIO:010069</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>cognitive representation</t>
-        </is>
-      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>personal services worker</t>
+        </is>
+      </c>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr">
         <is>
-          <t>A representation which specifically depends on an anatomical structure in the cognitive system of an organism.</t>
+          <t>A services and sales worker that provides personal services related to travel, housekeeping, catering and hospitality, hairdressing and beauty treatment, animal care grooming and training, companionship and other services of a personal nature.</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Travel Attendant, Conductor, Guide, Cook, Waiter, Bartender, Hairdresser, Beautician, Housekeeping Supervisor, Astrologer, Fortune-teller, Valet, Undertaker, Embalmer, Pet Groomer, Animal Care Worker</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ADDICTO:0000381</t>
+          <t>BCIO:010005</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -5105,27 +5061,39 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr">
         <is>
-          <t>A cognitive representation of themselves by a person or a group about themselves.</t>
+          <t>An occupational role of source that manages, plans and coordinates the overall activities of enterprises, governments and other organisations.</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Chief Executive Officers; Administrative Managers;  Commercial Managers</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ADDICTO:0000399</t>
+          <t>BCIO:010077</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -5134,26 +5102,38 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>self-identity</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>skilled agricultural, forestry and fishery worker</t>
+        </is>
+      </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr">
         <is>
-          <t>An identity that a person has about themselves.</t>
+          <t>An occupational role that grows and harvests plants or animals to provide food, shelter and income for themselves and their households.</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Market gardener, Crop grower, Animal Producer, Mixed Crop and Animal Producer, Forestry worker, Fishery worker, Hunter. Subsistence Crop Farmer, Subsistence Livestock Farmer</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BCIO:015098</t>
+          <t>BCIO:010067</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -5165,7 +5145,7 @@
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>gender identity</t>
+          <t>clerical support worker</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -5174,22 +5154,26 @@
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr">
         <is>
-          <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
-        </is>
-      </c>
-      <c r="P125" t="inlineStr"/>
+          <t>An occupational role that records, organizes, stores, computes and retrieves information, and performs a number of clerical duties in connection with money-handling operations, travel arrangements, requests for information, and appointments.</t>
+        </is>
+      </c>
       <c r="Q125" t="inlineStr"/>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>Population</t>
-        </is>
-      </c>
-      <c r="T125" t="inlineStr"/>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>General and Keyboard Clerk, customers Services Clerk, Numerical and Material Recording Clerk</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BCIO:010111</t>
+          <t>BCIO:010094</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -5198,38 +5182,34 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>relatedness between person source and the target population</t>
+        </is>
+      </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>female gender</t>
-        </is>
-      </c>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
-          <t>A gender identity as being female.</t>
-        </is>
-      </c>
-      <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>female, woman</t>
-        </is>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A personal role of source that is realised in some relationship to the characteristics of the intervention participants.</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr"/>
       <c r="T126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BCIO:010112</t>
+          <t>BCIO:010102</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -5239,229 +5219,217 @@
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>male gender</t>
-        </is>
-      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>colleague</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
-          <t>A gender identity as being male.</t>
-        </is>
-      </c>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>male, man</t>
-        </is>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A relatedness between person source and the target population that is a person with whom the participant works in a profession or business.</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr"/>
       <c r="T127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BCIO:010108</t>
+          <t>BCIO:010105</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>socio demographic attribute of person source</t>
-        </is>
-      </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>embedded in participants’ community</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr">
         <is>
-          <t>A social or demographic characteristic of a human being who is the bearer of a person source role.</t>
-        </is>
-      </c>
-      <c r="P128" t="inlineStr"/>
+          <t>A relatedness between person source and the target population that is a source who is known and working to deliver intervention in own community.</t>
+        </is>
+      </c>
       <c r="Q128" t="inlineStr"/>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BCIO:010116</t>
+          <t>BCIO:010104</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>language proficiency of person source</t>
-        </is>
-      </c>
+      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>peer</t>
+        </is>
+      </c>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is an individual’s ability to speak or perform in the intervention language.</t>
-        </is>
-      </c>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>fluent, native</t>
-        </is>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A relatedness between person source and the target population that is descried as matched to intervention recipients on the basis of ‘peerness’ – age, social status, gender, shared experience, shared health status etc.</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr"/>
       <c r="T129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BCIO:010117</t>
+          <t>BCIO:010101</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>health status of person source</t>
-        </is>
-      </c>
+      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that represents their mental or physical condition.</t>
-        </is>
-      </c>
-      <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr">
-        <is>
-          <t>diabetes, cancer, depression, obesity, overweight</t>
-        </is>
-      </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A relatedness between person source and the target population that is a person whom the participant knows, likes and trusts, typically exclusive of sexual or family relations.</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr"/>
       <c r="T130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BCIO:010109</t>
+          <t>BCIO:010103</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>age of person source</t>
-        </is>
-      </c>
+      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>employer</t>
+        </is>
+      </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is a time quality inhering in a bearer by virtue of how long the bearer has existed.</t>
-        </is>
-      </c>
-      <c r="P131" t="inlineStr"/>
+          <t>A relatedness between person source and the target population that is a person which hires the services of the participant.</t>
+        </is>
+      </c>
       <c r="Q131" t="inlineStr"/>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr"/>
       <c r="T131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BCIO:010114</t>
+          <t>BCIO:010100</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>ethnic group membership of person source</t>
-        </is>
-      </c>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>carer</t>
+        </is>
+      </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is the ethnic group to which an individual identifies as belonging, where an ethic group is a population whose members have a common heritage that is real or presumed such as common culture, language, religion, behaviour or biological trait.</t>
-        </is>
-      </c>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr">
-        <is>
-          <t>black, white, Indian, Chinese, Somalian</t>
-        </is>
-      </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T132" t="inlineStr"/>
+          <t>A relatedness between person source and the target population that is an individual who cares, unpaid, for a friend or family member who, due to illness or disability, requires support in their daily life activities.</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr"/>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>carer</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BCIO:010110</t>
+          <t>BFO:0000016</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -5470,7 +5438,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>gender of person source</t>
+          <t>disposition</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -5480,28 +5448,11 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>A socio-demographic attribute of person source that is an individual's perception of having a particular gender, which may or may not correspond with their birth sex.</t>
-        </is>
-      </c>
-      <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr">
-        <is>
-          <t>gender</t>
-        </is>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BCIO:010113</t>
+          <t>BCIO:010120</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5511,7 +5462,7 @@
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>other gender</t>
+          <t>expertise of person source</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
@@ -5522,39 +5473,35 @@
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr">
         <is>
-          <t>A gender of person source that reports not belonging to the cultural gender role distinctions of either male or female.</t>
-        </is>
-      </c>
-      <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="inlineStr">
-        <is>
-          <t>non-binary, transexual</t>
-        </is>
-      </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A disposition that is an expert skill or knowledge held by the source delivering the behaviour change intervention.</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr"/>
       <c r="T134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BCIO:010119</t>
+          <t>BCIO:010122</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>psychological influence on intervention delivery of person source</t>
-        </is>
-      </c>
+      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>pre-existing expertise</t>
+        </is>
+      </c>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
@@ -5562,35 +5509,39 @@
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is their existing psychological attributes related to or potentially affecting the target behaviour.</t>
-        </is>
-      </c>
-      <c r="P135" t="inlineStr"/>
+          <t>An expertise of person source that is already possessed by the source which allows them to deliver the intervention, including educational level and qualifications.</t>
+        </is>
+      </c>
       <c r="Q135" t="inlineStr"/>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T135" t="inlineStr"/>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Bachelor’s degree, certification, accredited, qualified</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BCIO:010115</t>
+          <t>BCIO:010125</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>religious group membership of person source</t>
-        </is>
-      </c>
+      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>acquired expertise</t>
+        </is>
+      </c>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
@@ -5598,37 +5549,33 @@
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is a religious group to which an individual identifies as belonging, where a religious group is a group of people characterised by the practice of a common religion.</t>
-        </is>
-      </c>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>Muslim, Christian, Hindu, Sikh, Buddhist, Judaism</t>
-        </is>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>An expertise of person source that is additional knowledge or skills supplied to the source to allow them to deliver the intervention, including educational level and qualifications.</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr"/>
       <c r="T136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BCIO:010118</t>
+          <t>MF:0000030</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>target behaviour of person source</t>
-        </is>
-      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>representation</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
@@ -5638,37 +5585,25 @@
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr">
         <is>
-          <t>A socio-demographic attribute of person source that is their amount or experience of the intervention’s target behaviour.</t>
-        </is>
-      </c>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>source is highly physically active</t>
-        </is>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T137" t="inlineStr"/>
+          <t>A dependent continuant which is about a portion of reality.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BFO:0000031</t>
+          <t>MF:0000031</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>generically dependent continuant</t>
-        </is>
-      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>cognitive representation</t>
+        </is>
+      </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
@@ -5678,26 +5613,26 @@
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr">
         <is>
-          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
+          <t>A representation which specifically depends on an anatomical structure in the cognitive system of an organism.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>IAO:0000030</t>
+          <t>ADDICTO:0000381</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>information content entity</t>
-        </is>
-      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
@@ -5706,27 +5641,27 @@
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr">
         <is>
-          <t>A generically dependent continuant that is about some thing.</t>
+          <t>A cognitive representation of themselves by a person or a group about themselves.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>IAO:0000027</t>
+          <t>ADDICTO:0000399</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
+      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>self-identity</t>
+        </is>
+      </c>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
@@ -5734,14 +5669,14 @@
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr">
         <is>
-          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
+          <t>An identity that a person has about themselves.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BCIO:010107</t>
+          <t>BCIO:015098</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -5749,35 +5684,35 @@
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>total number of people able to deliver intervention</t>
-        </is>
-      </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>gender identity</t>
+        </is>
+      </c>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr">
         <is>
-          <t>A count data item that is the total number of providers that are available and able to deliver the intervention.</t>
-        </is>
-      </c>
-      <c r="P141" t="inlineStr"/>
+          <t>A self-identity as having a particular gender, which may or may not correspond with sex assigned at birth.</t>
+        </is>
+      </c>
       <c r="Q141" t="inlineStr"/>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr"/>
       <c r="T141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BCIO:010106</t>
+          <t>BCIO:010111</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -5785,35 +5720,39 @@
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>number of people delivering intervention to each participant</t>
-        </is>
-      </c>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>female gender</t>
+        </is>
+      </c>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr">
         <is>
-          <t>A count data item that is the number of providers that an individual participant in the intervention encounters.</t>
-        </is>
-      </c>
-      <c r="P142" t="inlineStr"/>
+          <t>A gender identity as being female.</t>
+        </is>
+      </c>
       <c r="Q142" t="inlineStr"/>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T142" t="inlineStr"/>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr"/>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>female, woman</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BCIO:010126</t>
+          <t>BCIO:010112</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -5821,49 +5760,49 @@
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>amount of experience</t>
-        </is>
-      </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>male gender</t>
+        </is>
+      </c>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr">
         <is>
-          <t>A knowledge or skill that is the duration of experience in related domain held by person source.</t>
-        </is>
-      </c>
-      <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="inlineStr">
-        <is>
-          <t>full-day, 6 years</t>
-        </is>
-      </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T143" t="inlineStr"/>
+          <t>A gender identity as being male.</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr"/>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>male, man</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BFO:0000004</t>
+          <t>BCIO:010123</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>independent continuant</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>expertise discipline</t>
+        </is>
+      </c>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
@@ -5874,25 +5813,42 @@
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr">
         <is>
-          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
+          <t>An attribute that is a field of knowledge or practice.</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>The division of expertise into different disciplines or fields is complex and depends on historical, social and structural factors.</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr"/>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BFO:0000040</t>
+          <t>BCIO:010124</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>discipline of pre-existing expertise</t>
+        </is>
+      </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
@@ -5902,14 +5858,26 @@
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr">
         <is>
-          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+          <t>The expertise discipline in which the person source has acquired their pre-existing knowledge and skills.</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr"/>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>psychology, yoga, cognitive behavioural therapy, hypnotism</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>OGMS:0000087</t>
+          <t>BCIO:010093</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -5918,7 +5886,7 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>extended organism</t>
+          <t>discipline of current programme of study or training</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -5930,26 +5898,38 @@
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr">
         <is>
-          <t>An object aggregate consisting of an organism and all material entities located within the organism, overlapping the organism, or occupying sites formed in part by the organism.</t>
+          <t>An expertise discipline of the programme of study currently undertaken by the bearer of a student or trainee role.</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>psychology, medicine, hairdressing</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MF:0000016</t>
+          <t>BCIO:010108</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>socio demographic attribute of person source</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>human being</t>
-        </is>
-      </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
@@ -5958,35 +5938,35 @@
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr">
         <is>
-          <t>An extended organism that is a member of the species Homo sapiens.</t>
-        </is>
-      </c>
-      <c r="P147" t="inlineStr"/>
+          <t>A social or demographic characteristic of a human being who is the bearer of a person source role.</t>
+        </is>
+      </c>
       <c r="Q147" t="inlineStr"/>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr"/>
       <c r="T147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BCIO:010095</t>
+          <t>BCIO:010109</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>age of person source</t>
+        </is>
+      </c>
       <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>family member</t>
-        </is>
-      </c>
+      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
@@ -5994,62 +5974,62 @@
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr">
         <is>
-          <t>A person who is a member of a group of persons united by blood, or by marriage or other legal arrangement, or by self-identity as belonging to the same family.</t>
-        </is>
-      </c>
-      <c r="P148" t="inlineStr"/>
+          <t>A socio-demographic attribute of person source that is a time quality inhering in a bearer by virtue of how long the bearer has existed.</t>
+        </is>
+      </c>
       <c r="Q148" t="inlineStr"/>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr"/>
       <c r="T148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BCIO:010097</t>
+          <t>BCIO:010110</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>gender of person source</t>
+        </is>
+      </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>spouse or partner</t>
-        </is>
-      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr">
         <is>
-          <t>A family member that is an individual who is married or in a committed relationship with another individual.</t>
-        </is>
-      </c>
-      <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>boyfriend, girlfriend, partner, fiance, wife, husband</t>
-        </is>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T149" t="inlineStr"/>
+          <t>A socio-demographic attribute of person source that is an individual's perception of having a particular gender, which may or may not correspond with their birth sex.</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr"/>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BCIO:010099</t>
+          <t>BCIO:010113</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -6057,132 +6037,128 @@
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>other gender</t>
+        </is>
+      </c>
       <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>child relationship</t>
-        </is>
-      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr">
         <is>
-          <t>A family member that is an offspring relationship from a person to their parent.</t>
-        </is>
-      </c>
-      <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>daughter, son, step-daughter, step-son</t>
-        </is>
-      </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T150" t="inlineStr"/>
+          <t>A gender of person source that reports not belonging to the cultural gender role distinctions of either male or female.</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr"/>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>non-binary, transexual</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BCIO:010098</t>
+          <t>BCIO:010116</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>language proficiency of person source</t>
+        </is>
+      </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>sibling relationship</t>
-        </is>
-      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr">
         <is>
-          <t>A family member that is a family relationship between two persons with at least one shared parent.</t>
-        </is>
-      </c>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>brother, sister, step-brother, step-sister</t>
-        </is>
-      </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T151" t="inlineStr"/>
+          <t>A socio-demographic attribute of person source that is an individual’s ability to speak or perform in the intervention language.</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr"/>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>fluent, native</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BCIO:010096</t>
+          <t>BCIO:010119</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>psychological influence on intervention delivery of person source</t>
+        </is>
+      </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>parent or guardian</t>
-        </is>
-      </c>
+      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
-          <t>A family member that is a mother, father or legal carer of a child.</t>
-        </is>
-      </c>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>mother, father, step-mother, step-father, guardian</t>
-        </is>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+          <t>A socio-demographic attribute of person source that is their existing psychological attributes related to or potentially affecting the target behaviour.</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr"/>
       <c r="T152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BCIO:010002</t>
+          <t>BCIO:010117</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>health status of person source</t>
+        </is>
+      </c>
       <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>person source</t>
-        </is>
-      </c>
+      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
@@ -6190,35 +6166,39 @@
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr">
         <is>
-          <t>A person who is the bearer of a behaviour change intervention source role.</t>
-        </is>
-      </c>
-      <c r="P153" t="inlineStr"/>
+          <t>A socio-demographic attribute of person source that represents their mental or physical condition.</t>
+        </is>
+      </c>
       <c r="Q153" t="inlineStr"/>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T153" t="inlineStr"/>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr"/>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>diabetes, cancer, depression, obesity, overweight</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BCIO:050842</t>
+          <t>BCIO:010118</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>target behaviour of person source</t>
+        </is>
+      </c>
       <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>role model for a person</t>
-        </is>
-      </c>
+      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
@@ -6226,27 +6206,26 @@
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr">
         <is>
-          <t>A &lt;person&gt; that influences a recipient by being perceived to be similar or admired.</t>
-        </is>
-      </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>This class lies at the intersection between a person and their environment and is defined from the perspective of the person.</t>
-        </is>
-      </c>
-      <c r="P154" t="inlineStr"/>
+          <t>A socio-demographic attribute of person source that is their amount or experience of the intervention’s target behaviour.</t>
+        </is>
+      </c>
       <c r="Q154" t="inlineStr"/>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T154" t="inlineStr"/>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr"/>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>source is highly physically active</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BCIO:010139</t>
+          <t>BCIO:010115</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -6255,7 +6234,7 @@
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>organisation source</t>
+          <t>religious group membership of person source</t>
         </is>
       </c>
       <c r="G155" t="inlineStr"/>
@@ -6267,22 +6246,26 @@
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr">
         <is>
-          <t>An organisation that is the bearer of a behaviour change intervention source role, such as voluntary, public or commercial organisations delivering a behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="P155" t="inlineStr"/>
+          <t>A socio-demographic attribute of person source that is a religious group to which an individual identifies as belonging, where a religious group is a group of people characterised by the practice of a common religion.</t>
+        </is>
+      </c>
       <c r="Q155" t="inlineStr"/>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T155" t="inlineStr"/>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr"/>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Muslim, Christian, Hindu, Sikh, Buddhist, Judaism</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>OBI:0000245</t>
+          <t>BCIO:010114</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -6291,7 +6274,7 @@
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>organisation</t>
+          <t>ethnic group membership of person source</t>
         </is>
       </c>
       <c r="G156" t="inlineStr"/>
@@ -6303,17 +6286,21 @@
       <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr">
         <is>
-          <t>An entity that can bear roles, has members, and has a set of organization rules. Members of organizations are either organizations themselves or individual people. Members can bear specific organization member roles that are determined in the organization rules. The organization rules also determine how decisions are made on behalf of the organization by the organization members.</t>
-        </is>
-      </c>
-      <c r="P156" t="inlineStr"/>
+          <t>A socio-demographic attribute of person source that is the ethnic group to which an individual identifies as belonging, where an ethic group is a population whose members have a common heritage that is real or presumed such as common culture, language, religion, behaviour or biological trait.</t>
+        </is>
+      </c>
       <c r="Q156" t="inlineStr"/>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T156" t="inlineStr"/>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr"/>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>black, white, Indian, Chinese, Somalian</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6367,7 +6354,7 @@
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr">
         <is>
-          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
+          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
         </is>
       </c>
     </row>
@@ -6398,13 +6385,13 @@
           <t>A process in which a person source is paid or compensated for delivering the intervention.</t>
         </is>
       </c>
-      <c r="P159" t="inlineStr"/>
       <c r="Q159" t="inlineStr"/>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr"/>
       <c r="T159" t="inlineStr"/>
     </row>
     <row r="160">
@@ -6434,18 +6421,18 @@
           <t>A payment of person source that is money, vouchers or valued objects given to the source for delivering the intervention.</t>
         </is>
       </c>
-      <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr">
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr"/>
+      <c r="T160" t="inlineStr">
         <is>
           <t>paid in cash, vouchers</t>
         </is>
       </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6474,23 +6461,23 @@
           <t>A payment of person source that is non-monetary compensation given to the source for delivering the intervention.</t>
         </is>
       </c>
-      <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr">
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr"/>
+      <c r="T161" t="inlineStr">
         <is>
           <t>course credit</t>
         </is>
       </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BCIO:010129</t>
+          <t>BCIO:010128</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -6498,7 +6485,7 @@
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>volunteering of person source</t>
+          <t>supervision of person source</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -6511,26 +6498,26 @@
       <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr">
         <is>
-          <t>A process in which a person source delivers the intervention on a voluntary basis without formal compensation.</t>
-        </is>
-      </c>
-      <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>voluntary basis, volunteering</t>
-        </is>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T162" t="inlineStr"/>
+          <t>A process in which a person source is formally provided, by an individual with appropriate expertise, with corrective and skill-enhancing feedback, regarding the person source’s performance in delivering the intervention.</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr"/>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>supervised</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>BCIO:010128</t>
+          <t>BCIO:010129</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
@@ -6538,7 +6525,7 @@
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>supervision of person source</t>
+          <t>volunteering of person source</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -6551,21 +6538,21 @@
       <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr">
         <is>
-          <t>A process in which a person source is formally provided, by an individual with appropriate expertise, with corrective and skill-enhancing feedback, regarding the person source’s performance in delivering the intervention.</t>
-        </is>
-      </c>
-      <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="inlineStr">
-        <is>
-          <t>supervised</t>
-        </is>
-      </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="T163" t="inlineStr"/>
+          <t>A process in which a person source delivers the intervention on a voluntary basis without formal compensation.</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr"/>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>voluntary basis, volunteering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Source/BCIO-source-hierarchy.xlsx
+++ b/Source/BCIO-source-hierarchy.xlsx
@@ -582,7 +582,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
+          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
+          <t>A continuant that is a bearer of quality and realizable entity entities, in which other entities inhere and which itself cannot inhere in anything.</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>organisation</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1229,7 +1229,7 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>characteristic</t>
+          <t>specifically dependent continuant</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1258,7 +1258,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>realizable</t>
+          <t>realizable entity</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -1306,7 +1306,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:010084</t>
+          <t>BCIO:006081</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1316,7 +1316,7 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>student or trainee role</t>
+          <t>personal role</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1327,22 +1327,22 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>A role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
+          <t>A role that inheres in a human being by virtue of their social and institutional circumstances.</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:010086</t>
+          <t>BCIO:010084</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1353,7 +1353,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>school student role</t>
+          <t>student or trainee role</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1363,7 +1363,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting.</t>
+          <t>A personal role which inheres in a person and is realised by being enrolled in an educational institution or a formal programme of professional training.</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr"/>
@@ -1378,7 +1378,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:010087</t>
+          <t>BCIO:010086</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1387,19 +1387,19 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>trainee role</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>school student role</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
+          <t>A student or trainee role realised by currently learning at a primary or secondary education level in an institutional, organised setting.</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr"/>
@@ -1414,7 +1414,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:010085</t>
+          <t>BCIO:010087</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1423,19 +1423,19 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>informal education student role</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>trainee role</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>A student or trainee role that is currently learning in a non-institutional setting.</t>
+          <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr"/>
@@ -1450,7 +1450,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:010088</t>
+          <t>BCIO:010085</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1459,19 +1459,19 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>higher education student role</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>informal education student role</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school.</t>
+          <t>A student or trainee role that is currently learning in a non-institutional setting.</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr"/>
@@ -1481,16 +1481,12 @@
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
-        </is>
-      </c>
+      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:010092</t>
+          <t>BCIO:010088</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1502,7 +1498,7 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>doctoral student role</t>
+          <t>higher education student role</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -1511,7 +1507,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
+          <t>A student or trainee role realised by currently learning on an advanced educational programme in a university, college or professional school.</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr"/>
@@ -1523,14 +1519,14 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
-          <t>PhD student</t>
+          <t>completing a university bachelor's or master's course of study, medical school or other professional school.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:010090</t>
+          <t>BCIO:010092</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1540,18 +1536,18 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>graduate student role</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>doctoral student role</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
+          <t>A higher education student  role realised by currently studying for a doctoral degree.</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr"/>
@@ -1563,14 +1559,14 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
-          <t>graduate student</t>
+          <t>PhD student</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:010089</t>
+          <t>BCIO:010090</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1580,18 +1576,18 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>undergraduate student role</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>graduate student role</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
+          <t>A higher education student role realised by currently studying for a more advanced degree after completing an undergraduate degree.</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr"/>
@@ -1603,14 +1599,14 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
         <is>
-          <t>undergraduate student</t>
+          <t>graduate student</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:010091</t>
+          <t>BCIO:010089</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1620,18 +1616,18 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>masters student role</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>undergraduate student role</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>A higher education student  role realised by currently studying for a masters degree.</t>
+          <t>A higher education student role realised by currently studying for an undergraduate degree.</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr"/>
@@ -1643,14 +1639,14 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
         <is>
-          <t>MSc student, Masters student</t>
+          <t>undergraduate student</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:006081</t>
+          <t>BCIO:010091</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1658,30 +1654,34 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>personal role</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>masters student role</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>A role that inheres in a human being by virtue of their social and institutional circumstances.</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>A role can be assigned without being realised. A person realises a role by doing something.</t>
+          <t>A higher education student  role realised by currently studying for a masters degree.</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
       <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>MSc student, Masters student</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6354,7 +6354,7 @@
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr">
         <is>
-          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
+          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
         </is>
       </c>
     </row>
